--- a/downloads/indicadores/SIC/SIC_datos.xlsx
+++ b/downloads/indicadores/SIC/SIC_datos.xlsx
@@ -682,7 +682,7 @@
         <v>96.01242499999999</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>100.456039</v>
+        <v>100.456177</v>
       </c>
       <c r="P6" s="6" t="n"/>
       <c r="Q6" s="6" t="n"/>
@@ -754,7 +754,7 @@
         <v>96.64352700000001</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>100.496364</v>
+        <v>100.496514</v>
       </c>
       <c r="P7" s="9" t="n"/>
       <c r="Q7" s="9" t="n"/>
@@ -826,7 +826,7 @@
         <v>97.27531399999999</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>100.519039</v>
+        <v>100.519198</v>
       </c>
       <c r="P8" s="6" t="n"/>
       <c r="Q8" s="6" t="n"/>
@@ -898,7 +898,7 @@
         <v>97.912537</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>100.564523</v>
+        <v>100.5647</v>
       </c>
       <c r="P9" s="9" t="n"/>
       <c r="Q9" s="9" t="n"/>
@@ -970,7 +970,7 @@
         <v>98.55596799999999</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>100.709107</v>
+        <v>100.709344</v>
       </c>
       <c r="P10" s="6" t="n"/>
       <c r="Q10" s="6" t="n"/>
@@ -1042,7 +1042,7 @@
         <v>99.21331600000001</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>100.953048</v>
+        <v>100.953386</v>
       </c>
       <c r="P11" s="9" t="n"/>
       <c r="Q11" s="9" t="n"/>
@@ -1114,7 +1114,7 @@
         <v>99.898045</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>101.227234</v>
+        <v>101.227689</v>
       </c>
       <c r="P12" s="6" t="n"/>
       <c r="Q12" s="6" t="n"/>
@@ -1186,7 +1186,7 @@
         <v>100.597885</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>101.474348</v>
+        <v>101.474909</v>
       </c>
       <c r="P13" s="9" t="n"/>
       <c r="Q13" s="9" t="n"/>
@@ -1258,7 +1258,7 @@
         <v>101.291187</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>101.610097</v>
+        <v>101.610715</v>
       </c>
       <c r="P14" s="6" t="n"/>
       <c r="Q14" s="6" t="n"/>
@@ -1330,7 +1330,7 @@
         <v>101.939694</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>101.581292</v>
+        <v>101.581897</v>
       </c>
       <c r="P15" s="9" t="n"/>
       <c r="Q15" s="9" t="n"/>
@@ -1402,7 +1402,7 @@
         <v>102.50843</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>101.442635</v>
+        <v>101.443181</v>
       </c>
       <c r="P16" s="6" t="n"/>
       <c r="Q16" s="6" t="n"/>
@@ -1474,7 +1474,7 @@
         <v>102.975587</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>101.28566</v>
+        <v>101.286133</v>
       </c>
       <c r="P17" s="9" t="n"/>
       <c r="Q17" s="9" t="n"/>
@@ -1550,7 +1550,7 @@
         <v>103.335084</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>101.197565</v>
+        <v>101.197989</v>
       </c>
       <c r="P18" s="6" t="n"/>
       <c r="Q18" s="6" t="n">
@@ -1628,7 +1628,7 @@
         <v>103.589263</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>101.198266</v>
+        <v>101.198674</v>
       </c>
       <c r="P19" s="9" t="n"/>
       <c r="Q19" s="9" t="n">
@@ -1706,7 +1706,7 @@
         <v>103.759695</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>101.302743</v>
+        <v>101.303176</v>
       </c>
       <c r="P20" s="6" t="n"/>
       <c r="Q20" s="6" t="n">
@@ -1784,7 +1784,7 @@
         <v>103.856387</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>101.485284</v>
+        <v>101.485779</v>
       </c>
       <c r="P21" s="9" t="n"/>
       <c r="Q21" s="9" t="n">
@@ -1862,7 +1862,7 @@
         <v>103.911966</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>101.604094</v>
+        <v>101.604639</v>
       </c>
       <c r="P22" s="6" t="n"/>
       <c r="Q22" s="6" t="n">
@@ -1940,7 +1940,7 @@
         <v>103.957181</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>101.631494</v>
+        <v>101.632068</v>
       </c>
       <c r="P23" s="9" t="n"/>
       <c r="Q23" s="9" t="n">
@@ -2018,7 +2018,7 @@
         <v>104.023248</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>101.519098</v>
+        <v>101.51966</v>
       </c>
       <c r="P24" s="6" t="n"/>
       <c r="Q24" s="6" t="n">
@@ -2096,7 +2096,7 @@
         <v>104.122772</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>101.295118</v>
+        <v>101.29563</v>
       </c>
       <c r="P25" s="9" t="n"/>
       <c r="Q25" s="9" t="n">
@@ -2174,7 +2174,7 @@
         <v>104.257082</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>101.044692</v>
+        <v>101.045131</v>
       </c>
       <c r="P26" s="6" t="n"/>
       <c r="Q26" s="6" t="n">
@@ -2252,7 +2252,7 @@
         <v>104.391011</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>100.80367</v>
+        <v>100.804025</v>
       </c>
       <c r="P27" s="9" t="n"/>
       <c r="Q27" s="9" t="n">
@@ -2330,7 +2330,7 @@
         <v>104.442679</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>100.566829</v>
+        <v>100.567089</v>
       </c>
       <c r="P28" s="6" t="n"/>
       <c r="Q28" s="6" t="n">
@@ -2408,7 +2408,7 @@
         <v>104.329097</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>100.300575</v>
+        <v>100.300723</v>
       </c>
       <c r="P29" s="9" t="n"/>
       <c r="Q29" s="9" t="n">
@@ -2486,7 +2486,7 @@
         <v>104.026813</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>99.92826700000001</v>
+        <v>99.928262</v>
       </c>
       <c r="P30" s="6" t="n"/>
       <c r="Q30" s="6" t="n">
@@ -2564,7 +2564,7 @@
         <v>103.541811</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>99.481003</v>
+        <v>99.480819</v>
       </c>
       <c r="P31" s="9" t="n"/>
       <c r="Q31" s="9" t="n">
@@ -2642,7 +2642,7 @@
         <v>102.872517</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>98.97059299999999</v>
+        <v>98.970206</v>
       </c>
       <c r="P32" s="6" t="n"/>
       <c r="Q32" s="6" t="n">
@@ -2720,7 +2720,7 @@
         <v>102.051892</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>98.37559</v>
+        <v>98.374971</v>
       </c>
       <c r="P33" s="9" t="n"/>
       <c r="Q33" s="9" t="n">
@@ -2798,7 +2798,7 @@
         <v>101.096432</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>97.75762400000001</v>
+        <v>97.75676300000001</v>
       </c>
       <c r="P34" s="6" t="n"/>
       <c r="Q34" s="6" t="n">
@@ -2876,7 +2876,7 @@
         <v>100.035675</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>97.092029</v>
+        <v>97.090909</v>
       </c>
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n">
@@ -2954,7 +2954,7 @@
         <v>98.904843</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>96.469695</v>
+        <v>96.468333</v>
       </c>
       <c r="P36" s="6" t="n"/>
       <c r="Q36" s="6" t="n">
@@ -3032,7 +3032,7 @@
         <v>97.73985999999999</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>95.94784799999999</v>
+        <v>95.94629</v>
       </c>
       <c r="P37" s="9" t="n"/>
       <c r="Q37" s="9" t="n">
@@ -3110,7 +3110,7 @@
         <v>96.632527</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>95.562692</v>
+        <v>95.561008</v>
       </c>
       <c r="P38" s="6" t="n"/>
       <c r="Q38" s="6" t="n">
@@ -3188,7 +3188,7 @@
         <v>95.672223</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>95.39073399999999</v>
+        <v>95.389027</v>
       </c>
       <c r="P39" s="9" t="n"/>
       <c r="Q39" s="9" t="n">
@@ -3266,7 +3266,7 @@
         <v>94.948302</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>95.474411</v>
+        <v>95.47277</v>
       </c>
       <c r="P40" s="6" t="n"/>
       <c r="Q40" s="6" t="n">
@@ -3344,7 +3344,7 @@
         <v>94.52375499999999</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>95.73555899999999</v>
+        <v>95.734038</v>
       </c>
       <c r="P41" s="9" t="n"/>
       <c r="Q41" s="9" t="n">
@@ -3422,7 +3422,7 @@
         <v>94.399659</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>96.125552</v>
+        <v>96.124185</v>
       </c>
       <c r="P42" s="6" t="n"/>
       <c r="Q42" s="6" t="n">
@@ -3500,7 +3500,7 @@
         <v>94.55231000000001</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>96.547344</v>
+        <v>96.546133</v>
       </c>
       <c r="P43" s="9" t="n"/>
       <c r="Q43" s="9" t="n">
@@ -3578,7 +3578,7 @@
         <v>94.93962399999999</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>96.933302</v>
+        <v>96.932231</v>
       </c>
       <c r="P44" s="6" t="n"/>
       <c r="Q44" s="6" t="n">
@@ -3656,7 +3656,7 @@
         <v>95.460307</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>97.238209</v>
+        <v>97.23724799999999</v>
       </c>
       <c r="P45" s="9" t="n"/>
       <c r="Q45" s="9" t="n">
@@ -3734,7 +3734,7 @@
         <v>96.009186</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>97.485252</v>
+        <v>97.484387</v>
       </c>
       <c r="P46" s="6" t="n"/>
       <c r="Q46" s="6" t="n">
@@ -3812,7 +3812,7 @@
         <v>96.50832200000001</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>97.759541</v>
+        <v>97.758787</v>
       </c>
       <c r="P47" s="9" t="n"/>
       <c r="Q47" s="9" t="n">
@@ -3890,7 +3890,7 @@
         <v>96.914438</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>98.09373600000001</v>
+        <v>98.09311599999999</v>
       </c>
       <c r="P48" s="6" t="n"/>
       <c r="Q48" s="6" t="n">
@@ -3968,7 +3968,7 @@
         <v>97.228043</v>
       </c>
       <c r="O49" s="9" t="n">
-        <v>98.43785200000001</v>
+        <v>98.43737</v>
       </c>
       <c r="P49" s="9" t="n"/>
       <c r="Q49" s="9" t="n">
@@ -4046,7 +4046,7 @@
         <v>97.452884</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>98.815397</v>
+        <v>98.815051</v>
       </c>
       <c r="P50" s="6" t="n"/>
       <c r="Q50" s="6" t="n">
@@ -4124,7 +4124,7 @@
         <v>97.59644900000001</v>
       </c>
       <c r="O51" s="9" t="n">
-        <v>99.222887</v>
+        <v>99.222675</v>
       </c>
       <c r="P51" s="9" t="n"/>
       <c r="Q51" s="9" t="n">
@@ -4202,7 +4202,7 @@
         <v>97.683627</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>99.62365</v>
+        <v>99.62356200000001</v>
       </c>
       <c r="P52" s="6" t="n"/>
       <c r="Q52" s="6" t="n">
@@ -4280,7 +4280,7 @@
         <v>97.789714</v>
       </c>
       <c r="O53" s="9" t="n">
-        <v>99.996374</v>
+        <v>99.996397</v>
       </c>
       <c r="P53" s="9" t="n"/>
       <c r="Q53" s="9" t="n">
@@ -4358,7 +4358,7 @@
         <v>97.96185199999999</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>100.355016</v>
+        <v>100.355146</v>
       </c>
       <c r="P54" s="6" t="n"/>
       <c r="Q54" s="6" t="n">
@@ -4436,7 +4436,7 @@
         <v>98.226009</v>
       </c>
       <c r="O55" s="9" t="n">
-        <v>100.705386</v>
+        <v>100.705625</v>
       </c>
       <c r="P55" s="9" t="n"/>
       <c r="Q55" s="9" t="n">
@@ -4514,7 +4514,7 @@
         <v>98.559972</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>101.106751</v>
+        <v>101.107123</v>
       </c>
       <c r="P56" s="6" t="n"/>
       <c r="Q56" s="6" t="n">
@@ -4592,7 +4592,7 @@
         <v>98.935433</v>
       </c>
       <c r="O57" s="9" t="n">
-        <v>101.579205</v>
+        <v>101.579741</v>
       </c>
       <c r="P57" s="9" t="n"/>
       <c r="Q57" s="9" t="n">
@@ -4670,7 +4670,7 @@
         <v>99.34794100000001</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>102.069355</v>
+        <v>102.070067</v>
       </c>
       <c r="P58" s="6" t="n"/>
       <c r="Q58" s="6" t="n">
@@ -4748,7 +4748,7 @@
         <v>99.802111</v>
       </c>
       <c r="O59" s="9" t="n">
-        <v>102.46286</v>
+        <v>102.463717</v>
       </c>
       <c r="P59" s="9" t="n"/>
       <c r="Q59" s="9" t="n">
@@ -4826,7 +4826,7 @@
         <v>100.258498</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>102.72338</v>
+        <v>102.724338</v>
       </c>
       <c r="P60" s="6" t="n"/>
       <c r="Q60" s="6" t="n">
@@ -4904,7 +4904,7 @@
         <v>100.666431</v>
       </c>
       <c r="O61" s="9" t="n">
-        <v>102.873687</v>
+        <v>102.874708</v>
       </c>
       <c r="P61" s="9" t="n"/>
       <c r="Q61" s="9" t="n">
@@ -4982,7 +4982,7 @@
         <v>101.005984</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>102.890059</v>
+        <v>102.891089</v>
       </c>
       <c r="P62" s="6" t="n"/>
       <c r="Q62" s="6" t="n">
@@ -5060,7 +5060,7 @@
         <v>101.274153</v>
       </c>
       <c r="O63" s="9" t="n">
-        <v>102.823247</v>
+        <v>102.82425</v>
       </c>
       <c r="P63" s="9" t="n"/>
       <c r="Q63" s="9" t="n">
@@ -5138,7 +5138,7 @@
         <v>101.486346</v>
       </c>
       <c r="O64" s="6" t="n">
-        <v>102.756268</v>
+        <v>102.757241</v>
       </c>
       <c r="P64" s="6" t="n"/>
       <c r="Q64" s="6" t="n">
@@ -5216,7 +5216,7 @@
         <v>101.63459</v>
       </c>
       <c r="O65" s="9" t="n">
-        <v>102.781491</v>
+        <v>102.782464</v>
       </c>
       <c r="P65" s="9" t="n"/>
       <c r="Q65" s="9" t="n">
@@ -5294,7 +5294,7 @@
         <v>101.692098</v>
       </c>
       <c r="O66" s="6" t="n">
-        <v>102.872687</v>
+        <v>102.873683</v>
       </c>
       <c r="P66" s="6" t="n"/>
       <c r="Q66" s="6" t="n">
@@ -5372,7 +5372,7 @@
         <v>101.64247</v>
       </c>
       <c r="O67" s="9" t="n">
-        <v>102.965277</v>
+        <v>102.9663</v>
       </c>
       <c r="P67" s="9" t="n"/>
       <c r="Q67" s="9" t="n">
@@ -5450,7 +5450,7 @@
         <v>101.536096</v>
       </c>
       <c r="O68" s="6" t="n">
-        <v>102.95509</v>
+        <v>102.956107</v>
       </c>
       <c r="P68" s="6" t="n"/>
       <c r="Q68" s="6" t="n">
@@ -5528,7 +5528,7 @@
         <v>101.415654</v>
       </c>
       <c r="O69" s="9" t="n">
-        <v>102.852148</v>
+        <v>102.85313</v>
       </c>
       <c r="P69" s="9" t="n"/>
       <c r="Q69" s="9" t="n">
@@ -5606,7 +5606,7 @@
         <v>101.296348</v>
       </c>
       <c r="O70" s="6" t="n">
-        <v>102.640131</v>
+        <v>102.641042</v>
       </c>
       <c r="P70" s="6" t="n"/>
       <c r="Q70" s="6" t="n">
@@ -5684,7 +5684,7 @@
         <v>101.184754</v>
       </c>
       <c r="O71" s="9" t="n">
-        <v>102.337859</v>
+        <v>102.338669</v>
       </c>
       <c r="P71" s="9" t="n"/>
       <c r="Q71" s="9" t="n">
@@ -5762,7 +5762,7 @@
         <v>101.099793</v>
       </c>
       <c r="O72" s="6" t="n">
-        <v>101.933233</v>
+        <v>101.933907</v>
       </c>
       <c r="P72" s="6" t="n"/>
       <c r="Q72" s="6" t="n">
@@ -5840,7 +5840,7 @@
         <v>101.056817</v>
       </c>
       <c r="O73" s="9" t="n">
-        <v>101.451513</v>
+        <v>101.452023</v>
       </c>
       <c r="P73" s="9" t="n"/>
       <c r="Q73" s="9" t="n">
@@ -5918,7 +5918,7 @@
         <v>101.023148</v>
       </c>
       <c r="O74" s="6" t="n">
-        <v>100.976236</v>
+        <v>100.976584</v>
       </c>
       <c r="P74" s="6" t="n"/>
       <c r="Q74" s="6" t="n">
@@ -5996,7 +5996,7 @@
         <v>100.986004</v>
       </c>
       <c r="O75" s="9" t="n">
-        <v>100.492818</v>
+        <v>100.493</v>
       </c>
       <c r="P75" s="9" t="n"/>
       <c r="Q75" s="9" t="n">
@@ -6074,7 +6074,7 @@
         <v>100.922261</v>
       </c>
       <c r="O76" s="6" t="n">
-        <v>100.004748</v>
+        <v>100.004761</v>
       </c>
       <c r="P76" s="6" t="n"/>
       <c r="Q76" s="6" t="n">
@@ -6152,7 +6152,7 @@
         <v>100.793314</v>
       </c>
       <c r="O77" s="9" t="n">
-        <v>99.48126600000001</v>
+        <v>99.481098</v>
       </c>
       <c r="P77" s="9" t="n"/>
       <c r="Q77" s="9" t="n">
@@ -6232,7 +6232,7 @@
         <v>100.594857</v>
       </c>
       <c r="O78" s="6" t="n">
-        <v>98.958561</v>
+        <v>98.95821100000001</v>
       </c>
       <c r="P78" s="6" t="n"/>
       <c r="Q78" s="6" t="n">
@@ -6312,7 +6312,7 @@
         <v>100.322039</v>
       </c>
       <c r="O79" s="9" t="n">
-        <v>98.47679599999999</v>
+        <v>98.47627799999999</v>
       </c>
       <c r="P79" s="9" t="n"/>
       <c r="Q79" s="9" t="n">
@@ -6392,7 +6392,7 @@
         <v>99.992361</v>
       </c>
       <c r="O80" s="6" t="n">
-        <v>98.035158</v>
+        <v>98.034485</v>
       </c>
       <c r="P80" s="6" t="n"/>
       <c r="Q80" s="6" t="n">
@@ -6472,7 +6472,7 @@
         <v>99.64582</v>
       </c>
       <c r="O81" s="9" t="n">
-        <v>97.602271</v>
+        <v>97.601446</v>
       </c>
       <c r="P81" s="9" t="n"/>
       <c r="Q81" s="9" t="n">
@@ -6552,7 +6552,7 @@
         <v>99.276055</v>
       </c>
       <c r="O82" s="6" t="n">
-        <v>97.190648</v>
+        <v>97.18968</v>
       </c>
       <c r="P82" s="6" t="n"/>
       <c r="Q82" s="6" t="n">
@@ -6632,7 +6632,7 @@
         <v>98.88478499999999</v>
       </c>
       <c r="O83" s="9" t="n">
-        <v>96.903791</v>
+        <v>96.90272400000001</v>
       </c>
       <c r="P83" s="9" t="n"/>
       <c r="Q83" s="9" t="n">
@@ -6712,7 +6712,7 @@
         <v>98.505931</v>
       </c>
       <c r="O84" s="6" t="n">
-        <v>96.83458299999999</v>
+        <v>96.833494</v>
       </c>
       <c r="P84" s="6" t="n"/>
       <c r="Q84" s="6" t="n">
@@ -6792,7 +6792,7 @@
         <v>98.178217</v>
       </c>
       <c r="O85" s="9" t="n">
-        <v>97.01045499999999</v>
+        <v>97.009427</v>
       </c>
       <c r="P85" s="9" t="n"/>
       <c r="Q85" s="9" t="n">
@@ -6872,7 +6872,7 @@
         <v>97.947701</v>
       </c>
       <c r="O86" s="6" t="n">
-        <v>97.360434</v>
+        <v>97.359527</v>
       </c>
       <c r="P86" s="6" t="n"/>
       <c r="Q86" s="6" t="n">
@@ -6952,7 +6952,7 @@
         <v>97.836123</v>
       </c>
       <c r="O87" s="9" t="n">
-        <v>97.797646</v>
+        <v>97.79688899999999</v>
       </c>
       <c r="P87" s="9" t="n"/>
       <c r="Q87" s="9" t="n">
@@ -7032,7 +7032,7 @@
         <v>97.80819200000001</v>
       </c>
       <c r="O88" s="6" t="n">
-        <v>98.271218</v>
+        <v>98.270624</v>
       </c>
       <c r="P88" s="6" t="n"/>
       <c r="Q88" s="6" t="n">
@@ -7112,7 +7112,7 @@
         <v>97.83842199999999</v>
       </c>
       <c r="O89" s="9" t="n">
-        <v>98.76442900000001</v>
+        <v>98.764004</v>
       </c>
       <c r="P89" s="9" t="n"/>
       <c r="Q89" s="9" t="n">
@@ -7194,7 +7194,7 @@
         <v>97.889831</v>
       </c>
       <c r="O90" s="6" t="n">
-        <v>99.218924</v>
+        <v>99.218654</v>
       </c>
       <c r="P90" s="6" t="n"/>
       <c r="Q90" s="6" t="n">
@@ -7276,7 +7276,7 @@
         <v>97.94937</v>
       </c>
       <c r="O91" s="9" t="n">
-        <v>99.61531600000001</v>
+        <v>99.615182</v>
       </c>
       <c r="P91" s="9" t="n"/>
       <c r="Q91" s="9" t="n">
@@ -7358,7 +7358,7 @@
         <v>98.01599299999999</v>
       </c>
       <c r="O92" s="6" t="n">
-        <v>99.989586</v>
+        <v>99.989581</v>
       </c>
       <c r="P92" s="6" t="n"/>
       <c r="Q92" s="6" t="n">
@@ -7440,7 +7440,7 @@
         <v>98.08319899999999</v>
       </c>
       <c r="O93" s="9" t="n">
-        <v>100.385428</v>
+        <v>100.385563</v>
       </c>
       <c r="P93" s="9" t="n"/>
       <c r="Q93" s="9" t="n">
@@ -7522,7 +7522,7 @@
         <v>98.162494</v>
       </c>
       <c r="O94" s="6" t="n">
-        <v>100.83826</v>
+        <v>100.838551</v>
       </c>
       <c r="P94" s="6" t="n"/>
       <c r="Q94" s="6" t="n">
@@ -7604,7 +7604,7 @@
         <v>98.269811</v>
       </c>
       <c r="O95" s="9" t="n">
-        <v>101.241875</v>
+        <v>101.242305</v>
       </c>
       <c r="P95" s="9" t="n"/>
       <c r="Q95" s="9" t="n">
@@ -7686,7 +7686,7 @@
         <v>98.409961</v>
       </c>
       <c r="O96" s="6" t="n">
-        <v>101.462322</v>
+        <v>101.462828</v>
       </c>
       <c r="P96" s="6" t="n"/>
       <c r="Q96" s="6" t="n">
@@ -7768,7 +7768,7 @@
         <v>98.54351800000001</v>
       </c>
       <c r="O97" s="9" t="n">
-        <v>101.455065</v>
+        <v>101.455567</v>
       </c>
       <c r="P97" s="9" t="n"/>
       <c r="Q97" s="9" t="n">
@@ -7850,7 +7850,7 @@
         <v>98.65055599999999</v>
       </c>
       <c r="O98" s="6" t="n">
-        <v>101.241024</v>
+        <v>101.241452</v>
       </c>
       <c r="P98" s="6" t="n"/>
       <c r="Q98" s="6" t="n">
@@ -7932,7 +7932,7 @@
         <v>98.743258</v>
       </c>
       <c r="O99" s="9" t="n">
-        <v>100.868424</v>
+        <v>100.868724</v>
       </c>
       <c r="P99" s="9" t="n"/>
       <c r="Q99" s="9" t="n">
@@ -8014,7 +8014,7 @@
         <v>98.843352</v>
       </c>
       <c r="O100" s="6" t="n">
-        <v>100.352865</v>
+        <v>100.352987</v>
       </c>
       <c r="P100" s="6" t="n"/>
       <c r="Q100" s="6" t="n">
@@ -8096,7 +8096,7 @@
         <v>98.9953</v>
       </c>
       <c r="O101" s="9" t="n">
-        <v>99.789568</v>
+        <v>99.789496</v>
       </c>
       <c r="P101" s="9" t="n"/>
       <c r="Q101" s="9" t="n">
@@ -8178,7 +8178,7 @@
         <v>99.239958</v>
       </c>
       <c r="O102" s="6" t="n">
-        <v>99.272901</v>
+        <v>99.272651</v>
       </c>
       <c r="P102" s="6" t="n"/>
       <c r="Q102" s="6" t="n">
@@ -8260,7 +8260,7 @@
         <v>99.544714</v>
       </c>
       <c r="O103" s="9" t="n">
-        <v>98.86248500000001</v>
+        <v>98.862094</v>
       </c>
       <c r="P103" s="9" t="n"/>
       <c r="Q103" s="9" t="n">
@@ -8342,7 +8342,7 @@
         <v>99.882284</v>
       </c>
       <c r="O104" s="6" t="n">
-        <v>98.624667</v>
+        <v>98.62419300000001</v>
       </c>
       <c r="P104" s="6" t="n"/>
       <c r="Q104" s="6" t="n">
@@ -8424,7 +8424,7 @@
         <v>100.223042</v>
       </c>
       <c r="O105" s="9" t="n">
-        <v>98.56236699999999</v>
+        <v>98.561871</v>
       </c>
       <c r="P105" s="9" t="n"/>
       <c r="Q105" s="9" t="n">
@@ -8506,7 +8506,7 @@
         <v>100.543221</v>
       </c>
       <c r="O106" s="6" t="n">
-        <v>98.62916199999999</v>
+        <v>98.628688</v>
       </c>
       <c r="P106" s="6" t="n"/>
       <c r="Q106" s="6" t="n">
@@ -8588,7 +8588,7 @@
         <v>100.827865</v>
       </c>
       <c r="O107" s="9" t="n">
-        <v>98.84322299999999</v>
+        <v>98.842822</v>
       </c>
       <c r="P107" s="9" t="n"/>
       <c r="Q107" s="9" t="n">
@@ -8670,7 +8670,7 @@
         <v>101.067592</v>
       </c>
       <c r="O108" s="6" t="n">
-        <v>99.194541</v>
+        <v>99.19426199999999</v>
       </c>
       <c r="P108" s="6" t="n"/>
       <c r="Q108" s="6" t="n">
@@ -8752,7 +8752,7 @@
         <v>101.257588</v>
       </c>
       <c r="O109" s="9" t="n">
-        <v>99.65160400000001</v>
+        <v>99.651482</v>
       </c>
       <c r="P109" s="9" t="n"/>
       <c r="Q109" s="9" t="n">
@@ -8834,7 +8834,7 @@
         <v>101.38472</v>
       </c>
       <c r="O110" s="6" t="n">
-        <v>100.156392</v>
+        <v>100.156445</v>
       </c>
       <c r="P110" s="6" t="n"/>
       <c r="Q110" s="6" t="n">
@@ -8916,7 +8916,7 @@
         <v>101.455399</v>
       </c>
       <c r="O111" s="9" t="n">
-        <v>100.686409</v>
+        <v>100.686644</v>
       </c>
       <c r="P111" s="9" t="n"/>
       <c r="Q111" s="9" t="n">
@@ -8998,7 +8998,7 @@
         <v>101.487237</v>
       </c>
       <c r="O112" s="6" t="n">
-        <v>101.221976</v>
+        <v>101.222396</v>
       </c>
       <c r="P112" s="6" t="n"/>
       <c r="Q112" s="6" t="n">
@@ -9080,7 +9080,7 @@
         <v>101.487498</v>
       </c>
       <c r="O113" s="9" t="n">
-        <v>101.652606</v>
+        <v>101.653175</v>
       </c>
       <c r="P113" s="9" t="n"/>
       <c r="Q113" s="9" t="n">
@@ -9162,7 +9162,7 @@
         <v>101.474435</v>
       </c>
       <c r="O114" s="6" t="n">
-        <v>101.95194</v>
+        <v>101.952612</v>
       </c>
       <c r="P114" s="6" t="n"/>
       <c r="Q114" s="6" t="n">
@@ -9244,7 +9244,7 @@
         <v>101.436576</v>
       </c>
       <c r="O115" s="9" t="n">
-        <v>102.127609</v>
+        <v>102.128342</v>
       </c>
       <c r="P115" s="9" t="n"/>
       <c r="Q115" s="9" t="n">
@@ -9326,7 +9326,7 @@
         <v>101.35198</v>
       </c>
       <c r="O116" s="6" t="n">
-        <v>102.151375</v>
+        <v>102.152115</v>
       </c>
       <c r="P116" s="6" t="n"/>
       <c r="Q116" s="6" t="n">
@@ -9408,7 +9408,7 @@
         <v>101.219874</v>
       </c>
       <c r="O117" s="9" t="n">
-        <v>102.021678</v>
+        <v>102.022372</v>
       </c>
       <c r="P117" s="9" t="n"/>
       <c r="Q117" s="9" t="n">
@@ -9490,7 +9490,7 @@
         <v>101.047109</v>
       </c>
       <c r="O118" s="6" t="n">
-        <v>101.788859</v>
+        <v>101.789472</v>
       </c>
       <c r="P118" s="6" t="n"/>
       <c r="Q118" s="6" t="n">
@@ -9572,7 +9572,7 @@
         <v>100.861248</v>
       </c>
       <c r="O119" s="9" t="n">
-        <v>101.501017</v>
+        <v>101.501531</v>
       </c>
       <c r="P119" s="9" t="n"/>
       <c r="Q119" s="9" t="n">
@@ -9654,7 +9654,7 @@
         <v>100.674677</v>
       </c>
       <c r="O120" s="6" t="n">
-        <v>101.188064</v>
+        <v>101.18847</v>
       </c>
       <c r="P120" s="6" t="n"/>
       <c r="Q120" s="6" t="n">
@@ -9736,7 +9736,7 @@
         <v>100.538541</v>
       </c>
       <c r="O121" s="9" t="n">
-        <v>100.842915</v>
+        <v>100.843202</v>
       </c>
       <c r="P121" s="9" t="n"/>
       <c r="Q121" s="9" t="n">
@@ -9818,7 +9818,7 @@
         <v>100.451891</v>
       </c>
       <c r="O122" s="6" t="n">
-        <v>100.555611</v>
+        <v>100.555799</v>
       </c>
       <c r="P122" s="6" t="n"/>
       <c r="Q122" s="6" t="n">
@@ -9900,7 +9900,7 @@
         <v>100.375072</v>
       </c>
       <c r="O123" s="9" t="n">
-        <v>100.409005</v>
+        <v>100.409143</v>
       </c>
       <c r="P123" s="9" t="n"/>
       <c r="Q123" s="9" t="n">
@@ -9982,7 +9982,7 @@
         <v>100.293934</v>
       </c>
       <c r="O124" s="6" t="n">
-        <v>100.407349</v>
+        <v>100.407487</v>
       </c>
       <c r="P124" s="6" t="n"/>
       <c r="Q124" s="6" t="n">
@@ -10064,7 +10064,7 @@
         <v>100.202263</v>
       </c>
       <c r="O125" s="9" t="n">
-        <v>100.508487</v>
+        <v>100.508659</v>
       </c>
       <c r="P125" s="9" t="n"/>
       <c r="Q125" s="9" t="n">
@@ -10146,7 +10146,7 @@
         <v>100.118217</v>
       </c>
       <c r="O126" s="6" t="n">
-        <v>100.648797</v>
+        <v>100.649017</v>
       </c>
       <c r="P126" s="6" t="n"/>
       <c r="Q126" s="6" t="n">
@@ -10228,7 +10228,7 @@
         <v>100.061134</v>
       </c>
       <c r="O127" s="9" t="n">
-        <v>100.780519</v>
+        <v>100.780785</v>
       </c>
       <c r="P127" s="9" t="n"/>
       <c r="Q127" s="9" t="n">
@@ -10310,7 +10310,7 @@
         <v>100.056587</v>
       </c>
       <c r="O128" s="6" t="n">
-        <v>100.890053</v>
+        <v>100.890357</v>
       </c>
       <c r="P128" s="6" t="n"/>
       <c r="Q128" s="6" t="n">
@@ -10392,7 +10392,7 @@
         <v>100.111083</v>
       </c>
       <c r="O129" s="9" t="n">
-        <v>100.950961</v>
+        <v>100.951289</v>
       </c>
       <c r="P129" s="9" t="n"/>
       <c r="Q129" s="9" t="n">
@@ -10474,7 +10474,7 @@
         <v>100.224766</v>
       </c>
       <c r="O130" s="6" t="n">
-        <v>100.974927</v>
+        <v>100.975265</v>
       </c>
       <c r="P130" s="6" t="n"/>
       <c r="Q130" s="6" t="n">
@@ -10556,7 +10556,7 @@
         <v>100.371558</v>
       </c>
       <c r="O131" s="9" t="n">
-        <v>100.954334</v>
+        <v>100.954664</v>
       </c>
       <c r="P131" s="9" t="n"/>
       <c r="Q131" s="9" t="n">
@@ -10638,7 +10638,7 @@
         <v>100.524099</v>
       </c>
       <c r="O132" s="6" t="n">
-        <v>100.947077</v>
+        <v>100.947405</v>
       </c>
       <c r="P132" s="6" t="n"/>
       <c r="Q132" s="6" t="n">
@@ -10720,7 +10720,7 @@
         <v>100.656981</v>
       </c>
       <c r="O133" s="9" t="n">
-        <v>101.000532</v>
+        <v>101.000878</v>
       </c>
       <c r="P133" s="9" t="n"/>
       <c r="Q133" s="9" t="n">
@@ -10802,7 +10802,7 @@
         <v>100.739497</v>
       </c>
       <c r="O134" s="6" t="n">
-        <v>101.065442</v>
+        <v>101.065809</v>
       </c>
       <c r="P134" s="6" t="n"/>
       <c r="Q134" s="6" t="n">
@@ -10884,7 +10884,7 @@
         <v>100.75915</v>
       </c>
       <c r="O135" s="9" t="n">
-        <v>101.068369</v>
+        <v>101.068738</v>
       </c>
       <c r="P135" s="9" t="n"/>
       <c r="Q135" s="9" t="n">
@@ -10966,7 +10966,7 @@
         <v>100.717678</v>
       </c>
       <c r="O136" s="6" t="n">
-        <v>100.934385</v>
+        <v>100.934708</v>
       </c>
       <c r="P136" s="6" t="n"/>
       <c r="Q136" s="6" t="n">
@@ -11048,7 +11048,7 @@
         <v>100.638116</v>
       </c>
       <c r="O137" s="9" t="n">
-        <v>100.718923</v>
+        <v>100.719173</v>
       </c>
       <c r="P137" s="9" t="n"/>
       <c r="Q137" s="9" t="n">
@@ -11130,7 +11130,7 @@
         <v>100.529789</v>
       </c>
       <c r="O138" s="6" t="n">
-        <v>100.479027</v>
+        <v>100.479194</v>
       </c>
       <c r="P138" s="6" t="n"/>
       <c r="Q138" s="6" t="n">
@@ -11212,7 +11212,7 @@
         <v>100.417675</v>
       </c>
       <c r="O139" s="9" t="n">
-        <v>100.282393</v>
+        <v>100.282492</v>
       </c>
       <c r="P139" s="9" t="n"/>
       <c r="Q139" s="9" t="n">
@@ -11294,7 +11294,7 @@
         <v>100.326796</v>
       </c>
       <c r="O140" s="6" t="n">
-        <v>100.143058</v>
+        <v>100.143109</v>
       </c>
       <c r="P140" s="6" t="n"/>
       <c r="Q140" s="6" t="n">
@@ -11376,7 +11376,7 @@
         <v>100.276567</v>
       </c>
       <c r="O141" s="9" t="n">
-        <v>100.08101</v>
+        <v>100.081037</v>
       </c>
       <c r="P141" s="9" t="n"/>
       <c r="Q141" s="9" t="n">
@@ -11458,7 +11458,7 @@
         <v>100.259426</v>
       </c>
       <c r="O142" s="6" t="n">
-        <v>100.088535</v>
+        <v>100.088563</v>
       </c>
       <c r="P142" s="6" t="n"/>
       <c r="Q142" s="6" t="n">
@@ -11540,7 +11540,7 @@
         <v>100.262412</v>
       </c>
       <c r="O143" s="9" t="n">
-        <v>100.126686</v>
+        <v>100.126727</v>
       </c>
       <c r="P143" s="9" t="n"/>
       <c r="Q143" s="9" t="n">
@@ -11622,7 +11622,7 @@
         <v>100.28414</v>
       </c>
       <c r="O144" s="6" t="n">
-        <v>100.15736</v>
+        <v>100.157413</v>
       </c>
       <c r="P144" s="6" t="n"/>
       <c r="Q144" s="6" t="n">
@@ -11704,7 +11704,7 @@
         <v>100.316903</v>
       </c>
       <c r="O145" s="9" t="n">
-        <v>100.162401</v>
+        <v>100.162456</v>
       </c>
       <c r="P145" s="9" t="n"/>
       <c r="Q145" s="9" t="n">
@@ -11786,7 +11786,7 @@
         <v>100.362035</v>
       </c>
       <c r="O146" s="6" t="n">
-        <v>100.114701</v>
+        <v>100.11474</v>
       </c>
       <c r="P146" s="6" t="n"/>
       <c r="Q146" s="6" t="n">
@@ -11868,7 +11868,7 @@
         <v>100.426178</v>
       </c>
       <c r="O147" s="9" t="n">
-        <v>99.996448</v>
+        <v>99.996447</v>
       </c>
       <c r="P147" s="9" t="n"/>
       <c r="Q147" s="9" t="n">
@@ -11950,7 +11950,7 @@
         <v>100.514866</v>
       </c>
       <c r="O148" s="6" t="n">
-        <v>99.907634</v>
+        <v>99.90760299999999</v>
       </c>
       <c r="P148" s="6" t="n"/>
       <c r="Q148" s="6" t="n">
@@ -12032,7 +12032,7 @@
         <v>100.612528</v>
       </c>
       <c r="O149" s="9" t="n">
-        <v>99.89575499999999</v>
+        <v>99.89572</v>
       </c>
       <c r="P149" s="9" t="n"/>
       <c r="Q149" s="9" t="n">
@@ -12114,7 +12114,7 @@
         <v>100.733488</v>
       </c>
       <c r="O150" s="6" t="n">
-        <v>99.94369500000001</v>
+        <v>99.943676</v>
       </c>
       <c r="P150" s="6" t="n"/>
       <c r="Q150" s="6" t="n">
@@ -12196,7 +12196,7 @@
         <v>100.875636</v>
       </c>
       <c r="O151" s="9" t="n">
-        <v>100.004611</v>
+        <v>100.004613</v>
       </c>
       <c r="P151" s="9" t="n"/>
       <c r="Q151" s="9" t="n">
@@ -12278,7 +12278,7 @@
         <v>101.01503</v>
       </c>
       <c r="O152" s="6" t="n">
-        <v>100.036698</v>
+        <v>100.036713</v>
       </c>
       <c r="P152" s="6" t="n"/>
       <c r="Q152" s="6" t="n">
@@ -12360,7 +12360,7 @@
         <v>101.118198</v>
       </c>
       <c r="O153" s="9" t="n">
-        <v>100.027139</v>
+        <v>100.027152</v>
       </c>
       <c r="P153" s="9" t="n"/>
       <c r="Q153" s="9" t="n">
@@ -12442,7 +12442,7 @@
         <v>101.172073</v>
       </c>
       <c r="O154" s="6" t="n">
-        <v>99.931414</v>
+        <v>99.931394</v>
       </c>
       <c r="P154" s="6" t="n"/>
       <c r="Q154" s="6" t="n">
@@ -12524,7 +12524,7 @@
         <v>101.173279</v>
       </c>
       <c r="O155" s="9" t="n">
-        <v>99.727313</v>
+        <v>99.727223</v>
       </c>
       <c r="P155" s="9" t="n"/>
       <c r="Q155" s="9" t="n">
@@ -12606,7 +12606,7 @@
         <v>101.129047</v>
       </c>
       <c r="O156" s="6" t="n">
-        <v>99.444508</v>
+        <v>99.44432</v>
       </c>
       <c r="P156" s="6" t="n"/>
       <c r="Q156" s="6" t="n">
@@ -12688,7 +12688,7 @@
         <v>101.044343</v>
       </c>
       <c r="O157" s="9" t="n">
-        <v>99.102294</v>
+        <v>99.10198800000001</v>
       </c>
       <c r="P157" s="9" t="n"/>
       <c r="Q157" s="9" t="n">
@@ -12770,7 +12770,7 @@
         <v>100.940255</v>
       </c>
       <c r="O158" s="6" t="n">
-        <v>98.75801800000001</v>
+        <v>98.757592</v>
       </c>
       <c r="P158" s="6" t="n"/>
       <c r="Q158" s="6" t="n">
@@ -12852,7 +12852,7 @@
         <v>100.826183</v>
       </c>
       <c r="O159" s="9" t="n">
-        <v>98.46812</v>
+        <v>98.467595</v>
       </c>
       <c r="P159" s="9" t="n"/>
       <c r="Q159" s="9" t="n">
@@ -12934,7 +12934,7 @@
         <v>100.694548</v>
       </c>
       <c r="O160" s="6" t="n">
-        <v>98.27145400000001</v>
+        <v>98.270861</v>
       </c>
       <c r="P160" s="6" t="n"/>
       <c r="Q160" s="6" t="n">
@@ -13016,7 +13016,7 @@
         <v>100.551939</v>
       </c>
       <c r="O161" s="9" t="n">
-        <v>98.153419</v>
+        <v>98.152787</v>
       </c>
       <c r="P161" s="9" t="n"/>
       <c r="Q161" s="9" t="n">
@@ -13098,7 +13098,7 @@
         <v>100.41285</v>
       </c>
       <c r="O162" s="6" t="n">
-        <v>98.095584</v>
+        <v>98.09493399999999</v>
       </c>
       <c r="P162" s="6" t="n"/>
       <c r="Q162" s="6" t="n">
@@ -13180,7 +13180,7 @@
         <v>100.31019</v>
       </c>
       <c r="O163" s="9" t="n">
-        <v>98.072366</v>
+        <v>98.071708</v>
       </c>
       <c r="P163" s="9" t="n"/>
       <c r="Q163" s="9" t="n">
@@ -13262,7 +13262,7 @@
         <v>100.23428</v>
       </c>
       <c r="O164" s="6" t="n">
-        <v>98.094238</v>
+        <v>98.09358899999999</v>
       </c>
       <c r="P164" s="6" t="n"/>
       <c r="Q164" s="6" t="n">
@@ -13344,7 +13344,7 @@
         <v>100.17566</v>
       </c>
       <c r="O165" s="9" t="n">
-        <v>98.15269499999999</v>
+        <v>98.152066</v>
       </c>
       <c r="P165" s="9" t="n"/>
       <c r="Q165" s="9" t="n">
@@ -13426,7 +13426,7 @@
         <v>100.113965</v>
       </c>
       <c r="O166" s="6" t="n">
-        <v>98.263279</v>
+        <v>98.262688</v>
       </c>
       <c r="P166" s="6" t="n"/>
       <c r="Q166" s="6" t="n">
@@ -13508,7 +13508,7 @@
         <v>100.040907</v>
       </c>
       <c r="O167" s="9" t="n">
-        <v>98.445206</v>
+        <v>98.444676</v>
       </c>
       <c r="P167" s="9" t="n"/>
       <c r="Q167" s="9" t="n">
@@ -13590,7 +13590,7 @@
         <v>99.94879</v>
       </c>
       <c r="O168" s="6" t="n">
-        <v>98.62581</v>
+        <v>98.62534100000001</v>
       </c>
       <c r="P168" s="6" t="n"/>
       <c r="Q168" s="6" t="n">
@@ -13672,7 +13672,7 @@
         <v>99.84265600000001</v>
       </c>
       <c r="O169" s="9" t="n">
-        <v>98.783198</v>
+        <v>98.78278299999999</v>
       </c>
       <c r="P169" s="9" t="n"/>
       <c r="Q169" s="9" t="n">
@@ -13754,7 +13754,7 @@
         <v>99.780244</v>
       </c>
       <c r="O170" s="6" t="n">
-        <v>98.93013500000001</v>
+        <v>98.92977</v>
       </c>
       <c r="P170" s="6" t="n"/>
       <c r="Q170" s="6" t="n">
@@ -13836,7 +13836,7 @@
         <v>99.774478</v>
       </c>
       <c r="O171" s="9" t="n">
-        <v>99.0835</v>
+        <v>99.083189</v>
       </c>
       <c r="P171" s="9" t="n"/>
       <c r="Q171" s="9" t="n">
@@ -13918,7 +13918,7 @@
         <v>99.842524</v>
       </c>
       <c r="O172" s="6" t="n">
-        <v>99.237149</v>
+        <v>99.23689299999999</v>
       </c>
       <c r="P172" s="6" t="n"/>
       <c r="Q172" s="6" t="n">
@@ -14000,7 +14000,7 @@
         <v>100.003542</v>
       </c>
       <c r="O173" s="9" t="n">
-        <v>99.379175</v>
+        <v>99.378972</v>
       </c>
       <c r="P173" s="9" t="n"/>
       <c r="Q173" s="9" t="n">
@@ -14082,7 +14082,7 @@
         <v>100.217521</v>
       </c>
       <c r="O174" s="6" t="n">
-        <v>99.55570899999999</v>
+        <v>99.55556900000001</v>
       </c>
       <c r="P174" s="6" t="n"/>
       <c r="Q174" s="6" t="n">
@@ -14164,7 +14164,7 @@
         <v>100.433683</v>
       </c>
       <c r="O175" s="9" t="n">
-        <v>99.762992</v>
+        <v>99.762925</v>
       </c>
       <c r="P175" s="9" t="n"/>
       <c r="Q175" s="9" t="n">
@@ -14246,7 +14246,7 @@
         <v>100.617396</v>
       </c>
       <c r="O176" s="6" t="n">
-        <v>99.946072</v>
+        <v>99.946068</v>
       </c>
       <c r="P176" s="6" t="n"/>
       <c r="Q176" s="6" t="n">
@@ -14328,7 +14328,7 @@
         <v>100.772735</v>
       </c>
       <c r="O177" s="9" t="n">
-        <v>100.037275</v>
+        <v>100.037299</v>
       </c>
       <c r="P177" s="9" t="n"/>
       <c r="Q177" s="9" t="n">
@@ -14410,7 +14410,7 @@
         <v>100.893156</v>
       </c>
       <c r="O178" s="6" t="n">
-        <v>100.024907</v>
+        <v>100.024924</v>
       </c>
       <c r="P178" s="6" t="n"/>
       <c r="Q178" s="6" t="n">
@@ -14492,7 +14492,7 @@
         <v>100.973359</v>
       </c>
       <c r="O179" s="9" t="n">
-        <v>99.937275</v>
+        <v>99.93726100000001</v>
       </c>
       <c r="P179" s="9" t="n"/>
       <c r="Q179" s="9" t="n">
@@ -14574,7 +14574,7 @@
         <v>101.003453</v>
       </c>
       <c r="O180" s="6" t="n">
-        <v>99.842341</v>
+        <v>99.842291</v>
       </c>
       <c r="P180" s="6" t="n"/>
       <c r="Q180" s="6" t="n">
@@ -14656,7 +14656,7 @@
         <v>100.979953</v>
       </c>
       <c r="O181" s="9" t="n">
-        <v>99.76645499999999</v>
+        <v>99.766375</v>
       </c>
       <c r="P181" s="9" t="n"/>
       <c r="Q181" s="9" t="n">
@@ -14738,7 +14738,7 @@
         <v>100.904273</v>
       </c>
       <c r="O182" s="6" t="n">
-        <v>99.68087</v>
+        <v>99.68075399999999</v>
       </c>
       <c r="P182" s="6" t="n"/>
       <c r="Q182" s="6" t="n">
@@ -14820,7 +14820,7 @@
         <v>100.764799</v>
       </c>
       <c r="O183" s="9" t="n">
-        <v>99.531374</v>
+        <v>99.531198</v>
       </c>
       <c r="P183" s="9" t="n"/>
       <c r="Q183" s="9" t="n">
@@ -14902,7 +14902,7 @@
         <v>100.521356</v>
       </c>
       <c r="O184" s="6" t="n">
-        <v>99.23327</v>
+        <v>99.232979</v>
       </c>
       <c r="P184" s="6" t="n"/>
       <c r="Q184" s="6" t="n">
@@ -14984,7 +14984,7 @@
         <v>100.154718</v>
       </c>
       <c r="O185" s="9" t="n">
-        <v>98.782079</v>
+        <v>98.78161900000001</v>
       </c>
       <c r="P185" s="9" t="n"/>
       <c r="Q185" s="9" t="n">
@@ -15066,7 +15066,7 @@
         <v>99.687623</v>
       </c>
       <c r="O186" s="6" t="n">
-        <v>98.204804</v>
+        <v>98.204131</v>
       </c>
       <c r="P186" s="6" t="n"/>
       <c r="Q186" s="6" t="n">
@@ -15148,7 +15148,7 @@
         <v>99.18918600000001</v>
       </c>
       <c r="O187" s="9" t="n">
-        <v>97.605278</v>
+        <v>97.60439100000001</v>
       </c>
       <c r="P187" s="9" t="n"/>
       <c r="Q187" s="9" t="n">
@@ -15230,7 +15230,7 @@
         <v>98.73203599999999</v>
       </c>
       <c r="O188" s="6" t="n">
-        <v>97.13097399999999</v>
+        <v>97.129926</v>
       </c>
       <c r="P188" s="6" t="n"/>
       <c r="Q188" s="6" t="n">
@@ -15312,7 +15312,7 @@
         <v>98.353084</v>
       </c>
       <c r="O189" s="9" t="n">
-        <v>96.93185</v>
+        <v>96.93074900000001</v>
       </c>
       <c r="P189" s="9" t="n"/>
       <c r="Q189" s="9" t="n">
@@ -15394,7 +15394,7 @@
         <v>98.10048399999999</v>
       </c>
       <c r="O190" s="6" t="n">
-        <v>97.055119</v>
+        <v>97.054075</v>
       </c>
       <c r="P190" s="6" t="n"/>
       <c r="Q190" s="6" t="n">
@@ -15476,7 +15476,7 @@
         <v>97.964465</v>
       </c>
       <c r="O191" s="9" t="n">
-        <v>97.46481</v>
+        <v>97.463922</v>
       </c>
       <c r="P191" s="9" t="n"/>
       <c r="Q191" s="9" t="n">
@@ -15558,7 +15558,7 @@
         <v>97.923315</v>
       </c>
       <c r="O192" s="6" t="n">
-        <v>98.041613</v>
+        <v>98.040933</v>
       </c>
       <c r="P192" s="6" t="n"/>
       <c r="Q192" s="6" t="n">
@@ -15640,7 +15640,7 @@
         <v>97.957207</v>
       </c>
       <c r="O193" s="9" t="n">
-        <v>98.690737</v>
+        <v>98.690287</v>
       </c>
       <c r="P193" s="9" t="n"/>
       <c r="Q193" s="9" t="n">
@@ -15722,7 +15722,7 @@
         <v>98.024897</v>
       </c>
       <c r="O194" s="6" t="n">
-        <v>99.35184099999999</v>
+        <v>99.351623</v>
       </c>
       <c r="P194" s="6" t="n"/>
       <c r="Q194" s="6" t="n">
@@ -15804,7 +15804,7 @@
         <v>98.115427</v>
       </c>
       <c r="O195" s="9" t="n">
-        <v>99.990295</v>
+        <v>99.99029899999999</v>
       </c>
       <c r="P195" s="9" t="n"/>
       <c r="Q195" s="9" t="n">
@@ -15886,7 +15886,7 @@
         <v>98.242285</v>
       </c>
       <c r="O196" s="6" t="n">
-        <v>100.595694</v>
+        <v>100.59591</v>
       </c>
       <c r="P196" s="6" t="n"/>
       <c r="Q196" s="6" t="n">
@@ -15968,7 +15968,7 @@
         <v>98.401079</v>
       </c>
       <c r="O197" s="9" t="n">
-        <v>101.118922</v>
+        <v>101.11932</v>
       </c>
       <c r="P197" s="9" t="n"/>
       <c r="Q197" s="9" t="n">
@@ -16050,7 +16050,7 @@
         <v>98.574071</v>
       </c>
       <c r="O198" s="6" t="n">
-        <v>101.512136</v>
+        <v>101.512671</v>
       </c>
       <c r="P198" s="6" t="n"/>
       <c r="Q198" s="6" t="n">
@@ -16132,7 +16132,7 @@
         <v>98.748597</v>
       </c>
       <c r="O199" s="9" t="n">
-        <v>101.759287</v>
+        <v>101.759907</v>
       </c>
       <c r="P199" s="9" t="n"/>
       <c r="Q199" s="9" t="n">
@@ -16214,7 +16214,7 @@
         <v>98.90607799999999</v>
       </c>
       <c r="O200" s="6" t="n">
-        <v>101.910694</v>
+        <v>101.911364</v>
       </c>
       <c r="P200" s="6" t="n"/>
       <c r="Q200" s="6" t="n">
@@ -16296,7 +16296,7 @@
         <v>99.043278</v>
       </c>
       <c r="O201" s="9" t="n">
-        <v>101.975651</v>
+        <v>101.976341</v>
       </c>
       <c r="P201" s="9" t="n"/>
       <c r="Q201" s="9" t="n">
@@ -16378,7 +16378,7 @@
         <v>99.152389</v>
       </c>
       <c r="O202" s="6" t="n">
-        <v>101.951092</v>
+        <v>101.951771</v>
       </c>
       <c r="P202" s="6" t="n"/>
       <c r="Q202" s="6" t="n">
@@ -16460,7 +16460,7 @@
         <v>99.23554900000001</v>
       </c>
       <c r="O203" s="9" t="n">
-        <v>101.829609</v>
+        <v>101.830243</v>
       </c>
       <c r="P203" s="9" t="n"/>
       <c r="Q203" s="9" t="n">
@@ -16542,7 +16542,7 @@
         <v>99.32303899999999</v>
       </c>
       <c r="O204" s="6" t="n">
-        <v>101.658241</v>
+        <v>101.658815</v>
       </c>
       <c r="P204" s="6" t="n"/>
       <c r="Q204" s="6" t="n">
@@ -16624,7 +16624,7 @@
         <v>99.406631</v>
       </c>
       <c r="O205" s="9" t="n">
-        <v>101.460879</v>
+        <v>101.461386</v>
       </c>
       <c r="P205" s="9" t="n"/>
       <c r="Q205" s="9" t="n">
@@ -16706,7 +16706,7 @@
         <v>99.47515300000001</v>
       </c>
       <c r="O206" s="6" t="n">
-        <v>101.237369</v>
+        <v>101.2378</v>
       </c>
       <c r="P206" s="6" t="n"/>
       <c r="Q206" s="6" t="n">
@@ -16788,7 +16788,7 @@
         <v>99.52127</v>
       </c>
       <c r="O207" s="9" t="n">
-        <v>101.030116</v>
+        <v>101.030478</v>
       </c>
       <c r="P207" s="9" t="n"/>
       <c r="Q207" s="9" t="n">
@@ -16870,7 +16870,7 @@
         <v>99.542169</v>
       </c>
       <c r="O208" s="6" t="n">
-        <v>100.894455</v>
+        <v>100.894773</v>
       </c>
       <c r="P208" s="6" t="n"/>
       <c r="Q208" s="6" t="n">
@@ -16952,7 +16952,7 @@
         <v>99.561707</v>
       </c>
       <c r="O209" s="9" t="n">
-        <v>100.873777</v>
+        <v>100.874089</v>
       </c>
       <c r="P209" s="9" t="n"/>
       <c r="Q209" s="9" t="n">
@@ -17034,7 +17034,7 @@
         <v>99.61749500000001</v>
       </c>
       <c r="O210" s="6" t="n">
-        <v>100.947579</v>
+        <v>100.947919</v>
       </c>
       <c r="P210" s="6" t="n"/>
       <c r="Q210" s="6" t="n">
@@ -17116,7 +17116,7 @@
         <v>99.702364</v>
       </c>
       <c r="O211" s="9" t="n">
-        <v>101.076476</v>
+        <v>101.076858</v>
       </c>
       <c r="P211" s="9" t="n"/>
       <c r="Q211" s="9" t="n">
@@ -17198,7 +17198,7 @@
         <v>99.80806</v>
       </c>
       <c r="O212" s="6" t="n">
-        <v>101.184566</v>
+        <v>101.18498</v>
       </c>
       <c r="P212" s="6" t="n"/>
       <c r="Q212" s="6" t="n">
@@ -17280,7 +17280,7 @@
         <v>99.920338</v>
       </c>
       <c r="O213" s="9" t="n">
-        <v>101.25649</v>
+        <v>101.256925</v>
       </c>
       <c r="P213" s="9" t="n"/>
       <c r="Q213" s="9" t="n">
@@ -17362,7 +17362,7 @@
         <v>100.031592</v>
       </c>
       <c r="O214" s="6" t="n">
-        <v>101.293937</v>
+        <v>101.294384</v>
       </c>
       <c r="P214" s="6" t="n"/>
       <c r="Q214" s="6" t="n">
@@ -17444,7 +17444,7 @@
         <v>100.143608</v>
       </c>
       <c r="O215" s="9" t="n">
-        <v>101.308141</v>
+        <v>101.30859</v>
       </c>
       <c r="P215" s="9" t="n"/>
       <c r="Q215" s="9" t="n">
@@ -17526,7 +17526,7 @@
         <v>100.24582</v>
       </c>
       <c r="O216" s="6" t="n">
-        <v>101.318901</v>
+        <v>101.319354</v>
       </c>
       <c r="P216" s="6" t="n"/>
       <c r="Q216" s="6" t="n">
@@ -17608,7 +17608,7 @@
         <v>100.332048</v>
       </c>
       <c r="O217" s="9" t="n">
-        <v>101.366452</v>
+        <v>101.366923</v>
       </c>
       <c r="P217" s="9" t="n"/>
       <c r="Q217" s="9" t="n">
@@ -17690,7 +17690,7 @@
         <v>100.406904</v>
       </c>
       <c r="O218" s="6" t="n">
-        <v>101.446219</v>
+        <v>101.446717</v>
       </c>
       <c r="P218" s="6" t="n"/>
       <c r="Q218" s="6" t="n">
@@ -17772,7 +17772,7 @@
         <v>100.472965</v>
       </c>
       <c r="O219" s="9" t="n">
-        <v>101.521468</v>
+        <v>101.521993</v>
       </c>
       <c r="P219" s="9" t="n"/>
       <c r="Q219" s="9" t="n">
@@ -17854,7 +17854,7 @@
         <v>100.530378</v>
       </c>
       <c r="O220" s="6" t="n">
-        <v>101.563324</v>
+        <v>101.56386</v>
       </c>
       <c r="P220" s="6" t="n"/>
       <c r="Q220" s="6" t="n">
@@ -17936,7 +17936,7 @@
         <v>100.572069</v>
       </c>
       <c r="O221" s="9" t="n">
-        <v>101.554177</v>
+        <v>101.554706</v>
       </c>
       <c r="P221" s="9" t="n"/>
       <c r="Q221" s="9" t="n">
@@ -18018,7 +18018,7 @@
         <v>100.598634</v>
       </c>
       <c r="O222" s="6" t="n">
-        <v>101.489577</v>
+        <v>101.490082</v>
       </c>
       <c r="P222" s="6" t="n"/>
       <c r="Q222" s="6" t="n">
@@ -18100,7 +18100,7 @@
         <v>100.595926</v>
       </c>
       <c r="O223" s="9" t="n">
-        <v>101.38938</v>
+        <v>101.389847</v>
       </c>
       <c r="P223" s="9" t="n"/>
       <c r="Q223" s="9" t="n">
@@ -18182,7 +18182,7 @@
         <v>100.556732</v>
       </c>
       <c r="O224" s="6" t="n">
-        <v>101.2257</v>
+        <v>101.226108</v>
       </c>
       <c r="P224" s="6" t="n"/>
       <c r="Q224" s="6" t="n">
@@ -18264,7 +18264,7 @@
         <v>100.475153</v>
       </c>
       <c r="O225" s="9" t="n">
-        <v>100.99614</v>
+        <v>100.996475</v>
       </c>
       <c r="P225" s="9" t="n"/>
       <c r="Q225" s="9" t="n">
@@ -18346,7 +18346,7 @@
         <v>100.357043</v>
       </c>
       <c r="O226" s="6" t="n">
-        <v>100.767236</v>
+        <v>100.767495</v>
       </c>
       <c r="P226" s="6" t="n"/>
       <c r="Q226" s="6" t="n">
@@ -18428,7 +18428,7 @@
         <v>100.220583</v>
       </c>
       <c r="O227" s="9" t="n">
-        <v>100.56595</v>
+        <v>100.566149</v>
       </c>
       <c r="P227" s="9" t="n"/>
       <c r="Q227" s="9" t="n">
@@ -18510,7 +18510,7 @@
         <v>100.090112</v>
       </c>
       <c r="O228" s="6" t="n">
-        <v>100.375553</v>
+        <v>100.375689</v>
       </c>
       <c r="P228" s="6" t="n"/>
       <c r="Q228" s="6" t="n">
@@ -18592,7 +18592,7 @@
         <v>99.981256</v>
       </c>
       <c r="O229" s="9" t="n">
-        <v>100.171042</v>
+        <v>100.1711</v>
       </c>
       <c r="P229" s="9" t="n"/>
       <c r="Q229" s="9" t="n">
@@ -18674,7 +18674,7 @@
         <v>99.901003</v>
       </c>
       <c r="O230" s="6" t="n">
-        <v>99.966813</v>
+        <v>99.96679899999999</v>
       </c>
       <c r="P230" s="6" t="n"/>
       <c r="Q230" s="6" t="n">
@@ -18756,7 +18756,7 @@
         <v>99.84118100000001</v>
       </c>
       <c r="O231" s="9" t="n">
-        <v>99.766784</v>
+        <v>99.766699</v>
       </c>
       <c r="P231" s="9" t="n"/>
       <c r="Q231" s="9" t="n">
@@ -18838,7 +18838,7 @@
         <v>99.799001</v>
       </c>
       <c r="O232" s="6" t="n">
-        <v>99.57031000000001</v>
+        <v>99.570155</v>
       </c>
       <c r="P232" s="6" t="n"/>
       <c r="Q232" s="6" t="n">
@@ -18920,7 +18920,7 @@
         <v>99.77095300000001</v>
       </c>
       <c r="O233" s="9" t="n">
-        <v>99.407854</v>
+        <v>99.407647</v>
       </c>
       <c r="P233" s="9" t="n"/>
       <c r="Q233" s="9" t="n">
@@ -19002,7 +19002,7 @@
         <v>99.77270900000001</v>
       </c>
       <c r="O234" s="6" t="n">
-        <v>99.312431</v>
+        <v>99.312195</v>
       </c>
       <c r="P234" s="6" t="n"/>
       <c r="Q234" s="6" t="n">
@@ -19084,7 +19084,7 @@
         <v>99.814262</v>
       </c>
       <c r="O235" s="9" t="n">
-        <v>99.309331</v>
+        <v>99.309106</v>
       </c>
       <c r="P235" s="9" t="n"/>
       <c r="Q235" s="9" t="n">
@@ -19166,7 +19166,7 @@
         <v>99.89098199999999</v>
       </c>
       <c r="O236" s="6" t="n">
-        <v>99.401433</v>
+        <v>99.40124900000001</v>
       </c>
       <c r="P236" s="6" t="n"/>
       <c r="Q236" s="6" t="n">
@@ -19248,7 +19248,7 @@
         <v>99.988924</v>
       </c>
       <c r="O237" s="9" t="n">
-        <v>99.582734</v>
+        <v>99.58260799999999</v>
       </c>
       <c r="P237" s="9" t="n"/>
       <c r="Q237" s="9" t="n">
@@ -19330,7 +19330,7 @@
         <v>100.093805</v>
       </c>
       <c r="O238" s="6" t="n">
-        <v>99.785808</v>
+        <v>99.785737</v>
       </c>
       <c r="P238" s="6" t="n"/>
       <c r="Q238" s="6" t="n">
@@ -19412,7 +19412,7 @@
         <v>100.193154</v>
       </c>
       <c r="O239" s="9" t="n">
-        <v>99.96147000000001</v>
+        <v>99.961455</v>
       </c>
       <c r="P239" s="9" t="n"/>
       <c r="Q239" s="9" t="n">
@@ -19494,7 +19494,7 @@
         <v>100.285531</v>
       </c>
       <c r="O240" s="6" t="n">
-        <v>100.12999</v>
+        <v>100.130032</v>
       </c>
       <c r="P240" s="6" t="n"/>
       <c r="Q240" s="6" t="n">
@@ -19576,7 +19576,7 @@
         <v>100.377911</v>
       </c>
       <c r="O241" s="9" t="n">
-        <v>100.274337</v>
+        <v>100.27443</v>
       </c>
       <c r="P241" s="9" t="n"/>
       <c r="Q241" s="9" t="n">
@@ -19658,7 +19658,7 @@
         <v>100.474494</v>
       </c>
       <c r="O242" s="6" t="n">
-        <v>100.421104</v>
+        <v>100.421249</v>
       </c>
       <c r="P242" s="6" t="n"/>
       <c r="Q242" s="6" t="n">
@@ -19740,7 +19740,7 @@
         <v>100.582905</v>
       </c>
       <c r="O243" s="9" t="n">
-        <v>100.588765</v>
+        <v>100.588967</v>
       </c>
       <c r="P243" s="9" t="n"/>
       <c r="Q243" s="9" t="n">
@@ -19822,7 +19822,7 @@
         <v>100.703875</v>
       </c>
       <c r="O244" s="6" t="n">
-        <v>100.745021</v>
+        <v>100.745287</v>
       </c>
       <c r="P244" s="6" t="n"/>
       <c r="Q244" s="6" t="n">
@@ -19904,7 +19904,7 @@
         <v>100.83703</v>
       </c>
       <c r="O245" s="9" t="n">
-        <v>100.881504</v>
+        <v>100.881821</v>
       </c>
       <c r="P245" s="9" t="n"/>
       <c r="Q245" s="9" t="n">
@@ -19986,7 +19986,7 @@
         <v>100.975501</v>
       </c>
       <c r="O246" s="6" t="n">
-        <v>100.992258</v>
+        <v>100.992605</v>
       </c>
       <c r="P246" s="6" t="n"/>
       <c r="Q246" s="6" t="n">
@@ -20068,7 +20068,7 @@
         <v>101.101968</v>
       </c>
       <c r="O247" s="9" t="n">
-        <v>101.037583</v>
+        <v>101.037945</v>
       </c>
       <c r="P247" s="9" t="n"/>
       <c r="Q247" s="9" t="n">
@@ -20150,7 +20150,7 @@
         <v>101.222493</v>
       </c>
       <c r="O248" s="6" t="n">
-        <v>101.058585</v>
+        <v>101.058954</v>
       </c>
       <c r="P248" s="6" t="n"/>
       <c r="Q248" s="6" t="n">
@@ -20232,7 +20232,7 @@
         <v>101.355417</v>
       </c>
       <c r="O249" s="9" t="n">
-        <v>101.055681</v>
+        <v>101.056045</v>
       </c>
       <c r="P249" s="9" t="n"/>
       <c r="Q249" s="9" t="n">
@@ -20314,7 +20314,7 @@
         <v>101.494197</v>
       </c>
       <c r="O250" s="6" t="n">
-        <v>101.023199</v>
+        <v>101.02356</v>
       </c>
       <c r="P250" s="6" t="n"/>
       <c r="Q250" s="6" t="n">
@@ -20396,7 +20396,7 @@
         <v>101.62275</v>
       </c>
       <c r="O251" s="9" t="n">
-        <v>100.989037</v>
+        <v>100.989385</v>
       </c>
       <c r="P251" s="9" t="n"/>
       <c r="Q251" s="9" t="n">
@@ -20478,7 +20478,7 @@
         <v>101.729905</v>
       </c>
       <c r="O252" s="6" t="n">
-        <v>100.901385</v>
+        <v>100.901694</v>
       </c>
       <c r="P252" s="6" t="n"/>
       <c r="Q252" s="6" t="n">
@@ -20560,7 +20560,7 @@
         <v>101.797824</v>
       </c>
       <c r="O253" s="9" t="n">
-        <v>100.77429</v>
+        <v>100.774554</v>
       </c>
       <c r="P253" s="9" t="n"/>
       <c r="Q253" s="9" t="n">
@@ -20642,7 +20642,7 @@
         <v>101.816273</v>
       </c>
       <c r="O254" s="6" t="n">
-        <v>100.595258</v>
+        <v>100.595455</v>
       </c>
       <c r="P254" s="6" t="n"/>
       <c r="Q254" s="6" t="n">
@@ -20724,7 +20724,7 @@
         <v>101.782986</v>
       </c>
       <c r="O255" s="9" t="n">
-        <v>100.325967</v>
+        <v>100.326067</v>
       </c>
       <c r="P255" s="9" t="n"/>
       <c r="Q255" s="9" t="n">
@@ -20806,7 +20806,7 @@
         <v>101.694376</v>
       </c>
       <c r="O256" s="6" t="n">
-        <v>100.000202</v>
+        <v>100.000187</v>
       </c>
       <c r="P256" s="6" t="n"/>
       <c r="Q256" s="6" t="n">
@@ -20888,7 +20888,7 @@
         <v>101.552745</v>
       </c>
       <c r="O257" s="9" t="n">
-        <v>99.61463999999999</v>
+        <v>99.614492</v>
       </c>
       <c r="P257" s="9" t="n"/>
       <c r="Q257" s="9" t="n">
@@ -20970,7 +20970,7 @@
         <v>101.364321</v>
       </c>
       <c r="O258" s="6" t="n">
-        <v>99.225857</v>
+        <v>99.225587</v>
       </c>
       <c r="P258" s="6" t="n"/>
       <c r="Q258" s="6" t="n">
@@ -21052,7 +21052,7 @@
         <v>101.156863</v>
       </c>
       <c r="O259" s="9" t="n">
-        <v>98.89134199999999</v>
+        <v>98.890961</v>
       </c>
       <c r="P259" s="9" t="n"/>
       <c r="Q259" s="9" t="n">
@@ -21134,7 +21134,7 @@
         <v>100.943332</v>
       </c>
       <c r="O260" s="6" t="n">
-        <v>98.62680899999999</v>
+        <v>98.626341</v>
       </c>
       <c r="P260" s="6" t="n"/>
       <c r="Q260" s="6" t="n">
@@ -21216,7 +21216,7 @@
         <v>100.714446</v>
       </c>
       <c r="O261" s="9" t="n">
-        <v>98.435892</v>
+        <v>98.435362</v>
       </c>
       <c r="P261" s="9" t="n"/>
       <c r="Q261" s="9" t="n">
@@ -21298,7 +21298,7 @@
         <v>100.47235</v>
       </c>
       <c r="O262" s="6" t="n">
-        <v>98.349403</v>
+        <v>98.348848</v>
       </c>
       <c r="P262" s="6" t="n"/>
       <c r="Q262" s="6" t="n">
@@ -21380,7 +21380,7 @@
         <v>100.240886</v>
       </c>
       <c r="O263" s="9" t="n">
-        <v>98.329122</v>
+        <v>98.328559</v>
       </c>
       <c r="P263" s="9" t="n"/>
       <c r="Q263" s="9" t="n">
@@ -21462,7 +21462,7 @@
         <v>100.034684</v>
       </c>
       <c r="O264" s="6" t="n">
-        <v>98.366945</v>
+        <v>98.366394</v>
       </c>
       <c r="P264" s="6" t="n"/>
       <c r="Q264" s="6" t="n">
@@ -21544,7 +21544,7 @@
         <v>99.867028</v>
       </c>
       <c r="O265" s="9" t="n">
-        <v>98.421514</v>
+        <v>98.42098</v>
       </c>
       <c r="P265" s="9" t="n"/>
       <c r="Q265" s="9" t="n">
@@ -21626,7 +21626,7 @@
         <v>99.733161</v>
       </c>
       <c r="O266" s="6" t="n">
-        <v>98.467558</v>
+        <v>98.467034</v>
       </c>
       <c r="P266" s="6" t="n"/>
       <c r="Q266" s="6" t="n">
@@ -21708,7 +21708,7 @@
         <v>99.62600999999999</v>
       </c>
       <c r="O267" s="9" t="n">
-        <v>98.555053</v>
+        <v>98.554562</v>
       </c>
       <c r="P267" s="9" t="n"/>
       <c r="Q267" s="9" t="n">
@@ -21790,7 +21790,7 @@
         <v>99.54742299999999</v>
       </c>
       <c r="O268" s="6" t="n">
-        <v>98.694441</v>
+        <v>98.693995</v>
       </c>
       <c r="P268" s="6" t="n"/>
       <c r="Q268" s="6" t="n">
@@ -21872,7 +21872,7 @@
         <v>99.50642000000001</v>
       </c>
       <c r="O269" s="9" t="n">
-        <v>98.90445699999999</v>
+        <v>98.90407399999999</v>
       </c>
       <c r="P269" s="9" t="n"/>
       <c r="Q269" s="9" t="n">
@@ -21954,7 +21954,7 @@
         <v>99.50514200000001</v>
       </c>
       <c r="O270" s="6" t="n">
-        <v>99.15715</v>
+        <v>99.156852</v>
       </c>
       <c r="P270" s="6" t="n"/>
       <c r="Q270" s="6" t="n">
@@ -22036,7 +22036,7 @@
         <v>99.54633</v>
       </c>
       <c r="O271" s="9" t="n">
-        <v>99.415251</v>
+        <v>99.415038</v>
       </c>
       <c r="P271" s="9" t="n"/>
       <c r="Q271" s="9" t="n">
@@ -22118,7 +22118,7 @@
         <v>99.59899</v>
       </c>
       <c r="O272" s="6" t="n">
-        <v>99.613815</v>
+        <v>99.61366700000001</v>
       </c>
       <c r="P272" s="6" t="n"/>
       <c r="Q272" s="6" t="n">
@@ -22200,7 +22200,7 @@
         <v>99.632284</v>
       </c>
       <c r="O273" s="9" t="n">
-        <v>99.693369</v>
+        <v>99.693254</v>
       </c>
       <c r="P273" s="9" t="n"/>
       <c r="Q273" s="9" t="n">
@@ -22282,7 +22282,7 @@
         <v>99.64018299999999</v>
       </c>
       <c r="O274" s="6" t="n">
-        <v>99.658903</v>
+        <v>99.658778</v>
       </c>
       <c r="P274" s="6" t="n"/>
       <c r="Q274" s="6" t="n">
@@ -22364,7 +22364,7 @@
         <v>99.616845</v>
       </c>
       <c r="O275" s="9" t="n">
-        <v>99.513836</v>
+        <v>99.51366</v>
       </c>
       <c r="P275" s="9" t="n"/>
       <c r="Q275" s="9" t="n">
@@ -22446,7 +22446,7 @@
         <v>99.56753999999999</v>
       </c>
       <c r="O276" s="6" t="n">
-        <v>99.328912</v>
+        <v>99.328683</v>
       </c>
       <c r="P276" s="6" t="n"/>
       <c r="Q276" s="6" t="n">
@@ -22528,7 +22528,7 @@
         <v>99.494981</v>
       </c>
       <c r="O277" s="9" t="n">
-        <v>99.16046900000001</v>
+        <v>99.16018800000001</v>
       </c>
       <c r="P277" s="9" t="n"/>
       <c r="Q277" s="9" t="n">
@@ -22610,7 +22610,7 @@
         <v>99.40487899999999</v>
       </c>
       <c r="O278" s="6" t="n">
-        <v>99.036153</v>
+        <v>99.03583500000001</v>
       </c>
       <c r="P278" s="6" t="n"/>
       <c r="Q278" s="6" t="n">
@@ -22692,7 +22692,7 @@
         <v>99.30386300000001</v>
       </c>
       <c r="O279" s="9" t="n">
-        <v>98.952626</v>
+        <v>98.952285</v>
       </c>
       <c r="P279" s="9" t="n"/>
       <c r="Q279" s="9" t="n">
@@ -22774,7 +22774,7 @@
         <v>99.206407</v>
       </c>
       <c r="O280" s="6" t="n">
-        <v>98.90523</v>
+        <v>98.904871</v>
       </c>
       <c r="P280" s="6" t="n"/>
       <c r="Q280" s="6" t="n">
@@ -22856,7 +22856,7 @@
         <v>99.118302</v>
       </c>
       <c r="O281" s="9" t="n">
-        <v>98.85795299999999</v>
+        <v>98.857575</v>
       </c>
       <c r="P281" s="9" t="n"/>
       <c r="Q281" s="9" t="n">
@@ -22938,7 +22938,7 @@
         <v>99.04019</v>
       </c>
       <c r="O282" s="6" t="n">
-        <v>98.80079000000001</v>
+        <v>98.800386</v>
       </c>
       <c r="P282" s="6" t="n"/>
       <c r="Q282" s="6" t="n">
@@ -23020,7 +23020,7 @@
         <v>98.96835299999999</v>
       </c>
       <c r="O283" s="9" t="n">
-        <v>98.756812</v>
+        <v>98.756376</v>
       </c>
       <c r="P283" s="9" t="n"/>
       <c r="Q283" s="9" t="n">
@@ -23102,7 +23102,7 @@
         <v>98.902925</v>
       </c>
       <c r="O284" s="6" t="n">
-        <v>98.73198499999999</v>
+        <v>98.731526</v>
       </c>
       <c r="P284" s="6" t="n"/>
       <c r="Q284" s="6" t="n">
@@ -23184,7 +23184,7 @@
         <v>98.83462900000001</v>
       </c>
       <c r="O285" s="9" t="n">
-        <v>98.77626100000001</v>
+        <v>98.77581600000001</v>
       </c>
       <c r="P285" s="9" t="n"/>
       <c r="Q285" s="9" t="n">
@@ -23266,7 +23266,7 @@
         <v>98.76460299999999</v>
       </c>
       <c r="O286" s="6" t="n">
-        <v>98.86704899999999</v>
+        <v>98.86663900000001</v>
       </c>
       <c r="P286" s="6" t="n"/>
       <c r="Q286" s="6" t="n">
@@ -23348,7 +23348,7 @@
         <v>98.707785</v>
       </c>
       <c r="O287" s="9" t="n">
-        <v>99.03984</v>
+        <v>99.039494</v>
       </c>
       <c r="P287" s="9" t="n"/>
       <c r="Q287" s="9" t="n">
@@ -23430,7 +23430,7 @@
         <v>98.672189</v>
       </c>
       <c r="O288" s="6" t="n">
-        <v>99.244181</v>
+        <v>99.24391199999999</v>
       </c>
       <c r="P288" s="6" t="n"/>
       <c r="Q288" s="6" t="n">
@@ -23512,7 +23512,7 @@
         <v>98.660612</v>
       </c>
       <c r="O289" s="9" t="n">
-        <v>99.458202</v>
+        <v>99.45800699999999</v>
       </c>
       <c r="P289" s="9" t="n"/>
       <c r="Q289" s="9" t="n">
@@ -23594,7 +23594,7 @@
         <v>98.68392299999999</v>
       </c>
       <c r="O290" s="6" t="n">
-        <v>99.69802300000001</v>
+        <v>99.697919</v>
       </c>
       <c r="P290" s="6" t="n"/>
       <c r="Q290" s="6" t="n">
@@ -23676,7 +23676,7 @@
         <v>98.743408</v>
       </c>
       <c r="O291" s="9" t="n">
-        <v>99.95480499999999</v>
+        <v>99.95479</v>
       </c>
       <c r="P291" s="9" t="n"/>
       <c r="Q291" s="9" t="n">
@@ -23758,7 +23758,7 @@
         <v>98.829741</v>
       </c>
       <c r="O292" s="6" t="n">
-        <v>100.185832</v>
+        <v>100.185889</v>
       </c>
       <c r="P292" s="6" t="n"/>
       <c r="Q292" s="6" t="n">
@@ -23840,7 +23840,7 @@
         <v>98.932936</v>
       </c>
       <c r="O293" s="9" t="n">
-        <v>100.399183</v>
+        <v>100.399319</v>
       </c>
       <c r="P293" s="9" t="n"/>
       <c r="Q293" s="9" t="n">
@@ -23922,7 +23922,7 @@
         <v>99.047489</v>
       </c>
       <c r="O294" s="6" t="n">
-        <v>100.592919</v>
+        <v>100.593126</v>
       </c>
       <c r="P294" s="6" t="n">
         <v>98.540752</v>
@@ -24006,7 +24006,7 @@
         <v>99.17718000000001</v>
       </c>
       <c r="O295" s="9" t="n">
-        <v>100.782518</v>
+        <v>100.782798</v>
       </c>
       <c r="P295" s="9" t="n">
         <v>98.703875</v>
@@ -24090,7 +24090,7 @@
         <v>99.305249</v>
       </c>
       <c r="O296" s="6" t="n">
-        <v>100.961795</v>
+        <v>100.962147</v>
       </c>
       <c r="P296" s="6" t="n">
         <v>98.876873</v>
@@ -24174,7 +24174,7 @@
         <v>99.420963</v>
       </c>
       <c r="O297" s="9" t="n">
-        <v>101.092884</v>
+        <v>101.09328</v>
       </c>
       <c r="P297" s="9" t="n">
         <v>99.06832300000001</v>
@@ -24258,7 +24258,7 @@
         <v>99.51691700000001</v>
       </c>
       <c r="O298" s="6" t="n">
-        <v>101.133943</v>
+        <v>101.134342</v>
       </c>
       <c r="P298" s="6" t="n">
         <v>99.247865</v>
@@ -24342,7 +24342,7 @@
         <v>99.580827</v>
       </c>
       <c r="O299" s="9" t="n">
-        <v>101.082737</v>
+        <v>101.083115</v>
       </c>
       <c r="P299" s="9" t="n">
         <v>99.386276</v>
@@ -24426,7 +24426,7 @@
         <v>99.624262</v>
       </c>
       <c r="O300" s="6" t="n">
-        <v>100.977304</v>
+        <v>100.977641</v>
       </c>
       <c r="P300" s="6" t="n">
         <v>99.484945</v>
@@ -24510,7 +24510,7 @@
         <v>99.657555</v>
       </c>
       <c r="O301" s="9" t="n">
-        <v>100.846079</v>
+        <v>100.846366</v>
       </c>
       <c r="P301" s="9" t="n">
         <v>99.551771</v>
@@ -24594,7 +24594,7 @@
         <v>99.693719</v>
       </c>
       <c r="O302" s="6" t="n">
-        <v>100.711618</v>
+        <v>100.711857</v>
       </c>
       <c r="P302" s="6" t="n">
         <v>99.60554</v>
@@ -24678,7 +24678,7 @@
         <v>99.744255</v>
       </c>
       <c r="O303" s="9" t="n">
-        <v>100.573247</v>
+        <v>100.573441</v>
       </c>
       <c r="P303" s="9" t="n">
         <v>99.662926</v>
@@ -24762,7 +24762,7 @@
         <v>99.794479</v>
       </c>
       <c r="O304" s="6" t="n">
-        <v>100.483811</v>
+        <v>100.483985</v>
       </c>
       <c r="P304" s="6" t="n">
         <v>99.722613</v>
@@ -24846,7 +24846,7 @@
         <v>99.821991</v>
       </c>
       <c r="O305" s="9" t="n">
-        <v>100.431215</v>
+        <v>100.431373</v>
       </c>
       <c r="P305" s="9" t="n">
         <v>99.780147</v>
@@ -24930,7 +24930,7 @@
         <v>99.829731</v>
       </c>
       <c r="O306" s="6" t="n">
-        <v>100.383506</v>
+        <v>100.383643</v>
       </c>
       <c r="P306" s="6" t="n">
         <v>99.83928299999999</v>
@@ -25014,7 +25014,7 @@
         <v>99.81782800000001</v>
       </c>
       <c r="O307" s="9" t="n">
-        <v>100.251315</v>
+        <v>100.251411</v>
       </c>
       <c r="P307" s="9" t="n">
         <v>99.90753599999999</v>
@@ -25098,7 +25098,7 @@
         <v>99.797179</v>
       </c>
       <c r="O308" s="6" t="n">
-        <v>100.070908</v>
+        <v>100.070944</v>
       </c>
       <c r="P308" s="6" t="n">
         <v>99.982005</v>
@@ -25182,7 +25182,7 @@
         <v>99.78207500000001</v>
       </c>
       <c r="O309" s="9" t="n">
-        <v>99.87656800000001</v>
+        <v>99.876531</v>
       </c>
       <c r="P309" s="9" t="n">
         <v>100.054023</v>
@@ -25266,7 +25266,7 @@
         <v>99.778564</v>
       </c>
       <c r="O310" s="6" t="n">
-        <v>99.730011</v>
+        <v>99.72992000000001</v>
       </c>
       <c r="P310" s="6" t="n">
         <v>100.112333</v>
@@ -25350,7 +25350,7 @@
         <v>99.799948</v>
       </c>
       <c r="O311" s="9" t="n">
-        <v>99.671705</v>
+        <v>99.671594</v>
       </c>
       <c r="P311" s="9" t="n">
         <v>100.157176</v>
@@ -25434,7 +25434,7 @@
         <v>99.848969</v>
       </c>
       <c r="O312" s="6" t="n">
-        <v>99.719691</v>
+        <v>99.719598</v>
       </c>
       <c r="P312" s="6" t="n">
         <v>100.183393</v>
@@ -25518,7 +25518,7 @@
         <v>99.93205399999999</v>
       </c>
       <c r="O313" s="9" t="n">
-        <v>99.86326699999999</v>
+        <v>99.86323</v>
       </c>
       <c r="P313" s="9" t="n">
         <v>100.203185</v>
@@ -25602,7 +25602,7 @@
         <v>100.052926</v>
       </c>
       <c r="O314" s="6" t="n">
-        <v>100.026429</v>
+        <v>100.026447</v>
       </c>
       <c r="P314" s="6" t="n">
         <v>100.233539</v>
@@ -25686,7 +25686,7 @@
         <v>100.206311</v>
       </c>
       <c r="O315" s="9" t="n">
-        <v>100.205249</v>
+        <v>100.20532</v>
       </c>
       <c r="P315" s="9" t="n">
         <v>100.273473</v>
@@ -25770,7 +25770,7 @@
         <v>100.364084</v>
       </c>
       <c r="O316" s="6" t="n">
-        <v>100.353453</v>
+        <v>100.353575</v>
       </c>
       <c r="P316" s="6" t="n">
         <v>100.319489</v>
@@ -25854,7 +25854,7 @@
         <v>100.498919</v>
       </c>
       <c r="O317" s="9" t="n">
-        <v>100.459487</v>
+        <v>100.459646</v>
       </c>
       <c r="P317" s="9" t="n">
         <v>100.381873</v>
@@ -25938,7 +25938,7 @@
         <v>100.596669</v>
       </c>
       <c r="O318" s="6" t="n">
-        <v>100.549996</v>
+        <v>100.550188</v>
       </c>
       <c r="P318" s="6" t="n">
         <v>100.46471</v>
@@ -26022,7 +26022,7 @@
         <v>100.670667</v>
       </c>
       <c r="O319" s="9" t="n">
-        <v>100.67344</v>
+        <v>100.673678</v>
       </c>
       <c r="P319" s="9" t="n">
         <v>100.575136</v>
@@ -26106,7 +26106,7 @@
         <v>100.727728</v>
       </c>
       <c r="O320" s="6" t="n">
-        <v>100.831126</v>
+        <v>100.831421</v>
       </c>
       <c r="P320" s="6" t="n">
         <v>100.680562</v>
@@ -26190,7 +26190,7 @@
         <v>100.769062</v>
       </c>
       <c r="O321" s="9" t="n">
-        <v>101.00381</v>
+        <v>101.004165</v>
       </c>
       <c r="P321" s="9" t="n">
         <v>100.774705</v>
@@ -26274,7 +26274,7 @@
         <v>100.791603</v>
       </c>
       <c r="O322" s="6" t="n">
-        <v>101.169518</v>
+        <v>101.169937</v>
       </c>
       <c r="P322" s="6" t="n">
         <v>100.863466</v>
@@ -26358,7 +26358,7 @@
         <v>100.79205</v>
       </c>
       <c r="O323" s="9" t="n">
-        <v>101.249565</v>
+        <v>101.250011</v>
       </c>
       <c r="P323" s="9" t="n">
         <v>100.951543</v>
@@ -26442,7 +26442,7 @@
         <v>100.778492</v>
       </c>
       <c r="O324" s="6" t="n">
-        <v>101.203191</v>
+        <v>101.203612</v>
       </c>
       <c r="P324" s="6" t="n">
         <v>101.056797</v>
@@ -26526,7 +26526,7 @@
         <v>100.757365</v>
       </c>
       <c r="O325" s="9" t="n">
-        <v>101.069374</v>
+        <v>101.069745</v>
       </c>
       <c r="P325" s="9" t="n">
         <v>101.179752</v>
@@ -26610,7 +26610,7 @@
         <v>100.728064</v>
       </c>
       <c r="O326" s="6" t="n">
-        <v>100.897079</v>
+        <v>100.897384</v>
       </c>
       <c r="P326" s="6" t="n">
         <v>101.292858</v>
@@ -26694,7 +26694,7 @@
         <v>100.689275</v>
       </c>
       <c r="O327" s="9" t="n">
-        <v>100.72705</v>
+        <v>100.727294</v>
       </c>
       <c r="P327" s="9" t="n">
         <v>101.390583</v>
@@ -26778,7 +26778,7 @@
         <v>100.652292</v>
       </c>
       <c r="O328" s="6" t="n">
-        <v>100.575382</v>
+        <v>100.575573</v>
       </c>
       <c r="P328" s="6" t="n">
         <v>101.492127</v>
@@ -26862,7 +26862,7 @@
         <v>100.634878</v>
       </c>
       <c r="O329" s="9" t="n">
-        <v>100.469114</v>
+        <v>100.469269</v>
       </c>
       <c r="P329" s="9" t="n">
         <v>101.602763</v>
@@ -26946,7 +26946,7 @@
         <v>100.641401</v>
       </c>
       <c r="O330" s="6" t="n">
-        <v>100.437241</v>
+        <v>100.437394</v>
       </c>
       <c r="P330" s="6" t="n">
         <v>101.716976</v>
@@ -27030,7 +27030,7 @@
         <v>100.676763</v>
       </c>
       <c r="O331" s="9" t="n">
-        <v>100.486235</v>
+        <v>100.486409</v>
       </c>
       <c r="P331" s="9" t="n">
         <v>101.814597</v>
@@ -27114,7 +27114,7 @@
         <v>100.736925</v>
       </c>
       <c r="O332" s="6" t="n">
-        <v>100.557153</v>
+        <v>100.557355</v>
       </c>
       <c r="P332" s="6" t="n">
         <v>101.884329</v>
@@ -27198,7 +27198,7 @@
         <v>100.815004</v>
       </c>
       <c r="O333" s="9" t="n">
-        <v>100.624833</v>
+        <v>100.625063</v>
       </c>
       <c r="P333" s="9" t="n">
         <v>101.925133</v>
@@ -27282,7 +27282,7 @@
         <v>100.89617</v>
       </c>
       <c r="O334" s="6" t="n">
-        <v>100.664717</v>
+        <v>100.664964</v>
       </c>
       <c r="P334" s="6" t="n">
         <v>101.945441</v>
@@ -27366,7 +27366,7 @@
         <v>100.964716</v>
       </c>
       <c r="O335" s="9" t="n">
-        <v>100.72645</v>
+        <v>100.726715</v>
       </c>
       <c r="P335" s="9" t="n">
         <v>101.973837</v>
@@ -27450,7 +27450,7 @@
         <v>101.016888</v>
       </c>
       <c r="O336" s="6" t="n">
-        <v>100.830433</v>
+        <v>100.830734</v>
       </c>
       <c r="P336" s="6" t="n">
         <v>102.019448</v>
@@ -27534,7 +27534,7 @@
         <v>101.070787</v>
       </c>
       <c r="O337" s="9" t="n">
-        <v>100.937913</v>
+        <v>100.938252</v>
       </c>
       <c r="P337" s="9" t="n">
         <v>102.073088</v>
@@ -27618,7 +27618,7 @@
         <v>101.128422</v>
       </c>
       <c r="O338" s="6" t="n">
-        <v>101.024877</v>
+        <v>101.025242</v>
       </c>
       <c r="P338" s="6" t="n">
         <v>102.117936</v>
@@ -27702,7 +27702,7 @@
         <v>101.192718</v>
       </c>
       <c r="O339" s="9" t="n">
-        <v>101.022608</v>
+        <v>101.022981</v>
       </c>
       <c r="P339" s="9" t="n">
         <v>102.126047</v>
@@ -27786,7 +27786,7 @@
         <v>101.277266</v>
       </c>
       <c r="O340" s="6" t="n">
-        <v>100.961967</v>
+        <v>100.962321</v>
       </c>
       <c r="P340" s="6" t="n">
         <v>102.054641</v>
@@ -27870,7 +27870,7 @@
         <v>101.389755</v>
       </c>
       <c r="O341" s="9" t="n">
-        <v>100.863925</v>
+        <v>100.864235</v>
       </c>
       <c r="P341" s="9" t="n">
         <v>101.867877</v>
@@ -27954,7 +27954,7 @@
         <v>101.525656</v>
       </c>
       <c r="O342" s="6" t="n">
-        <v>100.707734</v>
+        <v>100.707986</v>
       </c>
       <c r="P342" s="6" t="n">
         <v>101.585665</v>
@@ -28038,7 +28038,7 @@
         <v>101.665921</v>
       </c>
       <c r="O343" s="9" t="n">
-        <v>100.478067</v>
+        <v>100.478227</v>
       </c>
       <c r="P343" s="9" t="n">
         <v>101.243023</v>
@@ -28122,7 +28122,7 @@
         <v>101.797632</v>
       </c>
       <c r="O344" s="6" t="n">
-        <v>100.203409</v>
+        <v>100.20346</v>
       </c>
       <c r="P344" s="6" t="n">
         <v>100.88378</v>
@@ -28206,7 +28206,7 @@
         <v>101.907274</v>
       </c>
       <c r="O345" s="9" t="n">
-        <v>99.88565199999999</v>
+        <v>99.88559100000001</v>
       </c>
       <c r="P345" s="9" t="n">
         <v>100.531239</v>
@@ -28290,7 +28290,7 @@
         <v>101.969871</v>
       </c>
       <c r="O346" s="6" t="n">
-        <v>99.542089</v>
+        <v>99.541909</v>
       </c>
       <c r="P346" s="6" t="n">
         <v>100.187058</v>
@@ -28374,7 +28374,7 @@
         <v>101.960967</v>
       </c>
       <c r="O347" s="9" t="n">
-        <v>99.15440599999999</v>
+        <v>99.154095</v>
       </c>
       <c r="P347" s="9" t="n">
         <v>99.7984</v>
@@ -28458,7 +28458,7 @@
         <v>101.839141</v>
       </c>
       <c r="O348" s="6" t="n">
-        <v>98.72568</v>
+        <v>98.72523099999999</v>
       </c>
       <c r="P348" s="6" t="n">
         <v>99.30520300000001</v>
@@ -28542,7 +28542,7 @@
         <v>101.544885</v>
       </c>
       <c r="O349" s="9" t="n">
-        <v>98.23440600000001</v>
+        <v>98.233794</v>
       </c>
       <c r="P349" s="9" t="n">
         <v>98.675124</v>
@@ -28626,7 +28626,7 @@
         <v>101.053193</v>
       </c>
       <c r="O350" s="6" t="n">
-        <v>97.709874</v>
+        <v>97.709093</v>
       </c>
       <c r="P350" s="6" t="n">
         <v>97.90809900000001</v>
@@ -28710,7 +28710,7 @@
         <v>100.380012</v>
       </c>
       <c r="O351" s="9" t="n">
-        <v>97.212853</v>
+        <v>97.21190300000001</v>
       </c>
       <c r="P351" s="9" t="n">
         <v>97.08127500000001</v>
@@ -28794,7 +28794,7 @@
         <v>99.566422</v>
       </c>
       <c r="O352" s="6" t="n">
-        <v>96.80914900000001</v>
+        <v>96.808053</v>
       </c>
       <c r="P352" s="6" t="n">
         <v>96.31001500000001</v>
@@ -28878,7 +28878,7 @@
         <v>98.69760599999999</v>
       </c>
       <c r="O353" s="9" t="n">
-        <v>96.510042</v>
+        <v>96.50884600000001</v>
       </c>
       <c r="P353" s="9" t="n">
         <v>95.69615</v>
@@ -28962,7 +28962,7 @@
         <v>97.910884</v>
       </c>
       <c r="O354" s="6" t="n">
-        <v>96.278668</v>
+        <v>96.27739</v>
       </c>
       <c r="P354" s="6" t="n">
         <v>95.31896399999999</v>
@@ -29046,7 +29046,7 @@
         <v>97.28248499999999</v>
       </c>
       <c r="O355" s="9" t="n">
-        <v>96.15096</v>
+        <v>96.14963299999999</v>
       </c>
       <c r="P355" s="9" t="n">
         <v>95.183716</v>
@@ -29130,7 +29130,7 @@
         <v>96.84311</v>
       </c>
       <c r="O356" s="6" t="n">
-        <v>96.156488</v>
+        <v>96.15516</v>
       </c>
       <c r="P356" s="6" t="n">
         <v>95.27273</v>
@@ -29214,7 +29214,7 @@
         <v>96.60618599999999</v>
       </c>
       <c r="O357" s="9" t="n">
-        <v>96.35508</v>
+        <v>96.35382199999999</v>
       </c>
       <c r="P357" s="9" t="n">
         <v>95.499116</v>
@@ -29298,7 +29298,7 @@
         <v>96.56907099999999</v>
       </c>
       <c r="O358" s="6" t="n">
-        <v>96.74503799999999</v>
+        <v>96.743914</v>
       </c>
       <c r="P358" s="6" t="n">
         <v>95.785263</v>
@@ -29382,7 +29382,7 @@
         <v>96.708754</v>
       </c>
       <c r="O359" s="9" t="n">
-        <v>97.299018</v>
+        <v>97.298091</v>
       </c>
       <c r="P359" s="9" t="n">
         <v>96.093588</v>
@@ -29466,7 +29466,7 @@
         <v>96.965065</v>
       </c>
       <c r="O360" s="6" t="n">
-        <v>97.952968</v>
+        <v>97.952263</v>
       </c>
       <c r="P360" s="6" t="n">
         <v>96.397431</v>
@@ -29550,7 +29550,7 @@
         <v>97.290541</v>
       </c>
       <c r="O361" s="9" t="n">
-        <v>98.651495</v>
+        <v>98.65101900000001</v>
       </c>
       <c r="P361" s="9" t="n">
         <v>96.696</v>
@@ -29634,7 +29634,7 @@
         <v>97.646339</v>
       </c>
       <c r="O362" s="6" t="n">
-        <v>99.32890999999999</v>
+        <v>99.32866199999999</v>
       </c>
       <c r="P362" s="6" t="n">
         <v>97.00365499999999</v>
@@ -29718,7 +29718,7 @@
         <v>98.003462</v>
       </c>
       <c r="O363" s="9" t="n">
-        <v>99.963686</v>
+        <v>99.96365299999999</v>
       </c>
       <c r="P363" s="9" t="n">
         <v>97.308723</v>
@@ -29802,7 +29802,7 @@
         <v>98.34691100000001</v>
       </c>
       <c r="O364" s="6" t="n">
-        <v>100.459947</v>
+        <v>100.460083</v>
       </c>
       <c r="P364" s="6" t="n">
         <v>97.61432499999999</v>
@@ -29886,7 +29886,7 @@
         <v>98.64769099999999</v>
       </c>
       <c r="O365" s="9" t="n">
-        <v>100.819271</v>
+        <v>100.819533</v>
       </c>
       <c r="P365" s="9" t="n">
         <v>97.955451</v>
@@ -29970,7 +29970,7 @@
         <v>98.907893</v>
       </c>
       <c r="O366" s="6" t="n">
-        <v>101.100609</v>
+        <v>101.100972</v>
       </c>
       <c r="P366" s="6" t="n">
         <v>98.356904</v>
@@ -30054,7 +30054,7 @@
         <v>99.136805</v>
       </c>
       <c r="O367" s="9" t="n">
-        <v>101.309528</v>
+        <v>101.309975</v>
       </c>
       <c r="P367" s="9" t="n">
         <v>98.840416</v>
@@ -30138,7 +30138,7 @@
         <v>99.32791899999999</v>
       </c>
       <c r="O368" s="6" t="n">
-        <v>101.469321</v>
+        <v>101.469832</v>
       </c>
       <c r="P368" s="6" t="n">
         <v>99.365357</v>
@@ -30222,7 +30222,7 @@
         <v>99.465743</v>
       </c>
       <c r="O369" s="9" t="n">
-        <v>101.564787</v>
+        <v>101.565326</v>
       </c>
       <c r="P369" s="9" t="n">
         <v>99.872889</v>
@@ -30306,7 +30306,7 @@
         <v>99.548821</v>
       </c>
       <c r="O370" s="6" t="n">
-        <v>101.585771</v>
+        <v>101.586304</v>
       </c>
       <c r="P370" s="6" t="n">
         <v>100.319776</v>
@@ -30390,7 +30390,7 @@
         <v>99.597269</v>
       </c>
       <c r="O371" s="9" t="n">
-        <v>101.53844</v>
+        <v>101.538949</v>
       </c>
       <c r="P371" s="9" t="n">
         <v>100.683748</v>
@@ -30474,7 +30474,7 @@
         <v>99.649444</v>
       </c>
       <c r="O372" s="6" t="n">
-        <v>101.447159</v>
+        <v>101.447629</v>
       </c>
       <c r="P372" s="6" t="n">
         <v>100.964737</v>
@@ -30558,7 +30558,7 @@
         <v>99.724316</v>
       </c>
       <c r="O373" s="9" t="n">
-        <v>101.332565</v>
+        <v>101.332992</v>
       </c>
       <c r="P373" s="9" t="n">
         <v>101.177499</v>
@@ -30642,7 +30642,7 @@
         <v>99.822829</v>
       </c>
       <c r="O374" s="6" t="n">
-        <v>101.210316</v>
+        <v>101.210698</v>
       </c>
       <c r="P374" s="6" t="n">
         <v>101.333756</v>
@@ -30726,7 +30726,7 @@
         <v>99.94723500000001</v>
       </c>
       <c r="O375" s="9" t="n">
-        <v>101.050904</v>
+        <v>101.051229</v>
       </c>
       <c r="P375" s="9" t="n">
         <v>101.44882</v>
@@ -30810,7 +30810,7 @@
         <v>100.082606</v>
       </c>
       <c r="O376" s="6" t="n">
-        <v>100.902087</v>
+        <v>100.902368</v>
       </c>
       <c r="P376" s="6" t="n">
         <v>101.529301</v>
@@ -30894,7 +30894,7 @@
         <v>100.219442</v>
       </c>
       <c r="O377" s="9" t="n">
-        <v>100.800409</v>
+        <v>100.800654</v>
       </c>
       <c r="P377" s="9" t="n">
         <v>101.575154</v>
@@ -30978,7 +30978,7 @@
         <v>100.347233</v>
       </c>
       <c r="O378" s="6" t="n">
-        <v>100.754046</v>
+        <v>100.754268</v>
       </c>
       <c r="P378" s="6" t="n">
         <v>101.591076</v>
@@ -31062,7 +31062,7 @@
         <v>100.459197</v>
       </c>
       <c r="O379" s="9" t="n">
-        <v>100.764199</v>
+        <v>100.764424</v>
       </c>
       <c r="P379" s="9" t="n">
         <v>101.584829</v>
@@ -31146,7 +31146,7 @@
         <v>100.554858</v>
       </c>
       <c r="O380" s="6" t="n">
-        <v>100.807822</v>
+        <v>100.808062</v>
       </c>
       <c r="P380" s="6" t="n">
         <v>101.559793</v>
@@ -31230,7 +31230,7 @@
         <v>100.639007</v>
       </c>
       <c r="O381" s="9" t="n">
-        <v>100.86466</v>
+        <v>100.864915</v>
       </c>
       <c r="P381" s="9" t="n">
         <v>101.517019</v>
@@ -31314,7 +31314,7 @@
         <v>100.713288</v>
       </c>
       <c r="O382" s="6" t="n">
-        <v>100.915147</v>
+        <v>100.915419</v>
       </c>
       <c r="P382" s="6" t="n">
         <v>101.453464</v>
@@ -31398,7 +31398,7 @@
         <v>100.760865</v>
       </c>
       <c r="O383" s="9" t="n">
-        <v>100.956698</v>
+        <v>100.956983</v>
       </c>
       <c r="P383" s="9" t="n">
         <v>101.356787</v>
@@ -31482,7 +31482,7 @@
         <v>100.770945</v>
       </c>
       <c r="O384" s="6" t="n">
-        <v>100.983857</v>
+        <v>100.984146</v>
       </c>
       <c r="P384" s="6" t="n">
         <v>101.223873</v>
@@ -31566,7 +31566,7 @@
         <v>100.754741</v>
       </c>
       <c r="O385" s="9" t="n">
-        <v>101.020909</v>
+        <v>101.021215</v>
       </c>
       <c r="P385" s="9" t="n">
         <v>101.05839</v>
@@ -31650,7 +31650,7 @@
         <v>100.73223</v>
       </c>
       <c r="O386" s="6" t="n">
-        <v>101.075609</v>
+        <v>101.075927</v>
       </c>
       <c r="P386" s="6" t="n">
         <v>100.892982</v>
@@ -31734,7 +31734,7 @@
         <v>100.708188</v>
       </c>
       <c r="O387" s="9" t="n">
-        <v>101.167367</v>
+        <v>101.167702</v>
       </c>
       <c r="P387" s="9" t="n">
         <v>100.743841</v>
@@ -31818,7 +31818,7 @@
         <v>100.6967</v>
       </c>
       <c r="O388" s="6" t="n">
-        <v>101.293517</v>
+        <v>101.29389</v>
       </c>
       <c r="P388" s="6" t="n">
         <v>100.622468</v>
@@ -31902,7 +31902,7 @@
         <v>100.696862</v>
       </c>
       <c r="O389" s="9" t="n">
-        <v>101.411868</v>
+        <v>101.412279</v>
       </c>
       <c r="P389" s="9" t="n">
         <v>100.532177</v>
@@ -31986,7 +31986,7 @@
         <v>100.698227</v>
       </c>
       <c r="O390" s="6" t="n">
-        <v>101.530483</v>
+        <v>101.530935</v>
       </c>
       <c r="P390" s="6" t="n">
         <v>100.470968</v>
@@ -32070,7 +32070,7 @@
         <v>100.68824</v>
       </c>
       <c r="O391" s="9" t="n">
-        <v>101.597354</v>
+        <v>101.59783</v>
       </c>
       <c r="P391" s="9" t="n">
         <v>100.407419</v>
@@ -32154,7 +32154,7 @@
         <v>100.655404</v>
       </c>
       <c r="O392" s="6" t="n">
-        <v>101.557747</v>
+        <v>101.558208</v>
       </c>
       <c r="P392" s="6" t="n">
         <v>100.32358</v>
@@ -32238,7 +32238,7 @@
         <v>100.606927</v>
       </c>
       <c r="O393" s="9" t="n">
-        <v>101.422232</v>
+        <v>101.422647</v>
       </c>
       <c r="P393" s="9" t="n">
         <v>100.229832</v>
@@ -32322,7 +32322,7 @@
         <v>100.538502</v>
       </c>
       <c r="O394" s="6" t="n">
-        <v>101.268594</v>
+        <v>101.26896</v>
       </c>
       <c r="P394" s="6" t="n">
         <v>100.149119</v>
@@ -32406,7 +32406,7 @@
         <v>100.465662</v>
       </c>
       <c r="O395" s="9" t="n">
-        <v>101.119718</v>
+        <v>101.120029</v>
       </c>
       <c r="P395" s="9" t="n">
         <v>100.105785</v>
@@ -32490,7 +32490,7 @@
         <v>100.416724</v>
       </c>
       <c r="O396" s="6" t="n">
-        <v>100.957909</v>
+        <v>100.958158</v>
       </c>
       <c r="P396" s="6" t="n">
         <v>100.115546</v>
@@ -32574,7 +32574,7 @@
         <v>100.398944</v>
       </c>
       <c r="O397" s="9" t="n">
-        <v>100.79526</v>
+        <v>100.795446</v>
       </c>
       <c r="P397" s="9" t="n">
         <v>100.178485</v>
@@ -32658,7 +32658,7 @@
         <v>100.415212</v>
       </c>
       <c r="O398" s="6" t="n">
-        <v>100.665676</v>
+        <v>100.665807</v>
       </c>
       <c r="P398" s="6" t="n">
         <v>100.27945</v>
@@ -32742,7 +32742,7 @@
         <v>100.450686</v>
       </c>
       <c r="O399" s="9" t="n">
-        <v>100.591689</v>
+        <v>100.591797</v>
       </c>
       <c r="P399" s="9" t="n">
         <v>100.406936</v>
@@ -32826,7 +32826,7 @@
         <v>100.480564</v>
       </c>
       <c r="O400" s="6" t="n">
-        <v>100.536731</v>
+        <v>100.536814</v>
       </c>
       <c r="P400" s="6" t="n">
         <v>100.546553</v>
@@ -32910,7 +32910,7 @@
         <v>100.503075</v>
       </c>
       <c r="O401" s="9" t="n">
-        <v>100.474424</v>
+        <v>100.474474</v>
       </c>
       <c r="P401" s="9" t="n">
         <v>100.692626</v>
@@ -32994,7 +32994,7 @@
         <v>100.520293</v>
       </c>
       <c r="O402" s="6" t="n">
-        <v>100.31481</v>
+        <v>100.314802</v>
       </c>
       <c r="P402" s="6" t="n">
         <v>100.843309</v>
@@ -33078,7 +33078,7 @@
         <v>100.519411</v>
       </c>
       <c r="O403" s="9" t="n">
-        <v>100.059759</v>
+        <v>100.059657</v>
       </c>
       <c r="P403" s="9" t="n">
         <v>100.975911</v>
@@ -33162,7 +33162,7 @@
         <v>100.493714</v>
       </c>
       <c r="O404" s="6" t="n">
-        <v>99.78139899999999</v>
+        <v>99.78119700000001</v>
       </c>
       <c r="P404" s="6" t="n">
         <v>101.068183</v>
@@ -33246,7 +33246,7 @@
         <v>100.442384</v>
       </c>
       <c r="O405" s="9" t="n">
-        <v>99.525631</v>
+        <v>99.52534199999999</v>
       </c>
       <c r="P405" s="9" t="n">
         <v>101.113819</v>
@@ -33330,7 +33330,7 @@
         <v>100.371756</v>
       </c>
       <c r="O406" s="6" t="n">
-        <v>99.291769</v>
+        <v>99.291399</v>
       </c>
       <c r="P406" s="6" t="n">
         <v>101.105563</v>
@@ -33414,7 +33414,7 @@
         <v>100.295858</v>
       </c>
       <c r="O407" s="9" t="n">
-        <v>99.078024</v>
+        <v>99.077575</v>
       </c>
       <c r="P407" s="9" t="n">
         <v>101.035813</v>
@@ -33498,7 +33498,7 @@
         <v>100.217923</v>
       </c>
       <c r="O408" s="6" t="n">
-        <v>98.92501799999999</v>
+        <v>98.924522</v>
       </c>
       <c r="P408" s="6" t="n">
         <v>100.91346</v>
@@ -33582,7 +33582,7 @@
         <v>100.139757</v>
       </c>
       <c r="O409" s="9" t="n">
-        <v>98.833213</v>
+        <v>98.832689</v>
       </c>
       <c r="P409" s="9" t="n">
         <v>100.747792</v>
@@ -33666,7 +33666,7 @@
         <v>100.073031</v>
       </c>
       <c r="O410" s="6" t="n">
-        <v>98.801925</v>
+        <v>98.801393</v>
       </c>
       <c r="P410" s="6" t="n">
         <v>100.560894</v>
@@ -33750,7 +33750,7 @@
         <v>100.030443</v>
       </c>
       <c r="O411" s="9" t="n">
-        <v>98.810558</v>
+        <v>98.810033</v>
       </c>
       <c r="P411" s="9" t="n">
         <v>100.38404</v>
@@ -33834,7 +33834,7 @@
         <v>100.020267</v>
       </c>
       <c r="O412" s="6" t="n">
-        <v>98.831929</v>
+        <v>98.83141000000001</v>
       </c>
       <c r="P412" s="6" t="n">
         <v>100.250069</v>
@@ -33918,7 +33918,7 @@
         <v>100.05256</v>
       </c>
       <c r="O413" s="9" t="n">
-        <v>98.801619</v>
+        <v>98.801085</v>
       </c>
       <c r="P413" s="9" t="n">
         <v>100.169082</v>
@@ -34002,7 +34002,7 @@
         <v>100.124124</v>
       </c>
       <c r="O414" s="6" t="n">
-        <v>98.728016</v>
+        <v>98.72745</v>
       </c>
       <c r="P414" s="6" t="n">
         <v>100.124881</v>
@@ -34086,7 +34086,7 @@
         <v>100.217252</v>
       </c>
       <c r="O415" s="9" t="n">
-        <v>98.68688</v>
+        <v>98.686283</v>
       </c>
       <c r="P415" s="9" t="n">
         <v>100.123011</v>
@@ -34170,7 +34170,7 @@
         <v>100.31086</v>
       </c>
       <c r="O416" s="6" t="n">
-        <v>98.732624</v>
+        <v>98.732029</v>
       </c>
       <c r="P416" s="6" t="n">
         <v>100.147522</v>
@@ -34254,7 +34254,7 @@
         <v>100.39033</v>
       </c>
       <c r="O417" s="9" t="n">
-        <v>98.802791</v>
+        <v>98.80222000000001</v>
       </c>
       <c r="P417" s="9" t="n">
         <v>100.192245</v>
@@ -34338,7 +34338,7 @@
         <v>100.445697</v>
       </c>
       <c r="O418" s="6" t="n">
-        <v>98.85878599999999</v>
+        <v>98.85823499999999</v>
       </c>
       <c r="P418" s="6" t="n">
         <v>100.257431</v>
@@ -34422,7 +34422,7 @@
         <v>100.472978</v>
       </c>
       <c r="O419" s="9" t="n">
-        <v>98.889264</v>
+        <v>98.888727</v>
       </c>
       <c r="P419" s="9" t="n">
         <v>100.344123</v>
@@ -34506,7 +34506,7 @@
         <v>100.475552</v>
       </c>
       <c r="O420" s="6" t="n">
-        <v>98.908388</v>
+        <v>98.907864</v>
       </c>
       <c r="P420" s="6" t="n">
         <v>100.435663</v>
@@ -34590,7 +34590,7 @@
         <v>100.460325</v>
       </c>
       <c r="O421" s="9" t="n">
-        <v>98.93369800000001</v>
+        <v>98.933187</v>
       </c>
       <c r="P421" s="9" t="n">
         <v>100.500641</v>
@@ -34674,7 +34674,7 @@
         <v>100.419732</v>
       </c>
       <c r="O422" s="6" t="n">
-        <v>98.9473</v>
+        <v>98.946806</v>
       </c>
       <c r="P422" s="6" t="n">
         <v>100.513591</v>
@@ -34758,7 +34758,7 @@
         <v>100.369473</v>
       </c>
       <c r="O423" s="9" t="n">
-        <v>98.937303</v>
+        <v>98.93681100000001</v>
       </c>
       <c r="P423" s="9" t="n">
         <v>100.459976</v>
@@ -34842,7 +34842,7 @@
         <v>100.311294</v>
       </c>
       <c r="O424" s="6" t="n">
-        <v>98.92884599999999</v>
+        <v>98.92834999999999</v>
       </c>
       <c r="P424" s="6" t="n">
         <v>100.334583</v>
@@ -34926,7 +34926,7 @@
         <v>100.233727</v>
       </c>
       <c r="O425" s="9" t="n">
-        <v>98.98101699999999</v>
+        <v>98.980548</v>
       </c>
       <c r="P425" s="9" t="n">
         <v>100.156102</v>
@@ -35010,7 +35010,7 @@
         <v>100.155964</v>
       </c>
       <c r="O426" s="6" t="n">
-        <v>99.114785</v>
+        <v>99.114367</v>
       </c>
       <c r="P426" s="6" t="n">
         <v>99.95702199999999</v>
@@ -35094,7 +35094,7 @@
         <v>100.100529</v>
       </c>
       <c r="O427" s="9" t="n">
-        <v>99.27892199999999</v>
+        <v>99.278565</v>
       </c>
       <c r="P427" s="9" t="n">
         <v>99.764042</v>
@@ -35178,7 +35178,7 @@
         <v>100.076986</v>
       </c>
       <c r="O428" s="6" t="n">
-        <v>99.39868300000001</v>
+        <v>99.39837300000001</v>
       </c>
       <c r="P428" s="6" t="n">
         <v>99.597443</v>
@@ -35262,7 +35262,7 @@
         <v>100.073032</v>
       </c>
       <c r="O429" s="9" t="n">
-        <v>99.51593099999999</v>
+        <v>99.515666</v>
       </c>
       <c r="P429" s="9" t="n">
         <v>99.460455</v>
@@ -35346,7 +35346,7 @@
         <v>100.078958</v>
       </c>
       <c r="O430" s="6" t="n">
-        <v>99.643036</v>
+        <v>99.64281800000001</v>
       </c>
       <c r="P430" s="6" t="n">
         <v>99.355762</v>
@@ -35430,7 +35430,7 @@
         <v>100.079687</v>
       </c>
       <c r="O431" s="9" t="n">
-        <v>99.794938</v>
+        <v>99.794785</v>
       </c>
       <c r="P431" s="9" t="n">
         <v>99.277923</v>
@@ -35514,7 +35514,7 @@
         <v>100.052593</v>
       </c>
       <c r="O432" s="6" t="n">
-        <v>99.968901</v>
+        <v>99.968816</v>
       </c>
       <c r="P432" s="6" t="n">
         <v>99.223203</v>
@@ -35598,7 +35598,7 @@
         <v>99.991704</v>
       </c>
       <c r="O433" s="9" t="n">
-        <v>100.131194</v>
+        <v>100.131164</v>
       </c>
       <c r="P433" s="9" t="n">
         <v>99.196077</v>
@@ -35682,7 +35682,7 @@
         <v>99.890794</v>
       </c>
       <c r="O434" s="6" t="n">
-        <v>100.261648</v>
+        <v>100.261671</v>
       </c>
       <c r="P434" s="6" t="n">
         <v>99.198431</v>
@@ -35766,7 +35766,7 @@
         <v>99.76481699999999</v>
       </c>
       <c r="O435" s="9" t="n">
-        <v>100.360168</v>
+        <v>100.360237</v>
       </c>
       <c r="P435" s="9" t="n">
         <v>99.22541099999999</v>
@@ -35850,7 +35850,7 @@
         <v>99.624442</v>
       </c>
       <c r="O436" s="6" t="n">
-        <v>100.416192</v>
+        <v>100.416296</v>
       </c>
       <c r="P436" s="6" t="n">
         <v>99.253951</v>
@@ -35934,7 +35934,7 @@
         <v>99.486216</v>
       </c>
       <c r="O437" s="9" t="n">
-        <v>100.436967</v>
+        <v>100.437097</v>
       </c>
       <c r="P437" s="9" t="n">
         <v>99.272891</v>
@@ -36018,7 +36018,7 @@
         <v>99.372911</v>
       </c>
       <c r="O438" s="6" t="n">
-        <v>100.430442</v>
+        <v>100.430587</v>
       </c>
       <c r="P438" s="6" t="n">
         <v>99.284637</v>
@@ -36102,7 +36102,7 @@
         <v>99.28915499999999</v>
       </c>
       <c r="O439" s="9" t="n">
-        <v>100.389085</v>
+        <v>100.389244</v>
       </c>
       <c r="P439" s="9" t="n">
         <v>99.298716</v>
@@ -36186,7 +36186,7 @@
         <v>99.23840300000001</v>
       </c>
       <c r="O440" s="6" t="n">
-        <v>100.323053</v>
+        <v>100.323214</v>
       </c>
       <c r="P440" s="6" t="n">
         <v>99.330686</v>
@@ -36270,7 +36270,7 @@
         <v>99.222514</v>
       </c>
       <c r="O441" s="9" t="n">
-        <v>100.274958</v>
+        <v>100.275116</v>
       </c>
       <c r="P441" s="9" t="n">
         <v>99.382846</v>
@@ -36354,7 +36354,7 @@
         <v>99.230887</v>
       </c>
       <c r="O442" s="6" t="n">
-        <v>100.245475</v>
+        <v>100.245636</v>
       </c>
       <c r="P442" s="6" t="n">
         <v>99.443241</v>
@@ -36438,7 +36438,7 @@
         <v>99.26398399999999</v>
       </c>
       <c r="O443" s="9" t="n">
-        <v>100.246604</v>
+        <v>100.246782</v>
       </c>
       <c r="P443" s="9" t="n">
         <v>99.49529</v>
@@ -36522,7 +36522,7 @@
         <v>99.316062</v>
       </c>
       <c r="O444" s="6" t="n">
-        <v>100.254829</v>
+        <v>100.255031</v>
       </c>
       <c r="P444" s="6" t="n">
         <v>99.524237</v>
@@ -36606,7 +36606,7 @@
         <v>99.37822799999999</v>
       </c>
       <c r="O445" s="9" t="n">
-        <v>100.268665</v>
+        <v>100.268903</v>
       </c>
       <c r="P445" s="9" t="n">
         <v>99.530745</v>
@@ -36690,7 +36690,7 @@
         <v>99.447562</v>
       </c>
       <c r="O446" s="6" t="n">
-        <v>100.297519</v>
+        <v>100.297792</v>
       </c>
       <c r="P446" s="6" t="n">
         <v>99.51172800000001</v>
@@ -36774,7 +36774,7 @@
         <v>99.514724</v>
       </c>
       <c r="O447" s="9" t="n">
-        <v>100.335191</v>
+        <v>100.335496</v>
       </c>
       <c r="P447" s="9" t="n">
         <v>99.46035500000001</v>
@@ -36858,7 +36858,7 @@
         <v>99.58468499999999</v>
       </c>
       <c r="O448" s="6" t="n">
-        <v>100.402636</v>
+        <v>100.402995</v>
       </c>
       <c r="P448" s="6" t="n">
         <v>99.38675000000001</v>
@@ -36942,7 +36942,7 @@
         <v>99.64937399999999</v>
       </c>
       <c r="O449" s="9" t="n">
-        <v>100.484764</v>
+        <v>100.485181</v>
       </c>
       <c r="P449" s="9" t="n">
         <v>99.301405</v>
@@ -37026,7 +37026,7 @@
         <v>99.702195</v>
       </c>
       <c r="O450" s="6" t="n">
-        <v>100.631879</v>
+        <v>100.632379</v>
       </c>
       <c r="P450" s="6" t="n">
         <v>99.230868</v>
@@ -37110,7 +37110,7 @@
         <v>99.746343</v>
       </c>
       <c r="O451" s="9" t="n">
-        <v>100.85209</v>
+        <v>100.8527</v>
       </c>
       <c r="P451" s="9" t="n">
         <v>99.21886499999999</v>
@@ -37194,7 +37194,7 @@
         <v>99.788827</v>
       </c>
       <c r="O452" s="6" t="n">
-        <v>101.081714</v>
+        <v>101.08244</v>
       </c>
       <c r="P452" s="6" t="n">
         <v>99.29834200000001</v>
@@ -37278,7 +37278,7 @@
         <v>99.838741</v>
       </c>
       <c r="O453" s="9" t="n">
-        <v>101.238371</v>
+        <v>101.239188</v>
       </c>
       <c r="P453" s="9" t="n">
         <v>99.457239</v>
@@ -37362,7 +37362,7 @@
         <v>99.906627</v>
       </c>
       <c r="O454" s="6" t="n">
-        <v>101.304828</v>
+        <v>101.305714</v>
       </c>
       <c r="P454" s="6" t="n">
         <v>99.670069</v>
@@ -37446,7 +37446,7 @@
         <v>99.984734</v>
       </c>
       <c r="O455" s="9" t="n">
-        <v>101.22446</v>
+        <v>101.225357</v>
       </c>
       <c r="P455" s="9" t="n">
         <v>99.90283100000001</v>
@@ -37530,7 +37530,7 @@
         <v>100.070797</v>
       </c>
       <c r="O456" s="6" t="n">
-        <v>101.004264</v>
+        <v>101.005119</v>
       </c>
       <c r="P456" s="6" t="n">
         <v>100.121048</v>
@@ -37614,7 +37614,7 @@
         <v>100.1669</v>
       </c>
       <c r="O457" s="9" t="n">
-        <v>100.700396</v>
+        <v>100.701188</v>
       </c>
       <c r="P457" s="9" t="n">
         <v>100.296027</v>
@@ -37698,7 +37698,7 @@
         <v>100.263306</v>
       </c>
       <c r="O458" s="6" t="n">
-        <v>100.391236</v>
+        <v>100.391964</v>
       </c>
       <c r="P458" s="6" t="n">
         <v>100.419933</v>
@@ -37782,7 +37782,7 @@
         <v>100.362087</v>
       </c>
       <c r="O459" s="9" t="n">
-        <v>100.135444</v>
+        <v>100.136131</v>
       </c>
       <c r="P459" s="9" t="n">
         <v>100.493883</v>
@@ -37866,7 +37866,7 @@
         <v>100.45936</v>
       </c>
       <c r="O460" s="6" t="n">
-        <v>99.962052</v>
+        <v>99.96272999999999</v>
       </c>
       <c r="P460" s="6" t="n">
         <v>100.548219</v>
@@ -37950,7 +37950,7 @@
         <v>100.557882</v>
       </c>
       <c r="O461" s="9" t="n">
-        <v>99.897323</v>
+        <v>99.898034</v>
       </c>
       <c r="P461" s="9" t="n">
         <v>100.610985</v>
@@ -38034,7 +38034,7 @@
         <v>100.645344</v>
       </c>
       <c r="O462" s="6" t="n">
-        <v>99.888233</v>
+        <v>99.889002</v>
       </c>
       <c r="P462" s="6" t="n">
         <v>100.686658</v>
@@ -38118,7 +38118,7 @@
         <v>100.731875</v>
       </c>
       <c r="O463" s="9" t="n">
-        <v>99.918744</v>
+        <v>99.91958099999999</v>
       </c>
       <c r="P463" s="9" t="n">
         <v>100.766193</v>
@@ -38202,7 +38202,7 @@
         <v>100.81209</v>
       </c>
       <c r="O464" s="6" t="n">
-        <v>99.99302299999999</v>
+        <v>99.99393999999999</v>
       </c>
       <c r="P464" s="6" t="n">
         <v>100.826822</v>
@@ -38286,7 +38286,7 @@
         <v>100.879351</v>
       </c>
       <c r="O465" s="9" t="n">
-        <v>100.085622</v>
+        <v>100.086625</v>
       </c>
       <c r="P465" s="9" t="n">
         <v>100.848875</v>
@@ -38370,7 +38370,7 @@
         <v>100.94377</v>
       </c>
       <c r="O466" s="6" t="n">
-        <v>100.185927</v>
+        <v>100.187025</v>
       </c>
       <c r="P466" s="6" t="n">
         <v>100.848776</v>
@@ -38454,7 +38454,7 @@
         <v>100.997708</v>
       </c>
       <c r="O467" s="9" t="n">
-        <v>100.280267</v>
+        <v>100.281459</v>
       </c>
       <c r="P467" s="9" t="n">
         <v>100.857108</v>
@@ -38538,7 +38538,7 @@
         <v>101.031795</v>
       </c>
       <c r="O468" s="6" t="n">
-        <v>100.367143</v>
+        <v>100.36843</v>
       </c>
       <c r="P468" s="6" t="n">
         <v>100.896605</v>
@@ -38622,7 +38622,7 @@
         <v>101.041847</v>
       </c>
       <c r="O469" s="9" t="n">
-        <v>100.44809</v>
+        <v>100.449472</v>
       </c>
       <c r="P469" s="9" t="n">
         <v>100.950376</v>
@@ -38706,7 +38706,7 @@
         <v>101.026968</v>
       </c>
       <c r="O470" s="6" t="n">
-        <v>100.520965</v>
+        <v>100.522437</v>
       </c>
       <c r="P470" s="6" t="n">
         <v>101.002482</v>
@@ -38790,7 +38790,7 @@
         <v>100.981825</v>
       </c>
       <c r="O471" s="9" t="n">
-        <v>100.52974</v>
+        <v>100.531292</v>
       </c>
       <c r="P471" s="9" t="n">
         <v>101.060466</v>
@@ -38874,7 +38874,7 @@
         <v>100.904117</v>
       </c>
       <c r="O472" s="6" t="n">
-        <v>100.417445</v>
+        <v>100.419027</v>
       </c>
       <c r="P472" s="6" t="n">
         <v>101.133693</v>
@@ -38958,7 +38958,7 @@
         <v>100.805549</v>
       </c>
       <c r="O473" s="9" t="n">
-        <v>100.216487</v>
+        <v>100.218061</v>
       </c>
       <c r="P473" s="9" t="n">
         <v>101.230651</v>
@@ -39042,7 +39042,7 @@
         <v>100.712834</v>
       </c>
       <c r="O474" s="6" t="n">
-        <v>99.966802</v>
+        <v>99.968356</v>
       </c>
       <c r="P474" s="6" t="n">
         <v>101.352026</v>
@@ -39126,7 +39126,7 @@
         <v>100.629907</v>
       </c>
       <c r="O475" s="9" t="n">
-        <v>99.67906600000001</v>
+        <v>99.68058499999999</v>
       </c>
       <c r="P475" s="9" t="n">
         <v>101.465393</v>
@@ -39210,7 +39210,7 @@
         <v>100.559192</v>
       </c>
       <c r="O476" s="6" t="n">
-        <v>99.421451</v>
+        <v>99.42294800000001</v>
       </c>
       <c r="P476" s="6" t="n">
         <v>101.548096</v>
@@ -39294,7 +39294,7 @@
         <v>100.49821</v>
       </c>
       <c r="O477" s="9" t="n">
-        <v>99.213864</v>
+        <v>99.215371</v>
       </c>
       <c r="P477" s="9" t="n">
         <v>101.580587</v>
@@ -39378,7 +39378,7 @@
         <v>100.438772</v>
       </c>
       <c r="O478" s="6" t="n">
-        <v>99.049446</v>
+        <v>99.05097499999999</v>
       </c>
       <c r="P478" s="6" t="n">
         <v>101.544832</v>
@@ -39462,7 +39462,7 @@
         <v>100.379011</v>
       </c>
       <c r="O479" s="9" t="n">
-        <v>98.99370999999999</v>
+        <v>98.995295</v>
       </c>
       <c r="P479" s="9" t="n">
         <v>101.438764</v>
@@ -39546,7 +39546,7 @@
         <v>100.317631</v>
       </c>
       <c r="O480" s="6" t="n">
-        <v>99.04059599999999</v>
+        <v>99.042288</v>
       </c>
       <c r="P480" s="6" t="n">
         <v>101.290546</v>
@@ -39630,7 +39630,7 @@
         <v>100.239692</v>
       </c>
       <c r="O481" s="9" t="n">
-        <v>99.131083</v>
+        <v>99.132893</v>
       </c>
       <c r="P481" s="9" t="n">
         <v>101.125144</v>
@@ -39714,7 +39714,7 @@
         <v>100.136536</v>
       </c>
       <c r="O482" s="6" t="n">
-        <v>99.161734</v>
+        <v>99.16364</v>
       </c>
       <c r="P482" s="6" t="n">
         <v>100.943846</v>
@@ -39798,7 +39798,7 @@
         <v>100.000387</v>
       </c>
       <c r="O483" s="9" t="n">
-        <v>99.164749</v>
+        <v>99.16673400000001</v>
       </c>
       <c r="P483" s="9" t="n">
         <v>100.730865</v>
@@ -39882,7 +39882,7 @@
         <v>99.816075</v>
       </c>
       <c r="O484" s="6" t="n">
-        <v>99.16731299999999</v>
+        <v>99.169365</v>
       </c>
       <c r="P484" s="6" t="n">
         <v>100.460695</v>
@@ -39966,7 +39966,7 @@
         <v>99.565625</v>
       </c>
       <c r="O485" s="9" t="n">
-        <v>99.126498</v>
+        <v>99.12859899999999</v>
       </c>
       <c r="P485" s="9" t="n">
         <v>100.097811</v>
@@ -40050,7 +40050,7 @@
         <v>99.22620499999999</v>
       </c>
       <c r="O486" s="6" t="n">
-        <v>99.037143</v>
+        <v>99.03926800000001</v>
       </c>
       <c r="P486" s="6" t="n">
         <v>99.61394799999999</v>
@@ -40134,7 +40134,7 @@
         <v>98.779974</v>
       </c>
       <c r="O487" s="9" t="n">
-        <v>98.934038</v>
+        <v>98.93617</v>
       </c>
       <c r="P487" s="9" t="n">
         <v>99.00792</v>
@@ -40218,7 +40218,7 @@
         <v>98.24610699999999</v>
       </c>
       <c r="O488" s="6" t="n">
-        <v>98.796201</v>
+        <v>98.79833499999999</v>
       </c>
       <c r="P488" s="6" t="n">
         <v>98.32839300000001</v>
@@ -40302,7 +40302,7 @@
         <v>95.544766</v>
       </c>
       <c r="O489" s="9" t="n">
-        <v>98.66488200000001</v>
+        <v>98.667036</v>
       </c>
       <c r="P489" s="9" t="n">
         <v>97.684546</v>
@@ -40386,7 +40386,7 @@
         <v>93.05402599999999</v>
       </c>
       <c r="O490" s="6" t="n">
-        <v>98.58656000000001</v>
+        <v>98.58877699999999</v>
       </c>
       <c r="P490" s="6" t="n">
         <v>97.219554</v>
@@ -40470,7 +40470,7 @@
         <v>95.727931</v>
       </c>
       <c r="O491" s="9" t="n">
-        <v>98.582471</v>
+        <v>98.58478100000001</v>
       </c>
       <c r="P491" s="9" t="n">
         <v>96.981893</v>
@@ -40554,7 +40554,7 @@
         <v>96.061317</v>
       </c>
       <c r="O492" s="6" t="n">
-        <v>98.679256</v>
+        <v>98.681675</v>
       </c>
       <c r="P492" s="6" t="n">
         <v>96.936964</v>
@@ -40638,7 +40638,7 @@
         <v>97.099683</v>
       </c>
       <c r="O493" s="9" t="n">
-        <v>98.875979</v>
+        <v>98.878523</v>
       </c>
       <c r="P493" s="9" t="n">
         <v>97.027584</v>
@@ -40722,7 +40722,7 @@
         <v>97.44334499999999</v>
       </c>
       <c r="O494" s="6" t="n">
-        <v>99.156977</v>
+        <v>99.15967499999999</v>
       </c>
       <c r="P494" s="6" t="n">
         <v>97.19841700000001</v>
@@ -40806,7 +40806,7 @@
         <v>97.834868</v>
       </c>
       <c r="O495" s="9" t="n">
-        <v>99.46483600000001</v>
+        <v>99.46768899999999</v>
       </c>
       <c r="P495" s="9" t="n">
         <v>97.396779</v>
@@ -40890,7 +40890,7 @@
         <v>98.223889</v>
       </c>
       <c r="O496" s="6" t="n">
-        <v>99.76193000000001</v>
+        <v>99.764928</v>
       </c>
       <c r="P496" s="6" t="n">
         <v>97.597275</v>
@@ -40974,7 +40974,7 @@
         <v>98.561145</v>
       </c>
       <c r="O497" s="9" t="n">
-        <v>100.030906</v>
+        <v>100.034038</v>
       </c>
       <c r="P497" s="9" t="n">
         <v>97.78906000000001</v>
@@ -41058,7 +41058,7 @@
         <v>98.834394</v>
       </c>
       <c r="O498" s="6" t="n">
-        <v>100.251726</v>
+        <v>100.254969</v>
       </c>
       <c r="P498" s="6" t="n">
         <v>97.97939</v>
@@ -41142,7 +41142,7 @@
         <v>99.057787</v>
       </c>
       <c r="O499" s="9" t="n">
-        <v>100.430444</v>
+        <v>100.433784</v>
       </c>
       <c r="P499" s="9" t="n">
         <v>98.19193</v>
@@ -41226,7 +41226,7 @@
         <v>99.27468399999999</v>
       </c>
       <c r="O500" s="6" t="n">
-        <v>100.602549</v>
+        <v>100.605971</v>
       </c>
       <c r="P500" s="6" t="n">
         <v>98.442592</v>
@@ -41310,7 +41310,7 @@
         <v>99.496961</v>
       </c>
       <c r="O501" s="9" t="n">
-        <v>100.753029</v>
+        <v>100.7565</v>
       </c>
       <c r="P501" s="9" t="n">
         <v>98.716746</v>
@@ -41394,7 +41394,7 @@
         <v>99.71266900000001</v>
       </c>
       <c r="O502" s="6" t="n">
-        <v>100.849663</v>
+        <v>100.853147</v>
       </c>
       <c r="P502" s="6" t="n">
         <v>98.98921199999999</v>
@@ -41478,7 +41478,7 @@
         <v>99.901359</v>
       </c>
       <c r="O503" s="9" t="n">
-        <v>100.867018</v>
+        <v>100.870491</v>
       </c>
       <c r="P503" s="9" t="n">
         <v>99.235879</v>
@@ -41562,7 +41562,7 @@
         <v>100.059735</v>
       </c>
       <c r="O504" s="6" t="n">
-        <v>100.806092</v>
+        <v>100.809521</v>
       </c>
       <c r="P504" s="6" t="n">
         <v>99.43498599999999</v>
@@ -41646,7 +41646,7 @@
         <v>100.180721</v>
       </c>
       <c r="O505" s="9" t="n">
-        <v>100.686667</v>
+        <v>100.69003</v>
       </c>
       <c r="P505" s="9" t="n">
         <v>99.586682</v>
@@ -41730,7 +41730,7 @@
         <v>100.293809</v>
       </c>
       <c r="O506" s="6" t="n">
-        <v>100.537088</v>
+        <v>100.540372</v>
       </c>
       <c r="P506" s="6" t="n">
         <v>99.716379</v>
@@ -41814,7 +41814,7 @@
         <v>100.425671</v>
       </c>
       <c r="O507" s="9" t="n">
-        <v>100.377357</v>
+        <v>100.380557</v>
       </c>
       <c r="P507" s="9" t="n">
         <v>99.840755</v>
@@ -41898,7 +41898,7 @@
         <v>100.582879</v>
       </c>
       <c r="O508" s="6" t="n">
-        <v>100.247501</v>
+        <v>100.250627</v>
       </c>
       <c r="P508" s="6" t="n">
         <v>99.959497</v>
@@ -41982,7 +41982,7 @@
         <v>100.75952</v>
       </c>
       <c r="O509" s="9" t="n">
-        <v>100.16287</v>
+        <v>100.165921</v>
       </c>
       <c r="P509" s="9" t="n">
         <v>100.074469</v>
@@ -42066,7 +42066,7 @@
         <v>100.949082</v>
       </c>
       <c r="O510" s="6" t="n">
-        <v>100.121207</v>
+        <v>100.124167</v>
       </c>
       <c r="P510" s="6" t="n">
         <v>100.183225</v>
@@ -42150,7 +42150,7 @@
         <v>101.158641</v>
       </c>
       <c r="O511" s="9" t="n">
-        <v>100.112028</v>
+        <v>100.114886</v>
       </c>
       <c r="P511" s="9" t="n">
         <v>100.285788</v>
@@ -42234,7 +42234,7 @@
         <v>101.360203</v>
       </c>
       <c r="O512" s="6" t="n">
-        <v>100.110512</v>
+        <v>100.113233</v>
       </c>
       <c r="P512" s="6" t="n">
         <v>100.356675</v>
@@ -42318,7 +42318,7 @@
         <v>101.528176</v>
       </c>
       <c r="O513" s="9" t="n">
-        <v>100.127605</v>
+        <v>100.130151</v>
       </c>
       <c r="P513" s="9" t="n">
         <v>100.41075</v>
@@ -42402,7 +42402,7 @@
         <v>101.638937</v>
       </c>
       <c r="O514" s="6" t="n">
-        <v>100.181923</v>
+        <v>100.184271</v>
       </c>
       <c r="P514" s="6" t="n">
         <v>100.445469</v>
@@ -42486,7 +42486,7 @@
         <v>101.676133</v>
       </c>
       <c r="O515" s="9" t="n">
-        <v>100.257843</v>
+        <v>100.25998</v>
       </c>
       <c r="P515" s="9" t="n">
         <v>100.451074</v>
@@ -42570,7 +42570,7 @@
         <v>101.626996</v>
       </c>
       <c r="O516" s="6" t="n">
-        <v>100.329706</v>
+        <v>100.331625</v>
       </c>
       <c r="P516" s="6" t="n">
         <v>100.42789</v>
@@ -42654,7 +42654,7 @@
         <v>101.505375</v>
       </c>
       <c r="O517" s="9" t="n">
-        <v>100.379213</v>
+        <v>100.380929</v>
       </c>
       <c r="P517" s="9" t="n">
         <v>100.391979</v>
@@ -42738,7 +42738,7 @@
         <v>101.3427</v>
       </c>
       <c r="O518" s="6" t="n">
-        <v>100.426774</v>
+        <v>100.428309</v>
       </c>
       <c r="P518" s="6" t="n">
         <v>100.348668</v>
@@ -42822,7 +42822,7 @@
         <v>101.166546</v>
       </c>
       <c r="O519" s="9" t="n">
-        <v>100.479358</v>
+        <v>100.480743</v>
       </c>
       <c r="P519" s="9" t="n">
         <v>100.315581</v>
@@ -42906,7 +42906,7 @@
         <v>101.002344</v>
       </c>
       <c r="O520" s="6" t="n">
-        <v>100.521996</v>
+        <v>100.523257</v>
       </c>
       <c r="P520" s="6" t="n">
         <v>100.303053</v>
@@ -42990,7 +42990,7 @@
         <v>100.871385</v>
       </c>
       <c r="O521" s="9" t="n">
-        <v>100.573207</v>
+        <v>100.574339</v>
       </c>
       <c r="P521" s="9" t="n">
         <v>100.320282</v>
@@ -43074,7 +43074,7 @@
         <v>100.764292</v>
       </c>
       <c r="O522" s="6" t="n">
-        <v>100.641688</v>
+        <v>100.642645</v>
       </c>
       <c r="P522" s="6" t="n">
         <v>100.375709</v>
@@ -43158,7 +43158,7 @@
         <v>100.663586</v>
       </c>
       <c r="O523" s="9" t="n">
-        <v>100.713057</v>
+        <v>100.713739</v>
       </c>
       <c r="P523" s="9" t="n">
         <v>100.459152</v>
@@ -43242,7 +43242,7 @@
         <v>100.567512</v>
       </c>
       <c r="O524" s="6" t="n">
-        <v>100.765901</v>
+        <v>100.766164</v>
       </c>
       <c r="P524" s="6" t="n">
         <v>100.546283</v>
@@ -43326,7 +43326,7 @@
         <v>100.476974</v>
       </c>
       <c r="O525" s="9" t="n">
-        <v>100.781153</v>
+        <v>100.780831</v>
       </c>
       <c r="P525" s="9" t="n">
         <v>100.629013</v>
@@ -43410,7 +43410,7 @@
         <v>100.38367</v>
       </c>
       <c r="O526" s="6" t="n">
-        <v>100.747544</v>
+        <v>100.74651</v>
       </c>
       <c r="P526" s="6" t="n">
         <v>100.710041</v>
@@ -43494,7 +43494,7 @@
         <v>100.292203</v>
       </c>
       <c r="O527" s="9" t="n">
-        <v>100.67572</v>
+        <v>100.673886</v>
       </c>
       <c r="P527" s="9" t="n">
         <v>100.79824</v>
@@ -43578,7 +43578,7 @@
         <v>100.21003</v>
       </c>
       <c r="O528" s="6" t="n">
-        <v>100.579659</v>
+        <v>100.57701</v>
       </c>
       <c r="P528" s="6" t="n">
         <v>100.883805</v>
@@ -43662,7 +43662,7 @@
         <v>100.14569</v>
       </c>
       <c r="O529" s="9" t="n">
-        <v>100.479925</v>
+        <v>100.476548</v>
       </c>
       <c r="P529" s="9" t="n">
         <v>100.962194</v>
@@ -43746,7 +43746,7 @@
         <v>100.094836</v>
       </c>
       <c r="O530" s="6" t="n">
-        <v>100.388934</v>
+        <v>100.384973</v>
       </c>
       <c r="P530" s="6" t="n">
         <v>101.036162</v>
@@ -43830,7 +43830,7 @@
         <v>100.044959</v>
       </c>
       <c r="O531" s="9" t="n">
-        <v>100.329233</v>
+        <v>100.324882</v>
       </c>
       <c r="P531" s="9" t="n">
         <v>101.107575</v>
@@ -43914,7 +43914,7 @@
         <v>100.007873</v>
       </c>
       <c r="O532" s="6" t="n">
-        <v>100.322449</v>
+        <v>100.317893</v>
       </c>
       <c r="P532" s="6" t="n">
         <v>101.182753</v>
@@ -43998,7 +43998,7 @@
         <v>99.99654700000001</v>
       </c>
       <c r="O533" s="9" t="n">
-        <v>100.356825</v>
+        <v>100.352183</v>
       </c>
       <c r="P533" s="9" t="n">
         <v>101.261328</v>
@@ -44082,7 +44082,7 @@
         <v>100.012407</v>
       </c>
       <c r="O534" s="6" t="n">
-        <v>100.406194</v>
+        <v>100.40148</v>
       </c>
       <c r="P534" s="6" t="n">
         <v>101.333157</v>
@@ -44166,7 +44166,7 @@
         <v>100.040139</v>
       </c>
       <c r="O535" s="9" t="n">
-        <v>100.443927</v>
+        <v>100.43898</v>
       </c>
       <c r="P535" s="9" t="n">
         <v>101.388526</v>
@@ -44250,7 +44250,7 @@
         <v>100.042585</v>
       </c>
       <c r="O536" s="6" t="n">
-        <v>100.468582</v>
+        <v>100.463058</v>
       </c>
       <c r="P536" s="6" t="n">
         <v>101.414975</v>
@@ -44334,7 +44334,7 @@
         <v>100.017249</v>
       </c>
       <c r="O537" s="9" t="n">
-        <v>100.471258</v>
+        <v>100.464657</v>
       </c>
       <c r="P537" s="9" t="n">
         <v>101.395846</v>
@@ -44418,7 +44418,7 @@
         <v>99.96810600000001</v>
       </c>
       <c r="O538" s="6" t="n">
-        <v>100.448925</v>
+        <v>100.44067</v>
       </c>
       <c r="P538" s="6" t="n">
         <v>101.329275</v>
@@ -44502,7 +44502,7 @@
         <v>99.90411899999999</v>
       </c>
       <c r="O539" s="9" t="n">
-        <v>100.402108</v>
+        <v>100.39169</v>
       </c>
       <c r="P539" s="9" t="n">
         <v>101.221741</v>
@@ -44586,7 +44586,7 @@
         <v>99.822546</v>
       </c>
       <c r="O540" s="6" t="n">
-        <v>100.336708</v>
+        <v>100.323872</v>
       </c>
       <c r="P540" s="6" t="n">
         <v>101.094689</v>
@@ -44670,7 +44670,7 @@
         <v>99.727885</v>
       </c>
       <c r="O541" s="9" t="n">
-        <v>100.269446</v>
+        <v>100.254403</v>
       </c>
       <c r="P541" s="9" t="n">
         <v>100.957811</v>
@@ -44754,7 +44754,7 @@
         <v>99.62104100000001</v>
       </c>
       <c r="O542" s="6" t="n">
-        <v>100.203555</v>
+        <v>100.187339</v>
       </c>
       <c r="P542" s="6" t="n">
         <v>100.80569</v>
@@ -44838,7 +44838,7 @@
         <v>99.524879</v>
       </c>
       <c r="O543" s="9" t="n">
-        <v>100.124501</v>
+        <v>100.10804</v>
       </c>
       <c r="P543" s="9" t="n">
         <v>100.650148</v>
@@ -44922,7 +44922,7 @@
         <v>99.43491299999999</v>
       </c>
       <c r="O544" s="6" t="n">
-        <v>100.023518</v>
+        <v>100.007474</v>
       </c>
       <c r="P544" s="6" t="n">
         <v>100.488316</v>
@@ -45006,7 +45006,7 @@
         <v>99.34053</v>
       </c>
       <c r="O545" s="9" t="n">
-        <v>99.89214800000001</v>
+        <v>99.876864</v>
       </c>
       <c r="P545" s="9" t="n">
         <v>100.314638</v>
@@ -45090,7 +45090,7 @@
         <v>99.249089</v>
       </c>
       <c r="O546" s="6" t="n">
-        <v>99.75042000000001</v>
+        <v>99.73588599999999</v>
       </c>
       <c r="P546" s="6" t="n">
         <v>100.133531</v>
@@ -45174,7 +45174,7 @@
         <v>99.171885</v>
       </c>
       <c r="O547" s="9" t="n">
-        <v>99.603573</v>
+        <v>99.589375</v>
       </c>
       <c r="P547" s="9" t="n">
         <v>99.948623</v>
@@ -45258,7 +45258,7 @@
         <v>99.12424900000001</v>
       </c>
       <c r="O548" s="6" t="n">
-        <v>99.458325</v>
+        <v>99.443596</v>
       </c>
       <c r="P548" s="6" t="n">
         <v>99.78811899999999</v>
@@ -45342,7 +45342,7 @@
         <v>99.098016</v>
       </c>
       <c r="O549" s="9" t="n">
-        <v>99.345944</v>
+        <v>99.329407</v>
       </c>
       <c r="P549" s="9" t="n">
         <v>99.674441</v>
@@ -45426,7 +45426,7 @@
         <v>99.09165400000001</v>
       </c>
       <c r="O550" s="6" t="n">
-        <v>99.27608600000001</v>
+        <v>99.256207</v>
       </c>
       <c r="P550" s="6" t="n">
         <v>99.62838499999999</v>
@@ -45510,7 +45510,7 @@
         <v>99.113012</v>
       </c>
       <c r="O551" s="9" t="n">
-        <v>99.244342</v>
+        <v>99.219632</v>
       </c>
       <c r="P551" s="9" t="n">
         <v>99.620283</v>
@@ -45594,7 +45594,7 @@
         <v>99.168695</v>
       </c>
       <c r="O552" s="6" t="n">
-        <v>99.236644</v>
+        <v>99.206112</v>
       </c>
       <c r="P552" s="6" t="n">
         <v>99.62472099999999</v>
@@ -45678,7 +45678,7 @@
         <v>99.263171</v>
       </c>
       <c r="O553" s="9" t="n">
-        <v>99.24212900000001</v>
+        <v>99.20610600000001</v>
       </c>
       <c r="P553" s="9" t="n">
         <v>99.61776999999999</v>
@@ -45762,7 +45762,7 @@
         <v>99.378964</v>
       </c>
       <c r="O554" s="6" t="n">
-        <v>99.247327</v>
+        <v>99.208668</v>
       </c>
       <c r="P554" s="6" t="n">
         <v>99.59324599999999</v>
@@ -45846,7 +45846,7 @@
         <v>99.505286</v>
       </c>
       <c r="O555" s="9" t="n">
-        <v>99.265945</v>
+        <v>99.22666700000001</v>
       </c>
       <c r="P555" s="9" t="n">
         <v>99.54774500000001</v>
@@ -45930,7 +45930,7 @@
         <v>99.634331</v>
       </c>
       <c r="O556" s="6" t="n">
-        <v>99.30649200000001</v>
+        <v>99.26781200000001</v>
       </c>
       <c r="P556" s="6" t="n">
         <v>99.488089</v>
@@ -46014,7 +46014,7 @@
         <v>99.773279</v>
       </c>
       <c r="O557" s="9" t="n">
-        <v>99.388276</v>
+        <v>99.350877</v>
       </c>
       <c r="P557" s="9" t="n">
         <v>99.424121</v>
@@ -46098,7 +46098,7 @@
         <v>99.933976</v>
       </c>
       <c r="O558" s="6" t="n">
-        <v>99.50973999999999</v>
+        <v>99.47413400000001</v>
       </c>
       <c r="P558" s="6" t="n">
         <v>99.36145999999999</v>
@@ -46182,7 +46182,7 @@
         <v>100.126678</v>
       </c>
       <c r="O559" s="9" t="n">
-        <v>99.654957</v>
+        <v>99.621951</v>
       </c>
       <c r="P559" s="9" t="n">
         <v>99.303361</v>
@@ -46266,7 +46266,7 @@
         <v>100.354928</v>
       </c>
       <c r="O560" s="6" t="n">
-        <v>99.811421</v>
+        <v>99.782504</v>
       </c>
       <c r="P560" s="6" t="n">
         <v>99.253698</v>
@@ -46350,7 +46350,7 @@
         <v>100.615919</v>
       </c>
       <c r="O561" s="9" t="n">
-        <v>99.94686299999999</v>
+        <v>99.92449000000001</v>
       </c>
       <c r="P561" s="9" t="n">
         <v>99.21717200000001</v>
@@ -46434,7 +46434,7 @@
         <v>100.906045</v>
       </c>
       <c r="O562" s="6" t="n">
-        <v>100.063264</v>
+        <v>100.050948</v>
       </c>
       <c r="P562" s="6" t="n">
         <v>99.195198</v>
@@ -46518,7 +46518,7 @@
         <v>101.22779</v>
       </c>
       <c r="O563" s="9" t="n">
-        <v>100.155459</v>
+        <v>100.157408</v>
       </c>
       <c r="P563" s="9" t="n">
         <v>99.194997</v>
@@ -46590,7 +46590,7 @@
         <v>101.591978</v>
       </c>
       <c r="O564" s="6" t="n">
-        <v>100.235256</v>
+        <v>100.255278</v>
       </c>
       <c r="P564" s="6" t="n">
         <v>99.205601</v>

--- a/downloads/indicadores/SIC/SIC_datos.xlsx
+++ b/downloads/indicadores/SIC/SIC_datos.xlsx
@@ -1554,7 +1554,7 @@
       </c>
       <c r="P18" s="6" t="n"/>
       <c r="Q18" s="6" t="n">
-        <v>106.941213</v>
+        <v>106.952153</v>
       </c>
       <c r="R18" s="6" t="n">
         <v>98.48235</v>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="P19" s="9" t="n"/>
       <c r="Q19" s="9" t="n">
-        <v>106.492297</v>
+        <v>106.502529</v>
       </c>
       <c r="R19" s="9" t="n">
         <v>98.19567499999999</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="P20" s="6" t="n"/>
       <c r="Q20" s="6" t="n">
-        <v>106.042259</v>
+        <v>106.051782</v>
       </c>
       <c r="R20" s="6" t="n">
         <v>97.928355</v>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P21" s="9" t="n"/>
       <c r="Q21" s="9" t="n">
-        <v>105.58577</v>
+        <v>105.594574</v>
       </c>
       <c r="R21" s="9" t="n">
         <v>97.68249900000001</v>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="P22" s="6" t="n"/>
       <c r="Q22" s="6" t="n">
-        <v>105.114597</v>
+        <v>105.122658</v>
       </c>
       <c r="R22" s="6" t="n">
         <v>97.45650500000001</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="P23" s="9" t="n"/>
       <c r="Q23" s="9" t="n">
-        <v>104.634116</v>
+        <v>104.64142</v>
       </c>
       <c r="R23" s="9" t="n">
         <v>97.24387900000001</v>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="P24" s="6" t="n"/>
       <c r="Q24" s="6" t="n">
-        <v>104.150717</v>
+        <v>104.157259</v>
       </c>
       <c r="R24" s="6" t="n">
         <v>97.040532</v>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="P25" s="9" t="n"/>
       <c r="Q25" s="9" t="n">
-        <v>103.666286</v>
+        <v>103.672064</v>
       </c>
       <c r="R25" s="9" t="n">
         <v>96.85361</v>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="6" t="n"/>
       <c r="Q26" s="6" t="n">
-        <v>103.178289</v>
+        <v>103.183298</v>
       </c>
       <c r="R26" s="6" t="n">
         <v>96.70961200000001</v>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="P27" s="9" t="n"/>
       <c r="Q27" s="9" t="n">
-        <v>102.681849</v>
+        <v>102.686076</v>
       </c>
       <c r="R27" s="9" t="n">
         <v>96.651156</v>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="6" t="n"/>
       <c r="Q28" s="6" t="n">
-        <v>102.166296</v>
+        <v>102.16971</v>
       </c>
       <c r="R28" s="6" t="n">
         <v>96.741212</v>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="P29" s="9" t="n"/>
       <c r="Q29" s="9" t="n">
-        <v>101.578105</v>
+        <v>101.580592</v>
       </c>
       <c r="R29" s="9" t="n">
         <v>97.047342</v>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P30" s="6" t="n"/>
       <c r="Q30" s="6" t="n">
-        <v>100.875176</v>
+        <v>100.876556</v>
       </c>
       <c r="R30" s="6" t="n">
         <v>97.61970100000001</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="P31" s="9" t="n"/>
       <c r="Q31" s="9" t="n">
-        <v>100.081091</v>
+        <v>100.081219</v>
       </c>
       <c r="R31" s="9" t="n">
         <v>98.446913</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="P32" s="6" t="n"/>
       <c r="Q32" s="6" t="n">
-        <v>99.205951</v>
+        <v>99.2047</v>
       </c>
       <c r="R32" s="6" t="n">
         <v>99.368572</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="P33" s="9" t="n"/>
       <c r="Q33" s="9" t="n">
-        <v>98.29227899999999</v>
+        <v>98.289587</v>
       </c>
       <c r="R33" s="9" t="n">
         <v>100.19379</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="P34" s="6" t="n"/>
       <c r="Q34" s="6" t="n">
-        <v>97.454133</v>
+        <v>97.450121</v>
       </c>
       <c r="R34" s="6" t="n">
         <v>100.828526</v>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n">
-        <v>96.79218299999999</v>
+        <v>96.787127</v>
       </c>
       <c r="R35" s="9" t="n">
         <v>101.307262</v>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="P36" s="6" t="n"/>
       <c r="Q36" s="6" t="n">
-        <v>96.309439</v>
+        <v>96.303622</v>
       </c>
       <c r="R36" s="6" t="n">
         <v>101.705298</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P37" s="9" t="n"/>
       <c r="Q37" s="9" t="n">
-        <v>96.00638499999999</v>
+        <v>96.00009</v>
       </c>
       <c r="R37" s="9" t="n">
         <v>102.074932</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="P38" s="6" t="n"/>
       <c r="Q38" s="6" t="n">
-        <v>95.839912</v>
+        <v>95.833355</v>
       </c>
       <c r="R38" s="6" t="n">
         <v>102.375824</v>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="P39" s="9" t="n"/>
       <c r="Q39" s="9" t="n">
-        <v>95.71947299999999</v>
+        <v>95.712726</v>
       </c>
       <c r="R39" s="9" t="n">
         <v>102.563586</v>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="P40" s="6" t="n"/>
       <c r="Q40" s="6" t="n">
-        <v>95.614642</v>
+        <v>95.60773</v>
       </c>
       <c r="R40" s="6" t="n">
         <v>102.684777</v>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="P41" s="9" t="n"/>
       <c r="Q41" s="9" t="n">
-        <v>95.51251499999999</v>
+        <v>95.505442</v>
       </c>
       <c r="R41" s="9" t="n">
         <v>102.798247</v>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="P42" s="6" t="n"/>
       <c r="Q42" s="6" t="n">
-        <v>95.474712</v>
+        <v>95.467579</v>
       </c>
       <c r="R42" s="6" t="n">
         <v>102.897725</v>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="P43" s="9" t="n"/>
       <c r="Q43" s="9" t="n">
-        <v>95.529231</v>
+        <v>95.52218499999999</v>
       </c>
       <c r="R43" s="9" t="n">
         <v>102.933648</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="P44" s="6" t="n"/>
       <c r="Q44" s="6" t="n">
-        <v>95.704453</v>
+        <v>95.697683</v>
       </c>
       <c r="R44" s="6" t="n">
         <v>102.889904</v>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="P45" s="9" t="n"/>
       <c r="Q45" s="9" t="n">
-        <v>96.040631</v>
+        <v>96.034391</v>
       </c>
       <c r="R45" s="9" t="n">
         <v>102.779724</v>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="P46" s="6" t="n"/>
       <c r="Q46" s="6" t="n">
-        <v>96.530602</v>
+        <v>96.52513399999999</v>
       </c>
       <c r="R46" s="6" t="n">
         <v>102.628501</v>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="P47" s="9" t="n"/>
       <c r="Q47" s="9" t="n">
-        <v>97.108997</v>
+        <v>97.10444099999999</v>
       </c>
       <c r="R47" s="9" t="n">
         <v>102.452495</v>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="P48" s="6" t="n"/>
       <c r="Q48" s="6" t="n">
-        <v>97.687276</v>
+        <v>97.68363100000001</v>
       </c>
       <c r="R48" s="6" t="n">
         <v>102.25915</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="P49" s="9" t="n"/>
       <c r="Q49" s="9" t="n">
-        <v>98.229585</v>
+        <v>98.226795</v>
       </c>
       <c r="R49" s="9" t="n">
         <v>102.051668</v>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="P50" s="6" t="n"/>
       <c r="Q50" s="6" t="n">
-        <v>98.741343</v>
+        <v>98.73935899999999</v>
       </c>
       <c r="R50" s="6" t="n">
         <v>101.8218</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="P51" s="9" t="n"/>
       <c r="Q51" s="9" t="n">
-        <v>99.19819699999999</v>
+        <v>99.196934</v>
       </c>
       <c r="R51" s="9" t="n">
         <v>101.554162</v>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P52" s="6" t="n"/>
       <c r="Q52" s="6" t="n">
-        <v>99.619529</v>
+        <v>99.61892899999999</v>
       </c>
       <c r="R52" s="6" t="n">
         <v>101.241426</v>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="P53" s="9" t="n"/>
       <c r="Q53" s="9" t="n">
-        <v>100.009555</v>
+        <v>100.00957</v>
       </c>
       <c r="R53" s="9" t="n">
         <v>100.896087</v>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="P54" s="6" t="n"/>
       <c r="Q54" s="6" t="n">
-        <v>100.298065</v>
+        <v>100.298536</v>
       </c>
       <c r="R54" s="6" t="n">
         <v>100.535219</v>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="P55" s="9" t="n"/>
       <c r="Q55" s="9" t="n">
-        <v>100.383504</v>
+        <v>100.384109</v>
       </c>
       <c r="R55" s="9" t="n">
         <v>100.184056</v>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="P56" s="6" t="n"/>
       <c r="Q56" s="6" t="n">
-        <v>100.242182</v>
+        <v>100.242564</v>
       </c>
       <c r="R56" s="6" t="n">
         <v>99.86263599999999</v>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="P57" s="9" t="n"/>
       <c r="Q57" s="9" t="n">
-        <v>99.98227199999999</v>
+        <v>99.98224500000001</v>
       </c>
       <c r="R57" s="9" t="n">
         <v>99.580629</v>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="P58" s="6" t="n"/>
       <c r="Q58" s="6" t="n">
-        <v>99.72452699999999</v>
+        <v>99.72409399999999</v>
       </c>
       <c r="R58" s="6" t="n">
         <v>99.337833</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="P59" s="9" t="n"/>
       <c r="Q59" s="9" t="n">
-        <v>99.508745</v>
+        <v>99.507971</v>
       </c>
       <c r="R59" s="9" t="n">
         <v>99.124133</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="P60" s="6" t="n"/>
       <c r="Q60" s="6" t="n">
-        <v>99.355003</v>
+        <v>99.353987</v>
       </c>
       <c r="R60" s="6" t="n">
         <v>98.925122</v>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="P61" s="9" t="n"/>
       <c r="Q61" s="9" t="n">
-        <v>99.232197</v>
+        <v>99.230988</v>
       </c>
       <c r="R61" s="9" t="n">
         <v>98.72202799999999</v>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="P62" s="6" t="n"/>
       <c r="Q62" s="6" t="n">
-        <v>99.06312</v>
+        <v>99.061644</v>
       </c>
       <c r="R62" s="6" t="n">
         <v>98.49393000000001</v>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="P63" s="9" t="n"/>
       <c r="Q63" s="9" t="n">
-        <v>98.794132</v>
+        <v>98.792233</v>
       </c>
       <c r="R63" s="9" t="n">
         <v>98.226176</v>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="P64" s="6" t="n"/>
       <c r="Q64" s="6" t="n">
-        <v>98.442848</v>
+        <v>98.440395</v>
       </c>
       <c r="R64" s="6" t="n">
         <v>97.91884899999999</v>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P65" s="9" t="n"/>
       <c r="Q65" s="9" t="n">
-        <v>98.04024</v>
+        <v>98.03715200000001</v>
       </c>
       <c r="R65" s="9" t="n">
         <v>97.589376</v>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="P66" s="6" t="n"/>
       <c r="Q66" s="6" t="n">
-        <v>97.65330899999999</v>
+        <v>97.649612</v>
       </c>
       <c r="R66" s="6" t="n">
         <v>97.27527000000001</v>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="P67" s="9" t="n"/>
       <c r="Q67" s="9" t="n">
-        <v>97.357377</v>
+        <v>97.353213</v>
       </c>
       <c r="R67" s="9" t="n">
         <v>97.03260400000001</v>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="P68" s="6" t="n"/>
       <c r="Q68" s="6" t="n">
-        <v>97.16871999999999</v>
+        <v>97.164259</v>
       </c>
       <c r="R68" s="6" t="n">
         <v>96.90470500000001</v>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="P69" s="9" t="n"/>
       <c r="Q69" s="9" t="n">
-        <v>97.09718700000001</v>
+        <v>97.092613</v>
       </c>
       <c r="R69" s="9" t="n">
         <v>96.92171399999999</v>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="P70" s="6" t="n"/>
       <c r="Q70" s="6" t="n">
-        <v>97.14954</v>
+        <v>97.145049</v>
       </c>
       <c r="R70" s="6" t="n">
         <v>97.097365</v>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P71" s="9" t="n"/>
       <c r="Q71" s="9" t="n">
-        <v>97.353302</v>
+        <v>97.349131</v>
       </c>
       <c r="R71" s="9" t="n">
         <v>97.428268</v>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="P72" s="6" t="n"/>
       <c r="Q72" s="6" t="n">
-        <v>97.701221</v>
+        <v>97.69759999999999</v>
       </c>
       <c r="R72" s="6" t="n">
         <v>97.888482</v>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="P73" s="9" t="n"/>
       <c r="Q73" s="9" t="n">
-        <v>98.14915499999999</v>
+        <v>98.14623899999999</v>
       </c>
       <c r="R73" s="9" t="n">
         <v>98.409899</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P74" s="6" t="n"/>
       <c r="Q74" s="6" t="n">
-        <v>98.632266</v>
+        <v>98.630112</v>
       </c>
       <c r="R74" s="6" t="n">
         <v>98.890839</v>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="P75" s="9" t="n"/>
       <c r="Q75" s="9" t="n">
-        <v>99.085206</v>
+        <v>99.083766</v>
       </c>
       <c r="R75" s="9" t="n">
         <v>99.298456</v>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P76" s="6" t="n"/>
       <c r="Q76" s="6" t="n">
-        <v>99.41213399999999</v>
+        <v>99.411209</v>
       </c>
       <c r="R76" s="6" t="n">
         <v>99.636045</v>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="P77" s="9" t="n"/>
       <c r="Q77" s="9" t="n">
-        <v>99.566199</v>
+        <v>99.565517</v>
       </c>
       <c r="R77" s="9" t="n">
         <v>99.927035</v>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P78" s="6" t="n"/>
       <c r="Q78" s="6" t="n">
-        <v>99.550303</v>
+        <v>99.54959599999999</v>
       </c>
       <c r="R78" s="6" t="n">
         <v>100.200076</v>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="P79" s="9" t="n"/>
       <c r="Q79" s="9" t="n">
-        <v>99.372034</v>
+        <v>99.37104600000001</v>
       </c>
       <c r="R79" s="9" t="n">
         <v>100.479713</v>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="P80" s="6" t="n"/>
       <c r="Q80" s="6" t="n">
-        <v>99.110281</v>
+        <v>99.10888</v>
       </c>
       <c r="R80" s="6" t="n">
         <v>100.765946</v>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="P81" s="9" t="n"/>
       <c r="Q81" s="9" t="n">
-        <v>98.884337</v>
+        <v>98.88258</v>
       </c>
       <c r="R81" s="9" t="n">
         <v>101.050641</v>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="P82" s="6" t="n"/>
       <c r="Q82" s="6" t="n">
-        <v>98.800386</v>
+        <v>98.798497</v>
       </c>
       <c r="R82" s="6" t="n">
         <v>101.338639</v>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="P83" s="9" t="n"/>
       <c r="Q83" s="9" t="n">
-        <v>98.903086</v>
+        <v>98.901359</v>
       </c>
       <c r="R83" s="9" t="n">
         <v>101.639309</v>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="P84" s="6" t="n"/>
       <c r="Q84" s="6" t="n">
-        <v>99.209515</v>
+        <v>99.208271</v>
       </c>
       <c r="R84" s="6" t="n">
         <v>101.95443</v>
@@ -6796,7 +6796,7 @@
       </c>
       <c r="P85" s="9" t="n"/>
       <c r="Q85" s="9" t="n">
-        <v>99.693275</v>
+        <v>99.69279299999999</v>
       </c>
       <c r="R85" s="9" t="n">
         <v>102.267121</v>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="P86" s="6" t="n"/>
       <c r="Q86" s="6" t="n">
-        <v>100.3227</v>
+        <v>100.323211</v>
       </c>
       <c r="R86" s="6" t="n">
         <v>102.552632</v>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="P87" s="9" t="n"/>
       <c r="Q87" s="9" t="n">
-        <v>101.044998</v>
+        <v>101.046648</v>
       </c>
       <c r="R87" s="9" t="n">
         <v>102.782188</v>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="P88" s="6" t="n"/>
       <c r="Q88" s="6" t="n">
-        <v>101.825486</v>
+        <v>101.828367</v>
       </c>
       <c r="R88" s="6" t="n">
         <v>102.939585</v>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P89" s="9" t="n"/>
       <c r="Q89" s="9" t="n">
-        <v>102.659598</v>
+        <v>102.663793</v>
       </c>
       <c r="R89" s="9" t="n">
         <v>103.027697</v>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="P90" s="6" t="n"/>
       <c r="Q90" s="6" t="n">
-        <v>103.555126</v>
+        <v>103.560733</v>
       </c>
       <c r="R90" s="6" t="n">
         <v>103.061161</v>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="P91" s="9" t="n"/>
       <c r="Q91" s="9" t="n">
-        <v>104.479521</v>
+        <v>104.486584</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>103.0532</v>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="P92" s="6" t="n"/>
       <c r="Q92" s="6" t="n">
-        <v>105.368605</v>
+        <v>105.377068</v>
       </c>
       <c r="R92" s="6" t="n">
         <v>103.007634</v>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="P93" s="9" t="n"/>
       <c r="Q93" s="9" t="n">
-        <v>106.155877</v>
+        <v>106.165579</v>
       </c>
       <c r="R93" s="9" t="n">
         <v>102.922382</v>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="P94" s="6" t="n"/>
       <c r="Q94" s="6" t="n">
-        <v>106.769969</v>
+        <v>106.780635</v>
       </c>
       <c r="R94" s="6" t="n">
         <v>102.80317</v>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="P95" s="9" t="n"/>
       <c r="Q95" s="9" t="n">
-        <v>107.131989</v>
+        <v>107.143222</v>
       </c>
       <c r="R95" s="9" t="n">
         <v>102.652046</v>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P96" s="6" t="n"/>
       <c r="Q96" s="6" t="n">
-        <v>107.140638</v>
+        <v>107.151878</v>
       </c>
       <c r="R96" s="6" t="n">
         <v>102.468884</v>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="P97" s="9" t="n"/>
       <c r="Q97" s="9" t="n">
-        <v>106.656806</v>
+        <v>106.667278</v>
       </c>
       <c r="R97" s="9" t="n">
         <v>102.262226</v>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="P98" s="6" t="n"/>
       <c r="Q98" s="6" t="n">
-        <v>105.626282</v>
+        <v>105.635126</v>
       </c>
       <c r="R98" s="6" t="n">
         <v>102.040322</v>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="P99" s="9" t="n"/>
       <c r="Q99" s="9" t="n">
-        <v>104.182427</v>
+        <v>104.188999</v>
       </c>
       <c r="R99" s="9" t="n">
         <v>101.80166</v>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="P100" s="6" t="n"/>
       <c r="Q100" s="6" t="n">
-        <v>102.606213</v>
+        <v>102.610306</v>
       </c>
       <c r="R100" s="6" t="n">
         <v>101.544477</v>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="P101" s="9" t="n"/>
       <c r="Q101" s="9" t="n">
-        <v>101.241725</v>
+        <v>101.243674</v>
       </c>
       <c r="R101" s="9" t="n">
         <v>101.254362</v>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P102" s="6" t="n"/>
       <c r="Q102" s="6" t="n">
-        <v>100.250982</v>
+        <v>100.251374</v>
       </c>
       <c r="R102" s="6" t="n">
         <v>100.905123</v>
@@ -8264,7 +8264,7 @@
       </c>
       <c r="P103" s="9" t="n"/>
       <c r="Q103" s="9" t="n">
-        <v>99.58410499999999</v>
+        <v>99.58345</v>
       </c>
       <c r="R103" s="9" t="n">
         <v>100.517894</v>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="P104" s="6" t="n"/>
       <c r="Q104" s="6" t="n">
-        <v>99.10717200000001</v>
+        <v>99.105767</v>
       </c>
       <c r="R104" s="6" t="n">
         <v>100.140475</v>
@@ -8428,7 +8428,7 @@
       </c>
       <c r="P105" s="9" t="n"/>
       <c r="Q105" s="9" t="n">
-        <v>98.78567</v>
+        <v>98.783759</v>
       </c>
       <c r="R105" s="9" t="n">
         <v>99.808216</v>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P106" s="6" t="n"/>
       <c r="Q106" s="6" t="n">
-        <v>98.60233700000001</v>
+        <v>98.600138</v>
       </c>
       <c r="R106" s="6" t="n">
         <v>99.54073099999999</v>
@@ -8592,7 +8592,7 @@
       </c>
       <c r="P107" s="9" t="n"/>
       <c r="Q107" s="9" t="n">
-        <v>98.48329</v>
+        <v>98.480902</v>
       </c>
       <c r="R107" s="9" t="n">
         <v>99.342063</v>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="P108" s="6" t="n"/>
       <c r="Q108" s="6" t="n">
-        <v>98.392346</v>
+        <v>98.389815</v>
       </c>
       <c r="R108" s="6" t="n">
         <v>99.207239</v>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="P109" s="9" t="n"/>
       <c r="Q109" s="9" t="n">
-        <v>98.309836</v>
+        <v>98.307175</v>
       </c>
       <c r="R109" s="9" t="n">
         <v>99.12385500000001</v>
@@ -8838,7 +8838,7 @@
       </c>
       <c r="P110" s="6" t="n"/>
       <c r="Q110" s="6" t="n">
-        <v>98.22001299999999</v>
+        <v>98.21720999999999</v>
       </c>
       <c r="R110" s="6" t="n">
         <v>99.073103</v>
@@ -8920,7 +8920,7 @@
       </c>
       <c r="P111" s="9" t="n"/>
       <c r="Q111" s="9" t="n">
-        <v>98.121025</v>
+        <v>98.118065</v>
       </c>
       <c r="R111" s="9" t="n">
         <v>99.03675800000001</v>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="P112" s="6" t="n"/>
       <c r="Q112" s="6" t="n">
-        <v>98.01755799999999</v>
+        <v>98.01443500000001</v>
       </c>
       <c r="R112" s="6" t="n">
         <v>99.007864</v>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="P113" s="9" t="n"/>
       <c r="Q113" s="9" t="n">
-        <v>97.909402</v>
+        <v>97.906109</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>98.994766</v>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="P114" s="6" t="n"/>
       <c r="Q114" s="6" t="n">
-        <v>97.85701400000001</v>
+        <v>97.853639</v>
       </c>
       <c r="R114" s="6" t="n">
         <v>99.01557699999999</v>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="P115" s="9" t="n"/>
       <c r="Q115" s="9" t="n">
-        <v>97.920311</v>
+        <v>97.917035</v>
       </c>
       <c r="R115" s="9" t="n">
         <v>99.08313800000001</v>
@@ -9330,7 +9330,7 @@
       </c>
       <c r="P116" s="6" t="n"/>
       <c r="Q116" s="6" t="n">
-        <v>98.132012</v>
+        <v>98.129069</v>
       </c>
       <c r="R116" s="6" t="n">
         <v>99.19528099999999</v>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="P117" s="9" t="n"/>
       <c r="Q117" s="9" t="n">
-        <v>98.466954</v>
+        <v>98.464539</v>
       </c>
       <c r="R117" s="9" t="n">
         <v>99.340371</v>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="P118" s="6" t="n"/>
       <c r="Q118" s="6" t="n">
-        <v>98.864662</v>
+        <v>98.86287400000001</v>
       </c>
       <c r="R118" s="6" t="n">
         <v>99.504935</v>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="P119" s="9" t="n"/>
       <c r="Q119" s="9" t="n">
-        <v>99.247743</v>
+        <v>99.246559</v>
       </c>
       <c r="R119" s="9" t="n">
         <v>99.67598599999999</v>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="P120" s="6" t="n"/>
       <c r="Q120" s="6" t="n">
-        <v>99.55019900000001</v>
+        <v>99.549491</v>
       </c>
       <c r="R120" s="6" t="n">
         <v>99.841255</v>
@@ -9740,7 +9740,7 @@
       </c>
       <c r="P121" s="9" t="n"/>
       <c r="Q121" s="9" t="n">
-        <v>99.744427</v>
+        <v>99.74402600000001</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>99.987199</v>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="P122" s="6" t="n"/>
       <c r="Q122" s="6" t="n">
-        <v>99.809157</v>
+        <v>99.808858</v>
       </c>
       <c r="R122" s="6" t="n">
         <v>100.100111</v>
@@ -9904,7 +9904,7 @@
       </c>
       <c r="P123" s="9" t="n"/>
       <c r="Q123" s="9" t="n">
-        <v>99.761126</v>
+        <v>99.760751</v>
       </c>
       <c r="R123" s="9" t="n">
         <v>100.167315</v>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="P124" s="6" t="n"/>
       <c r="Q124" s="6" t="n">
-        <v>99.66788200000001</v>
+        <v>99.66736</v>
       </c>
       <c r="R124" s="6" t="n">
         <v>100.183762</v>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P125" s="9" t="n"/>
       <c r="Q125" s="9" t="n">
-        <v>99.59457399999999</v>
+        <v>99.593937</v>
       </c>
       <c r="R125" s="9" t="n">
         <v>100.156052</v>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="P126" s="6" t="n"/>
       <c r="Q126" s="6" t="n">
-        <v>99.56847399999999</v>
+        <v>99.567795</v>
       </c>
       <c r="R126" s="6" t="n">
         <v>100.108383</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="P127" s="9" t="n"/>
       <c r="Q127" s="9" t="n">
-        <v>99.59855899999999</v>
+        <v>99.597928</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>100.068729</v>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="P128" s="6" t="n"/>
       <c r="Q128" s="6" t="n">
-        <v>99.670835</v>
+        <v>99.67031799999999</v>
       </c>
       <c r="R128" s="6" t="n">
         <v>100.050125</v>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="P129" s="9" t="n"/>
       <c r="Q129" s="9" t="n">
-        <v>99.75390400000001</v>
+        <v>99.753517</v>
       </c>
       <c r="R129" s="9" t="n">
         <v>100.052915</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="P130" s="6" t="n"/>
       <c r="Q130" s="6" t="n">
-        <v>99.78973000000001</v>
+        <v>99.7894</v>
       </c>
       <c r="R130" s="6" t="n">
         <v>100.072087</v>
@@ -10560,7 +10560,7 @@
       </c>
       <c r="P131" s="9" t="n"/>
       <c r="Q131" s="9" t="n">
-        <v>99.70446699999999</v>
+        <v>99.704002</v>
       </c>
       <c r="R131" s="9" t="n">
         <v>100.10163</v>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="P132" s="6" t="n"/>
       <c r="Q132" s="6" t="n">
-        <v>99.497398</v>
+        <v>99.496607</v>
       </c>
       <c r="R132" s="6" t="n">
         <v>100.134788</v>
@@ -10724,7 +10724,7 @@
       </c>
       <c r="P133" s="9" t="n"/>
       <c r="Q133" s="9" t="n">
-        <v>99.19310900000001</v>
+        <v>99.191838</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>100.161324</v>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="P134" s="6" t="n"/>
       <c r="Q134" s="6" t="n">
-        <v>98.88196499999999</v>
+        <v>98.88020299999999</v>
       </c>
       <c r="R134" s="6" t="n">
         <v>100.165749</v>
@@ -10888,7 +10888,7 @@
       </c>
       <c r="P135" s="9" t="n"/>
       <c r="Q135" s="9" t="n">
-        <v>98.641739</v>
+        <v>98.639599</v>
       </c>
       <c r="R135" s="9" t="n">
         <v>100.132646</v>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="P136" s="6" t="n"/>
       <c r="Q136" s="6" t="n">
-        <v>98.482868</v>
+        <v>98.48047800000001</v>
       </c>
       <c r="R136" s="6" t="n">
         <v>100.056365</v>
@@ -11052,7 +11052,7 @@
       </c>
       <c r="P137" s="9" t="n"/>
       <c r="Q137" s="9" t="n">
-        <v>98.430097</v>
+        <v>98.427623</v>
       </c>
       <c r="R137" s="9" t="n">
         <v>99.95037000000001</v>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="P138" s="6" t="n"/>
       <c r="Q138" s="6" t="n">
-        <v>98.520954</v>
+        <v>98.51862300000001</v>
       </c>
       <c r="R138" s="6" t="n">
         <v>99.839725</v>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="P139" s="9" t="n"/>
       <c r="Q139" s="9" t="n">
-        <v>98.78272800000001</v>
+        <v>98.78081</v>
       </c>
       <c r="R139" s="9" t="n">
         <v>99.744871</v>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="P140" s="6" t="n"/>
       <c r="Q140" s="6" t="n">
-        <v>99.19569799999999</v>
+        <v>99.19443099999999</v>
       </c>
       <c r="R140" s="6" t="n">
         <v>99.67775399999999</v>
@@ -11380,7 +11380,7 @@
       </c>
       <c r="P141" s="9" t="n"/>
       <c r="Q141" s="9" t="n">
-        <v>99.683555</v>
+        <v>99.68305700000001</v>
       </c>
       <c r="R141" s="9" t="n">
         <v>99.641248</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="P142" s="6" t="n"/>
       <c r="Q142" s="6" t="n">
-        <v>100.170318</v>
+        <v>100.170586</v>
       </c>
       <c r="R142" s="6" t="n">
         <v>99.629503</v>
@@ -11544,7 +11544,7 @@
       </c>
       <c r="P143" s="9" t="n"/>
       <c r="Q143" s="9" t="n">
-        <v>100.589758</v>
+        <v>100.590688</v>
       </c>
       <c r="R143" s="9" t="n">
         <v>99.63114899999999</v>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="P144" s="6" t="n"/>
       <c r="Q144" s="6" t="n">
-        <v>100.938762</v>
+        <v>100.940242</v>
       </c>
       <c r="R144" s="6" t="n">
         <v>99.632515</v>
@@ -11708,7 +11708,7 @@
       </c>
       <c r="P145" s="9" t="n"/>
       <c r="Q145" s="9" t="n">
-        <v>101.211804</v>
+        <v>101.213714</v>
       </c>
       <c r="R145" s="9" t="n">
         <v>99.61829899999999</v>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="P146" s="6" t="n"/>
       <c r="Q146" s="6" t="n">
-        <v>101.424908</v>
+        <v>101.427154</v>
       </c>
       <c r="R146" s="6" t="n">
         <v>99.573066</v>
@@ -11872,7 +11872,7 @@
       </c>
       <c r="P147" s="9" t="n"/>
       <c r="Q147" s="9" t="n">
-        <v>101.608465</v>
+        <v>101.611</v>
       </c>
       <c r="R147" s="9" t="n">
         <v>99.48729899999999</v>
@@ -11954,7 +11954,7 @@
       </c>
       <c r="P148" s="6" t="n"/>
       <c r="Q148" s="6" t="n">
-        <v>101.777552</v>
+        <v>101.780354</v>
       </c>
       <c r="R148" s="6" t="n">
         <v>99.36391</v>
@@ -12036,7 +12036,7 @@
       </c>
       <c r="P149" s="9" t="n"/>
       <c r="Q149" s="9" t="n">
-        <v>101.94885</v>
+        <v>101.951922</v>
       </c>
       <c r="R149" s="9" t="n">
         <v>99.221248</v>
@@ -12118,7 +12118,7 @@
       </c>
       <c r="P150" s="6" t="n"/>
       <c r="Q150" s="6" t="n">
-        <v>102.110797</v>
+        <v>102.114124</v>
       </c>
       <c r="R150" s="6" t="n">
         <v>99.084107</v>
@@ -12200,7 +12200,7 @@
       </c>
       <c r="P151" s="9" t="n"/>
       <c r="Q151" s="9" t="n">
-        <v>102.207348</v>
+        <v>102.210828</v>
       </c>
       <c r="R151" s="9" t="n">
         <v>98.972076</v>
@@ -12282,7 +12282,7 @@
       </c>
       <c r="P152" s="6" t="n"/>
       <c r="Q152" s="6" t="n">
-        <v>102.174783</v>
+        <v>102.178211</v>
       </c>
       <c r="R152" s="6" t="n">
         <v>98.89405600000001</v>
@@ -12364,7 +12364,7 @@
       </c>
       <c r="P153" s="9" t="n"/>
       <c r="Q153" s="9" t="n">
-        <v>101.992398</v>
+        <v>101.995538</v>
       </c>
       <c r="R153" s="9" t="n">
         <v>98.84835200000001</v>
@@ -12446,7 +12446,7 @@
       </c>
       <c r="P154" s="6" t="n"/>
       <c r="Q154" s="6" t="n">
-        <v>101.675147</v>
+        <v>101.677787</v>
       </c>
       <c r="R154" s="6" t="n">
         <v>98.826466</v>
@@ -12528,7 +12528,7 @@
       </c>
       <c r="P155" s="9" t="n"/>
       <c r="Q155" s="9" t="n">
-        <v>101.262913</v>
+        <v>101.264903</v>
       </c>
       <c r="R155" s="9" t="n">
         <v>98.81174300000001</v>
@@ -12610,7 +12610,7 @@
       </c>
       <c r="P156" s="6" t="n"/>
       <c r="Q156" s="6" t="n">
-        <v>100.847214</v>
+        <v>100.84855</v>
       </c>
       <c r="R156" s="6" t="n">
         <v>98.789278</v>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="P157" s="9" t="n"/>
       <c r="Q157" s="9" t="n">
-        <v>100.499604</v>
+        <v>100.500391</v>
       </c>
       <c r="R157" s="9" t="n">
         <v>98.75291799999999</v>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="P158" s="6" t="n"/>
       <c r="Q158" s="6" t="n">
-        <v>100.280753</v>
+        <v>100.281196</v>
       </c>
       <c r="R158" s="6" t="n">
         <v>98.70359000000001</v>
@@ -12856,7 +12856,7 @@
       </c>
       <c r="P159" s="9" t="n"/>
       <c r="Q159" s="9" t="n">
-        <v>100.19402</v>
+        <v>100.194326</v>
       </c>
       <c r="R159" s="9" t="n">
         <v>98.640694</v>
@@ -12938,7 +12938,7 @@
       </c>
       <c r="P160" s="6" t="n"/>
       <c r="Q160" s="6" t="n">
-        <v>100.160968</v>
+        <v>100.161221</v>
       </c>
       <c r="R160" s="6" t="n">
         <v>98.558735</v>
@@ -13020,7 +13020,7 @@
       </c>
       <c r="P161" s="9" t="n"/>
       <c r="Q161" s="9" t="n">
-        <v>100.116181</v>
+        <v>100.116365</v>
       </c>
       <c r="R161" s="9" t="n">
         <v>98.461055</v>
@@ -13102,7 +13102,7 @@
       </c>
       <c r="P162" s="6" t="n"/>
       <c r="Q162" s="6" t="n">
-        <v>100.037123</v>
+        <v>100.037181</v>
       </c>
       <c r="R162" s="6" t="n">
         <v>98.35937300000001</v>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="P163" s="9" t="n"/>
       <c r="Q163" s="9" t="n">
-        <v>99.947254</v>
+        <v>99.947171</v>
       </c>
       <c r="R163" s="9" t="n">
         <v>98.264456</v>
@@ -13266,7 +13266,7 @@
       </c>
       <c r="P164" s="6" t="n"/>
       <c r="Q164" s="6" t="n">
-        <v>99.876104</v>
+        <v>99.87590899999999</v>
       </c>
       <c r="R164" s="6" t="n">
         <v>98.181434</v>
@@ -13348,7 +13348,7 @@
       </c>
       <c r="P165" s="9" t="n"/>
       <c r="Q165" s="9" t="n">
-        <v>99.820386</v>
+        <v>99.820103</v>
       </c>
       <c r="R165" s="9" t="n">
         <v>98.10794199999999</v>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="P166" s="6" t="n"/>
       <c r="Q166" s="6" t="n">
-        <v>99.813419</v>
+        <v>99.813124</v>
       </c>
       <c r="R166" s="6" t="n">
         <v>98.04061799999999</v>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="P167" s="9" t="n"/>
       <c r="Q167" s="9" t="n">
-        <v>99.888167</v>
+        <v>99.887991</v>
       </c>
       <c r="R167" s="9" t="n">
         <v>97.97162899999999</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="P168" s="6" t="n"/>
       <c r="Q168" s="6" t="n">
-        <v>100.05306</v>
+        <v>100.053144</v>
       </c>
       <c r="R168" s="6" t="n">
         <v>97.898585</v>
@@ -13676,7 +13676,7 @@
       </c>
       <c r="P169" s="9" t="n"/>
       <c r="Q169" s="9" t="n">
-        <v>100.297998</v>
+        <v>100.298468</v>
       </c>
       <c r="R169" s="9" t="n">
         <v>97.822744</v>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="P170" s="6" t="n"/>
       <c r="Q170" s="6" t="n">
-        <v>100.606832</v>
+        <v>100.607789</v>
       </c>
       <c r="R170" s="6" t="n">
         <v>97.74899600000001</v>
@@ -13840,7 +13840,7 @@
       </c>
       <c r="P171" s="9" t="n"/>
       <c r="Q171" s="9" t="n">
-        <v>100.972717</v>
+        <v>100.97425</v>
       </c>
       <c r="R171" s="9" t="n">
         <v>97.68316</v>
@@ -13922,7 +13922,7 @@
       </c>
       <c r="P172" s="6" t="n"/>
       <c r="Q172" s="6" t="n">
-        <v>101.350055</v>
+        <v>101.352183</v>
       </c>
       <c r="R172" s="6" t="n">
         <v>97.629305</v>
@@ -14004,7 +14004,7 @@
       </c>
       <c r="P173" s="9" t="n"/>
       <c r="Q173" s="9" t="n">
-        <v>101.672592</v>
+        <v>101.675228</v>
       </c>
       <c r="R173" s="9" t="n">
         <v>97.592961</v>
@@ -14086,7 +14086,7 @@
       </c>
       <c r="P174" s="6" t="n"/>
       <c r="Q174" s="6" t="n">
-        <v>101.870391</v>
+        <v>101.873339</v>
       </c>
       <c r="R174" s="6" t="n">
         <v>97.594255</v>
@@ -14168,7 +14168,7 @@
       </c>
       <c r="P175" s="9" t="n"/>
       <c r="Q175" s="9" t="n">
-        <v>101.925971</v>
+        <v>101.929007</v>
       </c>
       <c r="R175" s="9" t="n">
         <v>97.641627</v>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="P176" s="6" t="n"/>
       <c r="Q176" s="6" t="n">
-        <v>101.889104</v>
+        <v>101.892081</v>
       </c>
       <c r="R176" s="6" t="n">
         <v>97.722865</v>
@@ -14332,7 +14332,7 @@
       </c>
       <c r="P177" s="9" t="n"/>
       <c r="Q177" s="9" t="n">
-        <v>101.828994</v>
+        <v>101.831877</v>
       </c>
       <c r="R177" s="9" t="n">
         <v>97.798485</v>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="P178" s="6" t="n"/>
       <c r="Q178" s="6" t="n">
-        <v>101.794939</v>
+        <v>101.797768</v>
       </c>
       <c r="R178" s="6" t="n">
         <v>97.85409799999999</v>
@@ -14496,7 +14496,7 @@
       </c>
       <c r="P179" s="9" t="n"/>
       <c r="Q179" s="9" t="n">
-        <v>101.790064</v>
+        <v>101.792885</v>
       </c>
       <c r="R179" s="9" t="n">
         <v>97.911231</v>
@@ -14578,7 +14578,7 @@
       </c>
       <c r="P180" s="6" t="n"/>
       <c r="Q180" s="6" t="n">
-        <v>101.81229</v>
+        <v>101.815146</v>
       </c>
       <c r="R180" s="6" t="n">
         <v>98.00146100000001</v>
@@ -14660,7 +14660,7 @@
       </c>
       <c r="P181" s="9" t="n"/>
       <c r="Q181" s="9" t="n">
-        <v>101.801166</v>
+        <v>101.804005</v>
       </c>
       <c r="R181" s="9" t="n">
         <v>98.173715</v>
@@ -14742,7 +14742,7 @@
       </c>
       <c r="P182" s="6" t="n"/>
       <c r="Q182" s="6" t="n">
-        <v>101.678244</v>
+        <v>101.680889</v>
       </c>
       <c r="R182" s="6" t="n">
         <v>98.495824</v>
@@ -14824,7 +14824,7 @@
       </c>
       <c r="P183" s="9" t="n"/>
       <c r="Q183" s="9" t="n">
-        <v>101.394531</v>
+        <v>101.396729</v>
       </c>
       <c r="R183" s="9" t="n">
         <v>99.03205199999999</v>
@@ -14906,7 +14906,7 @@
       </c>
       <c r="P184" s="6" t="n"/>
       <c r="Q184" s="6" t="n">
-        <v>100.943646</v>
+        <v>100.945133</v>
       </c>
       <c r="R184" s="6" t="n">
         <v>99.817069</v>
@@ -14988,7 +14988,7 @@
       </c>
       <c r="P185" s="9" t="n"/>
       <c r="Q185" s="9" t="n">
-        <v>100.34007</v>
+        <v>100.340606</v>
       </c>
       <c r="R185" s="9" t="n">
         <v>100.814493</v>
@@ -15070,7 +15070,7 @@
       </c>
       <c r="P186" s="6" t="n"/>
       <c r="Q186" s="6" t="n">
-        <v>99.65680399999999</v>
+        <v>99.656263</v>
       </c>
       <c r="R186" s="6" t="n">
         <v>101.8613</v>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="P187" s="9" t="n"/>
       <c r="Q187" s="9" t="n">
-        <v>99.017819</v>
+        <v>99.016271</v>
       </c>
       <c r="R187" s="9" t="n">
         <v>102.73503</v>
@@ -15234,7 +15234,7 @@
       </c>
       <c r="P188" s="6" t="n"/>
       <c r="Q188" s="6" t="n">
-        <v>98.56031</v>
+        <v>98.558041</v>
       </c>
       <c r="R188" s="6" t="n">
         <v>103.270128</v>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="P189" s="9" t="n"/>
       <c r="Q189" s="9" t="n">
-        <v>98.29816099999999</v>
+        <v>98.295478</v>
       </c>
       <c r="R189" s="9" t="n">
         <v>103.441168</v>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="P190" s="6" t="n"/>
       <c r="Q190" s="6" t="n">
-        <v>98.214389</v>
+        <v>98.211574</v>
       </c>
       <c r="R190" s="6" t="n">
         <v>103.352978</v>
@@ -15480,7 +15480,7 @@
       </c>
       <c r="P191" s="9" t="n"/>
       <c r="Q191" s="9" t="n">
-        <v>98.27572600000001</v>
+        <v>98.273008</v>
       </c>
       <c r="R191" s="9" t="n">
         <v>103.164471</v>
@@ -15562,7 +15562,7 @@
       </c>
       <c r="P192" s="6" t="n"/>
       <c r="Q192" s="6" t="n">
-        <v>98.41340099999999</v>
+        <v>98.4109</v>
       </c>
       <c r="R192" s="6" t="n">
         <v>102.983103</v>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="P193" s="9" t="n"/>
       <c r="Q193" s="9" t="n">
-        <v>98.56780500000001</v>
+        <v>98.56554800000001</v>
       </c>
       <c r="R193" s="9" t="n">
         <v>102.890902</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="P194" s="6" t="n"/>
       <c r="Q194" s="6" t="n">
-        <v>98.710729</v>
+        <v>98.708696</v>
       </c>
       <c r="R194" s="6" t="n">
         <v>102.916397</v>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P195" s="9" t="n"/>
       <c r="Q195" s="9" t="n">
-        <v>98.85756000000001</v>
+        <v>98.85575900000001</v>
       </c>
       <c r="R195" s="9" t="n">
         <v>103.031675</v>
@@ -15890,7 +15890,7 @@
       </c>
       <c r="P196" s="6" t="n"/>
       <c r="Q196" s="6" t="n">
-        <v>99.020126</v>
+        <v>99.01858199999999</v>
       </c>
       <c r="R196" s="6" t="n">
         <v>103.147506</v>
@@ -15972,7 +15972,7 @@
       </c>
       <c r="P197" s="9" t="n"/>
       <c r="Q197" s="9" t="n">
-        <v>99.16596199999999</v>
+        <v>99.164647</v>
       </c>
       <c r="R197" s="9" t="n">
         <v>103.151519</v>
@@ -16054,7 +16054,7 @@
       </c>
       <c r="P198" s="6" t="n"/>
       <c r="Q198" s="6" t="n">
-        <v>99.277894</v>
+        <v>99.27675600000001</v>
       </c>
       <c r="R198" s="6" t="n">
         <v>103.024948</v>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="P199" s="9" t="n"/>
       <c r="Q199" s="9" t="n">
-        <v>99.34527199999999</v>
+        <v>99.34424</v>
       </c>
       <c r="R199" s="9" t="n">
         <v>102.803113</v>
@@ -16218,7 +16218,7 @@
       </c>
       <c r="P200" s="6" t="n"/>
       <c r="Q200" s="6" t="n">
-        <v>99.38553899999999</v>
+        <v>99.38457099999999</v>
       </c>
       <c r="R200" s="6" t="n">
         <v>102.524982</v>
@@ -16300,7 +16300,7 @@
       </c>
       <c r="P201" s="9" t="n"/>
       <c r="Q201" s="9" t="n">
-        <v>99.391657</v>
+        <v>99.390698</v>
       </c>
       <c r="R201" s="9" t="n">
         <v>102.225146</v>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="P202" s="6" t="n"/>
       <c r="Q202" s="6" t="n">
-        <v>99.362435</v>
+        <v>99.36143</v>
       </c>
       <c r="R202" s="6" t="n">
         <v>101.943742</v>
@@ -16464,7 +16464,7 @@
       </c>
       <c r="P203" s="9" t="n"/>
       <c r="Q203" s="9" t="n">
-        <v>99.308171</v>
+        <v>99.307081</v>
       </c>
       <c r="R203" s="9" t="n">
         <v>101.70314</v>
@@ -16546,7 +16546,7 @@
       </c>
       <c r="P204" s="6" t="n"/>
       <c r="Q204" s="6" t="n">
-        <v>99.24763299999999</v>
+        <v>99.246447</v>
       </c>
       <c r="R204" s="6" t="n">
         <v>101.502802</v>
@@ -16628,7 +16628,7 @@
       </c>
       <c r="P205" s="9" t="n"/>
       <c r="Q205" s="9" t="n">
-        <v>99.205702</v>
+        <v>99.20444999999999</v>
       </c>
       <c r="R205" s="9" t="n">
         <v>101.335259</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="P206" s="6" t="n"/>
       <c r="Q206" s="6" t="n">
-        <v>99.176698</v>
+        <v>99.17540099999999</v>
       </c>
       <c r="R206" s="6" t="n">
         <v>101.198348</v>
@@ -16792,7 +16792,7 @@
       </c>
       <c r="P207" s="9" t="n"/>
       <c r="Q207" s="9" t="n">
-        <v>99.172353</v>
+        <v>99.171048</v>
       </c>
       <c r="R207" s="9" t="n">
         <v>101.077062</v>
@@ -16874,7 +16874,7 @@
       </c>
       <c r="P208" s="6" t="n"/>
       <c r="Q208" s="6" t="n">
-        <v>99.205634</v>
+        <v>99.204382</v>
       </c>
       <c r="R208" s="6" t="n">
         <v>100.943835</v>
@@ -16956,7 +16956,7 @@
       </c>
       <c r="P209" s="9" t="n"/>
       <c r="Q209" s="9" t="n">
-        <v>99.28213700000001</v>
+        <v>99.28100499999999</v>
       </c>
       <c r="R209" s="9" t="n">
         <v>100.777999</v>
@@ -17038,7 +17038,7 @@
       </c>
       <c r="P210" s="6" t="n"/>
       <c r="Q210" s="6" t="n">
-        <v>99.404049</v>
+        <v>99.403109</v>
       </c>
       <c r="R210" s="6" t="n">
         <v>100.595372</v>
@@ -17120,7 +17120,7 @@
       </c>
       <c r="P211" s="9" t="n"/>
       <c r="Q211" s="9" t="n">
-        <v>99.56046000000001</v>
+        <v>99.55976699999999</v>
       </c>
       <c r="R211" s="9" t="n">
         <v>100.418429</v>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="P212" s="6" t="n"/>
       <c r="Q212" s="6" t="n">
-        <v>99.750196</v>
+        <v>99.749802</v>
       </c>
       <c r="R212" s="6" t="n">
         <v>100.258383</v>
@@ -17284,7 +17284,7 @@
       </c>
       <c r="P213" s="9" t="n"/>
       <c r="Q213" s="9" t="n">
-        <v>99.990835</v>
+        <v>99.990821</v>
       </c>
       <c r="R213" s="9" t="n">
         <v>100.10798</v>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="P214" s="6" t="n"/>
       <c r="Q214" s="6" t="n">
-        <v>100.286883</v>
+        <v>100.287335</v>
       </c>
       <c r="R214" s="6" t="n">
         <v>99.96771099999999</v>
@@ -17448,7 +17448,7 @@
       </c>
       <c r="P215" s="9" t="n"/>
       <c r="Q215" s="9" t="n">
-        <v>100.609463</v>
+        <v>100.610424</v>
       </c>
       <c r="R215" s="9" t="n">
         <v>99.838172</v>
@@ -17530,7 +17530,7 @@
       </c>
       <c r="P216" s="6" t="n"/>
       <c r="Q216" s="6" t="n">
-        <v>100.901033</v>
+        <v>100.902453</v>
       </c>
       <c r="R216" s="6" t="n">
         <v>99.72147</v>
@@ -17612,7 +17612,7 @@
       </c>
       <c r="P217" s="9" t="n"/>
       <c r="Q217" s="9" t="n">
-        <v>101.111051</v>
+        <v>101.112802</v>
       </c>
       <c r="R217" s="9" t="n">
         <v>99.62966299999999</v>
@@ -17694,7 +17694,7 @@
       </c>
       <c r="P218" s="6" t="n"/>
       <c r="Q218" s="6" t="n">
-        <v>101.240335</v>
+        <v>101.24229</v>
       </c>
       <c r="R218" s="6" t="n">
         <v>99.57756999999999</v>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="P219" s="9" t="n"/>
       <c r="Q219" s="9" t="n">
-        <v>101.276574</v>
+        <v>101.278586</v>
       </c>
       <c r="R219" s="9" t="n">
         <v>99.56864400000001</v>
@@ -17858,7 +17858,7 @@
       </c>
       <c r="P220" s="6" t="n"/>
       <c r="Q220" s="6" t="n">
-        <v>101.252101</v>
+        <v>101.254075</v>
       </c>
       <c r="R220" s="6" t="n">
         <v>99.589437</v>
@@ -17940,7 +17940,7 @@
       </c>
       <c r="P221" s="9" t="n"/>
       <c r="Q221" s="9" t="n">
-        <v>101.166176</v>
+        <v>101.168014</v>
       </c>
       <c r="R221" s="9" t="n">
         <v>99.611009</v>
@@ -18022,7 +18022,7 @@
       </c>
       <c r="P222" s="6" t="n"/>
       <c r="Q222" s="6" t="n">
-        <v>101.018499</v>
+        <v>101.020104</v>
       </c>
       <c r="R222" s="6" t="n">
         <v>99.644571</v>
@@ -18104,7 +18104,7 @@
       </c>
       <c r="P223" s="9" t="n"/>
       <c r="Q223" s="9" t="n">
-        <v>100.836014</v>
+        <v>100.837332</v>
       </c>
       <c r="R223" s="9" t="n">
         <v>99.704275</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="P224" s="6" t="n"/>
       <c r="Q224" s="6" t="n">
-        <v>100.601341</v>
+        <v>100.602289</v>
       </c>
       <c r="R224" s="6" t="n">
         <v>99.79154200000001</v>
@@ -18268,7 +18268,7 @@
       </c>
       <c r="P225" s="9" t="n"/>
       <c r="Q225" s="9" t="n">
-        <v>100.282516</v>
+        <v>100.282961</v>
       </c>
       <c r="R225" s="9" t="n">
         <v>99.918818</v>
@@ -18350,7 +18350,7 @@
       </c>
       <c r="P226" s="6" t="n"/>
       <c r="Q226" s="6" t="n">
-        <v>99.870193</v>
+        <v>99.869989</v>
       </c>
       <c r="R226" s="6" t="n">
         <v>100.105488</v>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P227" s="9" t="n"/>
       <c r="Q227" s="9" t="n">
-        <v>99.405529</v>
+        <v>99.40459199999999</v>
       </c>
       <c r="R227" s="9" t="n">
         <v>100.354335</v>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="P228" s="6" t="n"/>
       <c r="Q228" s="6" t="n">
-        <v>98.943639</v>
+        <v>98.941974</v>
       </c>
       <c r="R228" s="6" t="n">
         <v>100.642772</v>
@@ -18596,7 +18596,7 @@
       </c>
       <c r="P229" s="9" t="n"/>
       <c r="Q229" s="9" t="n">
-        <v>98.551868</v>
+        <v>98.54958499999999</v>
       </c>
       <c r="R229" s="9" t="n">
         <v>100.940268</v>
@@ -18678,7 +18678,7 @@
       </c>
       <c r="P230" s="6" t="n"/>
       <c r="Q230" s="6" t="n">
-        <v>98.334239</v>
+        <v>98.331613</v>
       </c>
       <c r="R230" s="6" t="n">
         <v>101.182746</v>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="P231" s="9" t="n"/>
       <c r="Q231" s="9" t="n">
-        <v>98.268714</v>
+        <v>98.265986</v>
       </c>
       <c r="R231" s="9" t="n">
         <v>101.290946</v>
@@ -18842,7 +18842,7 @@
       </c>
       <c r="P232" s="6" t="n"/>
       <c r="Q232" s="6" t="n">
-        <v>98.309544</v>
+        <v>98.30688000000001</v>
       </c>
       <c r="R232" s="6" t="n">
         <v>101.25276</v>
@@ -18924,7 +18924,7 @@
       </c>
       <c r="P233" s="9" t="n"/>
       <c r="Q233" s="9" t="n">
-        <v>98.455951</v>
+        <v>98.45351700000001</v>
       </c>
       <c r="R233" s="9" t="n">
         <v>101.098551</v>
@@ -19006,7 +19006,7 @@
       </c>
       <c r="P234" s="6" t="n"/>
       <c r="Q234" s="6" t="n">
-        <v>98.69913</v>
+        <v>98.69708</v>
       </c>
       <c r="R234" s="6" t="n">
         <v>100.868658</v>
@@ -19088,7 +19088,7 @@
       </c>
       <c r="P235" s="9" t="n"/>
       <c r="Q235" s="9" t="n">
-        <v>99.025865</v>
+        <v>99.02433000000001</v>
       </c>
       <c r="R235" s="9" t="n">
         <v>100.591129</v>
@@ -19170,7 +19170,7 @@
       </c>
       <c r="P236" s="6" t="n"/>
       <c r="Q236" s="6" t="n">
-        <v>99.388211</v>
+        <v>99.387246</v>
       </c>
       <c r="R236" s="6" t="n">
         <v>100.299435</v>
@@ -19252,7 +19252,7 @@
       </c>
       <c r="P237" s="9" t="n"/>
       <c r="Q237" s="9" t="n">
-        <v>99.71289899999999</v>
+        <v>99.712446</v>
       </c>
       <c r="R237" s="9" t="n">
         <v>100.031519</v>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="P238" s="6" t="n"/>
       <c r="Q238" s="6" t="n">
-        <v>99.948865</v>
+        <v>99.948785</v>
       </c>
       <c r="R238" s="6" t="n">
         <v>99.81901499999999</v>
@@ -19416,7 +19416,7 @@
       </c>
       <c r="P239" s="9" t="n"/>
       <c r="Q239" s="9" t="n">
-        <v>100.089535</v>
+        <v>100.089676</v>
       </c>
       <c r="R239" s="9" t="n">
         <v>99.669139</v>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="P240" s="6" t="n"/>
       <c r="Q240" s="6" t="n">
-        <v>100.15925</v>
+        <v>100.159501</v>
       </c>
       <c r="R240" s="6" t="n">
         <v>99.56666300000001</v>
@@ -19580,7 +19580,7 @@
       </c>
       <c r="P241" s="9" t="n"/>
       <c r="Q241" s="9" t="n">
-        <v>100.233221</v>
+        <v>100.233589</v>
       </c>
       <c r="R241" s="9" t="n">
         <v>99.50362</v>
@@ -19662,7 +19662,7 @@
       </c>
       <c r="P242" s="6" t="n"/>
       <c r="Q242" s="6" t="n">
-        <v>100.374365</v>
+        <v>100.374955</v>
       </c>
       <c r="R242" s="6" t="n">
         <v>99.464894</v>
@@ -19744,7 +19744,7 @@
       </c>
       <c r="P243" s="9" t="n"/>
       <c r="Q243" s="9" t="n">
-        <v>100.607233</v>
+        <v>100.60819</v>
       </c>
       <c r="R243" s="9" t="n">
         <v>99.437659</v>
@@ -19826,7 +19826,7 @@
       </c>
       <c r="P244" s="6" t="n"/>
       <c r="Q244" s="6" t="n">
-        <v>100.898981</v>
+        <v>100.900397</v>
       </c>
       <c r="R244" s="6" t="n">
         <v>99.405107</v>
@@ -19908,7 +19908,7 @@
       </c>
       <c r="P245" s="9" t="n"/>
       <c r="Q245" s="9" t="n">
-        <v>101.17997</v>
+        <v>101.18183</v>
       </c>
       <c r="R245" s="9" t="n">
         <v>99.371922</v>
@@ -19990,7 +19990,7 @@
       </c>
       <c r="P246" s="6" t="n"/>
       <c r="Q246" s="6" t="n">
-        <v>101.381345</v>
+        <v>101.383522</v>
       </c>
       <c r="R246" s="6" t="n">
         <v>99.346295</v>
@@ -20072,7 +20072,7 @@
       </c>
       <c r="P247" s="9" t="n"/>
       <c r="Q247" s="9" t="n">
-        <v>101.489514</v>
+        <v>101.491861</v>
       </c>
       <c r="R247" s="9" t="n">
         <v>99.33412</v>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="P248" s="6" t="n"/>
       <c r="Q248" s="6" t="n">
-        <v>101.481945</v>
+        <v>101.484281</v>
       </c>
       <c r="R248" s="6" t="n">
         <v>99.34107299999999</v>
@@ -20236,7 +20236,7 @@
       </c>
       <c r="P249" s="9" t="n"/>
       <c r="Q249" s="9" t="n">
-        <v>101.374379</v>
+        <v>101.376545</v>
       </c>
       <c r="R249" s="9" t="n">
         <v>99.36963299999999</v>
@@ -20318,7 +20318,7 @@
       </c>
       <c r="P250" s="6" t="n"/>
       <c r="Q250" s="6" t="n">
-        <v>101.225578</v>
+        <v>101.227509</v>
       </c>
       <c r="R250" s="6" t="n">
         <v>99.406792</v>
@@ -20400,7 +20400,7 @@
       </c>
       <c r="P251" s="9" t="n"/>
       <c r="Q251" s="9" t="n">
-        <v>101.078493</v>
+        <v>101.080193</v>
       </c>
       <c r="R251" s="9" t="n">
         <v>99.429805</v>
@@ -20482,7 +20482,7 @@
       </c>
       <c r="P252" s="6" t="n"/>
       <c r="Q252" s="6" t="n">
-        <v>100.91077</v>
+        <v>100.912205</v>
       </c>
       <c r="R252" s="6" t="n">
         <v>99.42</v>
@@ -20564,7 +20564,7 @@
       </c>
       <c r="P253" s="9" t="n"/>
       <c r="Q253" s="9" t="n">
-        <v>100.723372</v>
+        <v>100.724512</v>
       </c>
       <c r="R253" s="9" t="n">
         <v>99.398949</v>
@@ -20646,7 +20646,7 @@
       </c>
       <c r="P254" s="6" t="n"/>
       <c r="Q254" s="6" t="n">
-        <v>100.515382</v>
+        <v>100.516194</v>
       </c>
       <c r="R254" s="6" t="n">
         <v>99.390896</v>
@@ -20728,7 +20728,7 @@
       </c>
       <c r="P255" s="9" t="n"/>
       <c r="Q255" s="9" t="n">
-        <v>100.30593</v>
+        <v>100.306412</v>
       </c>
       <c r="R255" s="9" t="n">
         <v>99.398794</v>
@@ -20810,7 +20810,7 @@
       </c>
       <c r="P256" s="6" t="n"/>
       <c r="Q256" s="6" t="n">
-        <v>100.117188</v>
+        <v>100.117372</v>
       </c>
       <c r="R256" s="6" t="n">
         <v>99.411525</v>
@@ -20892,7 +20892,7 @@
       </c>
       <c r="P257" s="9" t="n"/>
       <c r="Q257" s="9" t="n">
-        <v>99.98974</v>
+        <v>99.989724</v>
       </c>
       <c r="R257" s="9" t="n">
         <v>99.423292</v>
@@ -20974,7 +20974,7 @@
       </c>
       <c r="P258" s="6" t="n"/>
       <c r="Q258" s="6" t="n">
-        <v>99.924623</v>
+        <v>99.924504</v>
       </c>
       <c r="R258" s="6" t="n">
         <v>99.426435</v>
@@ -21056,7 +21056,7 @@
       </c>
       <c r="P259" s="9" t="n"/>
       <c r="Q259" s="9" t="n">
-        <v>99.885426</v>
+        <v>99.885246</v>
       </c>
       <c r="R259" s="9" t="n">
         <v>99.391091</v>
@@ -21138,7 +21138,7 @@
       </c>
       <c r="P260" s="6" t="n"/>
       <c r="Q260" s="6" t="n">
-        <v>99.873029</v>
+        <v>99.872829</v>
       </c>
       <c r="R260" s="6" t="n">
         <v>99.307951</v>
@@ -21220,7 +21220,7 @@
       </c>
       <c r="P261" s="9" t="n"/>
       <c r="Q261" s="9" t="n">
-        <v>99.88760600000001</v>
+        <v>99.887429</v>
       </c>
       <c r="R261" s="9" t="n">
         <v>99.19095</v>
@@ -21302,7 +21302,7 @@
       </c>
       <c r="P262" s="6" t="n"/>
       <c r="Q262" s="6" t="n">
-        <v>99.896862</v>
+        <v>99.896699</v>
       </c>
       <c r="R262" s="6" t="n">
         <v>99.07110299999999</v>
@@ -21384,7 +21384,7 @@
       </c>
       <c r="P263" s="9" t="n"/>
       <c r="Q263" s="9" t="n">
-        <v>99.85414299999999</v>
+        <v>99.85391300000001</v>
       </c>
       <c r="R263" s="9" t="n">
         <v>98.972967</v>
@@ -21466,7 +21466,7 @@
       </c>
       <c r="P264" s="6" t="n"/>
       <c r="Q264" s="6" t="n">
-        <v>99.74625899999999</v>
+        <v>99.745859</v>
       </c>
       <c r="R264" s="6" t="n">
         <v>98.90224499999999</v>
@@ -21548,7 +21548,7 @@
       </c>
       <c r="P265" s="9" t="n"/>
       <c r="Q265" s="9" t="n">
-        <v>99.598876</v>
+        <v>99.59824399999999</v>
       </c>
       <c r="R265" s="9" t="n">
         <v>98.84800799999999</v>
@@ -21630,7 +21630,7 @@
       </c>
       <c r="P266" s="6" t="n"/>
       <c r="Q266" s="6" t="n">
-        <v>99.467776</v>
+        <v>99.466937</v>
       </c>
       <c r="R266" s="6" t="n">
         <v>98.796525</v>
@@ -21712,7 +21712,7 @@
       </c>
       <c r="P267" s="9" t="n"/>
       <c r="Q267" s="9" t="n">
-        <v>99.43015699999999</v>
+        <v>99.429259</v>
       </c>
       <c r="R267" s="9" t="n">
         <v>98.726811</v>
@@ -21794,7 +21794,7 @@
       </c>
       <c r="P268" s="6" t="n"/>
       <c r="Q268" s="6" t="n">
-        <v>99.50358199999999</v>
+        <v>99.50279999999999</v>
       </c>
       <c r="R268" s="6" t="n">
         <v>98.64193400000001</v>
@@ -21876,7 +21876,7 @@
       </c>
       <c r="P269" s="9" t="n"/>
       <c r="Q269" s="9" t="n">
-        <v>99.65648899999999</v>
+        <v>99.655947</v>
       </c>
       <c r="R269" s="9" t="n">
         <v>98.564362</v>
@@ -21958,7 +21958,7 @@
       </c>
       <c r="P270" s="6" t="n"/>
       <c r="Q270" s="6" t="n">
-        <v>99.82568999999999</v>
+        <v>99.825416</v>
       </c>
       <c r="R270" s="6" t="n">
         <v>98.518818</v>
@@ -22040,7 +22040,7 @@
       </c>
       <c r="P271" s="9" t="n"/>
       <c r="Q271" s="9" t="n">
-        <v>99.94869300000001</v>
+        <v>99.94861299999999</v>
       </c>
       <c r="R271" s="9" t="n">
         <v>98.52582700000001</v>
@@ -22122,7 +22122,7 @@
       </c>
       <c r="P272" s="6" t="n"/>
       <c r="Q272" s="6" t="n">
-        <v>99.98787799999999</v>
+        <v>99.987859</v>
       </c>
       <c r="R272" s="6" t="n">
         <v>98.59760199999999</v>
@@ -22204,7 +22204,7 @@
       </c>
       <c r="P273" s="9" t="n"/>
       <c r="Q273" s="9" t="n">
-        <v>99.90327499999999</v>
+        <v>99.90312299999999</v>
       </c>
       <c r="R273" s="9" t="n">
         <v>98.73663000000001</v>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="P274" s="6" t="n"/>
       <c r="Q274" s="6" t="n">
-        <v>99.690776</v>
+        <v>99.69028900000001</v>
       </c>
       <c r="R274" s="6" t="n">
         <v>98.928083</v>
@@ -22368,7 +22368,7 @@
       </c>
       <c r="P275" s="9" t="n"/>
       <c r="Q275" s="9" t="n">
-        <v>99.38981</v>
+        <v>99.38884899999999</v>
       </c>
       <c r="R275" s="9" t="n">
         <v>99.13712599999999</v>
@@ -22450,7 +22450,7 @@
       </c>
       <c r="P276" s="6" t="n"/>
       <c r="Q276" s="6" t="n">
-        <v>99.06020100000001</v>
+        <v>99.058719</v>
       </c>
       <c r="R276" s="6" t="n">
         <v>99.337366</v>
@@ -22532,7 +22532,7 @@
       </c>
       <c r="P277" s="9" t="n"/>
       <c r="Q277" s="9" t="n">
-        <v>98.751482</v>
+        <v>98.749514</v>
       </c>
       <c r="R277" s="9" t="n">
         <v>99.52105400000001</v>
@@ -22614,7 +22614,7 @@
       </c>
       <c r="P278" s="6" t="n"/>
       <c r="Q278" s="6" t="n">
-        <v>98.48273399999999</v>
+        <v>98.480343</v>
       </c>
       <c r="R278" s="6" t="n">
         <v>99.68986700000001</v>
@@ -22696,7 +22696,7 @@
       </c>
       <c r="P279" s="9" t="n"/>
       <c r="Q279" s="9" t="n">
-        <v>98.274755</v>
+        <v>98.272036</v>
       </c>
       <c r="R279" s="9" t="n">
         <v>99.84424300000001</v>
@@ -22778,7 +22778,7 @@
       </c>
       <c r="P280" s="6" t="n"/>
       <c r="Q280" s="6" t="n">
-        <v>98.11730799999999</v>
+        <v>98.114341</v>
       </c>
       <c r="R280" s="6" t="n">
         <v>99.99128899999999</v>
@@ -22860,7 +22860,7 @@
       </c>
       <c r="P281" s="9" t="n"/>
       <c r="Q281" s="9" t="n">
-        <v>97.998132</v>
+        <v>97.99497700000001</v>
       </c>
       <c r="R281" s="9" t="n">
         <v>100.136879</v>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="P282" s="6" t="n"/>
       <c r="Q282" s="6" t="n">
-        <v>97.920934</v>
+        <v>97.91765700000001</v>
       </c>
       <c r="R282" s="6" t="n">
         <v>100.27743</v>
@@ -23024,7 +23024,7 @@
       </c>
       <c r="P283" s="9" t="n"/>
       <c r="Q283" s="9" t="n">
-        <v>97.90312299999999</v>
+        <v>97.899818</v>
       </c>
       <c r="R283" s="9" t="n">
         <v>100.380908</v>
@@ -23106,7 +23106,7 @@
       </c>
       <c r="P284" s="6" t="n"/>
       <c r="Q284" s="6" t="n">
-        <v>97.95777</v>
+        <v>97.95455200000001</v>
       </c>
       <c r="R284" s="6" t="n">
         <v>100.41847</v>
@@ -23188,7 +23188,7 @@
       </c>
       <c r="P285" s="9" t="n"/>
       <c r="Q285" s="9" t="n">
-        <v>98.084552</v>
+        <v>98.08153299999999</v>
       </c>
       <c r="R285" s="9" t="n">
         <v>100.399436</v>
@@ -23270,7 +23270,7 @@
       </c>
       <c r="P286" s="6" t="n"/>
       <c r="Q286" s="6" t="n">
-        <v>98.254642</v>
+        <v>98.251891</v>
       </c>
       <c r="R286" s="6" t="n">
         <v>100.369852</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="P287" s="9" t="n"/>
       <c r="Q287" s="9" t="n">
-        <v>98.445086</v>
+        <v>98.442635</v>
       </c>
       <c r="R287" s="9" t="n">
         <v>100.375279</v>
@@ -23434,7 +23434,7 @@
       </c>
       <c r="P288" s="6" t="n"/>
       <c r="Q288" s="6" t="n">
-        <v>98.636504</v>
+        <v>98.634355</v>
       </c>
       <c r="R288" s="6" t="n">
         <v>100.422034</v>
@@ -23516,7 +23516,7 @@
       </c>
       <c r="P289" s="9" t="n"/>
       <c r="Q289" s="9" t="n">
-        <v>98.81926799999999</v>
+        <v>98.817407</v>
       </c>
       <c r="R289" s="9" t="n">
         <v>100.503759</v>
@@ -23598,7 +23598,7 @@
       </c>
       <c r="P290" s="6" t="n"/>
       <c r="Q290" s="6" t="n">
-        <v>98.993661</v>
+        <v>98.992075</v>
       </c>
       <c r="R290" s="6" t="n">
         <v>100.590902</v>
@@ -23680,7 +23680,7 @@
       </c>
       <c r="P291" s="9" t="n"/>
       <c r="Q291" s="9" t="n">
-        <v>99.164264</v>
+        <v>99.162947</v>
       </c>
       <c r="R291" s="9" t="n">
         <v>100.656472</v>
@@ -23762,7 +23762,7 @@
       </c>
       <c r="P292" s="6" t="n"/>
       <c r="Q292" s="6" t="n">
-        <v>99.332283</v>
+        <v>99.331231</v>
       </c>
       <c r="R292" s="6" t="n">
         <v>100.686141</v>
@@ -23844,7 +23844,7 @@
       </c>
       <c r="P293" s="9" t="n"/>
       <c r="Q293" s="9" t="n">
-        <v>99.48944400000001</v>
+        <v>99.48864</v>
       </c>
       <c r="R293" s="9" t="n">
         <v>100.693179</v>
@@ -23928,7 +23928,7 @@
         <v>98.540752</v>
       </c>
       <c r="Q294" s="6" t="n">
-        <v>99.62461500000001</v>
+        <v>99.62402400000001</v>
       </c>
       <c r="R294" s="6" t="n">
         <v>100.696753</v>
@@ -24012,7 +24012,7 @@
         <v>98.703875</v>
       </c>
       <c r="Q295" s="9" t="n">
-        <v>99.716482</v>
+        <v>99.71603500000001</v>
       </c>
       <c r="R295" s="9" t="n">
         <v>100.729609</v>
@@ -24096,7 +24096,7 @@
         <v>98.876873</v>
       </c>
       <c r="Q296" s="6" t="n">
-        <v>99.74894500000001</v>
+        <v>99.74854999999999</v>
       </c>
       <c r="R296" s="6" t="n">
         <v>100.801052</v>
@@ -24180,7 +24180,7 @@
         <v>99.06832300000001</v>
       </c>
       <c r="Q297" s="9" t="n">
-        <v>99.723411</v>
+        <v>99.722976</v>
       </c>
       <c r="R297" s="9" t="n">
         <v>100.901637</v>
@@ -24264,7 +24264,7 @@
         <v>99.247865</v>
       </c>
       <c r="Q298" s="6" t="n">
-        <v>99.672982</v>
+        <v>99.672467</v>
       </c>
       <c r="R298" s="6" t="n">
         <v>100.999136</v>
@@ -24348,7 +24348,7 @@
         <v>99.386276</v>
       </c>
       <c r="Q299" s="9" t="n">
-        <v>99.62456899999999</v>
+        <v>99.62397900000001</v>
       </c>
       <c r="R299" s="9" t="n">
         <v>101.058624</v>
@@ -24432,7 +24432,7 @@
         <v>99.484945</v>
       </c>
       <c r="Q300" s="6" t="n">
-        <v>99.599242</v>
+        <v>99.59861100000001</v>
       </c>
       <c r="R300" s="6" t="n">
         <v>101.070223</v>
@@ -24516,7 +24516,7 @@
         <v>99.551771</v>
       </c>
       <c r="Q301" s="9" t="n">
-        <v>99.61830500000001</v>
+        <v>99.617704</v>
       </c>
       <c r="R301" s="9" t="n">
         <v>101.03237</v>
@@ -24600,7 +24600,7 @@
         <v>99.60554</v>
       </c>
       <c r="Q302" s="6" t="n">
-        <v>99.685506</v>
+        <v>99.685011</v>
       </c>
       <c r="R302" s="6" t="n">
         <v>100.955224</v>
@@ -24684,7 +24684,7 @@
         <v>99.662926</v>
       </c>
       <c r="Q303" s="9" t="n">
-        <v>99.780474</v>
+        <v>99.780129</v>
       </c>
       <c r="R303" s="9" t="n">
         <v>100.847796</v>
@@ -24768,7 +24768,7 @@
         <v>99.722613</v>
       </c>
       <c r="Q304" s="6" t="n">
-        <v>99.87464799999999</v>
+        <v>99.87445099999999</v>
       </c>
       <c r="R304" s="6" t="n">
         <v>100.72448</v>
@@ -24852,7 +24852,7 @@
         <v>99.780147</v>
       </c>
       <c r="Q305" s="9" t="n">
-        <v>99.939751</v>
+        <v>99.939657</v>
       </c>
       <c r="R305" s="9" t="n">
         <v>100.600453</v>
@@ -24936,7 +24936,7 @@
         <v>99.83928299999999</v>
       </c>
       <c r="Q306" s="6" t="n">
-        <v>99.950898</v>
+        <v>99.950822</v>
       </c>
       <c r="R306" s="6" t="n">
         <v>100.491288</v>
@@ -25020,7 +25020,7 @@
         <v>99.90753599999999</v>
       </c>
       <c r="Q307" s="9" t="n">
-        <v>99.90570200000001</v>
+        <v>99.90555500000001</v>
       </c>
       <c r="R307" s="9" t="n">
         <v>100.395708</v>
@@ -25104,7 +25104,7 @@
         <v>99.982005</v>
       </c>
       <c r="Q308" s="6" t="n">
-        <v>99.82084</v>
+        <v>99.820559</v>
       </c>
       <c r="R308" s="6" t="n">
         <v>100.309547</v>
@@ -25188,7 +25188,7 @@
         <v>100.054023</v>
       </c>
       <c r="Q309" s="9" t="n">
-        <v>99.751019</v>
+        <v>99.75062800000001</v>
       </c>
       <c r="R309" s="9" t="n">
         <v>100.223831</v>
@@ -25272,7 +25272,7 @@
         <v>100.112333</v>
       </c>
       <c r="Q310" s="6" t="n">
-        <v>99.73772200000001</v>
+        <v>99.73730999999999</v>
       </c>
       <c r="R310" s="6" t="n">
         <v>100.132244</v>
@@ -25356,7 +25356,7 @@
         <v>100.157176</v>
       </c>
       <c r="Q311" s="9" t="n">
-        <v>99.787172</v>
+        <v>99.786838</v>
       </c>
       <c r="R311" s="9" t="n">
         <v>100.039561</v>
@@ -25440,7 +25440,7 @@
         <v>100.183393</v>
       </c>
       <c r="Q312" s="6" t="n">
-        <v>99.8897</v>
+        <v>99.889528</v>
       </c>
       <c r="R312" s="6" t="n">
         <v>99.955443</v>
@@ -25524,7 +25524,7 @@
         <v>100.203185</v>
       </c>
       <c r="Q313" s="9" t="n">
-        <v>100.027777</v>
+        <v>100.027822</v>
       </c>
       <c r="R313" s="9" t="n">
         <v>99.885206</v>
@@ -25608,7 +25608,7 @@
         <v>100.233539</v>
       </c>
       <c r="Q314" s="6" t="n">
-        <v>100.191965</v>
+        <v>100.192269</v>
       </c>
       <c r="R314" s="6" t="n">
         <v>99.820717</v>
@@ -25692,7 +25692,7 @@
         <v>100.273473</v>
       </c>
       <c r="Q315" s="9" t="n">
-        <v>100.354231</v>
+        <v>100.354791</v>
       </c>
       <c r="R315" s="9" t="n">
         <v>99.74682799999999</v>
@@ -25776,7 +25776,7 @@
         <v>100.319489</v>
       </c>
       <c r="Q316" s="6" t="n">
-        <v>100.510256</v>
+        <v>100.511062</v>
       </c>
       <c r="R316" s="6" t="n">
         <v>99.666473</v>
@@ -25860,7 +25860,7 @@
         <v>100.381873</v>
       </c>
       <c r="Q317" s="9" t="n">
-        <v>100.644593</v>
+        <v>100.645611</v>
       </c>
       <c r="R317" s="9" t="n">
         <v>99.61056000000001</v>
@@ -25944,7 +25944,7 @@
         <v>100.46471</v>
       </c>
       <c r="Q318" s="6" t="n">
-        <v>100.74103</v>
+        <v>100.742199</v>
       </c>
       <c r="R318" s="6" t="n">
         <v>99.61057</v>
@@ -26028,7 +26028,7 @@
         <v>100.575136</v>
       </c>
       <c r="Q319" s="9" t="n">
-        <v>100.790014</v>
+        <v>100.791261</v>
       </c>
       <c r="R319" s="9" t="n">
         <v>99.682152</v>
@@ -26112,7 +26112,7 @@
         <v>100.680562</v>
       </c>
       <c r="Q320" s="6" t="n">
-        <v>100.801222</v>
+        <v>100.802487</v>
       </c>
       <c r="R320" s="6" t="n">
         <v>99.82080000000001</v>
@@ -26196,7 +26196,7 @@
         <v>100.774705</v>
       </c>
       <c r="Q321" s="9" t="n">
-        <v>100.784107</v>
+        <v>100.785345</v>
       </c>
       <c r="R321" s="9" t="n">
         <v>99.987298</v>
@@ -26280,7 +26280,7 @@
         <v>100.863466</v>
       </c>
       <c r="Q322" s="6" t="n">
-        <v>100.753065</v>
+        <v>100.754254</v>
       </c>
       <c r="R322" s="6" t="n">
         <v>100.126705</v>
@@ -26364,7 +26364,7 @@
         <v>100.951543</v>
       </c>
       <c r="Q323" s="9" t="n">
-        <v>100.7555</v>
+        <v>100.756692</v>
       </c>
       <c r="R323" s="9" t="n">
         <v>100.19683</v>
@@ -26448,7 +26448,7 @@
         <v>101.056797</v>
       </c>
       <c r="Q324" s="6" t="n">
-        <v>100.813922</v>
+        <v>100.815207</v>
       </c>
       <c r="R324" s="6" t="n">
         <v>100.174171</v>
@@ -26532,7 +26532,7 @@
         <v>101.179752</v>
       </c>
       <c r="Q325" s="9" t="n">
-        <v>100.929726</v>
+        <v>100.931193</v>
       </c>
       <c r="R325" s="9" t="n">
         <v>100.081556</v>
@@ -26616,7 +26616,7 @@
         <v>101.292858</v>
       </c>
       <c r="Q326" s="6" t="n">
-        <v>101.094678</v>
+        <v>101.096405</v>
       </c>
       <c r="R326" s="6" t="n">
         <v>99.952275</v>
@@ -26700,7 +26700,7 @@
         <v>101.390583</v>
       </c>
       <c r="Q327" s="9" t="n">
-        <v>101.296138</v>
+        <v>101.298183</v>
       </c>
       <c r="R327" s="9" t="n">
         <v>99.81647</v>
@@ -26784,7 +26784,7 @@
         <v>101.492127</v>
       </c>
       <c r="Q328" s="6" t="n">
-        <v>101.513599</v>
+        <v>101.515987</v>
       </c>
       <c r="R328" s="6" t="n">
         <v>99.70278399999999</v>
@@ -26868,7 +26868,7 @@
         <v>101.602763</v>
       </c>
       <c r="Q329" s="9" t="n">
-        <v>101.720121</v>
+        <v>101.722834</v>
       </c>
       <c r="R329" s="9" t="n">
         <v>99.630548</v>
@@ -26952,7 +26952,7 @@
         <v>101.716976</v>
       </c>
       <c r="Q330" s="6" t="n">
-        <v>101.898633</v>
+        <v>101.901627</v>
       </c>
       <c r="R330" s="6" t="n">
         <v>99.60654700000001</v>
@@ -27036,7 +27036,7 @@
         <v>101.814597</v>
       </c>
       <c r="Q331" s="9" t="n">
-        <v>102.04719</v>
+        <v>102.050419</v>
       </c>
       <c r="R331" s="9" t="n">
         <v>99.621315</v>
@@ -27120,7 +27120,7 @@
         <v>101.884329</v>
       </c>
       <c r="Q332" s="6" t="n">
-        <v>102.177923</v>
+        <v>102.181358</v>
       </c>
       <c r="R332" s="6" t="n">
         <v>99.654983</v>
@@ -27204,7 +27204,7 @@
         <v>101.925133</v>
       </c>
       <c r="Q333" s="9" t="n">
-        <v>102.279412</v>
+        <v>102.283007</v>
       </c>
       <c r="R333" s="9" t="n">
         <v>99.68397400000001</v>
@@ -27288,7 +27288,7 @@
         <v>101.945441</v>
       </c>
       <c r="Q334" s="6" t="n">
-        <v>102.339764</v>
+        <v>102.343454</v>
       </c>
       <c r="R334" s="6" t="n">
         <v>99.700011</v>
@@ -27372,7 +27372,7 @@
         <v>101.973837</v>
       </c>
       <c r="Q335" s="9" t="n">
-        <v>102.337414</v>
+        <v>102.341101</v>
       </c>
       <c r="R335" s="9" t="n">
         <v>99.70149499999999</v>
@@ -27456,7 +27456,7 @@
         <v>102.019448</v>
       </c>
       <c r="Q336" s="6" t="n">
-        <v>102.275295</v>
+        <v>102.278883</v>
       </c>
       <c r="R336" s="6" t="n">
         <v>99.686976</v>
@@ -27540,7 +27540,7 @@
         <v>102.073088</v>
       </c>
       <c r="Q337" s="9" t="n">
-        <v>102.169743</v>
+        <v>102.173165</v>
       </c>
       <c r="R337" s="9" t="n">
         <v>99.655396</v>
@@ -27624,7 +27624,7 @@
         <v>102.117936</v>
       </c>
       <c r="Q338" s="6" t="n">
-        <v>102.038047</v>
+        <v>102.041262</v>
       </c>
       <c r="R338" s="6" t="n">
         <v>99.59702299999999</v>
@@ -27708,7 +27708,7 @@
         <v>102.126047</v>
       </c>
       <c r="Q339" s="9" t="n">
-        <v>101.892456</v>
+        <v>101.895441</v>
       </c>
       <c r="R339" s="9" t="n">
         <v>99.513344</v>
@@ -27792,7 +27792,7 @@
         <v>102.054641</v>
       </c>
       <c r="Q340" s="6" t="n">
-        <v>101.73888</v>
+        <v>101.741623</v>
       </c>
       <c r="R340" s="6" t="n">
         <v>99.415468</v>
@@ -27876,7 +27876,7 @@
         <v>101.867877</v>
       </c>
       <c r="Q341" s="9" t="n">
-        <v>101.599874</v>
+        <v>101.602397</v>
       </c>
       <c r="R341" s="9" t="n">
         <v>99.30570400000001</v>
@@ -27960,7 +27960,7 @@
         <v>101.585665</v>
       </c>
       <c r="Q342" s="6" t="n">
-        <v>101.487167</v>
+        <v>101.489513</v>
       </c>
       <c r="R342" s="6" t="n">
         <v>99.18487500000001</v>
@@ -28044,7 +28044,7 @@
         <v>101.243023</v>
       </c>
       <c r="Q343" s="9" t="n">
-        <v>101.400149</v>
+        <v>101.402357</v>
       </c>
       <c r="R343" s="9" t="n">
         <v>99.051922</v>
@@ -28128,7 +28128,7 @@
         <v>100.88378</v>
       </c>
       <c r="Q344" s="6" t="n">
-        <v>101.31299</v>
+        <v>101.315061</v>
       </c>
       <c r="R344" s="6" t="n">
         <v>98.91911500000001</v>
@@ -28212,7 +28212,7 @@
         <v>100.531239</v>
       </c>
       <c r="Q345" s="9" t="n">
-        <v>101.176926</v>
+        <v>101.178782</v>
       </c>
       <c r="R345" s="9" t="n">
         <v>98.805852</v>
@@ -28296,7 +28296,7 @@
         <v>100.187058</v>
       </c>
       <c r="Q346" s="6" t="n">
-        <v>100.953751</v>
+        <v>100.955255</v>
       </c>
       <c r="R346" s="6" t="n">
         <v>98.743972</v>
@@ -28380,7 +28380,7 @@
         <v>99.7984</v>
       </c>
       <c r="Q347" s="9" t="n">
-        <v>100.609001</v>
+        <v>100.609962</v>
       </c>
       <c r="R347" s="9" t="n">
         <v>98.766938</v>
@@ -28464,7 +28464,7 @@
         <v>99.30520300000001</v>
       </c>
       <c r="Q348" s="6" t="n">
-        <v>100.153439</v>
+        <v>100.153682</v>
       </c>
       <c r="R348" s="6" t="n">
         <v>98.91587</v>
@@ -28548,7 +28548,7 @@
         <v>98.675124</v>
       </c>
       <c r="Q349" s="9" t="n">
-        <v>99.616625</v>
+        <v>99.616022</v>
       </c>
       <c r="R349" s="9" t="n">
         <v>99.229921</v>
@@ -28632,7 +28632,7 @@
         <v>97.90809900000001</v>
       </c>
       <c r="Q350" s="6" t="n">
-        <v>99.03717899999999</v>
+        <v>99.035662</v>
       </c>
       <c r="R350" s="6" t="n">
         <v>99.723906</v>
@@ -28716,7 +28716,7 @@
         <v>97.08127500000001</v>
       </c>
       <c r="Q351" s="9" t="n">
-        <v>98.470426</v>
+        <v>98.46801499999999</v>
       </c>
       <c r="R351" s="9" t="n">
         <v>100.336613</v>
@@ -28800,7 +28800,7 @@
         <v>96.31001500000001</v>
       </c>
       <c r="Q352" s="6" t="n">
-        <v>97.99344000000001</v>
+        <v>97.99027700000001</v>
       </c>
       <c r="R352" s="6" t="n">
         <v>100.938932</v>
@@ -28884,7 +28884,7 @@
         <v>95.69615</v>
       </c>
       <c r="Q353" s="9" t="n">
-        <v>97.633504</v>
+        <v>97.629774</v>
       </c>
       <c r="R353" s="9" t="n">
         <v>101.459956</v>
@@ -28968,7 +28968,7 @@
         <v>95.31896399999999</v>
       </c>
       <c r="Q354" s="6" t="n">
-        <v>97.395167</v>
+        <v>97.39106099999999</v>
       </c>
       <c r="R354" s="6" t="n">
         <v>101.860491</v>
@@ -29052,7 +29052,7 @@
         <v>95.183716</v>
       </c>
       <c r="Q355" s="9" t="n">
-        <v>97.32495900000001</v>
+        <v>97.320742</v>
       </c>
       <c r="R355" s="9" t="n">
         <v>102.101981</v>
@@ -29136,7 +29136,7 @@
         <v>95.27273</v>
       </c>
       <c r="Q356" s="6" t="n">
-        <v>97.452134</v>
+        <v>97.448117</v>
       </c>
       <c r="R356" s="6" t="n">
         <v>102.159621</v>
@@ -29220,7 +29220,7 @@
         <v>95.499116</v>
       </c>
       <c r="Q357" s="9" t="n">
-        <v>97.737329</v>
+        <v>97.733762</v>
       </c>
       <c r="R357" s="9" t="n">
         <v>102.061785</v>
@@ -29304,7 +29304,7 @@
         <v>95.785263</v>
       </c>
       <c r="Q358" s="6" t="n">
-        <v>98.11075599999999</v>
+        <v>98.107777</v>
       </c>
       <c r="R358" s="6" t="n">
         <v>101.898745</v>
@@ -29388,7 +29388,7 @@
         <v>96.093588</v>
       </c>
       <c r="Q359" s="9" t="n">
-        <v>98.505179</v>
+        <v>98.502821</v>
       </c>
       <c r="R359" s="9" t="n">
         <v>101.725517</v>
@@ -29472,7 +29472,7 @@
         <v>96.397431</v>
       </c>
       <c r="Q360" s="6" t="n">
-        <v>98.88379500000001</v>
+        <v>98.882034</v>
       </c>
       <c r="R360" s="6" t="n">
         <v>101.556054</v>
@@ -29556,7 +29556,7 @@
         <v>96.696</v>
       </c>
       <c r="Q361" s="9" t="n">
-        <v>99.208642</v>
+        <v>99.207392</v>
       </c>
       <c r="R361" s="9" t="n">
         <v>101.393867</v>
@@ -29640,7 +29640,7 @@
         <v>97.00365499999999</v>
       </c>
       <c r="Q362" s="6" t="n">
-        <v>99.464538</v>
+        <v>99.463691</v>
       </c>
       <c r="R362" s="6" t="n">
         <v>101.240218</v>
@@ -29724,7 +29724,7 @@
         <v>97.308723</v>
       </c>
       <c r="Q363" s="9" t="n">
-        <v>99.65250399999999</v>
+        <v>99.65195300000001</v>
       </c>
       <c r="R363" s="9" t="n">
         <v>101.073537</v>
@@ -29808,7 +29808,7 @@
         <v>97.61432499999999</v>
       </c>
       <c r="Q364" s="6" t="n">
-        <v>99.78626800000001</v>
+        <v>99.785927</v>
       </c>
       <c r="R364" s="6" t="n">
         <v>100.889668</v>
@@ -29892,7 +29892,7 @@
         <v>97.955451</v>
       </c>
       <c r="Q365" s="9" t="n">
-        <v>99.8634</v>
+        <v>99.86318</v>
       </c>
       <c r="R365" s="9" t="n">
         <v>100.69928</v>
@@ -29976,7 +29976,7 @@
         <v>98.356904</v>
       </c>
       <c r="Q366" s="6" t="n">
-        <v>99.891479</v>
+        <v>99.891302</v>
       </c>
       <c r="R366" s="6" t="n">
         <v>100.524</v>
@@ -30060,7 +30060,7 @@
         <v>98.840416</v>
       </c>
       <c r="Q367" s="9" t="n">
-        <v>99.897188</v>
+        <v>99.89702</v>
       </c>
       <c r="R367" s="9" t="n">
         <v>100.378086</v>
@@ -30144,7 +30144,7 @@
         <v>99.365357</v>
       </c>
       <c r="Q368" s="6" t="n">
-        <v>99.886155</v>
+        <v>99.885969</v>
       </c>
       <c r="R368" s="6" t="n">
         <v>100.268295</v>
@@ -30228,7 +30228,7 @@
         <v>99.872889</v>
       </c>
       <c r="Q369" s="9" t="n">
-        <v>99.858081</v>
+        <v>99.85785</v>
       </c>
       <c r="R369" s="9" t="n">
         <v>100.211656</v>
@@ -30312,7 +30312,7 @@
         <v>100.319776</v>
       </c>
       <c r="Q370" s="6" t="n">
-        <v>99.827876</v>
+        <v>99.827597</v>
       </c>
       <c r="R370" s="6" t="n">
         <v>100.208252</v>
@@ -30396,7 +30396,7 @@
         <v>100.683748</v>
       </c>
       <c r="Q371" s="9" t="n">
-        <v>99.817297</v>
+        <v>99.817001</v>
       </c>
       <c r="R371" s="9" t="n">
         <v>100.216243</v>
@@ -30480,7 +30480,7 @@
         <v>100.964737</v>
       </c>
       <c r="Q372" s="6" t="n">
-        <v>99.847128</v>
+        <v>99.846878</v>
       </c>
       <c r="R372" s="6" t="n">
         <v>100.200928</v>
@@ -30564,7 +30564,7 @@
         <v>101.177499</v>
       </c>
       <c r="Q373" s="9" t="n">
-        <v>99.920586</v>
+        <v>99.920451</v>
       </c>
       <c r="R373" s="9" t="n">
         <v>100.136942</v>
@@ -30648,7 +30648,7 @@
         <v>101.333756</v>
       </c>
       <c r="Q374" s="6" t="n">
-        <v>100.036835</v>
+        <v>100.036883</v>
       </c>
       <c r="R374" s="6" t="n">
         <v>100.016933</v>
@@ -30732,7 +30732,7 @@
         <v>101.44882</v>
       </c>
       <c r="Q375" s="9" t="n">
-        <v>100.17121</v>
+        <v>100.171469</v>
       </c>
       <c r="R375" s="9" t="n">
         <v>99.844623</v>
@@ -30816,7 +30816,7 @@
         <v>101.529301</v>
       </c>
       <c r="Q376" s="6" t="n">
-        <v>100.288717</v>
+        <v>100.289159</v>
       </c>
       <c r="R376" s="6" t="n">
         <v>99.650063</v>
@@ -30900,7 +30900,7 @@
         <v>101.575154</v>
       </c>
       <c r="Q377" s="9" t="n">
-        <v>100.36337</v>
+        <v>100.363929</v>
       </c>
       <c r="R377" s="9" t="n">
         <v>99.458991</v>
@@ -30984,7 +30984,7 @@
         <v>101.591076</v>
       </c>
       <c r="Q378" s="6" t="n">
-        <v>100.381546</v>
+        <v>100.382134</v>
       </c>
       <c r="R378" s="6" t="n">
         <v>99.285921</v>
@@ -31068,7 +31068,7 @@
         <v>101.584829</v>
       </c>
       <c r="Q379" s="9" t="n">
-        <v>100.356222</v>
+        <v>100.356769</v>
       </c>
       <c r="R379" s="9" t="n">
         <v>99.15098999999999</v>
@@ -31152,7 +31152,7 @@
         <v>101.559793</v>
       </c>
       <c r="Q380" s="6" t="n">
-        <v>100.298608</v>
+        <v>100.299063</v>
       </c>
       <c r="R380" s="6" t="n">
         <v>99.068181</v>
@@ -31236,7 +31236,7 @@
         <v>101.517019</v>
       </c>
       <c r="Q381" s="9" t="n">
-        <v>100.216278</v>
+        <v>100.216602</v>
       </c>
       <c r="R381" s="9" t="n">
         <v>99.0489</v>
@@ -31320,7 +31320,7 @@
         <v>101.453464</v>
       </c>
       <c r="Q382" s="6" t="n">
-        <v>100.120142</v>
+        <v>100.120313</v>
       </c>
       <c r="R382" s="6" t="n">
         <v>99.11127399999999</v>
@@ -31404,7 +31404,7 @@
         <v>101.356787</v>
       </c>
       <c r="Q383" s="9" t="n">
-        <v>100.021413</v>
+        <v>100.021428</v>
       </c>
       <c r="R383" s="9" t="n">
         <v>99.263502</v>
@@ -31488,7 +31488,7 @@
         <v>101.223873</v>
       </c>
       <c r="Q384" s="6" t="n">
-        <v>99.923816</v>
+        <v>99.923676</v>
       </c>
       <c r="R384" s="6" t="n">
         <v>99.502</v>
@@ -31572,7 +31572,7 @@
         <v>101.05839</v>
       </c>
       <c r="Q385" s="9" t="n">
-        <v>99.839384</v>
+        <v>99.83911000000001</v>
       </c>
       <c r="R385" s="9" t="n">
         <v>99.812977</v>
@@ -31656,7 +31656,7 @@
         <v>100.892982</v>
       </c>
       <c r="Q386" s="6" t="n">
-        <v>99.782721</v>
+        <v>99.78235599999999</v>
       </c>
       <c r="R386" s="6" t="n">
         <v>100.138851</v>
@@ -31740,7 +31740,7 @@
         <v>100.743841</v>
       </c>
       <c r="Q387" s="9" t="n">
-        <v>99.77016399999999</v>
+        <v>99.769779</v>
       </c>
       <c r="R387" s="9" t="n">
         <v>100.404546</v>
@@ -31824,7 +31824,7 @@
         <v>100.622468</v>
       </c>
       <c r="Q388" s="6" t="n">
-        <v>99.786463</v>
+        <v>99.786102</v>
       </c>
       <c r="R388" s="6" t="n">
         <v>100.562091</v>
@@ -31908,7 +31908,7 @@
         <v>100.532177</v>
       </c>
       <c r="Q389" s="9" t="n">
-        <v>99.821031</v>
+        <v>99.820724</v>
       </c>
       <c r="R389" s="9" t="n">
         <v>100.608878</v>
@@ -31992,7 +31992,7 @@
         <v>100.470968</v>
       </c>
       <c r="Q390" s="6" t="n">
-        <v>99.86908200000001</v>
+        <v>99.868849</v>
       </c>
       <c r="R390" s="6" t="n">
         <v>100.575334</v>
@@ -32076,7 +32076,7 @@
         <v>100.407419</v>
       </c>
       <c r="Q391" s="9" t="n">
-        <v>99.926671</v>
+        <v>99.92652699999999</v>
       </c>
       <c r="R391" s="9" t="n">
         <v>100.518144</v>
@@ -32160,7 +32160,7 @@
         <v>100.32358</v>
       </c>
       <c r="Q392" s="6" t="n">
-        <v>99.986784</v>
+        <v>99.986734</v>
       </c>
       <c r="R392" s="6" t="n">
         <v>100.497711</v>
@@ -32244,7 +32244,7 @@
         <v>100.229832</v>
       </c>
       <c r="Q393" s="9" t="n">
-        <v>100.038137</v>
+        <v>100.038167</v>
       </c>
       <c r="R393" s="9" t="n">
         <v>100.522228</v>
@@ -32328,7 +32328,7 @@
         <v>100.149119</v>
       </c>
       <c r="Q394" s="6" t="n">
-        <v>100.082568</v>
+        <v>100.082667</v>
       </c>
       <c r="R394" s="6" t="n">
         <v>100.552005</v>
@@ -32412,7 +32412,7 @@
         <v>100.105785</v>
       </c>
       <c r="Q395" s="9" t="n">
-        <v>100.130743</v>
+        <v>100.130917</v>
       </c>
       <c r="R395" s="9" t="n">
         <v>100.529986</v>
@@ -32496,7 +32496,7 @@
         <v>100.115546</v>
       </c>
       <c r="Q396" s="6" t="n">
-        <v>100.177313</v>
+        <v>100.177558</v>
       </c>
       <c r="R396" s="6" t="n">
         <v>100.424373</v>
@@ -32580,7 +32580,7 @@
         <v>100.178485</v>
       </c>
       <c r="Q397" s="9" t="n">
-        <v>100.225478</v>
+        <v>100.225799</v>
       </c>
       <c r="R397" s="9" t="n">
         <v>100.257545</v>
@@ -32664,7 +32664,7 @@
         <v>100.27945</v>
       </c>
       <c r="Q398" s="6" t="n">
-        <v>100.286035</v>
+        <v>100.286449</v>
       </c>
       <c r="R398" s="6" t="n">
         <v>100.053832</v>
@@ -32748,7 +32748,7 @@
         <v>100.406936</v>
       </c>
       <c r="Q399" s="9" t="n">
-        <v>100.353976</v>
+        <v>100.354497</v>
       </c>
       <c r="R399" s="9" t="n">
         <v>99.834558</v>
@@ -32832,7 +32832,7 @@
         <v>100.546553</v>
       </c>
       <c r="Q400" s="6" t="n">
-        <v>100.419861</v>
+        <v>100.420484</v>
       </c>
       <c r="R400" s="6" t="n">
         <v>99.614092</v>
@@ -32916,7 +32916,7 @@
         <v>100.692626</v>
       </c>
       <c r="Q401" s="9" t="n">
-        <v>100.470873</v>
+        <v>100.471575</v>
       </c>
       <c r="R401" s="9" t="n">
         <v>99.397296</v>
@@ -33000,7 +33000,7 @@
         <v>100.843309</v>
       </c>
       <c r="Q402" s="6" t="n">
-        <v>100.484165</v>
+        <v>100.484887</v>
       </c>
       <c r="R402" s="6" t="n">
         <v>99.19916499999999</v>
@@ -33084,7 +33084,7 @@
         <v>100.975911</v>
       </c>
       <c r="Q403" s="9" t="n">
-        <v>100.444358</v>
+        <v>100.445016</v>
       </c>
       <c r="R403" s="9" t="n">
         <v>99.03298599999999</v>
@@ -33168,7 +33168,7 @@
         <v>101.068183</v>
       </c>
       <c r="Q404" s="6" t="n">
-        <v>100.358389</v>
+        <v>100.358911</v>
       </c>
       <c r="R404" s="6" t="n">
         <v>98.908034</v>
@@ -33252,7 +33252,7 @@
         <v>101.113819</v>
       </c>
       <c r="Q405" s="9" t="n">
-        <v>100.241056</v>
+        <v>100.241392</v>
       </c>
       <c r="R405" s="9" t="n">
         <v>98.84222800000001</v>
@@ -33336,7 +33336,7 @@
         <v>101.105563</v>
       </c>
       <c r="Q406" s="6" t="n">
-        <v>100.115944</v>
+        <v>100.116082</v>
       </c>
       <c r="R406" s="6" t="n">
         <v>98.850426</v>
@@ -33420,7 +33420,7 @@
         <v>101.035813</v>
       </c>
       <c r="Q407" s="9" t="n">
-        <v>100.000312</v>
+        <v>100.000267</v>
       </c>
       <c r="R407" s="9" t="n">
         <v>98.91202199999999</v>
@@ -33504,7 +33504,7 @@
         <v>100.91346</v>
       </c>
       <c r="Q408" s="6" t="n">
-        <v>99.906565</v>
+        <v>99.90637099999999</v>
       </c>
       <c r="R408" s="6" t="n">
         <v>98.976049</v>
@@ -33588,7 +33588,7 @@
         <v>100.747792</v>
       </c>
       <c r="Q409" s="9" t="n">
-        <v>99.83770699999999</v>
+        <v>99.83740400000001</v>
       </c>
       <c r="R409" s="9" t="n">
         <v>99.019975</v>
@@ -33672,7 +33672,7 @@
         <v>100.560894</v>
       </c>
       <c r="Q410" s="6" t="n">
-        <v>99.796488</v>
+        <v>99.796119</v>
       </c>
       <c r="R410" s="6" t="n">
         <v>99.029314</v>
@@ -33756,7 +33756,7 @@
         <v>100.38404</v>
       </c>
       <c r="Q411" s="9" t="n">
-        <v>99.77041</v>
+        <v>99.769999</v>
       </c>
       <c r="R411" s="9" t="n">
         <v>98.99702000000001</v>
@@ -33840,7 +33840,7 @@
         <v>100.250069</v>
       </c>
       <c r="Q412" s="6" t="n">
-        <v>99.741499</v>
+        <v>99.74104199999999</v>
       </c>
       <c r="R412" s="6" t="n">
         <v>98.93616299999999</v>
@@ -33924,7 +33924,7 @@
         <v>100.169082</v>
       </c>
       <c r="Q413" s="9" t="n">
-        <v>99.69644700000001</v>
+        <v>99.69591800000001</v>
       </c>
       <c r="R413" s="9" t="n">
         <v>98.863732</v>
@@ -34008,7 +34008,7 @@
         <v>100.124881</v>
       </c>
       <c r="Q414" s="6" t="n">
-        <v>99.642036</v>
+        <v>99.64142099999999</v>
       </c>
       <c r="R414" s="6" t="n">
         <v>98.792176</v>
@@ -34092,7 +34092,7 @@
         <v>100.123011</v>
       </c>
       <c r="Q415" s="9" t="n">
-        <v>99.60785799999999</v>
+        <v>99.60718799999999</v>
       </c>
       <c r="R415" s="9" t="n">
         <v>98.719301</v>
@@ -34176,7 +34176,7 @@
         <v>100.147522</v>
       </c>
       <c r="Q416" s="6" t="n">
-        <v>99.621589</v>
+        <v>99.620942</v>
       </c>
       <c r="R416" s="6" t="n">
         <v>98.63999</v>
@@ -34260,7 +34260,7 @@
         <v>100.192245</v>
       </c>
       <c r="Q417" s="9" t="n">
-        <v>99.681755</v>
+        <v>99.681202</v>
       </c>
       <c r="R417" s="9" t="n">
         <v>98.556501</v>
@@ -34344,7 +34344,7 @@
         <v>100.257431</v>
       </c>
       <c r="Q418" s="6" t="n">
-        <v>99.777734</v>
+        <v>99.777332</v>
       </c>
       <c r="R418" s="6" t="n">
         <v>98.477706</v>
@@ -34428,7 +34428,7 @@
         <v>100.344123</v>
       </c>
       <c r="Q419" s="9" t="n">
-        <v>99.889596</v>
+        <v>99.88937199999999</v>
       </c>
       <c r="R419" s="9" t="n">
         <v>98.413629</v>
@@ -34512,7 +34512,7 @@
         <v>100.435663</v>
       </c>
       <c r="Q420" s="6" t="n">
-        <v>99.99132</v>
+        <v>99.99125600000001</v>
       </c>
       <c r="R420" s="6" t="n">
         <v>98.37355100000001</v>
@@ -34596,7 +34596,7 @@
         <v>100.500641</v>
       </c>
       <c r="Q421" s="9" t="n">
-        <v>100.059256</v>
+        <v>100.0593</v>
       </c>
       <c r="R421" s="9" t="n">
         <v>98.369148</v>
@@ -34680,7 +34680,7 @@
         <v>100.513591</v>
       </c>
       <c r="Q422" s="6" t="n">
-        <v>100.076713</v>
+        <v>100.076785</v>
       </c>
       <c r="R422" s="6" t="n">
         <v>98.407995</v>
@@ -34764,7 +34764,7 @@
         <v>100.459976</v>
       </c>
       <c r="Q423" s="9" t="n">
-        <v>100.048848</v>
+        <v>100.048877</v>
       </c>
       <c r="R423" s="9" t="n">
         <v>98.498316</v>
@@ -34848,7 +34848,7 @@
         <v>100.334583</v>
       </c>
       <c r="Q424" s="6" t="n">
-        <v>99.991597</v>
+        <v>99.99153699999999</v>
       </c>
       <c r="R424" s="6" t="n">
         <v>98.641334</v>
@@ -34932,7 +34932,7 @@
         <v>100.156102</v>
       </c>
       <c r="Q425" s="9" t="n">
-        <v>99.931393</v>
+        <v>99.93123900000001</v>
       </c>
       <c r="R425" s="9" t="n">
         <v>98.83420599999999</v>
@@ -35016,7 +35016,7 @@
         <v>99.95702199999999</v>
       </c>
       <c r="Q426" s="6" t="n">
-        <v>99.89516999999999</v>
+        <v>99.894961</v>
       </c>
       <c r="R426" s="6" t="n">
         <v>99.04786</v>
@@ -35100,7 +35100,7 @@
         <v>99.764042</v>
       </c>
       <c r="Q427" s="9" t="n">
-        <v>99.89955999999999</v>
+        <v>99.89936</v>
       </c>
       <c r="R427" s="9" t="n">
         <v>99.265129</v>
@@ -35184,7 +35184,7 @@
         <v>99.597443</v>
       </c>
       <c r="Q428" s="6" t="n">
-        <v>99.92639699999999</v>
+        <v>99.926242</v>
       </c>
       <c r="R428" s="6" t="n">
         <v>99.475252</v>
@@ -35268,7 +35268,7 @@
         <v>99.460455</v>
       </c>
       <c r="Q429" s="9" t="n">
-        <v>99.96241000000001</v>
+        <v>99.96231400000001</v>
       </c>
       <c r="R429" s="9" t="n">
         <v>99.674285</v>
@@ -35352,7 +35352,7 @@
         <v>99.355762</v>
       </c>
       <c r="Q430" s="6" t="n">
-        <v>99.98988</v>
+        <v>99.989831</v>
       </c>
       <c r="R430" s="6" t="n">
         <v>99.86826000000001</v>
@@ -35436,7 +35436,7 @@
         <v>99.277923</v>
       </c>
       <c r="Q431" s="9" t="n">
-        <v>99.99627</v>
+        <v>99.996233</v>
       </c>
       <c r="R431" s="9" t="n">
         <v>100.060236</v>
@@ -35520,7 +35520,7 @@
         <v>99.223203</v>
       </c>
       <c r="Q432" s="6" t="n">
-        <v>99.97688599999999</v>
+        <v>99.976822</v>
       </c>
       <c r="R432" s="6" t="n">
         <v>100.244754</v>
@@ -35604,7 +35604,7 @@
         <v>99.196077</v>
       </c>
       <c r="Q433" s="9" t="n">
-        <v>99.938254</v>
+        <v>99.93813299999999</v>
       </c>
       <c r="R433" s="9" t="n">
         <v>100.40549</v>
@@ -35688,7 +35688,7 @@
         <v>99.198431</v>
       </c>
       <c r="Q434" s="6" t="n">
-        <v>99.89576</v>
+        <v>99.895577</v>
       </c>
       <c r="R434" s="6" t="n">
         <v>100.526421</v>
@@ -35772,7 +35772,7 @@
         <v>99.22541099999999</v>
       </c>
       <c r="Q435" s="9" t="n">
-        <v>99.863524</v>
+        <v>99.86329499999999</v>
       </c>
       <c r="R435" s="9" t="n">
         <v>100.613225</v>
@@ -35856,7 +35856,7 @@
         <v>99.253951</v>
       </c>
       <c r="Q436" s="6" t="n">
-        <v>99.842687</v>
+        <v>99.84242999999999</v>
       </c>
       <c r="R436" s="6" t="n">
         <v>100.696911</v>
@@ -35940,7 +35940,7 @@
         <v>99.272891</v>
       </c>
       <c r="Q437" s="9" t="n">
-        <v>99.84517</v>
+        <v>99.844922</v>
       </c>
       <c r="R437" s="9" t="n">
         <v>100.799189</v>
@@ -36024,7 +36024,7 @@
         <v>99.284637</v>
       </c>
       <c r="Q438" s="6" t="n">
-        <v>99.879435</v>
+        <v>99.87924700000001</v>
       </c>
       <c r="R438" s="6" t="n">
         <v>100.914326</v>
@@ -36108,7 +36108,7 @@
         <v>99.298716</v>
       </c>
       <c r="Q439" s="9" t="n">
-        <v>99.943557</v>
+        <v>99.943476</v>
       </c>
       <c r="R439" s="9" t="n">
         <v>101.012718</v>
@@ -36192,7 +36192,7 @@
         <v>99.330686</v>
       </c>
       <c r="Q440" s="6" t="n">
-        <v>100.029726</v>
+        <v>100.029788</v>
       </c>
       <c r="R440" s="6" t="n">
         <v>101.088973</v>
@@ -36276,7 +36276,7 @@
         <v>99.382846</v>
       </c>
       <c r="Q441" s="9" t="n">
-        <v>100.119328</v>
+        <v>100.119538</v>
       </c>
       <c r="R441" s="9" t="n">
         <v>101.177261</v>
@@ -36360,7 +36360,7 @@
         <v>99.443241</v>
       </c>
       <c r="Q442" s="6" t="n">
-        <v>100.202847</v>
+        <v>100.203196</v>
       </c>
       <c r="R442" s="6" t="n">
         <v>101.296184</v>
@@ -36444,7 +36444,7 @@
         <v>99.49529</v>
       </c>
       <c r="Q443" s="9" t="n">
-        <v>100.275104</v>
+        <v>100.275575</v>
       </c>
       <c r="R443" s="9" t="n">
         <v>101.430104</v>
@@ -36528,7 +36528,7 @@
         <v>99.524237</v>
       </c>
       <c r="Q444" s="6" t="n">
-        <v>100.329008</v>
+        <v>100.329573</v>
       </c>
       <c r="R444" s="6" t="n">
         <v>101.560803</v>
@@ -36612,7 +36612,7 @@
         <v>99.530745</v>
       </c>
       <c r="Q445" s="9" t="n">
-        <v>100.35692</v>
+        <v>100.357538</v>
       </c>
       <c r="R445" s="9" t="n">
         <v>101.693418</v>
@@ -36696,7 +36696,7 @@
         <v>99.51172800000001</v>
       </c>
       <c r="Q446" s="6" t="n">
-        <v>100.354681</v>
+        <v>100.355306</v>
       </c>
       <c r="R446" s="6" t="n">
         <v>101.832396</v>
@@ -36780,7 +36780,7 @@
         <v>99.46035500000001</v>
       </c>
       <c r="Q447" s="9" t="n">
-        <v>100.329432</v>
+        <v>100.330027</v>
       </c>
       <c r="R447" s="9" t="n">
         <v>101.959055</v>
@@ -36864,7 +36864,7 @@
         <v>99.38675000000001</v>
       </c>
       <c r="Q448" s="6" t="n">
-        <v>100.294593</v>
+        <v>100.295144</v>
       </c>
       <c r="R448" s="6" t="n">
         <v>102.053259</v>
@@ -36948,7 +36948,7 @@
         <v>99.301405</v>
       </c>
       <c r="Q449" s="9" t="n">
-        <v>100.278476</v>
+        <v>100.279013</v>
       </c>
       <c r="R449" s="9" t="n">
         <v>102.06262</v>
@@ -37032,7 +37032,7 @@
         <v>99.230868</v>
       </c>
       <c r="Q450" s="6" t="n">
-        <v>100.293313</v>
+        <v>100.293886</v>
       </c>
       <c r="R450" s="6" t="n">
         <v>101.93951</v>
@@ -37116,7 +37116,7 @@
         <v>99.21886499999999</v>
       </c>
       <c r="Q451" s="9" t="n">
-        <v>100.339387</v>
+        <v>100.340045</v>
       </c>
       <c r="R451" s="9" t="n">
         <v>101.663717</v>
@@ -37200,7 +37200,7 @@
         <v>99.29834200000001</v>
       </c>
       <c r="Q452" s="6" t="n">
-        <v>100.412266</v>
+        <v>100.413053</v>
       </c>
       <c r="R452" s="6" t="n">
         <v>101.281721</v>
@@ -37284,7 +37284,7 @@
         <v>99.457239</v>
       </c>
       <c r="Q453" s="9" t="n">
-        <v>100.496484</v>
+        <v>100.497417</v>
       </c>
       <c r="R453" s="9" t="n">
         <v>100.864579</v>
@@ -37368,7 +37368,7 @@
         <v>99.670069</v>
       </c>
       <c r="Q454" s="6" t="n">
-        <v>100.57767</v>
+        <v>100.578745</v>
       </c>
       <c r="R454" s="6" t="n">
         <v>100.468807</v>
@@ -37452,7 +37452,7 @@
         <v>99.90283100000001</v>
       </c>
       <c r="Q455" s="9" t="n">
-        <v>100.645531</v>
+        <v>100.646729</v>
       </c>
       <c r="R455" s="9" t="n">
         <v>100.125365</v>
@@ -37536,7 +37536,7 @@
         <v>100.121048</v>
       </c>
       <c r="Q456" s="6" t="n">
-        <v>100.685394</v>
+        <v>100.686671</v>
       </c>
       <c r="R456" s="6" t="n">
         <v>99.86854700000001</v>
@@ -37620,7 +37620,7 @@
         <v>100.296027</v>
       </c>
       <c r="Q457" s="9" t="n">
-        <v>100.685503</v>
+        <v>100.686797</v>
       </c>
       <c r="R457" s="9" t="n">
         <v>99.718109</v>
@@ -37704,7 +37704,7 @@
         <v>100.419933</v>
       </c>
       <c r="Q458" s="6" t="n">
-        <v>100.646359</v>
+        <v>100.647609</v>
       </c>
       <c r="R458" s="6" t="n">
         <v>99.66754299999999</v>
@@ -37788,7 +37788,7 @@
         <v>100.493883</v>
       </c>
       <c r="Q459" s="9" t="n">
-        <v>100.582199</v>
+        <v>100.583365</v>
       </c>
       <c r="R459" s="9" t="n">
         <v>99.686634</v>
@@ -37872,7 +37872,7 @@
         <v>100.548219</v>
       </c>
       <c r="Q460" s="6" t="n">
-        <v>100.515138</v>
+        <v>100.516217</v>
       </c>
       <c r="R460" s="6" t="n">
         <v>99.723964</v>
@@ -37956,7 +37956,7 @@
         <v>100.610985</v>
       </c>
       <c r="Q461" s="9" t="n">
-        <v>100.460003</v>
+        <v>100.461014</v>
       </c>
       <c r="R461" s="9" t="n">
         <v>99.753157</v>
@@ -38040,7 +38040,7 @@
         <v>100.686658</v>
       </c>
       <c r="Q462" s="6" t="n">
-        <v>100.408741</v>
+        <v>100.409692</v>
       </c>
       <c r="R462" s="6" t="n">
         <v>99.771046</v>
@@ -38124,7 +38124,7 @@
         <v>100.766193</v>
       </c>
       <c r="Q463" s="9" t="n">
-        <v>100.358516</v>
+        <v>100.359408</v>
       </c>
       <c r="R463" s="9" t="n">
         <v>99.79062</v>
@@ -38208,7 +38208,7 @@
         <v>100.826822</v>
       </c>
       <c r="Q464" s="6" t="n">
-        <v>100.326608</v>
+        <v>100.327472</v>
       </c>
       <c r="R464" s="6" t="n">
         <v>99.83372</v>
@@ -38292,7 +38292,7 @@
         <v>100.848875</v>
       </c>
       <c r="Q465" s="9" t="n">
-        <v>100.321349</v>
+        <v>100.322226</v>
       </c>
       <c r="R465" s="9" t="n">
         <v>99.9051</v>
@@ -38376,7 +38376,7 @@
         <v>100.848776</v>
       </c>
       <c r="Q466" s="6" t="n">
-        <v>100.330022</v>
+        <v>100.330935</v>
       </c>
       <c r="R466" s="6" t="n">
         <v>99.989377</v>
@@ -38460,7 +38460,7 @@
         <v>100.857108</v>
       </c>
       <c r="Q467" s="9" t="n">
-        <v>100.348656</v>
+        <v>100.349622</v>
       </c>
       <c r="R467" s="9" t="n">
         <v>100.031191</v>
@@ -38544,7 +38544,7 @@
         <v>100.896605</v>
       </c>
       <c r="Q468" s="6" t="n">
-        <v>100.342184</v>
+        <v>100.343164</v>
       </c>
       <c r="R468" s="6" t="n">
         <v>100.003532</v>
@@ -38628,7 +38628,7 @@
         <v>100.950376</v>
       </c>
       <c r="Q469" s="9" t="n">
-        <v>100.278163</v>
+        <v>100.279067</v>
       </c>
       <c r="R469" s="9" t="n">
         <v>99.947812</v>
@@ -38712,7 +38712,7 @@
         <v>101.002482</v>
       </c>
       <c r="Q470" s="6" t="n">
-        <v>100.149101</v>
+        <v>100.149826</v>
       </c>
       <c r="R470" s="6" t="n">
         <v>99.898082</v>
@@ -38796,7 +38796,7 @@
         <v>101.060466</v>
       </c>
       <c r="Q471" s="9" t="n">
-        <v>99.97473599999999</v>
+        <v>99.975212</v>
       </c>
       <c r="R471" s="9" t="n">
         <v>99.85851599999999</v>
@@ -38880,7 +38880,7 @@
         <v>101.133693</v>
       </c>
       <c r="Q472" s="6" t="n">
-        <v>99.810985</v>
+        <v>99.811229</v>
       </c>
       <c r="R472" s="6" t="n">
         <v>99.81680799999999</v>
@@ -38964,7 +38964,7 @@
         <v>101.230651</v>
       </c>
       <c r="Q473" s="9" t="n">
-        <v>99.698453</v>
+        <v>99.698545</v>
       </c>
       <c r="R473" s="9" t="n">
         <v>99.742237</v>
@@ -39048,7 +39048,7 @@
         <v>101.352026</v>
       </c>
       <c r="Q474" s="6" t="n">
-        <v>99.64450100000001</v>
+        <v>99.644536</v>
       </c>
       <c r="R474" s="6" t="n">
         <v>99.64331900000001</v>
@@ -39132,7 +39132,7 @@
         <v>101.465393</v>
       </c>
       <c r="Q475" s="9" t="n">
-        <v>99.628787</v>
+        <v>99.62882399999999</v>
       </c>
       <c r="R475" s="9" t="n">
         <v>99.556048</v>
@@ -39216,7 +39216,7 @@
         <v>101.548096</v>
       </c>
       <c r="Q476" s="6" t="n">
-        <v>99.63831999999999</v>
+        <v>99.6384</v>
       </c>
       <c r="R476" s="6" t="n">
         <v>99.494711</v>
@@ -39300,7 +39300,7 @@
         <v>101.580587</v>
       </c>
       <c r="Q477" s="9" t="n">
-        <v>99.656744</v>
+        <v>99.656881</v>
       </c>
       <c r="R477" s="9" t="n">
         <v>99.460824</v>
@@ -39384,7 +39384,7 @@
         <v>101.544832</v>
       </c>
       <c r="Q478" s="6" t="n">
-        <v>99.669568</v>
+        <v>99.669753</v>
       </c>
       <c r="R478" s="6" t="n">
         <v>99.451318</v>
@@ -39468,7 +39468,7 @@
         <v>101.438764</v>
       </c>
       <c r="Q479" s="9" t="n">
-        <v>99.68081599999999</v>
+        <v>99.68104700000001</v>
       </c>
       <c r="R479" s="9" t="n">
         <v>99.452952</v>
@@ -39552,7 +39552,7 @@
         <v>101.290546</v>
       </c>
       <c r="Q480" s="6" t="n">
-        <v>99.693254</v>
+        <v>99.693533</v>
       </c>
       <c r="R480" s="6" t="n">
         <v>99.45204</v>
@@ -39636,7 +39636,7 @@
         <v>101.125144</v>
       </c>
       <c r="Q481" s="9" t="n">
-        <v>99.71454199999999</v>
+        <v>99.714883</v>
       </c>
       <c r="R481" s="9" t="n">
         <v>99.44546800000001</v>
@@ -39720,7 +39720,7 @@
         <v>100.943846</v>
       </c>
       <c r="Q482" s="6" t="n">
-        <v>99.727238</v>
+        <v>99.727627</v>
       </c>
       <c r="R482" s="6" t="n">
         <v>99.42440000000001</v>
@@ -39804,7 +39804,7 @@
         <v>100.730865</v>
       </c>
       <c r="Q483" s="9" t="n">
-        <v>99.71194</v>
+        <v>99.712333</v>
       </c>
       <c r="R483" s="9" t="n">
         <v>99.40574599999999</v>
@@ -39888,7 +39888,7 @@
         <v>100.460695</v>
       </c>
       <c r="Q484" s="6" t="n">
-        <v>99.65183399999999</v>
+        <v>99.65216100000001</v>
       </c>
       <c r="R484" s="6" t="n">
         <v>99.43335999999999</v>
@@ -39972,7 +39972,7 @@
         <v>100.097811</v>
       </c>
       <c r="Q485" s="9" t="n">
-        <v>99.53690400000001</v>
+        <v>99.537077</v>
       </c>
       <c r="R485" s="9" t="n">
         <v>99.56064600000001</v>
@@ -40056,7 +40056,7 @@
         <v>99.61394799999999</v>
       </c>
       <c r="Q486" s="6" t="n">
-        <v>99.35942900000001</v>
+        <v>99.35934899999999</v>
       </c>
       <c r="R486" s="6" t="n">
         <v>99.834082</v>
@@ -40140,7 +40140,7 @@
         <v>99.00792</v>
       </c>
       <c r="Q487" s="9" t="n">
-        <v>99.12999499999999</v>
+        <v>99.12958</v>
       </c>
       <c r="R487" s="9" t="n">
         <v>100.269794</v>
@@ -40224,7 +40224,7 @@
         <v>98.32839300000001</v>
       </c>
       <c r="Q488" s="6" t="n">
-        <v>98.89631799999999</v>
+        <v>98.895561</v>
       </c>
       <c r="R488" s="6" t="n">
         <v>100.810475</v>
@@ -40308,7 +40308,7 @@
         <v>97.684546</v>
       </c>
       <c r="Q489" s="9" t="n">
-        <v>98.724356</v>
+        <v>98.723353</v>
       </c>
       <c r="R489" s="9" t="n">
         <v>101.290398</v>
@@ -40392,7 +40392,7 @@
         <v>97.219554</v>
       </c>
       <c r="Q490" s="6" t="n">
-        <v>98.62138899999999</v>
+        <v>98.620248</v>
       </c>
       <c r="R490" s="6" t="n">
         <v>101.576942</v>
@@ -40476,7 +40476,7 @@
         <v>96.981893</v>
       </c>
       <c r="Q491" s="9" t="n">
-        <v>98.584135</v>
+        <v>98.582958</v>
       </c>
       <c r="R491" s="9" t="n">
         <v>101.655127</v>
@@ -40560,7 +40560,7 @@
         <v>96.936964</v>
       </c>
       <c r="Q492" s="6" t="n">
-        <v>98.600416</v>
+        <v>98.59928600000001</v>
       </c>
       <c r="R492" s="6" t="n">
         <v>101.571659</v>
@@ -40644,7 +40644,7 @@
         <v>97.027584</v>
       </c>
       <c r="Q493" s="9" t="n">
-        <v>98.673326</v>
+        <v>98.672332</v>
       </c>
       <c r="R493" s="9" t="n">
         <v>101.360391</v>
@@ -40728,7 +40728,7 @@
         <v>97.19841700000001</v>
       </c>
       <c r="Q494" s="6" t="n">
-        <v>98.80788</v>
+        <v>98.80711599999999</v>
       </c>
       <c r="R494" s="6" t="n">
         <v>101.061429</v>
@@ -40812,7 +40812,7 @@
         <v>97.396779</v>
       </c>
       <c r="Q495" s="9" t="n">
-        <v>99.00228199999999</v>
+        <v>99.001842</v>
       </c>
       <c r="R495" s="9" t="n">
         <v>100.723807</v>
@@ -40896,7 +40896,7 @@
         <v>97.597275</v>
       </c>
       <c r="Q496" s="6" t="n">
-        <v>99.24704</v>
+        <v>99.247001</v>
       </c>
       <c r="R496" s="6" t="n">
         <v>100.396042</v>
@@ -40980,7 +40980,7 @@
         <v>97.78906000000001</v>
       </c>
       <c r="Q497" s="9" t="n">
-        <v>99.502031</v>
+        <v>99.50240700000001</v>
       </c>
       <c r="R497" s="9" t="n">
         <v>100.129687</v>
@@ -41064,7 +41064,7 @@
         <v>97.97939</v>
       </c>
       <c r="Q498" s="6" t="n">
-        <v>99.744533</v>
+        <v>99.745301</v>
       </c>
       <c r="R498" s="6" t="n">
         <v>99.956107</v>
@@ -41148,7 +41148,7 @@
         <v>98.19193</v>
       </c>
       <c r="Q499" s="9" t="n">
-        <v>99.97824</v>
+        <v>99.97938499999999</v>
       </c>
       <c r="R499" s="9" t="n">
         <v>99.87389899999999</v>
@@ -41232,7 +41232,7 @@
         <v>98.442592</v>
       </c>
       <c r="Q500" s="6" t="n">
-        <v>100.198837</v>
+        <v>100.200336</v>
       </c>
       <c r="R500" s="6" t="n">
         <v>99.852745</v>
@@ -41316,7 +41316,7 @@
         <v>98.716746</v>
       </c>
       <c r="Q501" s="9" t="n">
-        <v>100.39421</v>
+        <v>100.39602</v>
       </c>
       <c r="R501" s="9" t="n">
         <v>99.86048</v>
@@ -41400,7 +41400,7 @@
         <v>98.98921199999999</v>
       </c>
       <c r="Q502" s="6" t="n">
-        <v>100.555764</v>
+        <v>100.557828</v>
       </c>
       <c r="R502" s="6" t="n">
         <v>99.89606499999999</v>
@@ -41484,7 +41484,7 @@
         <v>99.235879</v>
       </c>
       <c r="Q503" s="9" t="n">
-        <v>100.671852</v>
+        <v>100.674094</v>
       </c>
       <c r="R503" s="9" t="n">
         <v>99.955201</v>
@@ -41568,7 +41568,7 @@
         <v>99.43498599999999</v>
       </c>
       <c r="Q504" s="6" t="n">
-        <v>100.74674</v>
+        <v>100.749093</v>
       </c>
       <c r="R504" s="6" t="n">
         <v>100.032761</v>
@@ -41652,7 +41652,7 @@
         <v>99.586682</v>
       </c>
       <c r="Q505" s="9" t="n">
-        <v>100.78368</v>
+        <v>100.78608</v>
       </c>
       <c r="R505" s="9" t="n">
         <v>100.128484</v>
@@ -41736,7 +41736,7 @@
         <v>99.716379</v>
       </c>
       <c r="Q506" s="6" t="n">
-        <v>100.782998</v>
+        <v>100.785381</v>
       </c>
       <c r="R506" s="6" t="n">
         <v>100.238834</v>
@@ -41820,7 +41820,7 @@
         <v>99.840755</v>
       </c>
       <c r="Q507" s="9" t="n">
-        <v>100.763861</v>
+        <v>100.766194</v>
       </c>
       <c r="R507" s="9" t="n">
         <v>100.3575</v>
@@ -41904,7 +41904,7 @@
         <v>99.959497</v>
       </c>
       <c r="Q508" s="6" t="n">
-        <v>100.74187</v>
+        <v>100.744143</v>
       </c>
       <c r="R508" s="6" t="n">
         <v>100.463508</v>
@@ -41988,7 +41988,7 @@
         <v>100.074469</v>
       </c>
       <c r="Q509" s="9" t="n">
-        <v>100.72556</v>
+        <v>100.727777</v>
       </c>
       <c r="R509" s="9" t="n">
         <v>100.541792</v>
@@ -42072,7 +42072,7 @@
         <v>100.183225</v>
       </c>
       <c r="Q510" s="6" t="n">
-        <v>100.695204</v>
+        <v>100.697338</v>
       </c>
       <c r="R510" s="6" t="n">
         <v>100.588335</v>
@@ -42156,7 +42156,7 @@
         <v>100.285788</v>
       </c>
       <c r="Q511" s="9" t="n">
-        <v>100.639434</v>
+        <v>100.641439</v>
       </c>
       <c r="R511" s="9" t="n">
         <v>100.617982</v>
@@ -42240,7 +42240,7 @@
         <v>100.356675</v>
       </c>
       <c r="Q512" s="6" t="n">
-        <v>100.534714</v>
+        <v>100.536507</v>
       </c>
       <c r="R512" s="6" t="n">
         <v>100.638299</v>
@@ -42324,7 +42324,7 @@
         <v>100.41075</v>
       </c>
       <c r="Q513" s="9" t="n">
-        <v>100.366279</v>
+        <v>100.367753</v>
       </c>
       <c r="R513" s="9" t="n">
         <v>100.651921</v>
@@ -42408,7 +42408,7 @@
         <v>100.445469</v>
       </c>
       <c r="Q514" s="6" t="n">
-        <v>100.16108</v>
+        <v>100.16217</v>
       </c>
       <c r="R514" s="6" t="n">
         <v>100.669074</v>
@@ -42492,7 +42492,7 @@
         <v>100.451074</v>
       </c>
       <c r="Q515" s="9" t="n">
-        <v>99.94648100000001</v>
+        <v>99.947166</v>
       </c>
       <c r="R515" s="9" t="n">
         <v>100.678249</v>
@@ -42576,7 +42576,7 @@
         <v>100.42789</v>
       </c>
       <c r="Q516" s="6" t="n">
-        <v>99.76766499999999</v>
+        <v>99.767995</v>
       </c>
       <c r="R516" s="6" t="n">
         <v>100.662405</v>
@@ -42660,7 +42660,7 @@
         <v>100.391979</v>
       </c>
       <c r="Q517" s="9" t="n">
-        <v>99.65313999999999</v>
+        <v>99.65320699999999</v>
       </c>
       <c r="R517" s="9" t="n">
         <v>100.599822</v>
@@ -42744,7 +42744,7 @@
         <v>100.348668</v>
       </c>
       <c r="Q518" s="6" t="n">
-        <v>99.630634</v>
+        <v>99.630576</v>
       </c>
       <c r="R518" s="6" t="n">
         <v>100.49133</v>
@@ -42828,7 +42828,7 @@
         <v>100.315581</v>
       </c>
       <c r="Q519" s="9" t="n">
-        <v>99.69463</v>
+        <v>99.69457300000001</v>
       </c>
       <c r="R519" s="9" t="n">
         <v>100.338027</v>
@@ -42912,7 +42912,7 @@
         <v>100.303053</v>
       </c>
       <c r="Q520" s="6" t="n">
-        <v>99.801198</v>
+        <v>99.801202</v>
       </c>
       <c r="R520" s="6" t="n">
         <v>100.143876</v>
@@ -42996,7 +42996,7 @@
         <v>100.320282</v>
       </c>
       <c r="Q521" s="9" t="n">
-        <v>99.92024600000001</v>
+        <v>99.920322</v>
       </c>
       <c r="R521" s="9" t="n">
         <v>99.924976</v>
@@ -43080,7 +43080,7 @@
         <v>100.375709</v>
       </c>
       <c r="Q522" s="6" t="n">
-        <v>100.043273</v>
+        <v>100.043416</v>
       </c>
       <c r="R522" s="6" t="n">
         <v>99.688965</v>
@@ -43164,7 +43164,7 @@
         <v>100.459152</v>
       </c>
       <c r="Q523" s="9" t="n">
-        <v>100.138321</v>
+        <v>100.138478</v>
       </c>
       <c r="R523" s="9" t="n">
         <v>99.45135500000001</v>
@@ -43248,7 +43248,7 @@
         <v>100.546283</v>
       </c>
       <c r="Q524" s="6" t="n">
-        <v>100.200723</v>
+        <v>100.200833</v>
       </c>
       <c r="R524" s="6" t="n">
         <v>99.225194</v>
@@ -43332,7 +43332,7 @@
         <v>100.629013</v>
       </c>
       <c r="Q525" s="9" t="n">
-        <v>100.225167</v>
+        <v>100.225158</v>
       </c>
       <c r="R525" s="9" t="n">
         <v>99.017049</v>
@@ -43416,7 +43416,7 @@
         <v>100.710041</v>
       </c>
       <c r="Q526" s="6" t="n">
-        <v>100.211056</v>
+        <v>100.210858</v>
       </c>
       <c r="R526" s="6" t="n">
         <v>98.832632</v>
@@ -43500,7 +43500,7 @@
         <v>100.79824</v>
       </c>
       <c r="Q527" s="9" t="n">
-        <v>100.172559</v>
+        <v>100.172121</v>
       </c>
       <c r="R527" s="9" t="n">
         <v>98.68146900000001</v>
@@ -43584,7 +43584,7 @@
         <v>100.883805</v>
       </c>
       <c r="Q528" s="6" t="n">
-        <v>100.116894</v>
+        <v>100.116177</v>
       </c>
       <c r="R528" s="6" t="n">
         <v>98.57841000000001</v>
@@ -43668,7 +43668,7 @@
         <v>100.962194</v>
       </c>
       <c r="Q529" s="9" t="n">
-        <v>100.054186</v>
+        <v>100.053167</v>
       </c>
       <c r="R529" s="9" t="n">
         <v>98.52924</v>
@@ -43752,7 +43752,7 @@
         <v>101.036162</v>
       </c>
       <c r="Q530" s="6" t="n">
-        <v>100.011305</v>
+        <v>100.010003</v>
       </c>
       <c r="R530" s="6" t="n">
         <v>98.51473300000001</v>
@@ -43836,7 +43836,7 @@
         <v>101.107575</v>
       </c>
       <c r="Q531" s="9" t="n">
-        <v>100.01524</v>
+        <v>100.013716</v>
       </c>
       <c r="R531" s="9" t="n">
         <v>98.497727</v>
@@ -43920,7 +43920,7 @@
         <v>101.182753</v>
       </c>
       <c r="Q532" s="6" t="n">
-        <v>100.071339</v>
+        <v>100.069662</v>
       </c>
       <c r="R532" s="6" t="n">
         <v>98.443996</v>
@@ -44004,7 +44004,7 @@
         <v>101.261328</v>
       </c>
       <c r="Q533" s="9" t="n">
-        <v>100.1412</v>
+        <v>100.139378</v>
       </c>
       <c r="R533" s="9" t="n">
         <v>98.37384900000001</v>
@@ -44088,7 +44088,7 @@
         <v>101.333157</v>
       </c>
       <c r="Q534" s="6" t="n">
-        <v>100.186566</v>
+        <v>100.184547</v>
       </c>
       <c r="R534" s="6" t="n">
         <v>98.32190900000001</v>
@@ -44172,7 +44172,7 @@
         <v>101.388526</v>
       </c>
       <c r="Q535" s="9" t="n">
-        <v>100.191925</v>
+        <v>100.189632</v>
       </c>
       <c r="R535" s="9" t="n">
         <v>98.320988</v>
@@ -44256,7 +44256,7 @@
         <v>101.414975</v>
       </c>
       <c r="Q536" s="6" t="n">
-        <v>100.155826</v>
+        <v>100.153181</v>
       </c>
       <c r="R536" s="6" t="n">
         <v>98.394139</v>
@@ -44340,7 +44340,7 @@
         <v>101.395846</v>
       </c>
       <c r="Q537" s="9" t="n">
-        <v>100.070851</v>
+        <v>100.067761</v>
       </c>
       <c r="R537" s="9" t="n">
         <v>98.56648199999999</v>
@@ -44424,7 +44424,7 @@
         <v>101.329275</v>
       </c>
       <c r="Q538" s="6" t="n">
-        <v>99.94256</v>
+        <v>99.93894299999999</v>
       </c>
       <c r="R538" s="6" t="n">
         <v>98.84993</v>
@@ -44508,7 +44508,7 @@
         <v>101.221741</v>
       </c>
       <c r="Q539" s="9" t="n">
-        <v>99.78784400000001</v>
+        <v>99.783644</v>
       </c>
       <c r="R539" s="9" t="n">
         <v>99.230948</v>
@@ -44592,7 +44592,7 @@
         <v>101.094689</v>
       </c>
       <c r="Q540" s="6" t="n">
-        <v>99.629643</v>
+        <v>99.62483899999999</v>
       </c>
       <c r="R540" s="6" t="n">
         <v>99.659589</v>
@@ -44676,7 +44676,7 @@
         <v>100.957811</v>
       </c>
       <c r="Q541" s="9" t="n">
-        <v>99.47808999999999</v>
+        <v>99.472677</v>
       </c>
       <c r="R541" s="9" t="n">
         <v>100.106184</v>
@@ -44760,7 +44760,7 @@
         <v>100.80569</v>
       </c>
       <c r="Q542" s="6" t="n">
-        <v>99.342145</v>
+        <v>99.336128</v>
       </c>
       <c r="R542" s="6" t="n">
         <v>100.522632</v>
@@ -44844,7 +44844,7 @@
         <v>100.650148</v>
       </c>
       <c r="Q543" s="9" t="n">
-        <v>99.22833199999999</v>
+        <v>99.221727</v>
       </c>
       <c r="R543" s="9" t="n">
         <v>100.875064</v>
@@ -44928,7 +44928,7 @@
         <v>100.488316</v>
       </c>
       <c r="Q544" s="6" t="n">
-        <v>99.15439499999999</v>
+        <v>99.14724099999999</v>
       </c>
       <c r="R544" s="6" t="n">
         <v>101.153039</v>
@@ -45012,7 +45012,7 @@
         <v>100.314638</v>
       </c>
       <c r="Q545" s="9" t="n">
-        <v>99.134806</v>
+        <v>99.127163</v>
       </c>
       <c r="R545" s="9" t="n">
         <v>101.343839</v>
@@ -45096,7 +45096,7 @@
         <v>100.133531</v>
       </c>
       <c r="Q546" s="6" t="n">
-        <v>99.173779</v>
+        <v>99.16571</v>
       </c>
       <c r="R546" s="6" t="n">
         <v>101.447589</v>
@@ -45180,7 +45180,7 @@
         <v>99.948623</v>
       </c>
       <c r="Q547" s="9" t="n">
-        <v>99.26040999999999</v>
+        <v>99.251963</v>
       </c>
       <c r="R547" s="9" t="n">
         <v>101.45805</v>
@@ -45264,7 +45264,7 @@
         <v>99.78811899999999</v>
       </c>
       <c r="Q548" s="6" t="n">
-        <v>99.38131</v>
+        <v>99.372514</v>
       </c>
       <c r="R548" s="6" t="n">
         <v>101.380664</v>
@@ -45348,7 +45348,7 @@
         <v>99.674441</v>
       </c>
       <c r="Q549" s="9" t="n">
-        <v>99.523329</v>
+        <v>99.51421000000001</v>
       </c>
       <c r="R549" s="9" t="n">
         <v>101.231243</v>
@@ -45432,7 +45432,7 @@
         <v>99.62838499999999</v>
       </c>
       <c r="Q550" s="6" t="n">
-        <v>99.663708</v>
+        <v>99.654281</v>
       </c>
       <c r="R550" s="6" t="n">
         <v>101.031533</v>
@@ -45516,7 +45516,7 @@
         <v>99.620283</v>
       </c>
       <c r="Q551" s="9" t="n">
-        <v>99.79405300000001</v>
+        <v>99.784363</v>
       </c>
       <c r="R551" s="9" t="n">
         <v>100.816525</v>
@@ -45600,7 +45600,7 @@
         <v>99.62472099999999</v>
       </c>
       <c r="Q552" s="6" t="n">
-        <v>99.92238</v>
+        <v>99.91254600000001</v>
       </c>
       <c r="R552" s="6" t="n">
         <v>100.611432</v>
@@ -45684,7 +45684,7 @@
         <v>99.61776999999999</v>
       </c>
       <c r="Q553" s="9" t="n">
-        <v>100.057421</v>
+        <v>100.047651</v>
       </c>
       <c r="R553" s="9" t="n">
         <v>100.428222</v>
@@ -45768,7 +45768,7 @@
         <v>99.59324599999999</v>
       </c>
       <c r="Q554" s="6" t="n">
-        <v>100.196242</v>
+        <v>100.186812</v>
       </c>
       <c r="R554" s="6" t="n">
         <v>100.258657</v>
@@ -45852,7 +45852,7 @@
         <v>99.54774500000001</v>
       </c>
       <c r="Q555" s="9" t="n">
-        <v>100.325005</v>
+        <v>100.316216</v>
       </c>
       <c r="R555" s="9" t="n">
         <v>100.094777</v>
@@ -45936,7 +45936,7 @@
         <v>99.488089</v>
       </c>
       <c r="Q556" s="6" t="n">
-        <v>100.443418</v>
+        <v>100.435533</v>
       </c>
       <c r="R556" s="6" t="n">
         <v>99.932554</v>
@@ -46020,7 +46020,7 @@
         <v>99.424121</v>
       </c>
       <c r="Q557" s="9" t="n">
-        <v>100.550998</v>
+        <v>100.544096</v>
       </c>
       <c r="R557" s="9" t="n">
         <v>99.776076</v>
@@ -46104,7 +46104,7 @@
         <v>99.36145999999999</v>
       </c>
       <c r="Q558" s="6" t="n">
-        <v>100.640728</v>
+        <v>100.634441</v>
       </c>
       <c r="R558" s="6" t="n">
         <v>99.643597</v>
@@ -46188,7 +46188,7 @@
         <v>99.303361</v>
       </c>
       <c r="Q559" s="9" t="n">
-        <v>100.694444</v>
+        <v>100.687597</v>
       </c>
       <c r="R559" s="9" t="n">
         <v>99.557343</v>
@@ -46272,7 +46272,7 @@
         <v>99.253698</v>
       </c>
       <c r="Q560" s="6" t="n">
-        <v>100.699667</v>
+        <v>100.689859</v>
       </c>
       <c r="R560" s="6" t="n">
         <v>99.530484</v>
@@ -46356,7 +46356,7 @@
         <v>99.21717200000001</v>
       </c>
       <c r="Q561" s="9" t="n">
-        <v>100.670984</v>
+        <v>100.654205</v>
       </c>
       <c r="R561" s="9" t="n">
         <v>99.544381</v>
@@ -46440,7 +46440,7 @@
         <v>99.195198</v>
       </c>
       <c r="Q562" s="6" t="n">
-        <v>100.622426</v>
+        <v>100.5928</v>
       </c>
       <c r="R562" s="6" t="n">
         <v>99.586506</v>
@@ -46524,7 +46524,7 @@
         <v>99.194997</v>
       </c>
       <c r="Q563" s="9" t="n">
-        <v>100.56123</v>
+        <v>100.511198</v>
       </c>
       <c r="R563" s="9" t="n">
         <v>99.64585</v>
@@ -46596,7 +46596,7 @@
         <v>99.205601</v>
       </c>
       <c r="Q564" s="6" t="n">
-        <v>100.496782</v>
+        <v>100.418174</v>
       </c>
       <c r="R564" s="6" t="n">
         <v>99.712586</v>

--- a/downloads/indicadores/SIC/SIC_datos.xlsx
+++ b/downloads/indicadores/SIC/SIC_datos.xlsx
@@ -671,11 +671,11 @@
         <v>97.07945100000001</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>98.58935</v>
+        <v>98.58717300000001</v>
       </c>
       <c r="K6" s="6" t="n"/>
       <c r="L6" s="6" t="n">
-        <v>97.32325899999999</v>
+        <v>97.319694</v>
       </c>
       <c r="M6" s="6" t="n"/>
       <c r="N6" s="6" t="n">
@@ -743,11 +743,11 @@
         <v>97.250129</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>98.622247</v>
+        <v>98.620119</v>
       </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n">
-        <v>97.46123299999999</v>
+        <v>97.457849</v>
       </c>
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n">
@@ -815,11 +815,11 @@
         <v>97.429852</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>98.658115</v>
+        <v>98.65603900000001</v>
       </c>
       <c r="K8" s="6" t="n"/>
       <c r="L8" s="6" t="n">
-        <v>97.592591</v>
+        <v>97.58938000000001</v>
       </c>
       <c r="M8" s="6" t="n"/>
       <c r="N8" s="6" t="n">
@@ -887,11 +887,11 @@
         <v>97.612549</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>98.70313899999999</v>
+        <v>98.701128</v>
       </c>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n">
-        <v>97.72369</v>
+        <v>97.720654</v>
       </c>
       <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n">
@@ -959,11 +959,11 @@
         <v>97.827876</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>98.770945</v>
+        <v>98.76903299999999</v>
       </c>
       <c r="K10" s="6" t="n"/>
       <c r="L10" s="6" t="n">
-        <v>97.863855</v>
+        <v>97.861007</v>
       </c>
       <c r="M10" s="6" t="n"/>
       <c r="N10" s="6" t="n">
@@ -1031,11 +1031,11 @@
         <v>98.094712</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>98.872792</v>
+        <v>98.871028</v>
       </c>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n">
-        <v>98.02603000000001</v>
+        <v>98.023399</v>
       </c>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n">
@@ -1103,11 +1103,11 @@
         <v>98.402804</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>99.019941</v>
+        <v>99.01839099999999</v>
       </c>
       <c r="K12" s="6" t="n"/>
       <c r="L12" s="6" t="n">
-        <v>98.21982</v>
+        <v>98.217446</v>
       </c>
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n">
@@ -1175,11 +1175,11 @@
         <v>98.744767</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>99.22602999999999</v>
+        <v>99.22478</v>
       </c>
       <c r="K13" s="9" t="n"/>
       <c r="L13" s="9" t="n">
-        <v>98.447202</v>
+        <v>98.445128</v>
       </c>
       <c r="M13" s="9" t="n"/>
       <c r="N13" s="9" t="n">
@@ -1247,11 +1247,11 @@
         <v>99.115554</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>99.475465</v>
+        <v>99.47457799999999</v>
       </c>
       <c r="K14" s="6" t="n"/>
       <c r="L14" s="6" t="n">
-        <v>98.698382</v>
+        <v>98.696641</v>
       </c>
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n">
@@ -1319,11 +1319,11 @@
         <v>99.51369</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>99.754203</v>
+        <v>99.753721</v>
       </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n">
-        <v>98.96257300000001</v>
+        <v>98.961184</v>
       </c>
       <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n">
@@ -1391,11 +1391,11 @@
         <v>99.91284400000001</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>100.04111</v>
+        <v>100.041046</v>
       </c>
       <c r="K16" s="6" t="n"/>
       <c r="L16" s="6" t="n">
-        <v>99.232394</v>
+        <v>99.231365</v>
       </c>
       <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n">
@@ -1463,11 +1463,11 @@
         <v>100.29497</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>100.321518</v>
+        <v>100.321862</v>
       </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n">
-        <v>99.519682</v>
+        <v>99.519037</v>
       </c>
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n">
@@ -1539,11 +1539,11 @@
         <v>100.670384</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>100.587278</v>
+        <v>100.588009</v>
       </c>
       <c r="K18" s="6" t="n"/>
       <c r="L18" s="6" t="n">
-        <v>99.83868699999999</v>
+        <v>99.83847</v>
       </c>
       <c r="M18" s="6" t="n"/>
       <c r="N18" s="6" t="n">
@@ -1617,11 +1617,11 @@
         <v>101.02324</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>100.837001</v>
+        <v>100.838095</v>
       </c>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n">
-        <v>100.187741</v>
+        <v>100.187992</v>
       </c>
       <c r="M19" s="9" t="n"/>
       <c r="N19" s="9" t="n">
@@ -1695,11 +1695,11 @@
         <v>101.348522</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>101.072042</v>
+        <v>101.073479</v>
       </c>
       <c r="K20" s="6" t="n"/>
       <c r="L20" s="6" t="n">
-        <v>100.558402</v>
+        <v>100.55915</v>
       </c>
       <c r="M20" s="6" t="n"/>
       <c r="N20" s="6" t="n">
@@ -1773,11 +1773,11 @@
         <v>101.650489</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>101.287742</v>
+        <v>101.289492</v>
       </c>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n">
-        <v>100.94178</v>
+        <v>100.943042</v>
       </c>
       <c r="M21" s="9" t="n"/>
       <c r="N21" s="9" t="n">
@@ -1851,11 +1851,11 @@
         <v>101.904045</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>101.479381</v>
+        <v>101.48141</v>
       </c>
       <c r="K22" s="6" t="n"/>
       <c r="L22" s="6" t="n">
-        <v>101.328437</v>
+        <v>101.330218</v>
       </c>
       <c r="M22" s="6" t="n"/>
       <c r="N22" s="6" t="n">
@@ -1929,11 +1929,11 @@
         <v>102.109505</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>101.649645</v>
+        <v>101.651922</v>
       </c>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n">
-        <v>101.708463</v>
+        <v>101.710752</v>
       </c>
       <c r="M23" s="9" t="n"/>
       <c r="N23" s="9" t="n">
@@ -2007,11 +2007,11 @@
         <v>102.283409</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>101.79942</v>
+        <v>101.801915</v>
       </c>
       <c r="K24" s="6" t="n"/>
       <c r="L24" s="6" t="n">
-        <v>102.069809</v>
+        <v>102.072578</v>
       </c>
       <c r="M24" s="6" t="n"/>
       <c r="N24" s="6" t="n">
@@ -2085,11 +2085,11 @@
         <v>102.434646</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>101.920626</v>
+        <v>101.923297</v>
       </c>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n">
-        <v>102.399888</v>
+        <v>102.403093</v>
       </c>
       <c r="M25" s="9" t="n"/>
       <c r="N25" s="9" t="n">
@@ -2163,11 +2163,11 @@
         <v>102.549871</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>102.00552</v>
+        <v>102.008314</v>
       </c>
       <c r="K26" s="6" t="n"/>
       <c r="L26" s="6" t="n">
-        <v>102.683582</v>
+        <v>102.68716</v>
       </c>
       <c r="M26" s="6" t="n"/>
       <c r="N26" s="6" t="n">
@@ -2241,11 +2241,11 @@
         <v>102.622129</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>102.050993</v>
+        <v>102.053854</v>
       </c>
       <c r="K27" s="9" t="n"/>
       <c r="L27" s="9" t="n">
-        <v>102.900914</v>
+        <v>102.904778</v>
       </c>
       <c r="M27" s="9" t="n"/>
       <c r="N27" s="9" t="n">
@@ -2319,11 +2319,11 @@
         <v>102.615231</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>102.065006</v>
+        <v>102.067887</v>
       </c>
       <c r="K28" s="6" t="n"/>
       <c r="L28" s="6" t="n">
-        <v>103.037238</v>
+        <v>103.041282</v>
       </c>
       <c r="M28" s="6" t="n"/>
       <c r="N28" s="6" t="n">
@@ -2397,11 +2397,11 @@
         <v>102.509532</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>102.054786</v>
+        <v>102.057652</v>
       </c>
       <c r="K29" s="9" t="n"/>
       <c r="L29" s="9" t="n">
-        <v>103.084149</v>
+        <v>103.088254</v>
       </c>
       <c r="M29" s="9" t="n"/>
       <c r="N29" s="9" t="n">
@@ -2475,11 +2475,11 @@
         <v>102.330116</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>102.02599</v>
+        <v>102.028814</v>
       </c>
       <c r="K30" s="6" t="n"/>
       <c r="L30" s="6" t="n">
-        <v>103.044942</v>
+        <v>103.048994</v>
       </c>
       <c r="M30" s="6" t="n"/>
       <c r="N30" s="6" t="n">
@@ -2553,11 +2553,11 @@
         <v>102.130745</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>101.969802</v>
+        <v>101.972544</v>
       </c>
       <c r="K31" s="9" t="n"/>
       <c r="L31" s="9" t="n">
-        <v>102.941093</v>
+        <v>102.94501</v>
       </c>
       <c r="M31" s="9" t="n"/>
       <c r="N31" s="9" t="n">
@@ -2631,11 +2631,11 @@
         <v>101.942022</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>101.876508</v>
+        <v>101.879115</v>
       </c>
       <c r="K32" s="6" t="n"/>
       <c r="L32" s="6" t="n">
-        <v>102.797372</v>
+        <v>102.801102</v>
       </c>
       <c r="M32" s="6" t="n"/>
       <c r="N32" s="6" t="n">
@@ -2709,11 +2709,11 @@
         <v>101.785462</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>101.740554</v>
+        <v>101.742962</v>
       </c>
       <c r="K33" s="9" t="n"/>
       <c r="L33" s="9" t="n">
-        <v>102.627505</v>
+        <v>102.631013</v>
       </c>
       <c r="M33" s="9" t="n"/>
       <c r="N33" s="9" t="n">
@@ -2787,11 +2787,11 @@
         <v>101.641114</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>101.560305</v>
+        <v>101.562451</v>
       </c>
       <c r="K34" s="6" t="n"/>
       <c r="L34" s="6" t="n">
-        <v>102.427312</v>
+        <v>102.430556</v>
       </c>
       <c r="M34" s="6" t="n"/>
       <c r="N34" s="6" t="n">
@@ -2865,11 +2865,11 @@
         <v>101.47724</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>101.330008</v>
+        <v>101.331819</v>
       </c>
       <c r="K35" s="9" t="n"/>
       <c r="L35" s="9" t="n">
-        <v>102.181904</v>
+        <v>102.184822</v>
       </c>
       <c r="M35" s="9" t="n"/>
       <c r="N35" s="9" t="n">
@@ -2943,11 +2943,11 @@
         <v>101.282818</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>101.053452</v>
+        <v>101.054861</v>
       </c>
       <c r="K36" s="6" t="n"/>
       <c r="L36" s="6" t="n">
-        <v>101.874126</v>
+        <v>101.876632</v>
       </c>
       <c r="M36" s="6" t="n"/>
       <c r="N36" s="6" t="n">
@@ -3021,11 +3021,11 @@
         <v>101.04874</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>100.742887</v>
+        <v>100.743844</v>
       </c>
       <c r="K37" s="9" t="n"/>
       <c r="L37" s="9" t="n">
-        <v>101.506998</v>
+        <v>101.50901</v>
       </c>
       <c r="M37" s="9" t="n"/>
       <c r="N37" s="9" t="n">
@@ -3099,11 +3099,11 @@
         <v>100.761233</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>100.410384</v>
+        <v>100.410857</v>
       </c>
       <c r="K38" s="6" t="n"/>
       <c r="L38" s="6" t="n">
-        <v>101.104491</v>
+        <v>101.105963</v>
       </c>
       <c r="M38" s="6" t="n"/>
       <c r="N38" s="6" t="n">
@@ -3177,11 +3177,11 @@
         <v>100.426897</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>100.07545</v>
+        <v>100.075436</v>
       </c>
       <c r="K39" s="9" t="n"/>
       <c r="L39" s="9" t="n">
-        <v>100.700541</v>
+        <v>100.70147</v>
       </c>
       <c r="M39" s="9" t="n"/>
       <c r="N39" s="9" t="n">
@@ -3255,11 +3255,11 @@
         <v>100.089284</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>99.761246</v>
+        <v>99.760775</v>
       </c>
       <c r="K40" s="6" t="n"/>
       <c r="L40" s="6" t="n">
-        <v>100.323359</v>
+        <v>100.323783</v>
       </c>
       <c r="M40" s="6" t="n"/>
       <c r="N40" s="6" t="n">
@@ -3333,11 +3333,11 @@
         <v>99.77172299999999</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>99.45737699999999</v>
+        <v>99.456463</v>
       </c>
       <c r="K41" s="9" t="n"/>
       <c r="L41" s="9" t="n">
-        <v>99.981059</v>
+        <v>99.981026</v>
       </c>
       <c r="M41" s="9" t="n"/>
       <c r="N41" s="9" t="n">
@@ -3411,11 +3411,11 @@
         <v>99.472623</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>99.166647</v>
+        <v>99.165311</v>
       </c>
       <c r="K42" s="6" t="n"/>
       <c r="L42" s="6" t="n">
-        <v>99.67756300000001</v>
+        <v>99.677126</v>
       </c>
       <c r="M42" s="6" t="n"/>
       <c r="N42" s="6" t="n">
@@ -3489,11 +3489,11 @@
         <v>99.193883</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>98.900745</v>
+        <v>98.899021</v>
       </c>
       <c r="K43" s="9" t="n"/>
       <c r="L43" s="9" t="n">
-        <v>99.41450399999999</v>
+        <v>99.413718</v>
       </c>
       <c r="M43" s="9" t="n"/>
       <c r="N43" s="9" t="n">
@@ -3567,11 +3567,11 @@
         <v>98.940072</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>98.677992</v>
+        <v>98.675944</v>
       </c>
       <c r="K44" s="6" t="n"/>
       <c r="L44" s="6" t="n">
-        <v>99.191836</v>
+        <v>99.190757</v>
       </c>
       <c r="M44" s="6" t="n"/>
       <c r="N44" s="6" t="n">
@@ -3645,11 +3645,11 @@
         <v>98.72941</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>98.50814</v>
+        <v>98.505844</v>
       </c>
       <c r="K45" s="9" t="n"/>
       <c r="L45" s="9" t="n">
-        <v>99.010448</v>
+        <v>99.00913</v>
       </c>
       <c r="M45" s="9" t="n"/>
       <c r="N45" s="9" t="n">
@@ -3723,11 +3723,11 @@
         <v>98.609694</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>98.388561</v>
+        <v>98.386092</v>
       </c>
       <c r="K46" s="6" t="n"/>
       <c r="L46" s="6" t="n">
-        <v>98.863429</v>
+        <v>98.86191599999999</v>
       </c>
       <c r="M46" s="6" t="n"/>
       <c r="N46" s="6" t="n">
@@ -3801,11 +3801,11 @@
         <v>98.57434000000001</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>98.32114</v>
+        <v>98.318573</v>
       </c>
       <c r="K47" s="9" t="n"/>
       <c r="L47" s="9" t="n">
-        <v>98.744265</v>
+        <v>98.742594</v>
       </c>
       <c r="M47" s="9" t="n"/>
       <c r="N47" s="9" t="n">
@@ -3879,11 +3879,11 @@
         <v>98.60993000000001</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>98.304159</v>
+        <v>98.30156700000001</v>
       </c>
       <c r="K48" s="6" t="n"/>
       <c r="L48" s="6" t="n">
-        <v>98.657923</v>
+        <v>98.656136</v>
       </c>
       <c r="M48" s="6" t="n"/>
       <c r="N48" s="6" t="n">
@@ -3957,11 +3957,11 @@
         <v>98.701831</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>98.334965</v>
+        <v>98.332418</v>
       </c>
       <c r="K49" s="9" t="n"/>
       <c r="L49" s="9" t="n">
-        <v>98.601078</v>
+        <v>98.59921199999999</v>
       </c>
       <c r="M49" s="9" t="n"/>
       <c r="N49" s="9" t="n">
@@ -4035,11 +4035,11 @@
         <v>98.86187099999999</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>98.407031</v>
+        <v>98.404588</v>
       </c>
       <c r="K50" s="6" t="n"/>
       <c r="L50" s="6" t="n">
-        <v>98.56989</v>
+        <v>98.56798000000001</v>
       </c>
       <c r="M50" s="6" t="n"/>
       <c r="N50" s="6" t="n">
@@ -4113,11 +4113,11 @@
         <v>99.075231</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>98.51320800000001</v>
+        <v>98.51092</v>
       </c>
       <c r="K51" s="9" t="n"/>
       <c r="L51" s="9" t="n">
-        <v>98.56132599999999</v>
+        <v>98.55940200000001</v>
       </c>
       <c r="M51" s="9" t="n"/>
       <c r="N51" s="9" t="n">
@@ -4191,11 +4191,11 @@
         <v>99.304771</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>98.645276</v>
+        <v>98.64318</v>
       </c>
       <c r="K52" s="6" t="n"/>
       <c r="L52" s="6" t="n">
-        <v>98.57610099999999</v>
+        <v>98.574197</v>
       </c>
       <c r="M52" s="6" t="n"/>
       <c r="N52" s="6" t="n">
@@ -4269,11 +4269,11 @@
         <v>99.55051899999999</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>98.794917</v>
+        <v>98.79303899999999</v>
       </c>
       <c r="K53" s="9" t="n"/>
       <c r="L53" s="9" t="n">
-        <v>98.617895</v>
+        <v>98.61604800000001</v>
       </c>
       <c r="M53" s="9" t="n"/>
       <c r="N53" s="9" t="n">
@@ -4347,11 +4347,11 @@
         <v>99.781324</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>98.94739199999999</v>
+        <v>98.945735</v>
       </c>
       <c r="K54" s="6" t="n"/>
       <c r="L54" s="6" t="n">
-        <v>98.687381</v>
+        <v>98.68562799999999</v>
       </c>
       <c r="M54" s="6" t="n"/>
       <c r="N54" s="6" t="n">
@@ -4425,11 +4425,11 @@
         <v>99.941276</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>99.102486</v>
+        <v>99.101055</v>
       </c>
       <c r="K55" s="9" t="n"/>
       <c r="L55" s="9" t="n">
-        <v>98.78101599999999</v>
+        <v>98.77939000000001</v>
       </c>
       <c r="M55" s="9" t="n"/>
       <c r="N55" s="9" t="n">
@@ -4503,11 +4503,11 @@
         <v>100.04085</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>99.259035</v>
+        <v>99.25783300000001</v>
       </c>
       <c r="K56" s="6" t="n"/>
       <c r="L56" s="6" t="n">
-        <v>98.894165</v>
+        <v>98.892691</v>
       </c>
       <c r="M56" s="6" t="n"/>
       <c r="N56" s="6" t="n">
@@ -4581,11 +4581,11 @@
         <v>100.101249</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>99.421817</v>
+        <v>99.420851</v>
       </c>
       <c r="K57" s="9" t="n"/>
       <c r="L57" s="9" t="n">
-        <v>99.01990600000001</v>
+        <v>99.018602</v>
       </c>
       <c r="M57" s="9" t="n"/>
       <c r="N57" s="9" t="n">
@@ -4659,11 +4659,11 @@
         <v>100.161775</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>99.596512</v>
+        <v>99.5958</v>
       </c>
       <c r="K58" s="6" t="n"/>
       <c r="L58" s="6" t="n">
-        <v>99.16272600000001</v>
+        <v>99.161614</v>
       </c>
       <c r="M58" s="6" t="n"/>
       <c r="N58" s="6" t="n">
@@ -4737,11 +4737,11 @@
         <v>100.272431</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>99.782274</v>
+        <v>99.78183300000001</v>
       </c>
       <c r="K59" s="9" t="n"/>
       <c r="L59" s="9" t="n">
-        <v>99.326973</v>
+        <v>99.326081</v>
       </c>
       <c r="M59" s="9" t="n"/>
       <c r="N59" s="9" t="n">
@@ -4815,11 +4815,11 @@
         <v>100.412885</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>99.965996</v>
+        <v>99.965822</v>
       </c>
       <c r="K60" s="6" t="n"/>
       <c r="L60" s="6" t="n">
-        <v>99.514467</v>
+        <v>99.513823</v>
       </c>
       <c r="M60" s="6" t="n"/>
       <c r="N60" s="6" t="n">
@@ -4893,11 +4893,11 @@
         <v>100.526602</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>100.1358</v>
+        <v>100.135873</v>
       </c>
       <c r="K61" s="9" t="n"/>
       <c r="L61" s="9" t="n">
-        <v>99.722132</v>
+        <v>99.721763</v>
       </c>
       <c r="M61" s="9" t="n"/>
       <c r="N61" s="9" t="n">
@@ -4971,11 +4971,11 @@
         <v>100.607962</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>100.290933</v>
+        <v>100.291232</v>
       </c>
       <c r="K62" s="6" t="n"/>
       <c r="L62" s="6" t="n">
-        <v>99.939431</v>
+        <v>99.93935</v>
       </c>
       <c r="M62" s="6" t="n"/>
       <c r="N62" s="6" t="n">
@@ -5049,11 +5049,11 @@
         <v>100.660417</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>100.437294</v>
+        <v>100.437806</v>
       </c>
       <c r="K63" s="9" t="n"/>
       <c r="L63" s="9" t="n">
-        <v>100.147791</v>
+        <v>100.147988</v>
       </c>
       <c r="M63" s="9" t="n"/>
       <c r="N63" s="9" t="n">
@@ -5127,11 +5127,11 @@
         <v>100.738791</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>100.602424</v>
+        <v>100.603176</v>
       </c>
       <c r="K64" s="6" t="n"/>
       <c r="L64" s="6" t="n">
-        <v>100.328309</v>
+        <v>100.328747</v>
       </c>
       <c r="M64" s="6" t="n"/>
       <c r="N64" s="6" t="n">
@@ -5205,11 +5205,11 @@
         <v>100.855855</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>100.772104</v>
+        <v>100.773103</v>
       </c>
       <c r="K65" s="9" t="n"/>
       <c r="L65" s="9" t="n">
-        <v>100.471213</v>
+        <v>100.471841</v>
       </c>
       <c r="M65" s="9" t="n"/>
       <c r="N65" s="9" t="n">
@@ -5283,11 +5283,11 @@
         <v>100.988432</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>100.929198</v>
+        <v>100.930425</v>
       </c>
       <c r="K66" s="6" t="n"/>
       <c r="L66" s="6" t="n">
-        <v>100.577195</v>
+        <v>100.577966</v>
       </c>
       <c r="M66" s="6" t="n"/>
       <c r="N66" s="6" t="n">
@@ -5361,11 +5361,11 @@
         <v>101.110681</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>101.062607</v>
+        <v>101.064028</v>
       </c>
       <c r="K67" s="9" t="n"/>
       <c r="L67" s="9" t="n">
-        <v>100.652599</v>
+        <v>100.653472</v>
       </c>
       <c r="M67" s="9" t="n"/>
       <c r="N67" s="9" t="n">
@@ -5439,11 +5439,11 @@
         <v>101.194781</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>101.163665</v>
+        <v>101.165233</v>
       </c>
       <c r="K68" s="6" t="n"/>
       <c r="L68" s="6" t="n">
-        <v>100.710123</v>
+        <v>100.711073</v>
       </c>
       <c r="M68" s="6" t="n"/>
       <c r="N68" s="6" t="n">
@@ -5517,11 +5517,11 @@
         <v>101.251699</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>101.236182</v>
+        <v>101.237855</v>
       </c>
       <c r="K69" s="9" t="n"/>
       <c r="L69" s="9" t="n">
-        <v>100.749759</v>
+        <v>100.750763</v>
       </c>
       <c r="M69" s="9" t="n"/>
       <c r="N69" s="9" t="n">
@@ -5595,11 +5595,11 @@
         <v>101.291784</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>101.299382</v>
+        <v>101.301148</v>
       </c>
       <c r="K70" s="6" t="n"/>
       <c r="L70" s="6" t="n">
-        <v>100.768711</v>
+        <v>100.76974</v>
       </c>
       <c r="M70" s="6" t="n"/>
       <c r="N70" s="6" t="n">
@@ -5673,11 +5673,11 @@
         <v>101.329983</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>101.352962</v>
+        <v>101.354806</v>
       </c>
       <c r="K71" s="9" t="n"/>
       <c r="L71" s="9" t="n">
-        <v>100.76354</v>
+        <v>100.764562</v>
       </c>
       <c r="M71" s="9" t="n"/>
       <c r="N71" s="9" t="n">
@@ -5751,11 +5751,11 @@
         <v>101.337441</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>101.379265</v>
+        <v>101.381146</v>
       </c>
       <c r="K72" s="6" t="n"/>
       <c r="L72" s="6" t="n">
-        <v>100.724239</v>
+        <v>100.725208</v>
       </c>
       <c r="M72" s="6" t="n"/>
       <c r="N72" s="6" t="n">
@@ -5829,11 +5829,11 @@
         <v>101.310338</v>
       </c>
       <c r="J73" s="9" t="n">
-        <v>101.363738</v>
+        <v>101.365597</v>
       </c>
       <c r="K73" s="9" t="n"/>
       <c r="L73" s="9" t="n">
-        <v>100.641573</v>
+        <v>100.642431</v>
       </c>
       <c r="M73" s="9" t="n"/>
       <c r="N73" s="9" t="n">
@@ -5907,11 +5907,11 @@
         <v>101.231405</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>101.309855</v>
+        <v>101.311635</v>
       </c>
       <c r="K74" s="6" t="n"/>
       <c r="L74" s="6" t="n">
-        <v>100.52238</v>
+        <v>100.523078</v>
       </c>
       <c r="M74" s="6" t="n"/>
       <c r="N74" s="6" t="n">
@@ -5985,11 +5985,11 @@
         <v>101.086615</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>101.220777</v>
+        <v>101.222428</v>
       </c>
       <c r="K75" s="9" t="n"/>
       <c r="L75" s="9" t="n">
-        <v>100.377874</v>
+        <v>100.37838</v>
       </c>
       <c r="M75" s="9" t="n"/>
       <c r="N75" s="9" t="n">
@@ -6063,11 +6063,11 @@
         <v>100.8942</v>
       </c>
       <c r="J76" s="6" t="n">
-        <v>101.100083</v>
+        <v>101.101558</v>
       </c>
       <c r="K76" s="6" t="n"/>
       <c r="L76" s="6" t="n">
-        <v>100.227707</v>
+        <v>100.228013</v>
       </c>
       <c r="M76" s="6" t="n"/>
       <c r="N76" s="6" t="n">
@@ -6141,11 +6141,11 @@
         <v>100.660268</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>100.95041</v>
+        <v>100.951667</v>
       </c>
       <c r="K77" s="9" t="n"/>
       <c r="L77" s="9" t="n">
-        <v>100.08358</v>
+        <v>100.083696</v>
       </c>
       <c r="M77" s="9" t="n"/>
       <c r="N77" s="9" t="n">
@@ -6219,13 +6219,13 @@
         <v>100.405843</v>
       </c>
       <c r="J78" s="6" t="n">
-        <v>100.776632</v>
+        <v>100.777636</v>
       </c>
       <c r="K78" s="6" t="n">
         <v>104.277162</v>
       </c>
       <c r="L78" s="6" t="n">
-        <v>99.94891800000001</v>
+        <v>99.94885499999999</v>
       </c>
       <c r="M78" s="6" t="n"/>
       <c r="N78" s="6" t="n">
@@ -6299,13 +6299,13 @@
         <v>100.200927</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>100.569842</v>
+        <v>100.570545</v>
       </c>
       <c r="K79" s="9" t="n">
         <v>103.636482</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>99.825474</v>
+        <v>99.825245</v>
       </c>
       <c r="M79" s="9" t="n"/>
       <c r="N79" s="9" t="n">
@@ -6379,13 +6379,13 @@
         <v>100.02684</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>100.321141</v>
+        <v>100.321482</v>
       </c>
       <c r="K80" s="6" t="n">
         <v>103.010763</v>
       </c>
       <c r="L80" s="6" t="n">
-        <v>99.71291600000001</v>
+        <v>99.712536</v>
       </c>
       <c r="M80" s="6" t="n"/>
       <c r="N80" s="6" t="n">
@@ -6459,13 +6459,13 @@
         <v>99.837746</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>100.034707</v>
+        <v>100.034632</v>
       </c>
       <c r="K81" s="9" t="n">
         <v>102.412687</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>99.604201</v>
+        <v>99.603674</v>
       </c>
       <c r="M81" s="9" t="n"/>
       <c r="N81" s="9" t="n">
@@ -6539,13 +6539,13 @@
         <v>99.643517</v>
       </c>
       <c r="J82" s="6" t="n">
-        <v>99.704797</v>
+        <v>99.70424199999999</v>
       </c>
       <c r="K82" s="6" t="n">
         <v>101.868368</v>
       </c>
       <c r="L82" s="6" t="n">
-        <v>99.488916</v>
+        <v>99.488235</v>
       </c>
       <c r="M82" s="6" t="n"/>
       <c r="N82" s="6" t="n">
@@ -6619,13 +6619,13 @@
         <v>99.397637</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>99.35336</v>
+        <v>99.352293</v>
       </c>
       <c r="K83" s="9" t="n">
         <v>101.38788</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>99.35478000000001</v>
+        <v>99.353919</v>
       </c>
       <c r="M83" s="9" t="n"/>
       <c r="N83" s="9" t="n">
@@ -6699,13 +6699,13 @@
         <v>99.089911</v>
       </c>
       <c r="J84" s="6" t="n">
-        <v>99.023065</v>
+        <v>99.021517</v>
       </c>
       <c r="K84" s="6" t="n">
         <v>100.980329</v>
       </c>
       <c r="L84" s="6" t="n">
-        <v>99.19711100000001</v>
+        <v>99.196039</v>
       </c>
       <c r="M84" s="6" t="n"/>
       <c r="N84" s="6" t="n">
@@ -6779,13 +6779,13 @@
         <v>98.80702100000001</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>98.744006</v>
+        <v>98.742053</v>
       </c>
       <c r="K85" s="9" t="n">
         <v>100.599872</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>99.03012099999999</v>
+        <v>99.028826</v>
       </c>
       <c r="M85" s="9" t="n"/>
       <c r="N85" s="9" t="n">
@@ -6859,13 +6859,13 @@
         <v>98.577631</v>
       </c>
       <c r="J86" s="6" t="n">
-        <v>98.535658</v>
+        <v>98.533401</v>
       </c>
       <c r="K86" s="6" t="n">
         <v>100.235006</v>
       </c>
       <c r="L86" s="6" t="n">
-        <v>98.86909199999999</v>
+        <v>98.867582</v>
       </c>
       <c r="M86" s="6" t="n"/>
       <c r="N86" s="6" t="n">
@@ -6939,13 +6939,13 @@
         <v>98.43034400000001</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>98.404346</v>
+        <v>98.401898</v>
       </c>
       <c r="K87" s="9" t="n">
         <v>99.87936000000001</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>98.72944200000001</v>
+        <v>98.72774699999999</v>
       </c>
       <c r="M87" s="9" t="n"/>
       <c r="N87" s="9" t="n">
@@ -7019,13 +7019,13 @@
         <v>98.37706799999999</v>
       </c>
       <c r="J88" s="6" t="n">
-        <v>98.351652</v>
+        <v>98.349127</v>
       </c>
       <c r="K88" s="6" t="n">
         <v>99.57098499999999</v>
       </c>
       <c r="L88" s="6" t="n">
-        <v>98.621529</v>
+        <v>98.619692</v>
       </c>
       <c r="M88" s="6" t="n"/>
       <c r="N88" s="6" t="n">
@@ -7099,13 +7099,13 @@
         <v>98.40593</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>98.389895</v>
+        <v>98.387426</v>
       </c>
       <c r="K89" s="9" t="n">
         <v>99.319245</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>98.550332</v>
+        <v>98.548402</v>
       </c>
       <c r="M89" s="9" t="n"/>
       <c r="N89" s="9" t="n">
@@ -7179,13 +7179,13 @@
         <v>98.52335600000001</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>98.518118</v>
+        <v>98.51583599999999</v>
       </c>
       <c r="K90" s="6" t="n">
         <v>99.06425</v>
       </c>
       <c r="L90" s="6" t="n">
-        <v>98.515828</v>
+        <v>98.513853</v>
       </c>
       <c r="M90" s="6" t="n">
         <v>102.496955</v>
@@ -7261,13 +7261,13 @@
         <v>98.706035</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>98.722116</v>
+        <v>98.72013099999999</v>
       </c>
       <c r="K91" s="9" t="n">
         <v>98.80973</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>98.520296</v>
+        <v>98.51832899999999</v>
       </c>
       <c r="M91" s="9" t="n">
         <v>102.13848</v>
@@ -7343,13 +7343,13 @@
         <v>98.927432</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>98.97447</v>
+        <v>98.972852</v>
       </c>
       <c r="K92" s="6" t="n">
         <v>98.547287</v>
       </c>
       <c r="L92" s="6" t="n">
-        <v>98.563</v>
+        <v>98.561089</v>
       </c>
       <c r="M92" s="6" t="n">
         <v>101.742059</v>
@@ -7425,13 +7425,13 @@
         <v>99.173542</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>99.233842</v>
+        <v>99.232601</v>
       </c>
       <c r="K93" s="9" t="n">
         <v>98.28620600000001</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>98.644469</v>
+        <v>98.64266600000001</v>
       </c>
       <c r="M93" s="9" t="n">
         <v>101.333438</v>
@@ -7507,13 +7507,13 @@
         <v>99.368635</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>99.46646200000001</v>
+        <v>99.465559</v>
       </c>
       <c r="K94" s="6" t="n">
         <v>98.06012699999999</v>
       </c>
       <c r="L94" s="6" t="n">
-        <v>98.764669</v>
+        <v>98.763024</v>
       </c>
       <c r="M94" s="6" t="n">
         <v>100.932229</v>
@@ -7589,13 +7589,13 @@
         <v>99.501644</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>99.655137</v>
+        <v>99.654509</v>
       </c>
       <c r="K95" s="9" t="n">
         <v>97.97647600000001</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>98.91637799999999</v>
+        <v>98.914935</v>
       </c>
       <c r="M95" s="9" t="n">
         <v>100.592383</v>
@@ -7671,13 +7671,13 @@
         <v>99.59035299999999</v>
       </c>
       <c r="J96" s="6" t="n">
-        <v>99.798359</v>
+        <v>99.797939</v>
       </c>
       <c r="K96" s="6" t="n">
         <v>98.006775</v>
       </c>
       <c r="L96" s="6" t="n">
-        <v>99.086656</v>
+        <v>99.085436</v>
       </c>
       <c r="M96" s="6" t="n">
         <v>100.330256</v>
@@ -7753,13 +7753,13 @@
         <v>99.653149</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>99.89887</v>
+        <v>99.898597</v>
       </c>
       <c r="K97" s="9" t="n">
         <v>98.084563</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>99.257881</v>
+        <v>99.256884</v>
       </c>
       <c r="M97" s="9" t="n">
         <v>100.148861</v>
@@ -7835,13 +7835,13 @@
         <v>99.68222</v>
       </c>
       <c r="J98" s="6" t="n">
-        <v>99.956087</v>
+        <v>99.95589699999999</v>
       </c>
       <c r="K98" s="6" t="n">
         <v>98.135368</v>
       </c>
       <c r="L98" s="6" t="n">
-        <v>99.408941</v>
+        <v>99.408141</v>
       </c>
       <c r="M98" s="6" t="n">
         <v>100.048261</v>
@@ -7917,13 +7917,13 @@
         <v>99.685993</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>99.95533500000001</v>
+        <v>99.955144</v>
       </c>
       <c r="K99" s="9" t="n">
         <v>98.124526</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>99.51175499999999</v>
+        <v>99.51108600000001</v>
       </c>
       <c r="M99" s="9" t="n">
         <v>100.011166</v>
@@ -7999,13 +7999,13 @@
         <v>99.632316</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>99.89943100000001</v>
+        <v>99.899158</v>
       </c>
       <c r="K100" s="6" t="n">
         <v>98.046059</v>
       </c>
       <c r="L100" s="6" t="n">
-        <v>99.54842499999999</v>
+        <v>99.5478</v>
       </c>
       <c r="M100" s="6" t="n">
         <v>100.001183</v>
@@ -8081,13 +8081,13 @@
         <v>99.51055599999999</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>99.795593</v>
+        <v>99.79517</v>
       </c>
       <c r="K101" s="9" t="n">
         <v>97.91142600000001</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>99.52074500000001</v>
+        <v>99.520081</v>
       </c>
       <c r="M101" s="9" t="n">
         <v>100.034274</v>
@@ -8163,13 +8163,13 @@
         <v>99.347176</v>
       </c>
       <c r="J102" s="6" t="n">
-        <v>99.653147</v>
+        <v>99.65251600000001</v>
       </c>
       <c r="K102" s="6" t="n">
         <v>97.75468600000001</v>
       </c>
       <c r="L102" s="6" t="n">
-        <v>99.454106</v>
+        <v>99.45335799999999</v>
       </c>
       <c r="M102" s="6" t="n">
         <v>100.15432</v>
@@ -8245,13 +8245,13 @@
         <v>99.17376299999999</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>99.49907</v>
+        <v>99.498215</v>
       </c>
       <c r="K103" s="9" t="n">
         <v>97.605265</v>
       </c>
       <c r="L103" s="9" t="n">
-        <v>99.37481099999999</v>
+        <v>99.373966</v>
       </c>
       <c r="M103" s="9" t="n">
         <v>100.324502</v>
@@ -8327,13 +8327,13 @@
         <v>99.02681800000001</v>
       </c>
       <c r="J104" s="6" t="n">
-        <v>99.345505</v>
+        <v>99.344427</v>
       </c>
       <c r="K104" s="6" t="n">
         <v>97.48639799999999</v>
       </c>
       <c r="L104" s="6" t="n">
-        <v>99.293886</v>
+        <v>99.29294</v>
       </c>
       <c r="M104" s="6" t="n">
         <v>100.51421</v>
@@ -8409,13 +8409,13 @@
         <v>98.913107</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>99.215294</v>
+        <v>99.214026</v>
       </c>
       <c r="K105" s="9" t="n">
         <v>97.414941</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>99.215969</v>
+        <v>99.214922</v>
       </c>
       <c r="M105" s="9" t="n">
         <v>100.675399</v>
@@ -8491,13 +8491,13 @@
         <v>98.822852</v>
       </c>
       <c r="J106" s="6" t="n">
-        <v>99.127696</v>
+        <v>99.126301</v>
       </c>
       <c r="K106" s="6" t="n">
         <v>97.41417199999999</v>
       </c>
       <c r="L106" s="6" t="n">
-        <v>99.141437</v>
+        <v>99.140293</v>
       </c>
       <c r="M106" s="6" t="n">
         <v>100.794127</v>
@@ -8573,13 +8573,13 @@
         <v>98.74999200000001</v>
       </c>
       <c r="J107" s="9" t="n">
-        <v>99.095167</v>
+        <v>99.09372500000001</v>
       </c>
       <c r="K107" s="9" t="n">
         <v>97.45710200000001</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>99.069624</v>
+        <v>99.06838399999999</v>
       </c>
       <c r="M107" s="9" t="n">
         <v>100.866162</v>
@@ -8655,13 +8655,13 @@
         <v>98.703363</v>
       </c>
       <c r="J108" s="6" t="n">
-        <v>99.11968</v>
+        <v>99.118274</v>
       </c>
       <c r="K108" s="6" t="n">
         <v>97.554169</v>
       </c>
       <c r="L108" s="6" t="n">
-        <v>99.00220299999999</v>
+        <v>99.000872</v>
       </c>
       <c r="M108" s="6" t="n">
         <v>100.89237</v>
@@ -8737,13 +8737,13 @@
         <v>98.707352</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>99.22493799999999</v>
+        <v>99.223685</v>
       </c>
       <c r="K109" s="9" t="n">
         <v>97.712599</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>98.94246</v>
+        <v>98.94105</v>
       </c>
       <c r="M109" s="9" t="n">
         <v>100.898806</v>
@@ -8819,13 +8819,13 @@
         <v>98.788275</v>
       </c>
       <c r="J110" s="6" t="n">
-        <v>99.379597</v>
+        <v>99.37857</v>
       </c>
       <c r="K110" s="6" t="n">
         <v>97.913828</v>
       </c>
       <c r="L110" s="6" t="n">
-        <v>98.899957</v>
+        <v>98.898489</v>
       </c>
       <c r="M110" s="6" t="n">
         <v>100.908962</v>
@@ -8901,13 +8901,13 @@
         <v>98.931273</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>99.56705100000001</v>
+        <v>99.56629599999999</v>
       </c>
       <c r="K111" s="9" t="n">
         <v>98.11767999999999</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>98.88174600000001</v>
+        <v>98.88025399999999</v>
       </c>
       <c r="M111" s="9" t="n">
         <v>100.897366</v>
@@ -8983,13 +8983,13 @@
         <v>99.083788</v>
       </c>
       <c r="J112" s="6" t="n">
-        <v>99.757126</v>
+        <v>99.756648</v>
       </c>
       <c r="K112" s="6" t="n">
         <v>98.26485700000001</v>
       </c>
       <c r="L112" s="6" t="n">
-        <v>98.885704</v>
+        <v>98.884218</v>
       </c>
       <c r="M112" s="6" t="n">
         <v>100.856823</v>
@@ -9065,13 +9065,13 @@
         <v>99.250187</v>
       </c>
       <c r="J113" s="9" t="n">
-        <v>99.911863</v>
+        <v>99.91161099999999</v>
       </c>
       <c r="K113" s="9" t="n">
         <v>98.35598</v>
       </c>
       <c r="L113" s="9" t="n">
-        <v>98.905053</v>
+        <v>98.903593</v>
       </c>
       <c r="M113" s="9" t="n">
         <v>100.757101</v>
@@ -9147,13 +9147,13 @@
         <v>99.416923</v>
       </c>
       <c r="J114" s="6" t="n">
-        <v>100.02154</v>
+        <v>100.021448</v>
       </c>
       <c r="K114" s="6" t="n">
         <v>98.400333</v>
       </c>
       <c r="L114" s="6" t="n">
-        <v>98.935163</v>
+        <v>98.93374300000001</v>
       </c>
       <c r="M114" s="6" t="n">
         <v>100.577202</v>
@@ -9229,13 +9229,13 @@
         <v>99.561936</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>100.091478</v>
+        <v>100.091487</v>
       </c>
       <c r="K115" s="9" t="n">
         <v>98.43590399999999</v>
       </c>
       <c r="L115" s="9" t="n">
-        <v>98.97424599999999</v>
+        <v>98.972877</v>
       </c>
       <c r="M115" s="9" t="n">
         <v>100.332324</v>
@@ -9311,13 +9311,13 @@
         <v>99.674353</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>100.135664</v>
+        <v>100.135738</v>
       </c>
       <c r="K116" s="6" t="n">
         <v>98.500176</v>
       </c>
       <c r="L116" s="6" t="n">
-        <v>99.016775</v>
+        <v>99.015461</v>
       </c>
       <c r="M116" s="6" t="n">
         <v>100.077711</v>
@@ -9393,13 +9393,13 @@
         <v>99.749804</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>100.164734</v>
+        <v>100.164851</v>
       </c>
       <c r="K117" s="9" t="n">
         <v>98.618269</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>99.06672500000001</v>
+        <v>99.065478</v>
       </c>
       <c r="M117" s="9" t="n">
         <v>99.848631</v>
@@ -9475,13 +9475,13 @@
         <v>99.792914</v>
       </c>
       <c r="J118" s="6" t="n">
-        <v>100.171399</v>
+        <v>100.171526</v>
       </c>
       <c r="K118" s="6" t="n">
         <v>98.78058799999999</v>
       </c>
       <c r="L118" s="6" t="n">
-        <v>99.13109</v>
+        <v>99.129929</v>
       </c>
       <c r="M118" s="6" t="n">
         <v>99.66045800000001</v>
@@ -9557,13 +9557,13 @@
         <v>99.80533</v>
       </c>
       <c r="J119" s="9" t="n">
-        <v>100.148845</v>
+        <v>100.14894</v>
       </c>
       <c r="K119" s="9" t="n">
         <v>98.98394399999999</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>99.21430599999999</v>
+        <v>99.213256</v>
       </c>
       <c r="M119" s="9" t="n">
         <v>99.493289</v>
@@ -9639,13 +9639,13 @@
         <v>99.771565</v>
       </c>
       <c r="J120" s="6" t="n">
-        <v>100.084683</v>
+        <v>100.084684</v>
       </c>
       <c r="K120" s="6" t="n">
         <v>99.214545</v>
       </c>
       <c r="L120" s="6" t="n">
-        <v>99.315089</v>
+        <v>99.314172</v>
       </c>
       <c r="M120" s="6" t="n">
         <v>99.351692</v>
@@ -9721,13 +9721,13 @@
         <v>99.688689</v>
       </c>
       <c r="J121" s="9" t="n">
-        <v>99.994499</v>
+        <v>99.99437</v>
       </c>
       <c r="K121" s="9" t="n">
         <v>99.442705</v>
       </c>
       <c r="L121" s="9" t="n">
-        <v>99.430256</v>
+        <v>99.42949299999999</v>
       </c>
       <c r="M121" s="9" t="n">
         <v>99.21385600000001</v>
@@ -9803,13 +9803,13 @@
         <v>99.592313</v>
       </c>
       <c r="J122" s="6" t="n">
-        <v>99.89542</v>
+        <v>99.89514699999999</v>
       </c>
       <c r="K122" s="6" t="n">
         <v>99.62115799999999</v>
       </c>
       <c r="L122" s="6" t="n">
-        <v>99.55282099999999</v>
+        <v>99.552221</v>
       </c>
       <c r="M122" s="6" t="n">
         <v>99.05425200000001</v>
@@ -9885,13 +9885,13 @@
         <v>99.514679</v>
       </c>
       <c r="J123" s="9" t="n">
-        <v>99.827986</v>
+        <v>99.82761499999999</v>
       </c>
       <c r="K123" s="9" t="n">
         <v>99.66643500000001</v>
       </c>
       <c r="L123" s="9" t="n">
-        <v>99.678712</v>
+        <v>99.678282</v>
       </c>
       <c r="M123" s="9" t="n">
         <v>98.887705</v>
@@ -9967,13 +9967,13 @@
         <v>99.49818</v>
       </c>
       <c r="J124" s="6" t="n">
-        <v>99.820161</v>
+        <v>99.819779</v>
       </c>
       <c r="K124" s="6" t="n">
         <v>99.616951</v>
       </c>
       <c r="L124" s="6" t="n">
-        <v>99.801867</v>
+        <v>99.801605</v>
       </c>
       <c r="M124" s="6" t="n">
         <v>98.75347499999999</v>
@@ -10049,13 +10049,13 @@
         <v>99.568594</v>
       </c>
       <c r="J125" s="9" t="n">
-        <v>99.88627099999999</v>
+        <v>99.88598500000001</v>
       </c>
       <c r="K125" s="9" t="n">
         <v>99.507013</v>
       </c>
       <c r="L125" s="9" t="n">
-        <v>99.92892000000001</v>
+        <v>99.92883</v>
       </c>
       <c r="M125" s="9" t="n">
         <v>98.657574</v>
@@ -10131,13 +10131,13 @@
         <v>99.710211</v>
       </c>
       <c r="J126" s="6" t="n">
-        <v>100.023017</v>
+        <v>100.022931</v>
       </c>
       <c r="K126" s="6" t="n">
         <v>99.340031</v>
       </c>
       <c r="L126" s="6" t="n">
-        <v>100.067424</v>
+        <v>100.067521</v>
       </c>
       <c r="M126" s="6" t="n">
         <v>98.611852</v>
@@ -10213,13 +10213,13 @@
         <v>99.885671</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>100.198627</v>
+        <v>100.198798</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>99.22066599999999</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>100.222238</v>
+        <v>100.222544</v>
       </c>
       <c r="M127" s="9" t="n">
         <v>98.667597</v>
@@ -10295,13 +10295,13 @@
         <v>100.068102</v>
       </c>
       <c r="J128" s="6" t="n">
-        <v>100.393322</v>
+        <v>100.393776</v>
       </c>
       <c r="K128" s="6" t="n">
         <v>99.24896200000001</v>
       </c>
       <c r="L128" s="6" t="n">
-        <v>100.393793</v>
+        <v>100.394328</v>
       </c>
       <c r="M128" s="6" t="n">
         <v>98.84280699999999</v>
@@ -10377,13 +10377,13 @@
         <v>100.257203</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>100.563498</v>
+        <v>100.5642</v>
       </c>
       <c r="K129" s="9" t="n">
         <v>99.384401</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>100.581</v>
+        <v>100.581786</v>
       </c>
       <c r="M129" s="9" t="n">
         <v>99.110589</v>
@@ -10459,13 +10459,13 @@
         <v>100.394832</v>
       </c>
       <c r="J130" s="6" t="n">
-        <v>100.712197</v>
+        <v>100.713116</v>
       </c>
       <c r="K130" s="6" t="n">
         <v>99.60697500000001</v>
       </c>
       <c r="L130" s="6" t="n">
-        <v>100.777689</v>
+        <v>100.778736</v>
       </c>
       <c r="M130" s="6" t="n">
         <v>99.397327</v>
@@ -10541,13 +10541,13 @@
         <v>100.505706</v>
       </c>
       <c r="J131" s="9" t="n">
-        <v>100.819985</v>
+        <v>100.821062</v>
       </c>
       <c r="K131" s="9" t="n">
         <v>99.88468899999999</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>100.982294</v>
+        <v>100.98361</v>
       </c>
       <c r="M131" s="9" t="n">
         <v>99.63914</v>
@@ -10623,13 +10623,13 @@
         <v>100.587575</v>
       </c>
       <c r="J132" s="6" t="n">
-        <v>100.880383</v>
+        <v>100.881548</v>
       </c>
       <c r="K132" s="6" t="n">
         <v>100.181375</v>
       </c>
       <c r="L132" s="6" t="n">
-        <v>101.190983</v>
+        <v>101.192575</v>
       </c>
       <c r="M132" s="6" t="n">
         <v>99.768687</v>
@@ -10705,13 +10705,13 @@
         <v>100.64489</v>
       </c>
       <c r="J133" s="9" t="n">
-        <v>100.888114</v>
+        <v>100.889291</v>
       </c>
       <c r="K133" s="9" t="n">
         <v>100.492003</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>101.399489</v>
+        <v>101.401357</v>
       </c>
       <c r="M133" s="9" t="n">
         <v>99.74057500000001</v>
@@ -10787,13 +10787,13 @@
         <v>100.694359</v>
       </c>
       <c r="J134" s="6" t="n">
-        <v>100.849595</v>
+        <v>100.850717</v>
       </c>
       <c r="K134" s="6" t="n">
         <v>100.810063</v>
       </c>
       <c r="L134" s="6" t="n">
-        <v>101.602138</v>
+        <v>101.604274</v>
       </c>
       <c r="M134" s="6" t="n">
         <v>99.62345000000001</v>
@@ -10869,13 +10869,13 @@
         <v>100.733577</v>
       </c>
       <c r="J135" s="9" t="n">
-        <v>100.776308</v>
+        <v>100.777324</v>
       </c>
       <c r="K135" s="9" t="n">
         <v>101.149559</v>
       </c>
       <c r="L135" s="9" t="n">
-        <v>101.793095</v>
+        <v>101.795487</v>
       </c>
       <c r="M135" s="9" t="n">
         <v>99.486448</v>
@@ -10951,13 +10951,13 @@
         <v>100.761333</v>
       </c>
       <c r="J136" s="6" t="n">
-        <v>100.677985</v>
+        <v>100.678858</v>
       </c>
       <c r="K136" s="6" t="n">
         <v>101.50124</v>
       </c>
       <c r="L136" s="6" t="n">
-        <v>101.973143</v>
+        <v>101.975778</v>
       </c>
       <c r="M136" s="6" t="n">
         <v>99.296544</v>
@@ -11033,13 +11033,13 @@
         <v>100.778761</v>
       </c>
       <c r="J137" s="9" t="n">
-        <v>100.583151</v>
+        <v>100.583887</v>
       </c>
       <c r="K137" s="9" t="n">
         <v>101.749734</v>
       </c>
       <c r="L137" s="9" t="n">
-        <v>102.142695</v>
+        <v>102.145559</v>
       </c>
       <c r="M137" s="9" t="n">
         <v>99.101662</v>
@@ -11115,13 +11115,13 @@
         <v>100.793475</v>
       </c>
       <c r="J138" s="6" t="n">
-        <v>100.516246</v>
+        <v>100.516886</v>
       </c>
       <c r="K138" s="6" t="n">
         <v>101.909866</v>
       </c>
       <c r="L138" s="6" t="n">
-        <v>102.29734</v>
+        <v>102.300413</v>
       </c>
       <c r="M138" s="6" t="n">
         <v>98.91026599999999</v>
@@ -11197,13 +11197,13 @@
         <v>100.843834</v>
       </c>
       <c r="J139" s="9" t="n">
-        <v>100.473163</v>
+        <v>100.473741</v>
       </c>
       <c r="K139" s="9" t="n">
         <v>101.988702</v>
       </c>
       <c r="L139" s="9" t="n">
-        <v>102.435345</v>
+        <v>102.438604</v>
       </c>
       <c r="M139" s="9" t="n">
         <v>98.717378</v>
@@ -11279,13 +11279,13 @@
         <v>100.920915</v>
       </c>
       <c r="J140" s="6" t="n">
-        <v>100.447981</v>
+        <v>100.448523</v>
       </c>
       <c r="K140" s="6" t="n">
         <v>102.03686</v>
       </c>
       <c r="L140" s="6" t="n">
-        <v>102.554626</v>
+        <v>102.558045</v>
       </c>
       <c r="M140" s="6" t="n">
         <v>98.53489999999999</v>
@@ -11361,13 +11361,13 @@
         <v>100.988605</v>
       </c>
       <c r="J141" s="9" t="n">
-        <v>100.439227</v>
+        <v>100.439758</v>
       </c>
       <c r="K141" s="9" t="n">
         <v>102.074398</v>
       </c>
       <c r="L141" s="9" t="n">
-        <v>102.654805</v>
+        <v>102.658359</v>
       </c>
       <c r="M141" s="9" t="n">
         <v>98.346403</v>
@@ -11443,13 +11443,13 @@
         <v>101.033444</v>
       </c>
       <c r="J142" s="6" t="n">
-        <v>100.423733</v>
+        <v>100.424242</v>
       </c>
       <c r="K142" s="6" t="n">
         <v>102.095122</v>
       </c>
       <c r="L142" s="6" t="n">
-        <v>102.738375</v>
+        <v>102.742039</v>
       </c>
       <c r="M142" s="6" t="n">
         <v>98.226761</v>
@@ -11525,13 +11525,13 @@
         <v>101.018411</v>
       </c>
       <c r="J143" s="9" t="n">
-        <v>100.398817</v>
+        <v>100.399291</v>
       </c>
       <c r="K143" s="9" t="n">
         <v>102.106415</v>
       </c>
       <c r="L143" s="9" t="n">
-        <v>102.799692</v>
+        <v>102.803434</v>
       </c>
       <c r="M143" s="9" t="n">
         <v>98.270596</v>
@@ -11607,13 +11607,13 @@
         <v>100.928267</v>
       </c>
       <c r="J144" s="6" t="n">
-        <v>100.382804</v>
+        <v>100.383255</v>
       </c>
       <c r="K144" s="6" t="n">
         <v>102.157903</v>
       </c>
       <c r="L144" s="6" t="n">
-        <v>102.83696</v>
+        <v>102.840748</v>
       </c>
       <c r="M144" s="6" t="n">
         <v>98.521176</v>
@@ -11689,13 +11689,13 @@
         <v>100.850567</v>
       </c>
       <c r="J145" s="9" t="n">
-        <v>100.377228</v>
+        <v>100.377672</v>
       </c>
       <c r="K145" s="9" t="n">
         <v>102.279108</v>
       </c>
       <c r="L145" s="9" t="n">
-        <v>102.85517</v>
+        <v>102.858978</v>
       </c>
       <c r="M145" s="9" t="n">
         <v>98.876863</v>
@@ -11771,13 +11771,13 @@
         <v>100.82501</v>
       </c>
       <c r="J146" s="6" t="n">
-        <v>100.393858</v>
+        <v>100.394328</v>
       </c>
       <c r="K146" s="6" t="n">
         <v>102.516068</v>
       </c>
       <c r="L146" s="6" t="n">
-        <v>102.85735</v>
+        <v>102.861156</v>
       </c>
       <c r="M146" s="6" t="n">
         <v>99.181747</v>
@@ -11853,13 +11853,13 @@
         <v>100.856509</v>
       </c>
       <c r="J147" s="9" t="n">
-        <v>100.426128</v>
+        <v>100.426646</v>
       </c>
       <c r="K147" s="9" t="n">
         <v>102.893429</v>
       </c>
       <c r="L147" s="9" t="n">
-        <v>102.843072</v>
+        <v>102.846857</v>
       </c>
       <c r="M147" s="9" t="n">
         <v>99.38202099999999</v>
@@ -11935,13 +11935,13 @@
         <v>100.904768</v>
       </c>
       <c r="J148" s="6" t="n">
-        <v>100.432642</v>
+        <v>100.433171</v>
       </c>
       <c r="K148" s="6" t="n">
         <v>103.358702</v>
       </c>
       <c r="L148" s="6" t="n">
-        <v>102.805875</v>
+        <v>102.809611</v>
       </c>
       <c r="M148" s="6" t="n">
         <v>99.452015</v>
@@ -12017,13 +12017,13 @@
         <v>100.947485</v>
       </c>
       <c r="J149" s="9" t="n">
-        <v>100.436294</v>
+        <v>100.436831</v>
       </c>
       <c r="K149" s="9" t="n">
         <v>103.837194</v>
       </c>
       <c r="L149" s="9" t="n">
-        <v>102.741459</v>
+        <v>102.745111</v>
       </c>
       <c r="M149" s="9" t="n">
         <v>99.41650199999999</v>
@@ -12099,13 +12099,13 @@
         <v>100.986634</v>
       </c>
       <c r="J150" s="6" t="n">
-        <v>100.475296</v>
+        <v>100.475893</v>
       </c>
       <c r="K150" s="6" t="n">
         <v>104.269634</v>
       </c>
       <c r="L150" s="6" t="n">
-        <v>102.645326</v>
+        <v>102.648853</v>
       </c>
       <c r="M150" s="6" t="n">
         <v>99.314211</v>
@@ -12181,13 +12181,13 @@
         <v>101.037413</v>
       </c>
       <c r="J151" s="9" t="n">
-        <v>100.580052</v>
+        <v>100.580804</v>
       </c>
       <c r="K151" s="9" t="n">
         <v>104.612728</v>
       </c>
       <c r="L151" s="9" t="n">
-        <v>102.514765</v>
+        <v>102.518122</v>
       </c>
       <c r="M151" s="9" t="n">
         <v>99.16305699999999</v>
@@ -12263,13 +12263,13 @@
         <v>101.115317</v>
       </c>
       <c r="J152" s="6" t="n">
-        <v>100.718648</v>
+        <v>100.719605</v>
       </c>
       <c r="K152" s="6" t="n">
         <v>104.775175</v>
       </c>
       <c r="L152" s="6" t="n">
-        <v>102.353633</v>
+        <v>102.356779</v>
       </c>
       <c r="M152" s="6" t="n">
         <v>98.96531899999999</v>
@@ -12345,13 +12345,13 @@
         <v>101.209877</v>
       </c>
       <c r="J153" s="9" t="n">
-        <v>100.834069</v>
+        <v>100.835197</v>
       </c>
       <c r="K153" s="9" t="n">
         <v>104.68406</v>
       </c>
       <c r="L153" s="9" t="n">
-        <v>102.172392</v>
+        <v>102.1753</v>
       </c>
       <c r="M153" s="9" t="n">
         <v>98.75939099999999</v>
@@ -12427,13 +12427,13 @@
         <v>101.260421</v>
       </c>
       <c r="J154" s="6" t="n">
-        <v>100.932287</v>
+        <v>100.933559</v>
       </c>
       <c r="K154" s="6" t="n">
         <v>104.382801</v>
       </c>
       <c r="L154" s="6" t="n">
-        <v>101.988084</v>
+        <v>101.990745</v>
       </c>
       <c r="M154" s="6" t="n">
         <v>98.55488699999999</v>
@@ -12509,13 +12509,13 @@
         <v>101.244913</v>
       </c>
       <c r="J155" s="9" t="n">
-        <v>100.983174</v>
+        <v>100.984516</v>
       </c>
       <c r="K155" s="9" t="n">
         <v>103.980196</v>
       </c>
       <c r="L155" s="9" t="n">
-        <v>101.813139</v>
+        <v>101.815565</v>
       </c>
       <c r="M155" s="9" t="n">
         <v>98.341466</v>
@@ -12591,13 +12591,13 @@
         <v>101.165925</v>
       </c>
       <c r="J156" s="6" t="n">
-        <v>100.968728</v>
+        <v>100.970039</v>
       </c>
       <c r="K156" s="6" t="n">
         <v>103.560859</v>
       </c>
       <c r="L156" s="6" t="n">
-        <v>101.656511</v>
+        <v>101.658723</v>
       </c>
       <c r="M156" s="6" t="n">
         <v>98.149564</v>
@@ -12673,13 +12673,13 @@
         <v>101.063598</v>
       </c>
       <c r="J157" s="9" t="n">
-        <v>100.895917</v>
+        <v>100.897102</v>
       </c>
       <c r="K157" s="9" t="n">
         <v>103.185515</v>
       </c>
       <c r="L157" s="9" t="n">
-        <v>101.514368</v>
+        <v>101.516383</v>
       </c>
       <c r="M157" s="9" t="n">
         <v>98.02409</v>
@@ -12755,13 +12755,13 @@
         <v>100.967689</v>
       </c>
       <c r="J158" s="6" t="n">
-        <v>100.805384</v>
+        <v>100.806405</v>
       </c>
       <c r="K158" s="6" t="n">
         <v>102.913052</v>
       </c>
       <c r="L158" s="6" t="n">
-        <v>101.3831</v>
+        <v>101.384932</v>
       </c>
       <c r="M158" s="6" t="n">
         <v>98.052525</v>
@@ -12837,13 +12837,13 @@
         <v>100.916811</v>
       </c>
       <c r="J159" s="9" t="n">
-        <v>100.70656</v>
+        <v>100.70739</v>
       </c>
       <c r="K159" s="9" t="n">
         <v>102.749224</v>
       </c>
       <c r="L159" s="9" t="n">
-        <v>101.261378</v>
+        <v>101.263042</v>
       </c>
       <c r="M159" s="9" t="n">
         <v>98.236671</v>
@@ -12919,13 +12919,13 @@
         <v>100.869191</v>
       </c>
       <c r="J160" s="6" t="n">
-        <v>100.621471</v>
+        <v>100.622121</v>
       </c>
       <c r="K160" s="6" t="n">
         <v>102.691821</v>
       </c>
       <c r="L160" s="6" t="n">
-        <v>101.155839</v>
+        <v>101.157358</v>
       </c>
       <c r="M160" s="6" t="n">
         <v>98.502843</v>
@@ -13001,13 +13001,13 @@
         <v>100.815894</v>
       </c>
       <c r="J161" s="9" t="n">
-        <v>100.584662</v>
+        <v>100.585203</v>
       </c>
       <c r="K161" s="9" t="n">
         <v>102.716523</v>
       </c>
       <c r="L161" s="9" t="n">
-        <v>101.072331</v>
+        <v>101.073739</v>
       </c>
       <c r="M161" s="9" t="n">
         <v>98.752332</v>
@@ -13083,13 +13083,13 @@
         <v>100.791526</v>
       </c>
       <c r="J162" s="6" t="n">
-        <v>100.604841</v>
+        <v>100.605382</v>
       </c>
       <c r="K162" s="6" t="n">
         <v>102.746672</v>
       </c>
       <c r="L162" s="6" t="n">
-        <v>101.012918</v>
+        <v>101.014253</v>
       </c>
       <c r="M162" s="6" t="n">
         <v>98.99847</v>
@@ -13165,13 +13165,13 @@
         <v>100.808325</v>
       </c>
       <c r="J163" s="9" t="n">
-        <v>100.668226</v>
+        <v>100.668895</v>
       </c>
       <c r="K163" s="9" t="n">
         <v>102.715374</v>
       </c>
       <c r="L163" s="9" t="n">
-        <v>100.970362</v>
+        <v>100.971649</v>
       </c>
       <c r="M163" s="9" t="n">
         <v>99.20557700000001</v>
@@ -13247,13 +13247,13 @@
         <v>100.821538</v>
       </c>
       <c r="J164" s="6" t="n">
-        <v>100.712862</v>
+        <v>100.713691</v>
       </c>
       <c r="K164" s="6" t="n">
         <v>102.58826</v>
       </c>
       <c r="L164" s="6" t="n">
-        <v>100.92919</v>
+        <v>100.930429</v>
       </c>
       <c r="M164" s="6" t="n">
         <v>99.334824</v>
@@ -13329,13 +13329,13 @@
         <v>100.816038</v>
       </c>
       <c r="J165" s="9" t="n">
-        <v>100.710577</v>
+        <v>100.711516</v>
       </c>
       <c r="K165" s="9" t="n">
         <v>102.345592</v>
       </c>
       <c r="L165" s="9" t="n">
-        <v>100.86553</v>
+        <v>100.86669</v>
       </c>
       <c r="M165" s="9" t="n">
         <v>99.396131</v>
@@ -13411,13 +13411,13 @@
         <v>100.804199</v>
       </c>
       <c r="J166" s="6" t="n">
-        <v>100.675666</v>
+        <v>100.676673</v>
       </c>
       <c r="K166" s="6" t="n">
         <v>101.99878</v>
       </c>
       <c r="L166" s="6" t="n">
-        <v>100.757128</v>
+        <v>100.758145</v>
       </c>
       <c r="M166" s="6" t="n">
         <v>99.4597</v>
@@ -13493,13 +13493,13 @@
         <v>100.775722</v>
       </c>
       <c r="J167" s="9" t="n">
-        <v>100.62882</v>
+        <v>100.629852</v>
       </c>
       <c r="K167" s="9" t="n">
         <v>101.570928</v>
       </c>
       <c r="L167" s="9" t="n">
-        <v>100.595555</v>
+        <v>100.596356</v>
       </c>
       <c r="M167" s="9" t="n">
         <v>99.53191099999999</v>
@@ -13575,13 +13575,13 @@
         <v>100.736747</v>
       </c>
       <c r="J168" s="6" t="n">
-        <v>100.593998</v>
+        <v>100.594988</v>
       </c>
       <c r="K168" s="6" t="n">
         <v>101.094371</v>
       </c>
       <c r="L168" s="6" t="n">
-        <v>100.385855</v>
+        <v>100.386373</v>
       </c>
       <c r="M168" s="6" t="n">
         <v>99.63737500000001</v>
@@ -13657,13 +13657,13 @@
         <v>100.674338</v>
       </c>
       <c r="J169" s="9" t="n">
-        <v>100.578259</v>
+        <v>100.579165</v>
       </c>
       <c r="K169" s="9" t="n">
         <v>100.611334</v>
       </c>
       <c r="L169" s="9" t="n">
-        <v>100.147755</v>
+        <v>100.147953</v>
       </c>
       <c r="M169" s="9" t="n">
         <v>99.742812</v>
@@ -13739,13 +13739,13 @@
         <v>100.609042</v>
       </c>
       <c r="J170" s="6" t="n">
-        <v>100.590817</v>
+        <v>100.591657</v>
       </c>
       <c r="K170" s="6" t="n">
         <v>100.195008</v>
       </c>
       <c r="L170" s="6" t="n">
-        <v>99.911269</v>
+        <v>99.91114899999999</v>
       </c>
       <c r="M170" s="6" t="n">
         <v>99.786491</v>
@@ -13821,13 +13821,13 @@
         <v>100.576462</v>
       </c>
       <c r="J171" s="9" t="n">
-        <v>100.644716</v>
+        <v>100.645569</v>
       </c>
       <c r="K171" s="9" t="n">
         <v>99.97027799999999</v>
       </c>
       <c r="L171" s="9" t="n">
-        <v>99.706924</v>
+        <v>99.706529</v>
       </c>
       <c r="M171" s="9" t="n">
         <v>99.756557</v>
@@ -13903,13 +13903,13 @@
         <v>100.607447</v>
       </c>
       <c r="J172" s="6" t="n">
-        <v>100.745114</v>
+        <v>100.746071</v>
       </c>
       <c r="K172" s="6" t="n">
         <v>99.976355</v>
       </c>
       <c r="L172" s="6" t="n">
-        <v>99.55777399999999</v>
+        <v>99.55718299999999</v>
       </c>
       <c r="M172" s="6" t="n">
         <v>99.681932</v>
@@ -13985,13 +13985,13 @@
         <v>100.716753</v>
       </c>
       <c r="J173" s="9" t="n">
-        <v>100.890841</v>
+        <v>100.891962</v>
       </c>
       <c r="K173" s="9" t="n">
         <v>100.23841</v>
       </c>
       <c r="L173" s="9" t="n">
-        <v>99.471058</v>
+        <v>99.470354</v>
       </c>
       <c r="M173" s="9" t="n">
         <v>99.56327400000001</v>
@@ -14067,13 +14067,13 @@
         <v>100.883377</v>
       </c>
       <c r="J174" s="6" t="n">
-        <v>101.063224</v>
+        <v>101.064597</v>
       </c>
       <c r="K174" s="6" t="n">
         <v>100.673993</v>
       </c>
       <c r="L174" s="6" t="n">
-        <v>99.444571</v>
+        <v>99.443833</v>
       </c>
       <c r="M174" s="6" t="n">
         <v>99.386021</v>
@@ -14149,13 +14149,13 @@
         <v>101.092654</v>
       </c>
       <c r="J175" s="9" t="n">
-        <v>101.247814</v>
+        <v>101.249497</v>
       </c>
       <c r="K175" s="9" t="n">
         <v>101.179567</v>
       </c>
       <c r="L175" s="9" t="n">
-        <v>99.47464100000001</v>
+        <v>99.473946</v>
       </c>
       <c r="M175" s="9" t="n">
         <v>99.15218900000001</v>
@@ -14231,13 +14231,13 @@
         <v>101.333522</v>
       </c>
       <c r="J176" s="6" t="n">
-        <v>101.434281</v>
+        <v>101.436302</v>
       </c>
       <c r="K176" s="6" t="n">
         <v>101.648286</v>
       </c>
       <c r="L176" s="6" t="n">
-        <v>99.547583</v>
+        <v>99.546986</v>
       </c>
       <c r="M176" s="6" t="n">
         <v>98.899001</v>
@@ -14313,13 +14313,13 @@
         <v>101.573585</v>
       </c>
       <c r="J177" s="9" t="n">
-        <v>101.584907</v>
+        <v>101.587182</v>
       </c>
       <c r="K177" s="9" t="n">
         <v>102.058611</v>
       </c>
       <c r="L177" s="9" t="n">
-        <v>99.649637</v>
+        <v>99.649176</v>
       </c>
       <c r="M177" s="9" t="n">
         <v>98.65521200000001</v>
@@ -14395,13 +14395,13 @@
         <v>101.765591</v>
       </c>
       <c r="J178" s="6" t="n">
-        <v>101.643071</v>
+        <v>101.645416</v>
       </c>
       <c r="K178" s="6" t="n">
         <v>102.385726</v>
       </c>
       <c r="L178" s="6" t="n">
-        <v>99.763503</v>
+        <v>99.763194</v>
       </c>
       <c r="M178" s="6" t="n">
         <v>98.44482000000001</v>
@@ -14477,13 +14477,13 @@
         <v>101.901437</v>
       </c>
       <c r="J179" s="9" t="n">
-        <v>101.644061</v>
+        <v>101.646356</v>
       </c>
       <c r="K179" s="9" t="n">
         <v>102.606225</v>
       </c>
       <c r="L179" s="9" t="n">
-        <v>99.87557099999999</v>
+        <v>99.875409</v>
       </c>
       <c r="M179" s="9" t="n">
         <v>98.325277</v>
@@ -14559,13 +14559,13 @@
         <v>101.985937</v>
       </c>
       <c r="J180" s="6" t="n">
-        <v>101.605319</v>
+        <v>101.60753</v>
       </c>
       <c r="K180" s="6" t="n">
         <v>102.719833</v>
       </c>
       <c r="L180" s="6" t="n">
-        <v>99.974825</v>
+        <v>99.97479300000001</v>
       </c>
       <c r="M180" s="6" t="n">
         <v>98.31177599999999</v>
@@ -14641,13 +14641,13 @@
         <v>102.024532</v>
       </c>
       <c r="J181" s="9" t="n">
-        <v>101.518684</v>
+        <v>101.520787</v>
       </c>
       <c r="K181" s="9" t="n">
         <v>102.738243</v>
       </c>
       <c r="L181" s="9" t="n">
-        <v>100.042752</v>
+        <v>100.042809</v>
       </c>
       <c r="M181" s="9" t="n">
         <v>98.415147</v>
@@ -14723,13 +14723,13 @@
         <v>101.978355</v>
       </c>
       <c r="J182" s="6" t="n">
-        <v>101.343681</v>
+        <v>101.345569</v>
       </c>
       <c r="K182" s="6" t="n">
         <v>102.642848</v>
       </c>
       <c r="L182" s="6" t="n">
-        <v>100.055838</v>
+        <v>100.05591</v>
       </c>
       <c r="M182" s="6" t="n">
         <v>98.660819</v>
@@ -14805,13 +14805,13 @@
         <v>101.786267</v>
       </c>
       <c r="J183" s="9" t="n">
-        <v>101.038122</v>
+        <v>101.039601</v>
       </c>
       <c r="K183" s="9" t="n">
         <v>102.413085</v>
       </c>
       <c r="L183" s="9" t="n">
-        <v>99.990315</v>
+        <v>99.990298</v>
       </c>
       <c r="M183" s="9" t="n">
         <v>99.035676</v>
@@ -14887,13 +14887,13 @@
         <v>101.3872</v>
       </c>
       <c r="J184" s="6" t="n">
-        <v>100.573321</v>
+        <v>100.574121</v>
       </c>
       <c r="K184" s="6" t="n">
         <v>102.043048</v>
       </c>
       <c r="L184" s="6" t="n">
-        <v>99.813222</v>
+        <v>99.81297000000001</v>
       </c>
       <c r="M184" s="6" t="n">
         <v>99.530185</v>
@@ -14969,13 +14969,13 @@
         <v>100.739302</v>
       </c>
       <c r="J185" s="9" t="n">
-        <v>99.93420500000001</v>
+        <v>99.934015</v>
       </c>
       <c r="K185" s="9" t="n">
         <v>101.536147</v>
       </c>
       <c r="L185" s="9" t="n">
-        <v>99.50743900000001</v>
+        <v>99.50678000000001</v>
       </c>
       <c r="M185" s="9" t="n">
         <v>100.13902</v>
@@ -15051,13 +15051,13 @@
         <v>99.854798</v>
       </c>
       <c r="J186" s="6" t="n">
-        <v>99.139152</v>
+        <v>99.137669</v>
       </c>
       <c r="K186" s="6" t="n">
         <v>100.911013</v>
       </c>
       <c r="L186" s="6" t="n">
-        <v>99.078919</v>
+        <v>99.077691</v>
       </c>
       <c r="M186" s="6" t="n">
         <v>100.871625</v>
@@ -15133,13 +15133,13 @@
         <v>98.80493199999999</v>
       </c>
       <c r="J187" s="9" t="n">
-        <v>98.273301</v>
+        <v>98.270432</v>
       </c>
       <c r="K187" s="9" t="n">
         <v>100.078365</v>
       </c>
       <c r="L187" s="9" t="n">
-        <v>98.552288</v>
+        <v>98.550358</v>
       </c>
       <c r="M187" s="9" t="n">
         <v>101.688614</v>
@@ -15215,13 +15215,13 @@
         <v>97.78291299999999</v>
       </c>
       <c r="J188" s="6" t="n">
-        <v>97.443752</v>
+        <v>97.439623</v>
       </c>
       <c r="K188" s="6" t="n">
         <v>99.057491</v>
       </c>
       <c r="L188" s="6" t="n">
-        <v>97.979088</v>
+        <v>97.976395</v>
       </c>
       <c r="M188" s="6" t="n">
         <v>102.513994</v>
@@ -15297,13 +15297,13 @@
         <v>96.91513500000001</v>
       </c>
       <c r="J189" s="9" t="n">
-        <v>96.737323</v>
+        <v>96.732235</v>
       </c>
       <c r="K189" s="9" t="n">
         <v>97.941221</v>
       </c>
       <c r="L189" s="9" t="n">
-        <v>97.41390699999999</v>
+        <v>97.410459</v>
       </c>
       <c r="M189" s="9" t="n">
         <v>103.270632</v>
@@ -15379,13 +15379,13 @@
         <v>96.30721</v>
       </c>
       <c r="J190" s="6" t="n">
-        <v>96.236592</v>
+        <v>96.230881</v>
       </c>
       <c r="K190" s="6" t="n">
         <v>96.96925299999999</v>
       </c>
       <c r="L190" s="6" t="n">
-        <v>96.892839</v>
+        <v>96.888695</v>
       </c>
       <c r="M190" s="6" t="n">
         <v>103.895876</v>
@@ -15461,13 +15461,13 @@
         <v>95.986278</v>
       </c>
       <c r="J191" s="9" t="n">
-        <v>95.967457</v>
+        <v>95.961422</v>
       </c>
       <c r="K191" s="9" t="n">
         <v>96.250635</v>
       </c>
       <c r="L191" s="9" t="n">
-        <v>96.444191</v>
+        <v>96.439447</v>
       </c>
       <c r="M191" s="9" t="n">
         <v>104.345641</v>
@@ -15543,13 +15543,13 @@
         <v>95.906893</v>
       </c>
       <c r="J192" s="6" t="n">
-        <v>95.91551200000001</v>
+        <v>95.90942200000001</v>
       </c>
       <c r="K192" s="6" t="n">
         <v>95.790237</v>
       </c>
       <c r="L192" s="6" t="n">
-        <v>96.084642</v>
+        <v>96.07941700000001</v>
       </c>
       <c r="M192" s="6" t="n">
         <v>104.600881</v>
@@ -15625,13 +15625,13 @@
         <v>96.007683</v>
       </c>
       <c r="J193" s="9" t="n">
-        <v>96.050577</v>
+        <v>96.044656</v>
       </c>
       <c r="K193" s="9" t="n">
         <v>95.54873499999999</v>
       </c>
       <c r="L193" s="9" t="n">
-        <v>95.82561</v>
+        <v>95.820037</v>
       </c>
       <c r="M193" s="9" t="n">
         <v>104.667286</v>
@@ -15707,13 +15707,13 @@
         <v>96.235477</v>
       </c>
       <c r="J194" s="6" t="n">
-        <v>96.34019000000001</v>
+        <v>96.334616</v>
       </c>
       <c r="K194" s="6" t="n">
         <v>95.460396</v>
       </c>
       <c r="L194" s="6" t="n">
-        <v>95.671449</v>
+        <v>95.665671</v>
       </c>
       <c r="M194" s="6" t="n">
         <v>104.558614</v>
@@ -15789,13 +15789,13 @@
         <v>96.55834</v>
       </c>
       <c r="J195" s="9" t="n">
-        <v>96.736999</v>
+        <v>96.731908</v>
       </c>
       <c r="K195" s="9" t="n">
         <v>95.478105</v>
       </c>
       <c r="L195" s="9" t="n">
-        <v>95.61797900000001</v>
+        <v>95.61212999999999</v>
       </c>
       <c r="M195" s="9" t="n">
         <v>104.324401</v>
@@ -15871,13 +15871,13 @@
         <v>96.972919</v>
       </c>
       <c r="J196" s="6" t="n">
-        <v>97.18664800000001</v>
+        <v>97.182171</v>
       </c>
       <c r="K196" s="6" t="n">
         <v>95.572959</v>
       </c>
       <c r="L196" s="6" t="n">
-        <v>95.65727200000001</v>
+        <v>95.651477</v>
       </c>
       <c r="M196" s="6" t="n">
         <v>104.0164</v>
@@ -15953,13 +15953,13 @@
         <v>97.387187</v>
       </c>
       <c r="J197" s="9" t="n">
-        <v>97.631382</v>
+        <v>97.62759200000001</v>
       </c>
       <c r="K197" s="9" t="n">
         <v>95.72209599999999</v>
       </c>
       <c r="L197" s="9" t="n">
-        <v>95.778364</v>
+        <v>95.772733</v>
       </c>
       <c r="M197" s="9" t="n">
         <v>103.66798</v>
@@ -16035,13 +16035,13 @@
         <v>97.702088</v>
       </c>
       <c r="J198" s="6" t="n">
-        <v>97.981044</v>
+        <v>97.977828</v>
       </c>
       <c r="K198" s="6" t="n">
         <v>95.94280000000001</v>
       </c>
       <c r="L198" s="6" t="n">
-        <v>95.96634</v>
+        <v>95.960961</v>
       </c>
       <c r="M198" s="6" t="n">
         <v>103.289933</v>
@@ -16117,13 +16117,13 @@
         <v>97.907241</v>
       </c>
       <c r="J199" s="9" t="n">
-        <v>98.231189</v>
+        <v>98.22838</v>
       </c>
       <c r="K199" s="9" t="n">
         <v>96.155137</v>
       </c>
       <c r="L199" s="9" t="n">
-        <v>96.200113</v>
+        <v>96.19504499999999</v>
       </c>
       <c r="M199" s="9" t="n">
         <v>102.918896</v>
@@ -16199,13 +16199,13 @@
         <v>98.042912</v>
       </c>
       <c r="J200" s="6" t="n">
-        <v>98.410782</v>
+        <v>98.40828</v>
       </c>
       <c r="K200" s="6" t="n">
         <v>96.319045</v>
       </c>
       <c r="L200" s="6" t="n">
-        <v>96.457094</v>
+        <v>96.45236800000001</v>
       </c>
       <c r="M200" s="6" t="n">
         <v>102.582451</v>
@@ -16281,13 +16281,13 @@
         <v>98.140366</v>
       </c>
       <c r="J201" s="9" t="n">
-        <v>98.539687</v>
+        <v>98.537435</v>
       </c>
       <c r="K201" s="9" t="n">
         <v>96.42022299999999</v>
       </c>
       <c r="L201" s="9" t="n">
-        <v>96.717162</v>
+        <v>96.712782</v>
       </c>
       <c r="M201" s="9" t="n">
         <v>102.303379</v>
@@ -16363,13 +16363,13 @@
         <v>98.234195</v>
       </c>
       <c r="J202" s="6" t="n">
-        <v>98.649863</v>
+        <v>98.64779900000001</v>
       </c>
       <c r="K202" s="6" t="n">
         <v>96.47741600000001</v>
       </c>
       <c r="L202" s="6" t="n">
-        <v>96.970341</v>
+        <v>96.96629799999999</v>
       </c>
       <c r="M202" s="6" t="n">
         <v>102.098908</v>
@@ -16445,13 +16445,13 @@
         <v>98.32529599999999</v>
       </c>
       <c r="J203" s="9" t="n">
-        <v>98.74590999999999</v>
+        <v>98.744041</v>
       </c>
       <c r="K203" s="9" t="n">
         <v>96.500541</v>
       </c>
       <c r="L203" s="9" t="n">
-        <v>97.211052</v>
+        <v>97.207329</v>
       </c>
       <c r="M203" s="9" t="n">
         <v>101.986719</v>
@@ -16527,13 +16527,13 @@
         <v>98.414328</v>
       </c>
       <c r="J204" s="6" t="n">
-        <v>98.82736800000001</v>
+        <v>98.825654</v>
       </c>
       <c r="K204" s="6" t="n">
         <v>96.516373</v>
       </c>
       <c r="L204" s="6" t="n">
-        <v>97.43933699999999</v>
+        <v>97.435919</v>
       </c>
       <c r="M204" s="6" t="n">
         <v>101.959261</v>
@@ -16609,13 +16609,13 @@
         <v>98.51594299999999</v>
       </c>
       <c r="J205" s="9" t="n">
-        <v>98.914637</v>
+        <v>98.91305199999999</v>
       </c>
       <c r="K205" s="9" t="n">
         <v>96.552881</v>
       </c>
       <c r="L205" s="9" t="n">
-        <v>97.665291</v>
+        <v>97.66217399999999</v>
       </c>
       <c r="M205" s="9" t="n">
         <v>102.015947</v>
@@ -16691,13 +16691,13 @@
         <v>98.642625</v>
       </c>
       <c r="J206" s="6" t="n">
-        <v>99.02634399999999</v>
+        <v>99.024914</v>
       </c>
       <c r="K206" s="6" t="n">
         <v>96.63799400000001</v>
       </c>
       <c r="L206" s="6" t="n">
-        <v>97.898805</v>
+        <v>97.896001</v>
       </c>
       <c r="M206" s="6" t="n">
         <v>102.13838</v>
@@ -16773,13 +16773,13 @@
         <v>98.786918</v>
       </c>
       <c r="J207" s="9" t="n">
-        <v>99.164799</v>
+        <v>99.163589</v>
       </c>
       <c r="K207" s="9" t="n">
         <v>96.788833</v>
       </c>
       <c r="L207" s="9" t="n">
-        <v>98.150826</v>
+        <v>98.148359</v>
       </c>
       <c r="M207" s="9" t="n">
         <v>102.24291</v>
@@ -16855,13 +16855,13 @@
         <v>98.93024699999999</v>
       </c>
       <c r="J208" s="6" t="n">
-        <v>99.30478599999999</v>
+        <v>99.30376</v>
       </c>
       <c r="K208" s="6" t="n">
         <v>97.008837</v>
       </c>
       <c r="L208" s="6" t="n">
-        <v>98.423506</v>
+        <v>98.421403</v>
       </c>
       <c r="M208" s="6" t="n">
         <v>102.246458</v>
@@ -16937,13 +16937,13 @@
         <v>99.05145</v>
       </c>
       <c r="J209" s="9" t="n">
-        <v>99.422055</v>
+        <v>99.421137</v>
       </c>
       <c r="K209" s="9" t="n">
         <v>97.293414</v>
       </c>
       <c r="L209" s="9" t="n">
-        <v>98.715626</v>
+        <v>98.71391300000001</v>
       </c>
       <c r="M209" s="9" t="n">
         <v>102.135273</v>
@@ -17019,13 +17019,13 @@
         <v>99.153318</v>
       </c>
       <c r="J210" s="6" t="n">
-        <v>99.501445</v>
+        <v>99.50055999999999</v>
       </c>
       <c r="K210" s="6" t="n">
         <v>97.64757</v>
       </c>
       <c r="L210" s="6" t="n">
-        <v>99.019666</v>
+        <v>99.018359</v>
       </c>
       <c r="M210" s="6" t="n">
         <v>101.935632</v>
@@ -17101,13 +17101,13 @@
         <v>99.267517</v>
       </c>
       <c r="J211" s="9" t="n">
-        <v>99.589134</v>
+        <v>99.588368</v>
       </c>
       <c r="K211" s="9" t="n">
         <v>98.00141600000001</v>
       </c>
       <c r="L211" s="9" t="n">
-        <v>99.339287</v>
+        <v>99.33840499999999</v>
       </c>
       <c r="M211" s="9" t="n">
         <v>101.688919</v>
@@ -17183,13 +17183,13 @@
         <v>99.414422</v>
       </c>
       <c r="J212" s="6" t="n">
-        <v>99.709205</v>
+        <v>99.708653</v>
       </c>
       <c r="K212" s="6" t="n">
         <v>98.311964</v>
       </c>
       <c r="L212" s="6" t="n">
-        <v>99.65988400000001</v>
+        <v>99.65942800000001</v>
       </c>
       <c r="M212" s="6" t="n">
         <v>101.444084</v>
@@ -17265,13 +17265,13 @@
         <v>99.597435</v>
       </c>
       <c r="J213" s="9" t="n">
-        <v>99.867848</v>
+        <v>99.86756200000001</v>
       </c>
       <c r="K213" s="9" t="n">
         <v>98.571168</v>
       </c>
       <c r="L213" s="9" t="n">
-        <v>99.97063</v>
+        <v>99.97058699999999</v>
       </c>
       <c r="M213" s="9" t="n">
         <v>101.20397</v>
@@ -17347,13 +17347,13 @@
         <v>99.802319</v>
       </c>
       <c r="J214" s="6" t="n">
-        <v>100.051063</v>
+        <v>100.051055</v>
       </c>
       <c r="K214" s="6" t="n">
         <v>98.78951499999999</v>
       </c>
       <c r="L214" s="6" t="n">
-        <v>100.254749</v>
+        <v>100.255084</v>
       </c>
       <c r="M214" s="6" t="n">
         <v>100.953772</v>
@@ -17429,13 +17429,13 @@
         <v>100.012214</v>
       </c>
       <c r="J215" s="9" t="n">
-        <v>100.242747</v>
+        <v>100.242996</v>
       </c>
       <c r="K215" s="9" t="n">
         <v>98.987549</v>
       </c>
       <c r="L215" s="9" t="n">
-        <v>100.492683</v>
+        <v>100.493336</v>
       </c>
       <c r="M215" s="9" t="n">
         <v>100.688729</v>
@@ -17511,13 +17511,13 @@
         <v>100.217371</v>
       </c>
       <c r="J216" s="6" t="n">
-        <v>100.429302</v>
+        <v>100.429828</v>
       </c>
       <c r="K216" s="6" t="n">
         <v>99.18158</v>
       </c>
       <c r="L216" s="6" t="n">
-        <v>100.671136</v>
+        <v>100.672029</v>
       </c>
       <c r="M216" s="6" t="n">
         <v>100.442566</v>
@@ -17593,13 +17593,13 @@
         <v>100.427421</v>
       </c>
       <c r="J217" s="9" t="n">
-        <v>100.606197</v>
+        <v>100.606981</v>
       </c>
       <c r="K217" s="9" t="n">
         <v>99.367919</v>
       </c>
       <c r="L217" s="9" t="n">
-        <v>100.778644</v>
+        <v>100.779683</v>
       </c>
       <c r="M217" s="9" t="n">
         <v>100.205179</v>
@@ -17675,13 +17675,13 @@
         <v>100.642805</v>
       </c>
       <c r="J218" s="6" t="n">
-        <v>100.776916</v>
+        <v>100.777972</v>
       </c>
       <c r="K218" s="6" t="n">
         <v>99.536793</v>
       </c>
       <c r="L218" s="6" t="n">
-        <v>100.812746</v>
+        <v>100.813832</v>
       </c>
       <c r="M218" s="6" t="n">
         <v>100.013169</v>
@@ -17757,13 +17757,13 @@
         <v>100.857957</v>
       </c>
       <c r="J219" s="9" t="n">
-        <v>100.950565</v>
+        <v>100.951876</v>
       </c>
       <c r="K219" s="9" t="n">
         <v>99.690074</v>
       </c>
       <c r="L219" s="9" t="n">
-        <v>100.783762</v>
+        <v>100.78481</v>
       </c>
       <c r="M219" s="9" t="n">
         <v>99.89203999999999</v>
@@ -17839,13 +17839,13 @@
         <v>101.052415</v>
       </c>
       <c r="J220" s="6" t="n">
-        <v>101.123881</v>
+        <v>101.125506</v>
       </c>
       <c r="K220" s="6" t="n">
         <v>99.817623</v>
       </c>
       <c r="L220" s="6" t="n">
-        <v>100.71536</v>
+        <v>100.716317</v>
       </c>
       <c r="M220" s="6" t="n">
         <v>99.844915</v>
@@ -17921,13 +17921,13 @@
         <v>101.216743</v>
       </c>
       <c r="J221" s="9" t="n">
-        <v>101.292855</v>
+        <v>101.294793</v>
       </c>
       <c r="K221" s="9" t="n">
         <v>99.93159900000001</v>
       </c>
       <c r="L221" s="9" t="n">
-        <v>100.633565</v>
+        <v>100.634413</v>
       </c>
       <c r="M221" s="9" t="n">
         <v>99.847084</v>
@@ -18003,13 +18003,13 @@
         <v>101.360058</v>
       </c>
       <c r="J222" s="6" t="n">
-        <v>101.451075</v>
+        <v>101.453255</v>
       </c>
       <c r="K222" s="6" t="n">
         <v>100.04831</v>
       </c>
       <c r="L222" s="6" t="n">
-        <v>100.561799</v>
+        <v>100.562551</v>
       </c>
       <c r="M222" s="6" t="n">
         <v>99.89039099999999</v>
@@ -18085,13 +18085,13 @@
         <v>101.472909</v>
       </c>
       <c r="J223" s="9" t="n">
-        <v>101.572831</v>
+        <v>101.575128</v>
       </c>
       <c r="K223" s="9" t="n">
         <v>100.172321</v>
       </c>
       <c r="L223" s="9" t="n">
-        <v>100.501801</v>
+        <v>100.502471</v>
       </c>
       <c r="M223" s="9" t="n">
         <v>99.93266</v>
@@ -18167,13 +18167,13 @@
         <v>101.528942</v>
       </c>
       <c r="J224" s="6" t="n">
-        <v>101.627031</v>
+        <v>101.629326</v>
       </c>
       <c r="K224" s="6" t="n">
         <v>100.277636</v>
       </c>
       <c r="L224" s="6" t="n">
-        <v>100.453639</v>
+        <v>100.454243</v>
       </c>
       <c r="M224" s="6" t="n">
         <v>99.95354399999999</v>
@@ -18249,13 +18249,13 @@
         <v>101.512951</v>
       </c>
       <c r="J225" s="9" t="n">
-        <v>101.603996</v>
+        <v>101.606158</v>
       </c>
       <c r="K225" s="9" t="n">
         <v>100.349137</v>
       </c>
       <c r="L225" s="9" t="n">
-        <v>100.413352</v>
+        <v>100.4139</v>
       </c>
       <c r="M225" s="9" t="n">
         <v>99.96745300000001</v>
@@ -18331,13 +18331,13 @@
         <v>101.435685</v>
       </c>
       <c r="J226" s="6" t="n">
-        <v>101.520083</v>
+        <v>101.52207</v>
       </c>
       <c r="K226" s="6" t="n">
         <v>100.376939</v>
       </c>
       <c r="L226" s="6" t="n">
-        <v>100.380584</v>
+        <v>100.381088</v>
       </c>
       <c r="M226" s="6" t="n">
         <v>100.000004</v>
@@ -18413,13 +18413,13 @@
         <v>101.322059</v>
       </c>
       <c r="J227" s="9" t="n">
-        <v>101.397665</v>
+        <v>101.399451</v>
       </c>
       <c r="K227" s="9" t="n">
         <v>100.350834</v>
       </c>
       <c r="L227" s="9" t="n">
-        <v>100.361925</v>
+        <v>100.362406</v>
       </c>
       <c r="M227" s="9" t="n">
         <v>100.026019</v>
@@ -18495,13 +18495,13 @@
         <v>101.198956</v>
       </c>
       <c r="J228" s="6" t="n">
-        <v>101.273894</v>
+        <v>101.275459</v>
       </c>
       <c r="K228" s="6" t="n">
         <v>100.269218</v>
       </c>
       <c r="L228" s="6" t="n">
-        <v>100.355892</v>
+        <v>100.356367</v>
       </c>
       <c r="M228" s="6" t="n">
         <v>100.013545</v>
@@ -18577,13 +18577,13 @@
         <v>101.071242</v>
       </c>
       <c r="J229" s="9" t="n">
-        <v>101.165515</v>
+        <v>101.166954</v>
       </c>
       <c r="K229" s="9" t="n">
         <v>100.131103</v>
       </c>
       <c r="L229" s="9" t="n">
-        <v>100.357734</v>
+        <v>100.358212</v>
       </c>
       <c r="M229" s="9" t="n">
         <v>99.974281</v>
@@ -18659,13 +18659,13 @@
         <v>100.945044</v>
       </c>
       <c r="J230" s="6" t="n">
-        <v>101.075336</v>
+        <v>101.076699</v>
       </c>
       <c r="K230" s="6" t="n">
         <v>99.91772400000001</v>
       </c>
       <c r="L230" s="6" t="n">
-        <v>100.366145</v>
+        <v>100.366635</v>
       </c>
       <c r="M230" s="6" t="n">
         <v>99.924311</v>
@@ -18741,13 +18741,13 @@
         <v>100.83971</v>
       </c>
       <c r="J231" s="9" t="n">
-        <v>101.008254</v>
+        <v>101.009552</v>
       </c>
       <c r="K231" s="9" t="n">
         <v>99.695739</v>
       </c>
       <c r="L231" s="9" t="n">
-        <v>100.379274</v>
+        <v>100.379782</v>
       </c>
       <c r="M231" s="9" t="n">
         <v>99.858368</v>
@@ -18823,13 +18823,13 @@
         <v>100.768867</v>
       </c>
       <c r="J232" s="6" t="n">
-        <v>100.962484</v>
+        <v>100.963714</v>
       </c>
       <c r="K232" s="6" t="n">
         <v>99.52135699999999</v>
       </c>
       <c r="L232" s="6" t="n">
-        <v>100.397488</v>
+        <v>100.39802</v>
       </c>
       <c r="M232" s="6" t="n">
         <v>99.76027000000001</v>
@@ -18905,13 +18905,13 @@
         <v>100.731165</v>
       </c>
       <c r="J233" s="9" t="n">
-        <v>100.931891</v>
+        <v>100.9331</v>
       </c>
       <c r="K233" s="9" t="n">
         <v>99.431949</v>
       </c>
       <c r="L233" s="9" t="n">
-        <v>100.422453</v>
+        <v>100.423018</v>
       </c>
       <c r="M233" s="9" t="n">
         <v>99.640958</v>
@@ -18987,13 +18987,13 @@
         <v>100.710584</v>
       </c>
       <c r="J234" s="6" t="n">
-        <v>100.899616</v>
+        <v>100.900787</v>
       </c>
       <c r="K234" s="6" t="n">
         <v>99.447104</v>
       </c>
       <c r="L234" s="6" t="n">
-        <v>100.454642</v>
+        <v>100.455249</v>
       </c>
       <c r="M234" s="6" t="n">
         <v>99.47528699999999</v>
@@ -19069,13 +19069,13 @@
         <v>100.688487</v>
       </c>
       <c r="J235" s="9" t="n">
-        <v>100.857916</v>
+        <v>100.859061</v>
       </c>
       <c r="K235" s="9" t="n">
         <v>99.563152</v>
       </c>
       <c r="L235" s="9" t="n">
-        <v>100.494273</v>
+        <v>100.494933</v>
       </c>
       <c r="M235" s="9" t="n">
         <v>99.288242</v>
@@ -19151,13 +19151,13 @@
         <v>100.662428</v>
       </c>
       <c r="J236" s="6" t="n">
-        <v>100.800395</v>
+        <v>100.801514</v>
       </c>
       <c r="K236" s="6" t="n">
         <v>99.738799</v>
       </c>
       <c r="L236" s="6" t="n">
-        <v>100.541088</v>
+        <v>100.54181</v>
       </c>
       <c r="M236" s="6" t="n">
         <v>99.06642600000001</v>
@@ -19233,13 +19233,13 @@
         <v>100.631096</v>
       </c>
       <c r="J237" s="9" t="n">
-        <v>100.723141</v>
+        <v>100.724187</v>
       </c>
       <c r="K237" s="9" t="n">
         <v>99.88226299999999</v>
       </c>
       <c r="L237" s="9" t="n">
-        <v>100.592972</v>
+        <v>100.593761</v>
       </c>
       <c r="M237" s="9" t="n">
         <v>98.821381</v>
@@ -19315,13 +19315,13 @@
         <v>100.598189</v>
       </c>
       <c r="J238" s="6" t="n">
-        <v>100.625956</v>
+        <v>100.626892</v>
       </c>
       <c r="K238" s="6" t="n">
         <v>100.010793</v>
       </c>
       <c r="L238" s="6" t="n">
-        <v>100.649725</v>
+        <v>100.65059</v>
       </c>
       <c r="M238" s="6" t="n">
         <v>98.580859</v>
@@ -19397,13 +19397,13 @@
         <v>100.572496</v>
       </c>
       <c r="J239" s="9" t="n">
-        <v>100.536582</v>
+        <v>100.537404</v>
       </c>
       <c r="K239" s="9" t="n">
         <v>100.113975</v>
       </c>
       <c r="L239" s="9" t="n">
-        <v>100.710178</v>
+        <v>100.711124</v>
       </c>
       <c r="M239" s="9" t="n">
         <v>98.38892300000001</v>
@@ -19479,13 +19479,13 @@
         <v>100.574426</v>
       </c>
       <c r="J240" s="6" t="n">
-        <v>100.483868</v>
+        <v>100.484594</v>
       </c>
       <c r="K240" s="6" t="n">
         <v>100.151697</v>
       </c>
       <c r="L240" s="6" t="n">
-        <v>100.778613</v>
+        <v>100.779653</v>
       </c>
       <c r="M240" s="6" t="n">
         <v>98.20914500000001</v>
@@ -19561,13 +19561,13 @@
         <v>100.610625</v>
       </c>
       <c r="J241" s="9" t="n">
-        <v>100.483727</v>
+        <v>100.484384</v>
       </c>
       <c r="K241" s="9" t="n">
         <v>100.165954</v>
       </c>
       <c r="L241" s="9" t="n">
-        <v>100.862684</v>
+        <v>100.863838</v>
       </c>
       <c r="M241" s="9" t="n">
         <v>98.08167400000001</v>
@@ -19643,13 +19643,13 @@
         <v>100.69332</v>
       </c>
       <c r="J242" s="6" t="n">
-        <v>100.541944</v>
+        <v>100.542596</v>
       </c>
       <c r="K242" s="6" t="n">
         <v>100.195213</v>
       </c>
       <c r="L242" s="6" t="n">
-        <v>100.964209</v>
+        <v>100.965499</v>
       </c>
       <c r="M242" s="6" t="n">
         <v>98.00392600000001</v>
@@ -19725,13 +19725,13 @@
         <v>100.822552</v>
       </c>
       <c r="J243" s="9" t="n">
-        <v>100.65614</v>
+        <v>100.656932</v>
       </c>
       <c r="K243" s="9" t="n">
         <v>100.251946</v>
       </c>
       <c r="L243" s="9" t="n">
-        <v>101.07901</v>
+        <v>101.080452</v>
       </c>
       <c r="M243" s="9" t="n">
         <v>97.993225</v>
@@ -19807,13 +19807,13 @@
         <v>101.006498</v>
       </c>
       <c r="J244" s="6" t="n">
-        <v>100.837827</v>
+        <v>100.838893</v>
       </c>
       <c r="K244" s="6" t="n">
         <v>100.331464</v>
       </c>
       <c r="L244" s="6" t="n">
-        <v>101.203812</v>
+        <v>101.205421</v>
       </c>
       <c r="M244" s="6" t="n">
         <v>98.036835</v>
@@ -19889,13 +19889,13 @@
         <v>101.236833</v>
       </c>
       <c r="J245" s="9" t="n">
-        <v>101.078333</v>
+        <v>101.079707</v>
       </c>
       <c r="K245" s="9" t="n">
         <v>100.428087</v>
       </c>
       <c r="L245" s="9" t="n">
-        <v>101.332013</v>
+        <v>101.333791</v>
       </c>
       <c r="M245" s="9" t="n">
         <v>98.11254</v>
@@ -19971,13 +19971,13 @@
         <v>101.476217</v>
       </c>
       <c r="J246" s="6" t="n">
-        <v>101.354855</v>
+        <v>101.35663</v>
       </c>
       <c r="K246" s="6" t="n">
         <v>100.551795</v>
       </c>
       <c r="L246" s="6" t="n">
-        <v>101.462717</v>
+        <v>101.464669</v>
       </c>
       <c r="M246" s="6" t="n">
         <v>98.198795</v>
@@ -20053,13 +20053,13 @@
         <v>101.668468</v>
       </c>
       <c r="J247" s="9" t="n">
-        <v>101.627041</v>
+        <v>101.62921</v>
       </c>
       <c r="K247" s="9" t="n">
         <v>100.700721</v>
       </c>
       <c r="L247" s="9" t="n">
-        <v>101.592148</v>
+        <v>101.594272</v>
       </c>
       <c r="M247" s="9" t="n">
         <v>98.29145800000001</v>
@@ -20135,13 +20135,13 @@
         <v>101.816855</v>
       </c>
       <c r="J248" s="6" t="n">
-        <v>101.857144</v>
+        <v>101.859607</v>
       </c>
       <c r="K248" s="6" t="n">
         <v>100.883766</v>
       </c>
       <c r="L248" s="6" t="n">
-        <v>101.723233</v>
+        <v>101.725532</v>
       </c>
       <c r="M248" s="6" t="n">
         <v>98.374453</v>
@@ -20217,13 +20217,13 @@
         <v>101.937711</v>
       </c>
       <c r="J249" s="9" t="n">
-        <v>102.030577</v>
+        <v>102.033326</v>
       </c>
       <c r="K249" s="9" t="n">
         <v>101.105969</v>
       </c>
       <c r="L249" s="9" t="n">
-        <v>101.862063</v>
+        <v>101.864546</v>
       </c>
       <c r="M249" s="9" t="n">
         <v>98.43563</v>
@@ -20299,13 +20299,13 @@
         <v>102.036641</v>
       </c>
       <c r="J250" s="6" t="n">
-        <v>102.151091</v>
+        <v>102.154063</v>
       </c>
       <c r="K250" s="6" t="n">
         <v>101.333646</v>
       </c>
       <c r="L250" s="6" t="n">
-        <v>102.016056</v>
+        <v>102.018747</v>
       </c>
       <c r="M250" s="6" t="n">
         <v>98.433443</v>
@@ -20381,13 +20381,13 @@
         <v>102.099148</v>
       </c>
       <c r="J251" s="9" t="n">
-        <v>102.204929</v>
+        <v>102.208027</v>
       </c>
       <c r="K251" s="9" t="n">
         <v>101.534957</v>
       </c>
       <c r="L251" s="9" t="n">
-        <v>102.180768</v>
+        <v>102.183681</v>
       </c>
       <c r="M251" s="9" t="n">
         <v>98.375146</v>
@@ -20463,13 +20463,13 @@
         <v>102.104737</v>
       </c>
       <c r="J252" s="6" t="n">
-        <v>102.170114</v>
+        <v>102.173246</v>
       </c>
       <c r="K252" s="6" t="n">
         <v>101.681386</v>
       </c>
       <c r="L252" s="6" t="n">
-        <v>102.343932</v>
+        <v>102.347064</v>
       </c>
       <c r="M252" s="6" t="n">
         <v>98.30978399999999</v>
@@ -20545,13 +20545,13 @@
         <v>102.042884</v>
       </c>
       <c r="J253" s="9" t="n">
-        <v>102.035908</v>
+        <v>102.038919</v>
       </c>
       <c r="K253" s="9" t="n">
         <v>101.767725</v>
       </c>
       <c r="L253" s="9" t="n">
-        <v>102.490088</v>
+        <v>102.493415</v>
       </c>
       <c r="M253" s="9" t="n">
         <v>98.248532</v>
@@ -20627,13 +20627,13 @@
         <v>101.92636</v>
       </c>
       <c r="J254" s="6" t="n">
-        <v>101.827489</v>
+        <v>101.830198</v>
       </c>
       <c r="K254" s="6" t="n">
         <v>101.795129</v>
       </c>
       <c r="L254" s="6" t="n">
-        <v>102.600374</v>
+        <v>102.603847</v>
       </c>
       <c r="M254" s="6" t="n">
         <v>98.14920100000001</v>
@@ -20709,13 +20709,13 @@
         <v>101.766719</v>
       </c>
       <c r="J255" s="9" t="n">
-        <v>101.574728</v>
+        <v>101.576997</v>
       </c>
       <c r="K255" s="9" t="n">
         <v>101.766421</v>
       </c>
       <c r="L255" s="9" t="n">
-        <v>102.662006</v>
+        <v>102.665559</v>
       </c>
       <c r="M255" s="9" t="n">
         <v>98.041589</v>
@@ -20791,13 +20791,13 @@
         <v>101.574575</v>
       </c>
       <c r="J256" s="6" t="n">
-        <v>101.30786</v>
+        <v>101.309641</v>
       </c>
       <c r="K256" s="6" t="n">
         <v>101.702931</v>
       </c>
       <c r="L256" s="6" t="n">
-        <v>102.665305</v>
+        <v>102.66886</v>
       </c>
       <c r="M256" s="6" t="n">
         <v>98.049093</v>
@@ -20873,13 +20873,13 @@
         <v>101.367834</v>
       </c>
       <c r="J257" s="9" t="n">
-        <v>101.065896</v>
+        <v>101.067279</v>
       </c>
       <c r="K257" s="9" t="n">
         <v>101.632565</v>
       </c>
       <c r="L257" s="9" t="n">
-        <v>102.611065</v>
+        <v>102.614546</v>
       </c>
       <c r="M257" s="9" t="n">
         <v>98.190365</v>
@@ -20955,13 +20955,13 @@
         <v>101.166312</v>
       </c>
       <c r="J258" s="6" t="n">
-        <v>100.877393</v>
+        <v>100.878504</v>
       </c>
       <c r="K258" s="6" t="n">
         <v>101.567712</v>
       </c>
       <c r="L258" s="6" t="n">
-        <v>102.506944</v>
+        <v>102.510288</v>
       </c>
       <c r="M258" s="6" t="n">
         <v>98.41492700000001</v>
@@ -21037,13 +21037,13 @@
         <v>100.964472</v>
       </c>
       <c r="J259" s="9" t="n">
-        <v>100.698047</v>
+        <v>100.698913</v>
       </c>
       <c r="K259" s="9" t="n">
         <v>101.477611</v>
       </c>
       <c r="L259" s="9" t="n">
-        <v>102.35765</v>
+        <v>102.360796</v>
       </c>
       <c r="M259" s="9" t="n">
         <v>98.63256199999999</v>
@@ -21119,13 +21119,13 @@
         <v>100.77503</v>
       </c>
       <c r="J260" s="6" t="n">
-        <v>100.521395</v>
+        <v>100.52203</v>
       </c>
       <c r="K260" s="6" t="n">
         <v>101.344554</v>
       </c>
       <c r="L260" s="6" t="n">
-        <v>102.168304</v>
+        <v>102.171199</v>
       </c>
       <c r="M260" s="6" t="n">
         <v>98.763634</v>
@@ -21201,13 +21201,13 @@
         <v>100.605579</v>
       </c>
       <c r="J261" s="9" t="n">
-        <v>100.364081</v>
+        <v>100.364493</v>
       </c>
       <c r="K261" s="9" t="n">
         <v>101.174112</v>
       </c>
       <c r="L261" s="9" t="n">
-        <v>101.948956</v>
+        <v>101.951559</v>
       </c>
       <c r="M261" s="9" t="n">
         <v>98.843035</v>
@@ -21283,13 +21283,13 @@
         <v>100.458232</v>
       </c>
       <c r="J262" s="6" t="n">
-        <v>100.23641</v>
+        <v>100.236657</v>
       </c>
       <c r="K262" s="6" t="n">
         <v>100.990553</v>
       </c>
       <c r="L262" s="6" t="n">
-        <v>101.703148</v>
+        <v>101.705424</v>
       </c>
       <c r="M262" s="6" t="n">
         <v>98.898658</v>
@@ -21365,13 +21365,13 @@
         <v>100.327363</v>
       </c>
       <c r="J263" s="9" t="n">
-        <v>100.122255</v>
+        <v>100.122309</v>
       </c>
       <c r="K263" s="9" t="n">
         <v>100.817643</v>
       </c>
       <c r="L263" s="9" t="n">
-        <v>101.440206</v>
+        <v>101.442132</v>
       </c>
       <c r="M263" s="9" t="n">
         <v>98.911664</v>
@@ -21447,13 +21447,13 @@
         <v>100.19933</v>
       </c>
       <c r="J264" s="6" t="n">
-        <v>100.006157</v>
+        <v>100.005972</v>
       </c>
       <c r="K264" s="6" t="n">
         <v>100.66794</v>
       </c>
       <c r="L264" s="6" t="n">
-        <v>101.170381</v>
+        <v>101.171947</v>
       </c>
       <c r="M264" s="6" t="n">
         <v>98.927457</v>
@@ -21529,13 +21529,13 @@
         <v>100.059678</v>
       </c>
       <c r="J265" s="9" t="n">
-        <v>99.870249</v>
+        <v>99.869801</v>
       </c>
       <c r="K265" s="9" t="n">
         <v>100.55022</v>
       </c>
       <c r="L265" s="9" t="n">
-        <v>100.904193</v>
+        <v>100.905403</v>
       </c>
       <c r="M265" s="9" t="n">
         <v>98.982375</v>
@@ -21611,13 +21611,13 @@
         <v>99.89010500000001</v>
       </c>
       <c r="J266" s="6" t="n">
-        <v>99.700175</v>
+        <v>99.69949699999999</v>
       </c>
       <c r="K266" s="6" t="n">
         <v>100.455605</v>
       </c>
       <c r="L266" s="6" t="n">
-        <v>100.65428</v>
+        <v>100.655154</v>
       </c>
       <c r="M266" s="6" t="n">
         <v>99.11982500000001</v>
@@ -21693,13 +21693,13 @@
         <v>99.69316000000001</v>
       </c>
       <c r="J267" s="9" t="n">
-        <v>99.49087400000001</v>
+        <v>99.48993400000001</v>
       </c>
       <c r="K267" s="9" t="n">
         <v>100.371826</v>
       </c>
       <c r="L267" s="9" t="n">
-        <v>100.43503</v>
+        <v>100.43561</v>
       </c>
       <c r="M267" s="9" t="n">
         <v>99.319587</v>
@@ -21775,13 +21775,13 @@
         <v>99.49404</v>
       </c>
       <c r="J268" s="6" t="n">
-        <v>99.266909</v>
+        <v>99.26567799999999</v>
       </c>
       <c r="K268" s="6" t="n">
         <v>100.296692</v>
       </c>
       <c r="L268" s="6" t="n">
-        <v>100.252186</v>
+        <v>100.252519</v>
       </c>
       <c r="M268" s="6" t="n">
         <v>99.515934</v>
@@ -21857,13 +21857,13 @@
         <v>99.30573200000001</v>
       </c>
       <c r="J269" s="9" t="n">
-        <v>99.03411199999999</v>
+        <v>99.032585</v>
       </c>
       <c r="K269" s="9" t="n">
         <v>100.224022</v>
       </c>
       <c r="L269" s="9" t="n">
-        <v>100.105383</v>
+        <v>100.105518</v>
       </c>
       <c r="M269" s="9" t="n">
         <v>99.687231</v>
@@ -21939,13 +21939,13 @@
         <v>99.153239</v>
       </c>
       <c r="J270" s="6" t="n">
-        <v>98.819659</v>
+        <v>98.817846</v>
       </c>
       <c r="K270" s="6" t="n">
         <v>100.158442</v>
       </c>
       <c r="L270" s="6" t="n">
-        <v>99.98877400000001</v>
+        <v>99.988755</v>
       </c>
       <c r="M270" s="6" t="n">
         <v>99.782456</v>
@@ -22021,13 +22021,13 @@
         <v>99.073294</v>
       </c>
       <c r="J271" s="9" t="n">
-        <v>98.66458</v>
+        <v>98.66255</v>
       </c>
       <c r="K271" s="9" t="n">
         <v>100.103399</v>
       </c>
       <c r="L271" s="9" t="n">
-        <v>99.903818</v>
+        <v>99.903689</v>
       </c>
       <c r="M271" s="9" t="n">
         <v>99.79913500000001</v>
@@ -22103,13 +22103,13 @@
         <v>99.073195</v>
       </c>
       <c r="J272" s="6" t="n">
-        <v>98.60776799999999</v>
+        <v>98.605656</v>
       </c>
       <c r="K272" s="6" t="n">
         <v>100.04936</v>
       </c>
       <c r="L272" s="6" t="n">
-        <v>99.848642</v>
+        <v>99.84844</v>
       </c>
       <c r="M272" s="6" t="n">
         <v>99.783709</v>
@@ -22185,13 +22185,13 @@
         <v>99.127313</v>
       </c>
       <c r="J273" s="9" t="n">
-        <v>98.63257299999999</v>
+        <v>98.630487</v>
       </c>
       <c r="K273" s="9" t="n">
         <v>99.98881299999999</v>
       </c>
       <c r="L273" s="9" t="n">
-        <v>99.81945</v>
+        <v>99.819211</v>
       </c>
       <c r="M273" s="9" t="n">
         <v>99.738292</v>
@@ -22267,13 +22267,13 @@
         <v>99.204289</v>
       </c>
       <c r="J274" s="6" t="n">
-        <v>98.70151199999999</v>
+        <v>98.699488</v>
       </c>
       <c r="K274" s="6" t="n">
         <v>99.92156</v>
       </c>
       <c r="L274" s="6" t="n">
-        <v>99.80420100000001</v>
+        <v>99.80394200000001</v>
       </c>
       <c r="M274" s="6" t="n">
         <v>99.675224</v>
@@ -22349,13 +22349,13 @@
         <v>99.287983</v>
       </c>
       <c r="J275" s="9" t="n">
-        <v>98.804149</v>
+        <v>98.802305</v>
       </c>
       <c r="K275" s="9" t="n">
         <v>99.84509799999999</v>
       </c>
       <c r="L275" s="9" t="n">
-        <v>99.78942600000001</v>
+        <v>99.789146</v>
       </c>
       <c r="M275" s="9" t="n">
         <v>99.60717200000001</v>
@@ -22431,13 +22431,13 @@
         <v>99.369147</v>
       </c>
       <c r="J276" s="6" t="n">
-        <v>98.926492</v>
+        <v>98.92487</v>
       </c>
       <c r="K276" s="6" t="n">
         <v>99.76624200000001</v>
       </c>
       <c r="L276" s="6" t="n">
-        <v>99.76782900000001</v>
+        <v>99.76751899999999</v>
       </c>
       <c r="M276" s="6" t="n">
         <v>99.560475</v>
@@ -22513,13 +22513,13 @@
         <v>99.43124299999999</v>
       </c>
       <c r="J277" s="9" t="n">
-        <v>99.047963</v>
+        <v>99.04654499999999</v>
       </c>
       <c r="K277" s="9" t="n">
         <v>99.682884</v>
       </c>
       <c r="L277" s="9" t="n">
-        <v>99.731865</v>
+        <v>99.731506</v>
       </c>
       <c r="M277" s="9" t="n">
         <v>99.490852</v>
@@ -22595,13 +22595,13 @@
         <v>99.454618</v>
       </c>
       <c r="J278" s="6" t="n">
-        <v>99.13732899999999</v>
+        <v>99.136026</v>
       </c>
       <c r="K278" s="6" t="n">
         <v>99.591202</v>
       </c>
       <c r="L278" s="6" t="n">
-        <v>99.68213299999999</v>
+        <v>99.681707</v>
       </c>
       <c r="M278" s="6" t="n">
         <v>99.399615</v>
@@ -22677,13 +22677,13 @@
         <v>99.43814</v>
       </c>
       <c r="J279" s="9" t="n">
-        <v>99.175793</v>
+        <v>99.174533</v>
       </c>
       <c r="K279" s="9" t="n">
         <v>99.499804</v>
       </c>
       <c r="L279" s="9" t="n">
-        <v>99.615481</v>
+        <v>99.614966</v>
       </c>
       <c r="M279" s="9" t="n">
         <v>99.28366200000001</v>
@@ -22759,13 +22759,13 @@
         <v>99.382769</v>
       </c>
       <c r="J280" s="6" t="n">
-        <v>99.14621099999999</v>
+        <v>99.144839</v>
       </c>
       <c r="K280" s="6" t="n">
         <v>99.412802</v>
       </c>
       <c r="L280" s="6" t="n">
-        <v>99.536176</v>
+        <v>99.53555799999999</v>
       </c>
       <c r="M280" s="6" t="n">
         <v>99.194016</v>
@@ -22841,13 +22841,13 @@
         <v>99.306066</v>
       </c>
       <c r="J281" s="9" t="n">
-        <v>99.06119200000001</v>
+        <v>99.05958800000001</v>
       </c>
       <c r="K281" s="9" t="n">
         <v>99.325695</v>
       </c>
       <c r="L281" s="9" t="n">
-        <v>99.44652000000001</v>
+        <v>99.445784</v>
       </c>
       <c r="M281" s="9" t="n">
         <v>99.154372</v>
@@ -22923,13 +22923,13 @@
         <v>99.217624</v>
       </c>
       <c r="J282" s="6" t="n">
-        <v>98.963224</v>
+        <v>98.96138500000001</v>
       </c>
       <c r="K282" s="6" t="n">
         <v>99.23634800000001</v>
       </c>
       <c r="L282" s="6" t="n">
-        <v>99.344902</v>
+        <v>99.344033</v>
       </c>
       <c r="M282" s="6" t="n">
         <v>99.21282100000001</v>
@@ -23005,13 +23005,13 @@
         <v>99.121774</v>
       </c>
       <c r="J283" s="9" t="n">
-        <v>98.896491</v>
+        <v>98.894606</v>
       </c>
       <c r="K283" s="9" t="n">
         <v>99.15377599999999</v>
       </c>
       <c r="L283" s="9" t="n">
-        <v>99.22969000000001</v>
+        <v>99.228668</v>
       </c>
       <c r="M283" s="9" t="n">
         <v>99.36743800000001</v>
@@ -23087,13 +23087,13 @@
         <v>99.015991</v>
       </c>
       <c r="J284" s="6" t="n">
-        <v>98.849355</v>
+        <v>98.847508</v>
       </c>
       <c r="K284" s="6" t="n">
         <v>99.084975</v>
       </c>
       <c r="L284" s="6" t="n">
-        <v>99.100807</v>
+        <v>99.09961</v>
       </c>
       <c r="M284" s="6" t="n">
         <v>99.618748</v>
@@ -23169,13 +23169,13 @@
         <v>98.91551800000001</v>
       </c>
       <c r="J285" s="9" t="n">
-        <v>98.822146</v>
+        <v>98.820352</v>
       </c>
       <c r="K285" s="9" t="n">
         <v>99.043097</v>
       </c>
       <c r="L285" s="9" t="n">
-        <v>98.96029299999999</v>
+        <v>98.95890199999999</v>
       </c>
       <c r="M285" s="9" t="n">
         <v>99.941157</v>
@@ -23251,13 +23251,13 @@
         <v>98.827195</v>
       </c>
       <c r="J286" s="6" t="n">
-        <v>98.80695</v>
+        <v>98.805173</v>
       </c>
       <c r="K286" s="6" t="n">
         <v>99.027874</v>
       </c>
       <c r="L286" s="6" t="n">
-        <v>98.81687599999999</v>
+        <v>98.815286</v>
       </c>
       <c r="M286" s="6" t="n">
         <v>100.316034</v>
@@ -23333,13 +23333,13 @@
         <v>98.756066</v>
       </c>
       <c r="J287" s="9" t="n">
-        <v>98.79254400000001</v>
+        <v>98.790729</v>
       </c>
       <c r="K287" s="9" t="n">
         <v>99.03524299999999</v>
       </c>
       <c r="L287" s="9" t="n">
-        <v>98.683761</v>
+        <v>98.68198700000001</v>
       </c>
       <c r="M287" s="9" t="n">
         <v>100.732498</v>
@@ -23415,13 +23415,13 @@
         <v>98.694964</v>
       </c>
       <c r="J288" s="6" t="n">
-        <v>98.771046</v>
+        <v>98.769188</v>
       </c>
       <c r="K288" s="6" t="n">
         <v>99.055537</v>
       </c>
       <c r="L288" s="6" t="n">
-        <v>98.57131800000001</v>
+        <v>98.56939199999999</v>
       </c>
       <c r="M288" s="6" t="n">
         <v>101.121582</v>
@@ -23497,13 +23497,13 @@
         <v>98.655738</v>
       </c>
       <c r="J289" s="9" t="n">
-        <v>98.75422</v>
+        <v>98.752323</v>
       </c>
       <c r="K289" s="9" t="n">
         <v>99.08980699999999</v>
       </c>
       <c r="L289" s="9" t="n">
-        <v>98.49062000000001</v>
+        <v>98.48859</v>
       </c>
       <c r="M289" s="9" t="n">
         <v>101.44805</v>
@@ -23579,13 +23579,13 @@
         <v>98.669175</v>
       </c>
       <c r="J290" s="6" t="n">
-        <v>98.762383</v>
+        <v>98.760479</v>
       </c>
       <c r="K290" s="6" t="n">
         <v>99.145516</v>
       </c>
       <c r="L290" s="6" t="n">
-        <v>98.447518</v>
+        <v>98.44544</v>
       </c>
       <c r="M290" s="6" t="n">
         <v>101.67769</v>
@@ -23661,13 +23661,13 @@
         <v>98.746233</v>
       </c>
       <c r="J291" s="9" t="n">
-        <v>98.81376400000001</v>
+        <v>98.811851</v>
       </c>
       <c r="K291" s="9" t="n">
         <v>99.228639</v>
       </c>
       <c r="L291" s="9" t="n">
-        <v>98.436029</v>
+        <v>98.433948</v>
       </c>
       <c r="M291" s="9" t="n">
         <v>101.817487</v>
@@ -23743,13 +23743,13 @@
         <v>98.88310799999999</v>
       </c>
       <c r="J292" s="6" t="n">
-        <v>98.912739</v>
+        <v>98.910938</v>
       </c>
       <c r="K292" s="6" t="n">
         <v>99.336675</v>
       </c>
       <c r="L292" s="6" t="n">
-        <v>98.448263</v>
+        <v>98.44621100000001</v>
       </c>
       <c r="M292" s="6" t="n">
         <v>101.890207</v>
@@ -23825,13 +23825,13 @@
         <v>99.06513699999999</v>
       </c>
       <c r="J293" s="9" t="n">
-        <v>99.063526</v>
+        <v>99.061953</v>
       </c>
       <c r="K293" s="9" t="n">
         <v>99.466025</v>
       </c>
       <c r="L293" s="9" t="n">
-        <v>98.47629499999999</v>
+        <v>98.47429200000001</v>
       </c>
       <c r="M293" s="9" t="n">
         <v>101.918851</v>
@@ -23907,13 +23907,13 @@
         <v>99.25819799999999</v>
       </c>
       <c r="J294" s="6" t="n">
-        <v>99.238958</v>
+        <v>99.237645</v>
       </c>
       <c r="K294" s="6" t="n">
         <v>99.606852</v>
       </c>
       <c r="L294" s="6" t="n">
-        <v>98.514768</v>
+        <v>98.512821</v>
       </c>
       <c r="M294" s="6" t="n">
         <v>101.952027</v>
@@ -23991,13 +23991,13 @@
         <v>99.435998</v>
       </c>
       <c r="J295" s="9" t="n">
-        <v>99.417867</v>
+        <v>99.416839</v>
       </c>
       <c r="K295" s="9" t="n">
         <v>99.75336</v>
       </c>
       <c r="L295" s="9" t="n">
-        <v>98.562715</v>
+        <v>98.56082600000001</v>
       </c>
       <c r="M295" s="9" t="n">
         <v>101.998139</v>
@@ -24075,13 +24075,13 @@
         <v>99.578211</v>
       </c>
       <c r="J296" s="6" t="n">
-        <v>99.57753200000001</v>
+        <v>99.576808</v>
       </c>
       <c r="K296" s="6" t="n">
         <v>99.90554299999999</v>
       </c>
       <c r="L296" s="6" t="n">
-        <v>98.618246</v>
+        <v>98.61641</v>
       </c>
       <c r="M296" s="6" t="n">
         <v>102.030771</v>
@@ -24159,13 +24159,13 @@
         <v>99.663112</v>
       </c>
       <c r="J297" s="9" t="n">
-        <v>99.680914</v>
+        <v>99.680408</v>
       </c>
       <c r="K297" s="9" t="n">
         <v>100.044057</v>
       </c>
       <c r="L297" s="9" t="n">
-        <v>98.673293</v>
+        <v>98.671498</v>
       </c>
       <c r="M297" s="9" t="n">
         <v>102.027148</v>
@@ -24243,13 +24243,13 @@
         <v>99.69833</v>
       </c>
       <c r="J298" s="6" t="n">
-        <v>99.725638</v>
+        <v>99.725283</v>
       </c>
       <c r="K298" s="6" t="n">
         <v>100.155683</v>
       </c>
       <c r="L298" s="6" t="n">
-        <v>98.72364899999999</v>
+        <v>98.721891</v>
       </c>
       <c r="M298" s="6" t="n">
         <v>101.996954</v>
@@ -24327,13 +24327,13 @@
         <v>99.695348</v>
       </c>
       <c r="J299" s="9" t="n">
-        <v>99.727113</v>
+        <v>99.726805</v>
       </c>
       <c r="K299" s="9" t="n">
         <v>100.248935</v>
       </c>
       <c r="L299" s="9" t="n">
-        <v>98.76752</v>
+        <v>98.765805</v>
       </c>
       <c r="M299" s="9" t="n">
         <v>101.95441</v>
@@ -24411,13 +24411,13 @@
         <v>99.667137</v>
       </c>
       <c r="J300" s="6" t="n">
-        <v>99.697565</v>
+        <v>99.697169</v>
       </c>
       <c r="K300" s="6" t="n">
         <v>100.33904</v>
       </c>
       <c r="L300" s="6" t="n">
-        <v>98.806816</v>
+        <v>98.805159</v>
       </c>
       <c r="M300" s="6" t="n">
         <v>101.878568</v>
@@ -24495,13 +24495,13 @@
         <v>99.640159</v>
       </c>
       <c r="J301" s="9" t="n">
-        <v>99.660428</v>
+        <v>99.659879</v>
       </c>
       <c r="K301" s="9" t="n">
         <v>100.422321</v>
       </c>
       <c r="L301" s="9" t="n">
-        <v>98.844065</v>
+        <v>98.842484</v>
       </c>
       <c r="M301" s="9" t="n">
         <v>101.77148</v>
@@ -24579,13 +24579,13 @@
         <v>99.626715</v>
       </c>
       <c r="J302" s="6" t="n">
-        <v>99.631787</v>
+        <v>99.63108200000001</v>
       </c>
       <c r="K302" s="6" t="n">
         <v>100.511676</v>
       </c>
       <c r="L302" s="6" t="n">
-        <v>98.880539</v>
+        <v>98.879046</v>
       </c>
       <c r="M302" s="6" t="n">
         <v>101.603877</v>
@@ -24663,13 +24663,13 @@
         <v>99.630121</v>
       </c>
       <c r="J303" s="9" t="n">
-        <v>99.617735</v>
+        <v>99.61694900000001</v>
       </c>
       <c r="K303" s="9" t="n">
         <v>100.59257</v>
       </c>
       <c r="L303" s="9" t="n">
-        <v>98.91962700000001</v>
+        <v>98.918227</v>
       </c>
       <c r="M303" s="9" t="n">
         <v>101.423221</v>
@@ -24747,13 +24747,13 @@
         <v>99.638679</v>
       </c>
       <c r="J304" s="6" t="n">
-        <v>99.61532699999999</v>
+        <v>99.61451599999999</v>
       </c>
       <c r="K304" s="6" t="n">
         <v>100.642998</v>
       </c>
       <c r="L304" s="6" t="n">
-        <v>98.964748</v>
+        <v>98.963444</v>
       </c>
       <c r="M304" s="6" t="n">
         <v>101.268851</v>
@@ -24831,13 +24831,13 @@
         <v>99.630498</v>
       </c>
       <c r="J305" s="9" t="n">
-        <v>99.62076399999999</v>
+        <v>99.619946</v>
       </c>
       <c r="K305" s="9" t="n">
         <v>100.643966</v>
       </c>
       <c r="L305" s="9" t="n">
-        <v>99.0102</v>
+        <v>99.008978</v>
       </c>
       <c r="M305" s="9" t="n">
         <v>101.115457</v>
@@ -24915,13 +24915,13 @@
         <v>99.60068</v>
       </c>
       <c r="J306" s="6" t="n">
-        <v>99.626198</v>
+        <v>99.625471</v>
       </c>
       <c r="K306" s="6" t="n">
         <v>100.611988</v>
       </c>
       <c r="L306" s="6" t="n">
-        <v>99.052356</v>
+        <v>99.051187</v>
       </c>
       <c r="M306" s="6" t="n">
         <v>100.972602</v>
@@ -24999,13 +24999,13 @@
         <v>99.551992</v>
       </c>
       <c r="J307" s="9" t="n">
-        <v>99.623851</v>
+        <v>99.623251</v>
       </c>
       <c r="K307" s="9" t="n">
         <v>100.557763</v>
       </c>
       <c r="L307" s="9" t="n">
-        <v>99.08854599999999</v>
+        <v>99.087394</v>
       </c>
       <c r="M307" s="9" t="n">
         <v>100.842558</v>
@@ -25083,13 +25083,13 @@
         <v>99.493798</v>
       </c>
       <c r="J308" s="6" t="n">
-        <v>99.608737</v>
+        <v>99.608205</v>
       </c>
       <c r="K308" s="6" t="n">
         <v>100.48503</v>
       </c>
       <c r="L308" s="6" t="n">
-        <v>99.120609</v>
+        <v>99.119439</v>
       </c>
       <c r="M308" s="6" t="n">
         <v>100.720444</v>
@@ -25167,13 +25167,13 @@
         <v>99.44589000000001</v>
       </c>
       <c r="J309" s="9" t="n">
-        <v>99.58783</v>
+        <v>99.587242</v>
       </c>
       <c r="K309" s="9" t="n">
         <v>100.392663</v>
       </c>
       <c r="L309" s="9" t="n">
-        <v>99.155028</v>
+        <v>99.15382200000001</v>
       </c>
       <c r="M309" s="9" t="n">
         <v>100.608651</v>
@@ -25251,13 +25251,13 @@
         <v>99.419293</v>
       </c>
       <c r="J310" s="6" t="n">
-        <v>99.56807499999999</v>
+        <v>99.567359</v>
       </c>
       <c r="K310" s="6" t="n">
         <v>100.312398</v>
       </c>
       <c r="L310" s="6" t="n">
-        <v>99.195976</v>
+        <v>99.19474700000001</v>
       </c>
       <c r="M310" s="6" t="n">
         <v>100.481347</v>
@@ -25335,13 +25335,13 @@
         <v>99.432997</v>
       </c>
       <c r="J311" s="9" t="n">
-        <v>99.564106</v>
+        <v>99.56325200000001</v>
       </c>
       <c r="K311" s="9" t="n">
         <v>100.260303</v>
       </c>
       <c r="L311" s="9" t="n">
-        <v>99.24315</v>
+        <v>99.241946</v>
       </c>
       <c r="M311" s="9" t="n">
         <v>100.320577</v>
@@ -25419,13 +25419,13 @@
         <v>99.518365</v>
       </c>
       <c r="J312" s="6" t="n">
-        <v>99.62410199999999</v>
+        <v>99.62327500000001</v>
       </c>
       <c r="K312" s="6" t="n">
         <v>100.260721</v>
       </c>
       <c r="L312" s="6" t="n">
-        <v>99.29792999999999</v>
+        <v>99.296852</v>
       </c>
       <c r="M312" s="6" t="n">
         <v>100.120086</v>
@@ -25503,13 +25503,13 @@
         <v>99.679074</v>
       </c>
       <c r="J313" s="9" t="n">
-        <v>99.78560400000001</v>
+        <v>99.78505800000001</v>
       </c>
       <c r="K313" s="9" t="n">
         <v>100.299162</v>
       </c>
       <c r="L313" s="9" t="n">
-        <v>99.36314900000001</v>
+        <v>99.362253</v>
       </c>
       <c r="M313" s="9" t="n">
         <v>99.856976</v>
@@ -25587,13 +25587,13 @@
         <v>99.891136</v>
       </c>
       <c r="J314" s="6" t="n">
-        <v>100.019199</v>
+        <v>100.019083</v>
       </c>
       <c r="K314" s="6" t="n">
         <v>100.347322</v>
       </c>
       <c r="L314" s="6" t="n">
-        <v>99.434991</v>
+        <v>99.434291</v>
       </c>
       <c r="M314" s="6" t="n">
         <v>99.584187</v>
@@ -25671,13 +25671,13 @@
         <v>100.13506</v>
       </c>
       <c r="J315" s="9" t="n">
-        <v>100.294672</v>
+        <v>100.295076</v>
       </c>
       <c r="K315" s="9" t="n">
         <v>100.369452</v>
       </c>
       <c r="L315" s="9" t="n">
-        <v>99.511138</v>
+        <v>99.51062</v>
       </c>
       <c r="M315" s="9" t="n">
         <v>99.355237</v>
@@ -25755,13 +25755,13 @@
         <v>100.39458</v>
       </c>
       <c r="J316" s="6" t="n">
-        <v>100.585533</v>
+        <v>100.586443</v>
       </c>
       <c r="K316" s="6" t="n">
         <v>100.375321</v>
       </c>
       <c r="L316" s="6" t="n">
-        <v>99.59164</v>
+        <v>99.59127599999999</v>
       </c>
       <c r="M316" s="6" t="n">
         <v>99.182243</v>
@@ -25839,13 +25839,13 @@
         <v>100.643766</v>
       </c>
       <c r="J317" s="9" t="n">
-        <v>100.853907</v>
+        <v>100.855207</v>
       </c>
       <c r="K317" s="9" t="n">
         <v>100.376468</v>
       </c>
       <c r="L317" s="9" t="n">
-        <v>99.679733</v>
+        <v>99.67949400000001</v>
       </c>
       <c r="M317" s="9" t="n">
         <v>99.09406300000001</v>
@@ -25923,13 +25923,13 @@
         <v>100.857087</v>
       </c>
       <c r="J318" s="6" t="n">
-        <v>101.073765</v>
+        <v>101.075279</v>
       </c>
       <c r="K318" s="6" t="n">
         <v>100.373609</v>
       </c>
       <c r="L318" s="6" t="n">
-        <v>99.77872499999999</v>
+        <v>99.778583</v>
       </c>
       <c r="M318" s="6" t="n">
         <v>99.07048</v>
@@ -26007,13 +26007,13 @@
         <v>101.008996</v>
       </c>
       <c r="J319" s="9" t="n">
-        <v>101.248246</v>
+        <v>101.249857</v>
       </c>
       <c r="K319" s="9" t="n">
         <v>100.360853</v>
       </c>
       <c r="L319" s="9" t="n">
-        <v>99.887298</v>
+        <v>99.88722199999999</v>
       </c>
       <c r="M319" s="9" t="n">
         <v>99.081197</v>
@@ -26091,13 +26091,13 @@
         <v>101.12354</v>
       </c>
       <c r="J320" s="6" t="n">
-        <v>101.398912</v>
+        <v>101.400614</v>
       </c>
       <c r="K320" s="6" t="n">
         <v>100.338976</v>
       </c>
       <c r="L320" s="6" t="n">
-        <v>100.003023</v>
+        <v>100.002986</v>
       </c>
       <c r="M320" s="6" t="n">
         <v>99.09997</v>
@@ -26175,13 +26175,13 @@
         <v>101.216754</v>
       </c>
       <c r="J321" s="9" t="n">
-        <v>101.527468</v>
+        <v>101.529361</v>
       </c>
       <c r="K321" s="9" t="n">
         <v>100.319182</v>
       </c>
       <c r="L321" s="9" t="n">
-        <v>100.121537</v>
+        <v>100.121526</v>
       </c>
       <c r="M321" s="9" t="n">
         <v>99.13301300000001</v>
@@ -26259,13 +26259,13 @@
         <v>101.286371</v>
       </c>
       <c r="J322" s="6" t="n">
-        <v>101.632846</v>
+        <v>101.634945</v>
       </c>
       <c r="K322" s="6" t="n">
         <v>100.296158</v>
       </c>
       <c r="L322" s="6" t="n">
-        <v>100.239301</v>
+        <v>100.239331</v>
       </c>
       <c r="M322" s="6" t="n">
         <v>99.193163</v>
@@ -26343,13 +26343,13 @@
         <v>101.320199</v>
       </c>
       <c r="J323" s="9" t="n">
-        <v>101.702434</v>
+        <v>101.70471</v>
       </c>
       <c r="K323" s="9" t="n">
         <v>100.273877</v>
       </c>
       <c r="L323" s="9" t="n">
-        <v>100.352949</v>
+        <v>100.353091</v>
       </c>
       <c r="M323" s="9" t="n">
         <v>99.28701700000001</v>
@@ -26427,13 +26427,13 @@
         <v>101.324739</v>
       </c>
       <c r="J324" s="6" t="n">
-        <v>101.734741</v>
+        <v>101.737187</v>
       </c>
       <c r="K324" s="6" t="n">
         <v>100.2593</v>
       </c>
       <c r="L324" s="6" t="n">
-        <v>100.459193</v>
+        <v>100.459599</v>
       </c>
       <c r="M324" s="6" t="n">
         <v>99.36984699999999</v>
@@ -26511,13 +26511,13 @@
         <v>101.311439</v>
       </c>
       <c r="J325" s="9" t="n">
-        <v>101.73399</v>
+        <v>101.736552</v>
       </c>
       <c r="K325" s="9" t="n">
         <v>100.259375</v>
       </c>
       <c r="L325" s="9" t="n">
-        <v>100.557131</v>
+        <v>100.557855</v>
       </c>
       <c r="M325" s="9" t="n">
         <v>99.43084</v>
@@ -26595,13 +26595,13 @@
         <v>101.289007</v>
       </c>
       <c r="J326" s="6" t="n">
-        <v>101.703491</v>
+        <v>101.706041</v>
       </c>
       <c r="K326" s="6" t="n">
         <v>100.270614</v>
       </c>
       <c r="L326" s="6" t="n">
-        <v>100.64956</v>
+        <v>100.650588</v>
       </c>
       <c r="M326" s="6" t="n">
         <v>99.496438</v>
@@ -26679,13 +26679,13 @@
         <v>101.26873</v>
       </c>
       <c r="J327" s="9" t="n">
-        <v>101.658759</v>
+        <v>101.661191</v>
       </c>
       <c r="K327" s="9" t="n">
         <v>100.281872</v>
       </c>
       <c r="L327" s="9" t="n">
-        <v>100.740173</v>
+        <v>100.741447</v>
       </c>
       <c r="M327" s="9" t="n">
         <v>99.56363399999999</v>
@@ -26763,13 +26763,13 @@
         <v>101.25935</v>
       </c>
       <c r="J328" s="6" t="n">
-        <v>101.615146</v>
+        <v>101.617412</v>
       </c>
       <c r="K328" s="6" t="n">
         <v>100.296229</v>
       </c>
       <c r="L328" s="6" t="n">
-        <v>100.832779</v>
+        <v>100.834196</v>
       </c>
       <c r="M328" s="6" t="n">
         <v>99.626017</v>
@@ -26847,13 +26847,13 @@
         <v>101.274311</v>
       </c>
       <c r="J329" s="9" t="n">
-        <v>101.588815</v>
+        <v>101.590988</v>
       </c>
       <c r="K329" s="9" t="n">
         <v>100.315116</v>
       </c>
       <c r="L329" s="9" t="n">
-        <v>100.92959</v>
+        <v>100.931086</v>
       </c>
       <c r="M329" s="9" t="n">
         <v>99.66143</v>
@@ -26931,13 +26931,13 @@
         <v>101.314738</v>
       </c>
       <c r="J330" s="6" t="n">
-        <v>101.604427</v>
+        <v>101.60662</v>
       </c>
       <c r="K330" s="6" t="n">
         <v>100.337885</v>
       </c>
       <c r="L330" s="6" t="n">
-        <v>101.032901</v>
+        <v>101.034435</v>
       </c>
       <c r="M330" s="6" t="n">
         <v>99.669005</v>
@@ -27015,13 +27015,13 @@
         <v>101.381146</v>
       </c>
       <c r="J331" s="9" t="n">
-        <v>101.660754</v>
+        <v>101.663041</v>
       </c>
       <c r="K331" s="9" t="n">
         <v>100.365142</v>
       </c>
       <c r="L331" s="9" t="n">
-        <v>101.13734</v>
+        <v>101.138876</v>
       </c>
       <c r="M331" s="9" t="n">
         <v>99.63724499999999</v>
@@ -27099,13 +27099,13 @@
         <v>101.46916</v>
       </c>
       <c r="J332" s="6" t="n">
-        <v>101.731085</v>
+        <v>101.73348</v>
       </c>
       <c r="K332" s="6" t="n">
         <v>100.399774</v>
       </c>
       <c r="L332" s="6" t="n">
-        <v>101.237624</v>
+        <v>101.239138</v>
       </c>
       <c r="M332" s="6" t="n">
         <v>99.55037400000001</v>
@@ -27183,13 +27183,13 @@
         <v>101.562618</v>
       </c>
       <c r="J333" s="9" t="n">
-        <v>101.783041</v>
+        <v>101.78549</v>
       </c>
       <c r="K333" s="9" t="n">
         <v>100.452937</v>
       </c>
       <c r="L333" s="9" t="n">
-        <v>101.331142</v>
+        <v>101.332629</v>
       </c>
       <c r="M333" s="9" t="n">
         <v>99.398448</v>
@@ -27267,13 +27267,13 @@
         <v>101.644557</v>
       </c>
       <c r="J334" s="6" t="n">
-        <v>101.807721</v>
+        <v>101.810185</v>
       </c>
       <c r="K334" s="6" t="n">
         <v>100.527947</v>
       </c>
       <c r="L334" s="6" t="n">
-        <v>101.41731</v>
+        <v>101.418797</v>
       </c>
       <c r="M334" s="6" t="n">
         <v>99.219463</v>
@@ -27351,13 +27351,13 @@
         <v>101.703641</v>
       </c>
       <c r="J335" s="9" t="n">
-        <v>101.805068</v>
+        <v>101.807483</v>
       </c>
       <c r="K335" s="9" t="n">
         <v>100.617413</v>
       </c>
       <c r="L335" s="9" t="n">
-        <v>101.499031</v>
+        <v>101.500618</v>
       </c>
       <c r="M335" s="9" t="n">
         <v>99.048348</v>
@@ -27435,13 +27435,13 @@
         <v>101.732377</v>
       </c>
       <c r="J336" s="6" t="n">
-        <v>101.781223</v>
+        <v>101.783563</v>
       </c>
       <c r="K336" s="6" t="n">
         <v>100.70444</v>
       </c>
       <c r="L336" s="6" t="n">
-        <v>101.581391</v>
+        <v>101.583306</v>
       </c>
       <c r="M336" s="6" t="n">
         <v>98.916072</v>
@@ -27519,13 +27519,13 @@
         <v>101.734831</v>
       </c>
       <c r="J337" s="9" t="n">
-        <v>101.746644</v>
+        <v>101.748897</v>
       </c>
       <c r="K337" s="9" t="n">
         <v>100.777061</v>
       </c>
       <c r="L337" s="9" t="n">
-        <v>101.663798</v>
+        <v>101.666105</v>
       </c>
       <c r="M337" s="9" t="n">
         <v>98.857578</v>
@@ -27603,13 +27603,13 @@
         <v>101.713921</v>
       </c>
       <c r="J338" s="6" t="n">
-        <v>101.715827</v>
+        <v>101.718082</v>
       </c>
       <c r="K338" s="6" t="n">
         <v>100.830152</v>
       </c>
       <c r="L338" s="6" t="n">
-        <v>101.746045</v>
+        <v>101.748682</v>
       </c>
       <c r="M338" s="6" t="n">
         <v>98.85244</v>
@@ -27687,13 +27687,13 @@
         <v>101.676251</v>
       </c>
       <c r="J339" s="9" t="n">
-        <v>101.691019</v>
+        <v>101.693324</v>
       </c>
       <c r="K339" s="9" t="n">
         <v>100.864801</v>
       </c>
       <c r="L339" s="9" t="n">
-        <v>101.826656</v>
+        <v>101.829521</v>
       </c>
       <c r="M339" s="9" t="n">
         <v>98.852841</v>
@@ -27771,13 +27771,13 @@
         <v>101.637715</v>
       </c>
       <c r="J340" s="6" t="n">
-        <v>101.684322</v>
+        <v>101.686671</v>
       </c>
       <c r="K340" s="6" t="n">
         <v>100.890541</v>
       </c>
       <c r="L340" s="6" t="n">
-        <v>101.900902</v>
+        <v>101.90382</v>
       </c>
       <c r="M340" s="6" t="n">
         <v>98.833071</v>
@@ -27855,13 +27855,13 @@
         <v>101.616887</v>
       </c>
       <c r="J341" s="9" t="n">
-        <v>101.706349</v>
+        <v>101.708757</v>
       </c>
       <c r="K341" s="9" t="n">
         <v>100.917425</v>
       </c>
       <c r="L341" s="9" t="n">
-        <v>101.961409</v>
+        <v>101.964273</v>
       </c>
       <c r="M341" s="9" t="n">
         <v>98.791768</v>
@@ -27939,13 +27939,13 @@
         <v>101.619496</v>
       </c>
       <c r="J342" s="6" t="n">
-        <v>101.742674</v>
+        <v>101.74514</v>
       </c>
       <c r="K342" s="6" t="n">
         <v>100.956526</v>
       </c>
       <c r="L342" s="6" t="n">
-        <v>102.00833</v>
+        <v>102.011084</v>
       </c>
       <c r="M342" s="6" t="n">
         <v>98.706869</v>
@@ -28023,13 +28023,13 @@
         <v>101.638386</v>
       </c>
       <c r="J343" s="9" t="n">
-        <v>101.773484</v>
+        <v>101.77598</v>
       </c>
       <c r="K343" s="9" t="n">
         <v>100.981659</v>
       </c>
       <c r="L343" s="9" t="n">
-        <v>102.040524</v>
+        <v>102.043142</v>
       </c>
       <c r="M343" s="9" t="n">
         <v>98.568127</v>
@@ -28107,13 +28107,13 @@
         <v>101.672584</v>
       </c>
       <c r="J344" s="6" t="n">
-        <v>101.76325</v>
+        <v>101.765745</v>
       </c>
       <c r="K344" s="6" t="n">
         <v>100.98351</v>
       </c>
       <c r="L344" s="6" t="n">
-        <v>102.056571</v>
+        <v>102.059054</v>
       </c>
       <c r="M344" s="6" t="n">
         <v>98.404978</v>
@@ -28191,13 +28191,13 @@
         <v>101.728032</v>
       </c>
       <c r="J345" s="9" t="n">
-        <v>101.731407</v>
+        <v>101.733837</v>
       </c>
       <c r="K345" s="9" t="n">
         <v>100.966988</v>
       </c>
       <c r="L345" s="9" t="n">
-        <v>102.052316</v>
+        <v>102.054679</v>
       </c>
       <c r="M345" s="9" t="n">
         <v>98.260772</v>
@@ -28275,13 +28275,13 @@
         <v>101.758282</v>
       </c>
       <c r="J346" s="6" t="n">
-        <v>101.673507</v>
+        <v>101.675774</v>
       </c>
       <c r="K346" s="6" t="n">
         <v>100.920002</v>
       </c>
       <c r="L346" s="6" t="n">
-        <v>102.02161</v>
+        <v>102.023885</v>
       </c>
       <c r="M346" s="6" t="n">
         <v>98.18028099999999</v>
@@ -28359,13 +28359,13 @@
         <v>101.73092</v>
       </c>
       <c r="J347" s="9" t="n">
-        <v>101.564594</v>
+        <v>101.566637</v>
       </c>
       <c r="K347" s="9" t="n">
         <v>100.843257</v>
       </c>
       <c r="L347" s="9" t="n">
-        <v>101.954305</v>
+        <v>101.956562</v>
       </c>
       <c r="M347" s="9" t="n">
         <v>98.200013</v>
@@ -28443,13 +28443,13 @@
         <v>101.601926</v>
       </c>
       <c r="J348" s="6" t="n">
-        <v>101.367653</v>
+        <v>101.36948</v>
       </c>
       <c r="K348" s="6" t="n">
         <v>100.737601</v>
       </c>
       <c r="L348" s="6" t="n">
-        <v>101.838619</v>
+        <v>101.840977</v>
       </c>
       <c r="M348" s="6" t="n">
         <v>98.329184</v>
@@ -28527,13 +28527,13 @@
         <v>101.345214</v>
       </c>
       <c r="J349" s="9" t="n">
-        <v>101.080293</v>
+        <v>101.081784</v>
       </c>
       <c r="K349" s="9" t="n">
         <v>100.60976</v>
       </c>
       <c r="L349" s="9" t="n">
-        <v>101.667329</v>
+        <v>101.669757</v>
       </c>
       <c r="M349" s="9" t="n">
         <v>98.54293</v>
@@ -28611,13 +28611,13 @@
         <v>100.955778</v>
       </c>
       <c r="J350" s="6" t="n">
-        <v>100.684658</v>
+        <v>100.685638</v>
       </c>
       <c r="K350" s="6" t="n">
         <v>100.475399</v>
       </c>
       <c r="L350" s="6" t="n">
-        <v>101.436691</v>
+        <v>101.439009</v>
       </c>
       <c r="M350" s="6" t="n">
         <v>98.840017</v>
@@ -28695,13 +28695,13 @@
         <v>100.423181</v>
       </c>
       <c r="J351" s="9" t="n">
-        <v>100.167976</v>
+        <v>100.168217</v>
       </c>
       <c r="K351" s="9" t="n">
         <v>100.347654</v>
       </c>
       <c r="L351" s="9" t="n">
-        <v>101.144722</v>
+        <v>101.14673</v>
       </c>
       <c r="M351" s="9" t="n">
         <v>99.232366</v>
@@ -28779,13 +28779,13 @@
         <v>99.745102</v>
       </c>
       <c r="J352" s="6" t="n">
-        <v>99.522937</v>
+        <v>99.52229199999999</v>
       </c>
       <c r="K352" s="6" t="n">
         <v>100.232412</v>
       </c>
       <c r="L352" s="6" t="n">
-        <v>100.795601</v>
+        <v>100.797024</v>
       </c>
       <c r="M352" s="6" t="n">
         <v>99.691626</v>
@@ -28863,13 +28863,13 @@
         <v>98.966379</v>
       </c>
       <c r="J353" s="9" t="n">
-        <v>98.78919999999999</v>
+        <v>98.787513</v>
       </c>
       <c r="K353" s="9" t="n">
         <v>100.133465</v>
       </c>
       <c r="L353" s="9" t="n">
-        <v>100.403086</v>
+        <v>100.403789</v>
       </c>
       <c r="M353" s="9" t="n">
         <v>100.153025</v>
@@ -28947,13 +28947,13 @@
         <v>98.171916</v>
       </c>
       <c r="J354" s="6" t="n">
-        <v>98.042632</v>
+        <v>98.03982000000001</v>
       </c>
       <c r="K354" s="6" t="n">
         <v>100.04508</v>
       </c>
       <c r="L354" s="6" t="n">
-        <v>99.98406199999999</v>
+        <v>99.98400100000001</v>
       </c>
       <c r="M354" s="6" t="n">
         <v>100.5842</v>
@@ -29031,13 +29031,13 @@
         <v>97.49587099999999</v>
       </c>
       <c r="J355" s="9" t="n">
-        <v>97.41056399999999</v>
+        <v>97.406745</v>
       </c>
       <c r="K355" s="9" t="n">
         <v>99.956264</v>
       </c>
       <c r="L355" s="9" t="n">
-        <v>99.5675</v>
+        <v>99.56670800000001</v>
       </c>
       <c r="M355" s="9" t="n">
         <v>100.985488</v>
@@ -29115,13 +29115,13 @@
         <v>97.003804</v>
       </c>
       <c r="J356" s="6" t="n">
-        <v>96.952521</v>
+        <v>96.94794</v>
       </c>
       <c r="K356" s="6" t="n">
         <v>99.86291300000001</v>
       </c>
       <c r="L356" s="6" t="n">
-        <v>99.179436</v>
+        <v>99.17800800000001</v>
       </c>
       <c r="M356" s="6" t="n">
         <v>101.346704</v>
@@ -29199,13 +29199,13 @@
         <v>96.722875</v>
       </c>
       <c r="J357" s="9" t="n">
-        <v>96.69207900000001</v>
+        <v>96.68701799999999</v>
       </c>
       <c r="K357" s="9" t="n">
         <v>99.756777</v>
       </c>
       <c r="L357" s="9" t="n">
-        <v>98.83576600000001</v>
+        <v>98.833833</v>
       </c>
       <c r="M357" s="9" t="n">
         <v>101.650508</v>
@@ -29283,13 +29283,13 @@
         <v>96.664252</v>
       </c>
       <c r="J358" s="6" t="n">
-        <v>96.62256600000001</v>
+        <v>96.617347</v>
       </c>
       <c r="K358" s="6" t="n">
         <v>99.65566</v>
       </c>
       <c r="L358" s="6" t="n">
-        <v>98.54675</v>
+        <v>98.54447</v>
       </c>
       <c r="M358" s="6" t="n">
         <v>101.85753</v>
@@ -29367,13 +29367,13 @@
         <v>96.805977</v>
       </c>
       <c r="J359" s="9" t="n">
-        <v>96.72652600000001</v>
+        <v>96.72145500000001</v>
       </c>
       <c r="K359" s="9" t="n">
         <v>99.574326</v>
       </c>
       <c r="L359" s="9" t="n">
-        <v>98.321325</v>
+        <v>98.31887999999999</v>
       </c>
       <c r="M359" s="9" t="n">
         <v>101.959495</v>
@@ -29451,13 +29451,13 @@
         <v>97.075354</v>
       </c>
       <c r="J360" s="6" t="n">
-        <v>96.972112</v>
+        <v>96.96740699999999</v>
       </c>
       <c r="K360" s="6" t="n">
         <v>99.513468</v>
       </c>
       <c r="L360" s="6" t="n">
-        <v>98.16127899999999</v>
+        <v>98.158868</v>
       </c>
       <c r="M360" s="6" t="n">
         <v>101.9983</v>
@@ -29535,13 +29535,13 @@
         <v>97.395588</v>
       </c>
       <c r="J361" s="9" t="n">
-        <v>97.29771700000001</v>
+        <v>97.293564</v>
       </c>
       <c r="K361" s="9" t="n">
         <v>99.465536</v>
       </c>
       <c r="L361" s="9" t="n">
-        <v>98.063371</v>
+        <v>98.061081</v>
       </c>
       <c r="M361" s="9" t="n">
         <v>101.968383</v>
@@ -29619,13 +29619,13 @@
         <v>97.73065800000001</v>
       </c>
       <c r="J362" s="6" t="n">
-        <v>97.663096</v>
+        <v>97.659549</v>
       </c>
       <c r="K362" s="6" t="n">
         <v>99.43131</v>
       </c>
       <c r="L362" s="6" t="n">
-        <v>98.021449</v>
+        <v>98.01920800000001</v>
       </c>
       <c r="M362" s="6" t="n">
         <v>101.860956</v>
@@ -29703,13 +29703,13 @@
         <v>98.050557</v>
       </c>
       <c r="J363" s="9" t="n">
-        <v>98.023454</v>
+        <v>98.020455</v>
       </c>
       <c r="K363" s="9" t="n">
         <v>99.41036200000001</v>
       </c>
       <c r="L363" s="9" t="n">
-        <v>98.031946</v>
+        <v>98.02971599999999</v>
       </c>
       <c r="M363" s="9" t="n">
         <v>101.673898</v>
@@ -29787,13 +29787,13 @@
         <v>98.33188699999999</v>
       </c>
       <c r="J364" s="6" t="n">
-        <v>98.34780600000001</v>
+        <v>98.34524</v>
       </c>
       <c r="K364" s="6" t="n">
         <v>99.407606</v>
       </c>
       <c r="L364" s="6" t="n">
-        <v>98.09162000000001</v>
+        <v>98.089327</v>
       </c>
       <c r="M364" s="6" t="n">
         <v>101.456985</v>
@@ -29871,13 +29871,13 @@
         <v>98.56007700000001</v>
       </c>
       <c r="J365" s="9" t="n">
-        <v>98.60802700000001</v>
+        <v>98.605819</v>
       </c>
       <c r="K365" s="9" t="n">
         <v>99.422563</v>
       </c>
       <c r="L365" s="9" t="n">
-        <v>98.188768</v>
+        <v>98.18641700000001</v>
       </c>
       <c r="M365" s="9" t="n">
         <v>101.270902</v>
@@ -29955,13 +29955,13 @@
         <v>98.74270199999999</v>
       </c>
       <c r="J366" s="6" t="n">
-        <v>98.80301300000001</v>
+        <v>98.801059</v>
       </c>
       <c r="K366" s="6" t="n">
         <v>99.450855</v>
       </c>
       <c r="L366" s="6" t="n">
-        <v>98.309288</v>
+        <v>98.306924</v>
       </c>
       <c r="M366" s="6" t="n">
         <v>101.128262</v>
@@ -30039,13 +30039,13 @@
         <v>98.910432</v>
       </c>
       <c r="J367" s="9" t="n">
-        <v>98.95261600000001</v>
+        <v>98.95089299999999</v>
       </c>
       <c r="K367" s="9" t="n">
         <v>99.49511099999999</v>
       </c>
       <c r="L367" s="9" t="n">
-        <v>98.441633</v>
+        <v>98.43932100000001</v>
       </c>
       <c r="M367" s="9" t="n">
         <v>100.995534</v>
@@ -30123,13 +30123,13 @@
         <v>99.06559900000001</v>
       </c>
       <c r="J368" s="6" t="n">
-        <v>99.075282</v>
+        <v>99.07379400000001</v>
       </c>
       <c r="K368" s="6" t="n">
         <v>99.541842</v>
       </c>
       <c r="L368" s="6" t="n">
-        <v>98.574877</v>
+        <v>98.572681</v>
       </c>
       <c r="M368" s="6" t="n">
         <v>100.889986</v>
@@ -30207,13 +30207,13 @@
         <v>99.196381</v>
       </c>
       <c r="J369" s="9" t="n">
-        <v>99.160676</v>
+        <v>99.159384</v>
       </c>
       <c r="K369" s="9" t="n">
         <v>99.57778399999999</v>
       </c>
       <c r="L369" s="9" t="n">
-        <v>98.70012199999999</v>
+        <v>98.69810200000001</v>
       </c>
       <c r="M369" s="9" t="n">
         <v>100.804366</v>
@@ -30291,13 +30291,13 @@
         <v>99.28661099999999</v>
       </c>
       <c r="J370" s="6" t="n">
-        <v>99.196951</v>
+        <v>99.19579299999999</v>
       </c>
       <c r="K370" s="6" t="n">
         <v>99.603939</v>
       </c>
       <c r="L370" s="6" t="n">
-        <v>98.812352</v>
+        <v>98.81057300000001</v>
       </c>
       <c r="M370" s="6" t="n">
         <v>100.719171</v>
@@ -30375,13 +30375,13 @@
         <v>99.345174</v>
       </c>
       <c r="J371" s="9" t="n">
-        <v>99.198037</v>
+        <v>99.19694699999999</v>
       </c>
       <c r="K371" s="9" t="n">
         <v>99.611013</v>
       </c>
       <c r="L371" s="9" t="n">
-        <v>98.909418</v>
+        <v>98.90791400000001</v>
       </c>
       <c r="M371" s="9" t="n">
         <v>100.635618</v>
@@ -30459,13 +30459,13 @@
         <v>99.38622700000001</v>
       </c>
       <c r="J372" s="6" t="n">
-        <v>99.178809</v>
+        <v>99.177706</v>
       </c>
       <c r="K372" s="6" t="n">
         <v>99.60080499999999</v>
       </c>
       <c r="L372" s="6" t="n">
-        <v>98.994325</v>
+        <v>98.99310699999999</v>
       </c>
       <c r="M372" s="6" t="n">
         <v>100.545647</v>
@@ -30543,13 +30543,13 @@
         <v>99.41812400000001</v>
       </c>
       <c r="J373" s="9" t="n">
-        <v>99.15304500000001</v>
+        <v>99.151837</v>
       </c>
       <c r="K373" s="9" t="n">
         <v>99.576633</v>
       </c>
       <c r="L373" s="9" t="n">
-        <v>99.07074900000001</v>
+        <v>99.069782</v>
       </c>
       <c r="M373" s="9" t="n">
         <v>100.476005</v>
@@ -30627,13 +30627,13 @@
         <v>99.44787599999999</v>
       </c>
       <c r="J374" s="6" t="n">
-        <v>99.122878</v>
+        <v>99.121506</v>
       </c>
       <c r="K374" s="6" t="n">
         <v>99.533044</v>
       </c>
       <c r="L374" s="6" t="n">
-        <v>99.14143199999999</v>
+        <v>99.14059399999999</v>
       </c>
       <c r="M374" s="6" t="n">
         <v>100.46045</v>
@@ -30711,13 +30711,13 @@
         <v>99.481613</v>
       </c>
       <c r="J375" s="9" t="n">
-        <v>99.104632</v>
+        <v>99.10315300000001</v>
       </c>
       <c r="K375" s="9" t="n">
         <v>99.478324</v>
       </c>
       <c r="L375" s="9" t="n">
-        <v>99.209397</v>
+        <v>99.20860999999999</v>
       </c>
       <c r="M375" s="9" t="n">
         <v>100.456118</v>
@@ -30795,13 +30795,13 @@
         <v>99.52737500000001</v>
       </c>
       <c r="J376" s="6" t="n">
-        <v>99.109511</v>
+        <v>99.107989</v>
       </c>
       <c r="K376" s="6" t="n">
         <v>99.42358</v>
       </c>
       <c r="L376" s="6" t="n">
-        <v>99.273802</v>
+        <v>99.27298500000001</v>
       </c>
       <c r="M376" s="6" t="n">
         <v>100.426559</v>
@@ -30879,13 +30879,13 @@
         <v>99.58476899999999</v>
       </c>
       <c r="J377" s="9" t="n">
-        <v>99.143646</v>
+        <v>99.142107</v>
       </c>
       <c r="K377" s="9" t="n">
         <v>99.395076</v>
       </c>
       <c r="L377" s="9" t="n">
-        <v>99.33303600000001</v>
+        <v>99.332167</v>
       </c>
       <c r="M377" s="9" t="n">
         <v>100.351096</v>
@@ -30963,13 +30963,13 @@
         <v>99.64292</v>
       </c>
       <c r="J378" s="6" t="n">
-        <v>99.197558</v>
+        <v>99.19612100000001</v>
       </c>
       <c r="K378" s="6" t="n">
         <v>99.375559</v>
       </c>
       <c r="L378" s="6" t="n">
-        <v>99.385701</v>
+        <v>99.384793</v>
       </c>
       <c r="M378" s="6" t="n">
         <v>100.21429</v>
@@ -31047,13 +31047,13 @@
         <v>99.70102799999999</v>
       </c>
       <c r="J379" s="9" t="n">
-        <v>99.270803</v>
+        <v>99.269543</v>
       </c>
       <c r="K379" s="9" t="n">
         <v>99.360636</v>
       </c>
       <c r="L379" s="9" t="n">
-        <v>99.431275</v>
+        <v>99.430361</v>
       </c>
       <c r="M379" s="9" t="n">
         <v>100.069054</v>
@@ -31131,13 +31131,13 @@
         <v>99.762861</v>
       </c>
       <c r="J380" s="6" t="n">
-        <v>99.36946500000001</v>
+        <v>99.36842799999999</v>
       </c>
       <c r="K380" s="6" t="n">
         <v>99.37269999999999</v>
       </c>
       <c r="L380" s="6" t="n">
-        <v>99.469431</v>
+        <v>99.46854500000001</v>
       </c>
       <c r="M380" s="6" t="n">
         <v>99.95332000000001</v>
@@ -31215,13 +31215,13 @@
         <v>99.834422</v>
       </c>
       <c r="J381" s="9" t="n">
-        <v>99.48952800000001</v>
+        <v>99.48869999999999</v>
       </c>
       <c r="K381" s="9" t="n">
         <v>99.407579</v>
       </c>
       <c r="L381" s="9" t="n">
-        <v>99.498628</v>
+        <v>99.497806</v>
       </c>
       <c r="M381" s="9" t="n">
         <v>99.893202</v>
@@ -31299,13 +31299,13 @@
         <v>99.93682099999999</v>
       </c>
       <c r="J382" s="6" t="n">
-        <v>99.630843</v>
+        <v>99.630185</v>
       </c>
       <c r="K382" s="6" t="n">
         <v>99.447647</v>
       </c>
       <c r="L382" s="6" t="n">
-        <v>99.518158</v>
+        <v>99.51745099999999</v>
       </c>
       <c r="M382" s="6" t="n">
         <v>99.905421</v>
@@ -31383,13 +31383,13 @@
         <v>100.056037</v>
       </c>
       <c r="J383" s="9" t="n">
-        <v>99.781178</v>
+        <v>99.780669</v>
       </c>
       <c r="K383" s="9" t="n">
         <v>99.49385599999999</v>
       </c>
       <c r="L383" s="9" t="n">
-        <v>99.533359</v>
+        <v>99.532777</v>
       </c>
       <c r="M383" s="9" t="n">
         <v>99.92591899999999</v>
@@ -31467,13 +31467,13 @@
         <v>100.180878</v>
       </c>
       <c r="J384" s="6" t="n">
-        <v>99.93117700000001</v>
+        <v>99.93088400000001</v>
       </c>
       <c r="K384" s="6" t="n">
         <v>99.554941</v>
       </c>
       <c r="L384" s="6" t="n">
-        <v>99.549567</v>
+        <v>99.54910700000001</v>
       </c>
       <c r="M384" s="6" t="n">
         <v>99.916524</v>
@@ -31557,7 +31557,7 @@
         <v>99.64139400000001</v>
       </c>
       <c r="L385" s="9" t="n">
-        <v>99.57058000000001</v>
+        <v>99.570215</v>
       </c>
       <c r="M385" s="9" t="n">
         <v>99.872393</v>
@@ -31635,13 +31635,13 @@
         <v>100.410564</v>
       </c>
       <c r="J386" s="6" t="n">
-        <v>100.264832</v>
+        <v>100.265147</v>
       </c>
       <c r="K386" s="6" t="n">
         <v>99.750096</v>
       </c>
       <c r="L386" s="6" t="n">
-        <v>99.59972</v>
+        <v>99.599389</v>
       </c>
       <c r="M386" s="6" t="n">
         <v>99.810945</v>
@@ -31719,13 +31719,13 @@
         <v>100.507348</v>
       </c>
       <c r="J387" s="9" t="n">
-        <v>100.456239</v>
+        <v>100.456892</v>
       </c>
       <c r="K387" s="9" t="n">
         <v>99.87071400000001</v>
       </c>
       <c r="L387" s="9" t="n">
-        <v>99.63779599999999</v>
+        <v>99.63746500000001</v>
       </c>
       <c r="M387" s="9" t="n">
         <v>99.75227099999999</v>
@@ -31803,13 +31803,13 @@
         <v>100.598694</v>
       </c>
       <c r="J388" s="6" t="n">
-        <v>100.640167</v>
+        <v>100.641121</v>
       </c>
       <c r="K388" s="6" t="n">
         <v>100.000022</v>
       </c>
       <c r="L388" s="6" t="n">
-        <v>99.68509</v>
+        <v>99.684757</v>
       </c>
       <c r="M388" s="6" t="n">
         <v>99.711022</v>
@@ -31887,13 +31887,13 @@
         <v>100.68062</v>
       </c>
       <c r="J389" s="9" t="n">
-        <v>100.792058</v>
+        <v>100.793208</v>
       </c>
       <c r="K389" s="9" t="n">
         <v>100.133444</v>
       </c>
       <c r="L389" s="9" t="n">
-        <v>99.741829</v>
+        <v>99.74150899999999</v>
       </c>
       <c r="M389" s="9" t="n">
         <v>99.692168</v>
@@ -31971,13 +31971,13 @@
         <v>100.75247</v>
       </c>
       <c r="J390" s="6" t="n">
-        <v>100.899936</v>
+        <v>100.901147</v>
       </c>
       <c r="K390" s="6" t="n">
         <v>100.251671</v>
       </c>
       <c r="L390" s="6" t="n">
-        <v>99.80525799999999</v>
+        <v>99.80497800000001</v>
       </c>
       <c r="M390" s="6" t="n">
         <v>99.712537</v>
@@ -32055,13 +32055,13 @@
         <v>100.801319</v>
       </c>
       <c r="J391" s="9" t="n">
-        <v>100.967179</v>
+        <v>100.968363</v>
       </c>
       <c r="K391" s="9" t="n">
         <v>100.343198</v>
       </c>
       <c r="L391" s="9" t="n">
-        <v>99.869983</v>
+        <v>99.86977</v>
       </c>
       <c r="M391" s="9" t="n">
         <v>99.75474699999999</v>
@@ -32139,13 +32139,13 @@
         <v>100.823524</v>
       </c>
       <c r="J392" s="6" t="n">
-        <v>101.003792</v>
+        <v>101.004983</v>
       </c>
       <c r="K392" s="6" t="n">
         <v>100.397579</v>
       </c>
       <c r="L392" s="6" t="n">
-        <v>99.931196</v>
+        <v>99.93106400000001</v>
       </c>
       <c r="M392" s="6" t="n">
         <v>99.76623600000001</v>
@@ -32223,13 +32223,13 @@
         <v>100.821467</v>
       </c>
       <c r="J393" s="9" t="n">
-        <v>101.016298</v>
+        <v>101.017521</v>
       </c>
       <c r="K393" s="9" t="n">
         <v>100.417901</v>
       </c>
       <c r="L393" s="9" t="n">
-        <v>99.986867</v>
+        <v>99.98683</v>
       </c>
       <c r="M393" s="9" t="n">
         <v>99.750426</v>
@@ -32307,13 +32307,13 @@
         <v>100.801819</v>
       </c>
       <c r="J394" s="6" t="n">
-        <v>101.003514</v>
+        <v>101.004797</v>
       </c>
       <c r="K394" s="6" t="n">
         <v>100.413471</v>
       </c>
       <c r="L394" s="6" t="n">
-        <v>100.041193</v>
+        <v>100.041283</v>
       </c>
       <c r="M394" s="6" t="n">
         <v>99.721917</v>
@@ -32391,13 +32391,13 @@
         <v>100.777404</v>
       </c>
       <c r="J395" s="9" t="n">
-        <v>100.969165</v>
+        <v>100.970435</v>
       </c>
       <c r="K395" s="9" t="n">
         <v>100.394728</v>
       </c>
       <c r="L395" s="9" t="n">
-        <v>100.096281</v>
+        <v>100.096492</v>
       </c>
       <c r="M395" s="9" t="n">
         <v>99.684596</v>
@@ -32475,13 +32475,13 @@
         <v>100.743712</v>
       </c>
       <c r="J396" s="6" t="n">
-        <v>100.902673</v>
+        <v>100.903814</v>
       </c>
       <c r="K396" s="6" t="n">
         <v>100.370828</v>
       </c>
       <c r="L396" s="6" t="n">
-        <v>100.148863</v>
+        <v>100.149178</v>
       </c>
       <c r="M396" s="6" t="n">
         <v>99.674216</v>
@@ -32559,13 +32559,13 @@
         <v>100.698871</v>
       </c>
       <c r="J397" s="9" t="n">
-        <v>100.794404</v>
+        <v>100.795328</v>
       </c>
       <c r="K397" s="9" t="n">
         <v>100.355348</v>
       </c>
       <c r="L397" s="9" t="n">
-        <v>100.196561</v>
+        <v>100.196955</v>
       </c>
       <c r="M397" s="9" t="n">
         <v>99.710047</v>
@@ -32643,13 +32643,13 @@
         <v>100.653855</v>
       </c>
       <c r="J398" s="6" t="n">
-        <v>100.663111</v>
+        <v>100.66385</v>
       </c>
       <c r="K398" s="6" t="n">
         <v>100.325437</v>
       </c>
       <c r="L398" s="6" t="n">
-        <v>100.237941</v>
+        <v>100.238385</v>
       </c>
       <c r="M398" s="6" t="n">
         <v>99.785157</v>
@@ -32727,13 +32727,13 @@
         <v>100.60579</v>
       </c>
       <c r="J399" s="9" t="n">
-        <v>100.508302</v>
+        <v>100.508824</v>
       </c>
       <c r="K399" s="9" t="n">
         <v>100.261109</v>
       </c>
       <c r="L399" s="9" t="n">
-        <v>100.270736</v>
+        <v>100.271204</v>
       </c>
       <c r="M399" s="9" t="n">
         <v>99.908596</v>
@@ -32811,13 +32811,13 @@
         <v>100.548795</v>
       </c>
       <c r="J400" s="6" t="n">
-        <v>100.360614</v>
+        <v>100.360917</v>
       </c>
       <c r="K400" s="6" t="n">
         <v>100.17405</v>
       </c>
       <c r="L400" s="6" t="n">
-        <v>100.295244</v>
+        <v>100.295719</v>
       </c>
       <c r="M400" s="6" t="n">
         <v>100.052666</v>
@@ -32895,13 +32895,13 @@
         <v>100.465353</v>
       </c>
       <c r="J401" s="9" t="n">
-        <v>100.219629</v>
+        <v>100.219762</v>
       </c>
       <c r="K401" s="9" t="n">
         <v>100.086018</v>
       </c>
       <c r="L401" s="9" t="n">
-        <v>100.310662</v>
+        <v>100.311138</v>
       </c>
       <c r="M401" s="9" t="n">
         <v>100.174522</v>
@@ -32979,13 +32979,13 @@
         <v>100.360024</v>
       </c>
       <c r="J402" s="6" t="n">
-        <v>100.08891</v>
+        <v>100.088888</v>
       </c>
       <c r="K402" s="6" t="n">
         <v>100.024913</v>
       </c>
       <c r="L402" s="6" t="n">
-        <v>100.3142</v>
+        <v>100.314671</v>
       </c>
       <c r="M402" s="6" t="n">
         <v>100.247749</v>
@@ -33063,13 +33063,13 @@
         <v>100.243889</v>
       </c>
       <c r="J403" s="9" t="n">
-        <v>99.961631</v>
+        <v>99.96141799999999</v>
       </c>
       <c r="K403" s="9" t="n">
         <v>99.97686899999999</v>
       </c>
       <c r="L403" s="9" t="n">
-        <v>100.304303</v>
+        <v>100.304761</v>
       </c>
       <c r="M403" s="9" t="n">
         <v>100.261196</v>
@@ -33147,13 +33147,13 @@
         <v>100.130992</v>
       </c>
       <c r="J404" s="6" t="n">
-        <v>99.829582</v>
+        <v>99.829155</v>
       </c>
       <c r="K404" s="6" t="n">
         <v>99.935231</v>
       </c>
       <c r="L404" s="6" t="n">
-        <v>100.280992</v>
+        <v>100.281423</v>
       </c>
       <c r="M404" s="6" t="n">
         <v>100.239181</v>
@@ -33231,13 +33231,13 @@
         <v>100.033544</v>
       </c>
       <c r="J405" s="9" t="n">
-        <v>99.713379</v>
+        <v>99.71278</v>
       </c>
       <c r="K405" s="9" t="n">
         <v>99.895686</v>
       </c>
       <c r="L405" s="9" t="n">
-        <v>100.246108</v>
+        <v>100.246501</v>
       </c>
       <c r="M405" s="9" t="n">
         <v>100.182651</v>
@@ -33315,13 +33315,13 @@
         <v>99.959633</v>
       </c>
       <c r="J406" s="6" t="n">
-        <v>99.630332</v>
+        <v>99.629597</v>
       </c>
       <c r="K406" s="6" t="n">
         <v>99.860005</v>
       </c>
       <c r="L406" s="6" t="n">
-        <v>100.202105</v>
+        <v>100.20246</v>
       </c>
       <c r="M406" s="6" t="n">
         <v>100.081421</v>
@@ -33399,13 +33399,13 @@
         <v>99.899542</v>
       </c>
       <c r="J407" s="9" t="n">
-        <v>99.56559900000001</v>
+        <v>99.564835</v>
       </c>
       <c r="K407" s="9" t="n">
         <v>99.81638</v>
       </c>
       <c r="L407" s="9" t="n">
-        <v>100.151069</v>
+        <v>100.151369</v>
       </c>
       <c r="M407" s="9" t="n">
         <v>99.988446</v>
@@ -33483,13 +33483,13 @@
         <v>99.854792</v>
       </c>
       <c r="J408" s="6" t="n">
-        <v>99.52857400000001</v>
+        <v>99.527833</v>
       </c>
       <c r="K408" s="6" t="n">
         <v>99.760096</v>
       </c>
       <c r="L408" s="6" t="n">
-        <v>100.095755</v>
+        <v>100.095988</v>
       </c>
       <c r="M408" s="6" t="n">
         <v>99.914834</v>
@@ -33567,13 +33567,13 @@
         <v>99.822543</v>
       </c>
       <c r="J409" s="9" t="n">
-        <v>99.517201</v>
+        <v>99.516475</v>
       </c>
       <c r="K409" s="9" t="n">
         <v>99.688177</v>
       </c>
       <c r="L409" s="9" t="n">
-        <v>100.039283</v>
+        <v>100.039442</v>
       </c>
       <c r="M409" s="9" t="n">
         <v>99.882953</v>
@@ -33651,13 +33651,13 @@
         <v>99.79326</v>
       </c>
       <c r="J410" s="6" t="n">
-        <v>99.521852</v>
+        <v>99.521102</v>
       </c>
       <c r="K410" s="6" t="n">
         <v>99.614542</v>
       </c>
       <c r="L410" s="6" t="n">
-        <v>99.982681</v>
+        <v>99.98276</v>
       </c>
       <c r="M410" s="6" t="n">
         <v>99.909919</v>
@@ -33735,7 +33735,7 @@
         <v>99.76964</v>
       </c>
       <c r="J411" s="9" t="n">
-        <v>99.55488200000001</v>
+        <v>99.554152</v>
       </c>
       <c r="K411" s="9" t="n">
         <v>99.54498</v>
@@ -33819,13 +33819,13 @@
         <v>99.755798</v>
       </c>
       <c r="J412" s="6" t="n">
-        <v>99.611918</v>
+        <v>99.61118999999999</v>
       </c>
       <c r="K412" s="6" t="n">
         <v>99.48368499999999</v>
       </c>
       <c r="L412" s="6" t="n">
-        <v>99.87623499999999</v>
+        <v>99.87616</v>
       </c>
       <c r="M412" s="6" t="n">
         <v>100.162724</v>
@@ -33903,13 +33903,13 @@
         <v>99.763592</v>
       </c>
       <c r="J413" s="9" t="n">
-        <v>99.70158000000001</v>
+        <v>99.700863</v>
       </c>
       <c r="K413" s="9" t="n">
         <v>99.431759</v>
       </c>
       <c r="L413" s="9" t="n">
-        <v>99.828253</v>
+        <v>99.828113</v>
       </c>
       <c r="M413" s="9" t="n">
         <v>100.414378</v>
@@ -33987,13 +33987,13 @@
         <v>99.79723</v>
       </c>
       <c r="J414" s="6" t="n">
-        <v>99.82667499999999</v>
+        <v>99.826043</v>
       </c>
       <c r="K414" s="6" t="n">
         <v>99.401104</v>
       </c>
       <c r="L414" s="6" t="n">
-        <v>99.787843</v>
+        <v>99.78765199999999</v>
       </c>
       <c r="M414" s="6" t="n">
         <v>100.674138</v>
@@ -34071,13 +34071,13 @@
         <v>99.868223</v>
       </c>
       <c r="J415" s="9" t="n">
-        <v>99.98394999999999</v>
+        <v>99.983569</v>
       </c>
       <c r="K415" s="9" t="n">
         <v>99.401213</v>
       </c>
       <c r="L415" s="9" t="n">
-        <v>99.76057900000001</v>
+        <v>99.760356</v>
       </c>
       <c r="M415" s="9" t="n">
         <v>100.881865</v>
@@ -34155,13 +34155,13 @@
         <v>99.953914</v>
       </c>
       <c r="J416" s="6" t="n">
-        <v>100.153509</v>
+        <v>100.153452</v>
       </c>
       <c r="K416" s="6" t="n">
         <v>99.422316</v>
       </c>
       <c r="L416" s="6" t="n">
-        <v>99.747505</v>
+        <v>99.74726800000001</v>
       </c>
       <c r="M416" s="6" t="n">
         <v>101.045797</v>
@@ -34239,13 +34239,13 @@
         <v>100.035193</v>
       </c>
       <c r="J417" s="9" t="n">
-        <v>100.295017</v>
+        <v>100.295257</v>
       </c>
       <c r="K417" s="9" t="n">
         <v>99.45326900000001</v>
       </c>
       <c r="L417" s="9" t="n">
-        <v>99.745333</v>
+        <v>99.74509500000001</v>
       </c>
       <c r="M417" s="9" t="n">
         <v>101.14644</v>
@@ -34323,13 +34323,13 @@
         <v>100.093726</v>
       </c>
       <c r="J418" s="6" t="n">
-        <v>100.384189</v>
+        <v>100.384612</v>
       </c>
       <c r="K418" s="6" t="n">
         <v>99.47739</v>
       </c>
       <c r="L418" s="6" t="n">
-        <v>99.746251</v>
+        <v>99.746015</v>
       </c>
       <c r="M418" s="6" t="n">
         <v>101.176454</v>
@@ -34407,13 +34407,13 @@
         <v>100.116339</v>
       </c>
       <c r="J419" s="9" t="n">
-        <v>100.418882</v>
+        <v>100.419364</v>
       </c>
       <c r="K419" s="9" t="n">
         <v>99.493461</v>
       </c>
       <c r="L419" s="9" t="n">
-        <v>99.745149</v>
+        <v>99.744907</v>
       </c>
       <c r="M419" s="9" t="n">
         <v>101.161277</v>
@@ -34491,13 +34491,13 @@
         <v>100.111751</v>
       </c>
       <c r="J420" s="6" t="n">
-        <v>100.411626</v>
+        <v>100.412135</v>
       </c>
       <c r="K420" s="6" t="n">
         <v>99.50578899999999</v>
       </c>
       <c r="L420" s="6" t="n">
-        <v>99.741666</v>
+        <v>99.74141400000001</v>
       </c>
       <c r="M420" s="6" t="n">
         <v>101.088385</v>
@@ -34575,13 +34575,13 @@
         <v>100.087375</v>
       </c>
       <c r="J421" s="9" t="n">
-        <v>100.392375</v>
+        <v>100.392867</v>
       </c>
       <c r="K421" s="9" t="n">
         <v>99.520962</v>
       </c>
       <c r="L421" s="9" t="n">
-        <v>99.73804800000001</v>
+        <v>99.737787</v>
       </c>
       <c r="M421" s="9" t="n">
         <v>100.928963</v>
@@ -34659,13 +34659,13 @@
         <v>100.066037</v>
       </c>
       <c r="J422" s="6" t="n">
-        <v>100.382226</v>
+        <v>100.382709</v>
       </c>
       <c r="K422" s="6" t="n">
         <v>99.54624800000001</v>
       </c>
       <c r="L422" s="6" t="n">
-        <v>99.738198</v>
+        <v>99.737934</v>
       </c>
       <c r="M422" s="6" t="n">
         <v>100.718963</v>
@@ -34743,13 +34743,13 @@
         <v>100.054426</v>
       </c>
       <c r="J423" s="9" t="n">
-        <v>100.373988</v>
+        <v>100.374417</v>
       </c>
       <c r="K423" s="9" t="n">
         <v>99.59605500000001</v>
       </c>
       <c r="L423" s="9" t="n">
-        <v>99.745344</v>
+        <v>99.745088</v>
       </c>
       <c r="M423" s="9" t="n">
         <v>100.49357</v>
@@ -34827,13 +34827,13 @@
         <v>100.046266</v>
       </c>
       <c r="J424" s="6" t="n">
-        <v>100.352109</v>
+        <v>100.352542</v>
       </c>
       <c r="K424" s="6" t="n">
         <v>99.66585499999999</v>
       </c>
       <c r="L424" s="6" t="n">
-        <v>99.758995</v>
+        <v>99.75875600000001</v>
       </c>
       <c r="M424" s="6" t="n">
         <v>100.273752</v>
@@ -34911,13 +34911,13 @@
         <v>100.043123</v>
       </c>
       <c r="J425" s="9" t="n">
-        <v>100.320977</v>
+        <v>100.321414</v>
       </c>
       <c r="K425" s="9" t="n">
         <v>99.745029</v>
       </c>
       <c r="L425" s="9" t="n">
-        <v>99.777265</v>
+        <v>99.777052</v>
       </c>
       <c r="M425" s="9" t="n">
         <v>100.106041</v>
@@ -34995,13 +34995,13 @@
         <v>100.054017</v>
       </c>
       <c r="J426" s="6" t="n">
-        <v>100.295949</v>
+        <v>100.296368</v>
       </c>
       <c r="K426" s="6" t="n">
         <v>99.829702</v>
       </c>
       <c r="L426" s="6" t="n">
-        <v>99.79768799999999</v>
+        <v>99.797504</v>
       </c>
       <c r="M426" s="6" t="n">
         <v>100.020804</v>
@@ -35079,13 +35079,13 @@
         <v>100.084315</v>
       </c>
       <c r="J427" s="9" t="n">
-        <v>100.294375</v>
+        <v>100.294732</v>
       </c>
       <c r="K427" s="9" t="n">
         <v>99.908661</v>
       </c>
       <c r="L427" s="9" t="n">
-        <v>99.81783</v>
+        <v>99.817672</v>
       </c>
       <c r="M427" s="9" t="n">
         <v>99.99379399999999</v>
@@ -35163,13 +35163,13 @@
         <v>100.130793</v>
       </c>
       <c r="J428" s="6" t="n">
-        <v>100.319558</v>
+        <v>100.319843</v>
       </c>
       <c r="K428" s="6" t="n">
         <v>99.97863099999999</v>
       </c>
       <c r="L428" s="6" t="n">
-        <v>99.836815</v>
+        <v>99.83668</v>
       </c>
       <c r="M428" s="6" t="n">
         <v>99.99829099999999</v>
@@ -35247,13 +35247,13 @@
         <v>100.187249</v>
       </c>
       <c r="J429" s="9" t="n">
-        <v>100.381909</v>
+        <v>100.382161</v>
       </c>
       <c r="K429" s="9" t="n">
         <v>100.043101</v>
       </c>
       <c r="L429" s="9" t="n">
-        <v>99.853644</v>
+        <v>99.853525</v>
       </c>
       <c r="M429" s="9" t="n">
         <v>100.03499</v>
@@ -35331,13 +35331,13 @@
         <v>100.242505</v>
       </c>
       <c r="J430" s="6" t="n">
-        <v>100.474273</v>
+        <v>100.474625</v>
       </c>
       <c r="K430" s="6" t="n">
         <v>100.106041</v>
       </c>
       <c r="L430" s="6" t="n">
-        <v>99.87019600000001</v>
+        <v>99.87008899999999</v>
       </c>
       <c r="M430" s="6" t="n">
         <v>100.089292</v>
@@ -35415,13 +35415,13 @@
         <v>100.304224</v>
       </c>
       <c r="J431" s="9" t="n">
-        <v>100.604303</v>
+        <v>100.604878</v>
       </c>
       <c r="K431" s="9" t="n">
         <v>100.167669</v>
       </c>
       <c r="L431" s="9" t="n">
-        <v>99.887719</v>
+        <v>99.88762699999999</v>
       </c>
       <c r="M431" s="9" t="n">
         <v>100.131823</v>
@@ -35499,13 +35499,13 @@
         <v>100.36124</v>
       </c>
       <c r="J432" s="6" t="n">
-        <v>100.752046</v>
+        <v>100.75284</v>
       </c>
       <c r="K432" s="6" t="n">
         <v>100.223304</v>
       </c>
       <c r="L432" s="6" t="n">
-        <v>99.905102</v>
+        <v>99.905023</v>
       </c>
       <c r="M432" s="6" t="n">
         <v>100.163105</v>
@@ -35583,13 +35583,13 @@
         <v>100.390876</v>
       </c>
       <c r="J433" s="9" t="n">
-        <v>100.874813</v>
+        <v>100.875865</v>
       </c>
       <c r="K433" s="9" t="n">
         <v>100.26246</v>
       </c>
       <c r="L433" s="9" t="n">
-        <v>99.919167</v>
+        <v>99.919095</v>
       </c>
       <c r="M433" s="9" t="n">
         <v>100.177776</v>
@@ -35667,13 +35667,13 @@
         <v>100.377994</v>
       </c>
       <c r="J434" s="6" t="n">
-        <v>100.934025</v>
+        <v>100.935262</v>
       </c>
       <c r="K434" s="6" t="n">
         <v>100.283753</v>
       </c>
       <c r="L434" s="6" t="n">
-        <v>99.926817</v>
+        <v>99.926748</v>
       </c>
       <c r="M434" s="6" t="n">
         <v>100.180258</v>
@@ -35751,13 +35751,13 @@
         <v>100.304765</v>
       </c>
       <c r="J435" s="9" t="n">
-        <v>100.89576</v>
+        <v>100.897003</v>
       </c>
       <c r="K435" s="9" t="n">
         <v>100.298322</v>
       </c>
       <c r="L435" s="9" t="n">
-        <v>99.92888499999999</v>
+        <v>99.928811</v>
       </c>
       <c r="M435" s="9" t="n">
         <v>100.163184</v>
@@ -35835,13 +35835,13 @@
         <v>100.203889</v>
       </c>
       <c r="J436" s="6" t="n">
-        <v>100.800952</v>
+        <v>100.802066</v>
       </c>
       <c r="K436" s="6" t="n">
         <v>100.324218</v>
       </c>
       <c r="L436" s="6" t="n">
-        <v>99.926401</v>
+        <v>99.926316</v>
       </c>
       <c r="M436" s="6" t="n">
         <v>100.128891</v>
@@ -35919,13 +35919,13 @@
         <v>100.1097</v>
       </c>
       <c r="J437" s="9" t="n">
-        <v>100.686762</v>
+        <v>100.687725</v>
       </c>
       <c r="K437" s="9" t="n">
         <v>100.3717</v>
       </c>
       <c r="L437" s="9" t="n">
-        <v>99.920939</v>
+        <v>99.92084</v>
       </c>
       <c r="M437" s="9" t="n">
         <v>100.113289</v>
@@ -36003,13 +36003,13 @@
         <v>100.033967</v>
       </c>
       <c r="J438" s="6" t="n">
-        <v>100.563875</v>
+        <v>100.564657</v>
       </c>
       <c r="K438" s="6" t="n">
         <v>100.437582</v>
       </c>
       <c r="L438" s="6" t="n">
-        <v>99.91564200000001</v>
+        <v>99.91552799999999</v>
       </c>
       <c r="M438" s="6" t="n">
         <v>100.060113</v>
@@ -36087,13 +36087,13 @@
         <v>99.97800700000001</v>
       </c>
       <c r="J439" s="9" t="n">
-        <v>100.439157</v>
+        <v>100.439752</v>
       </c>
       <c r="K439" s="9" t="n">
         <v>100.509397</v>
       </c>
       <c r="L439" s="9" t="n">
-        <v>99.912982</v>
+        <v>99.912856</v>
       </c>
       <c r="M439" s="9" t="n">
         <v>99.99088399999999</v>
@@ -36171,13 +36171,13 @@
         <v>99.93898299999999</v>
       </c>
       <c r="J440" s="6" t="n">
-        <v>100.319788</v>
+        <v>100.32016</v>
       </c>
       <c r="K440" s="6" t="n">
         <v>100.590122</v>
       </c>
       <c r="L440" s="6" t="n">
-        <v>99.917473</v>
+        <v>99.91734099999999</v>
       </c>
       <c r="M440" s="6" t="n">
         <v>99.91515800000001</v>
@@ -36255,13 +36255,13 @@
         <v>99.92813099999999</v>
       </c>
       <c r="J441" s="9" t="n">
-        <v>100.2246</v>
+        <v>100.224722</v>
       </c>
       <c r="K441" s="9" t="n">
         <v>100.680885</v>
       </c>
       <c r="L441" s="9" t="n">
-        <v>99.93453</v>
+        <v>99.934405</v>
       </c>
       <c r="M441" s="9" t="n">
         <v>99.84824</v>
@@ -36339,13 +36339,13 @@
         <v>99.949501</v>
       </c>
       <c r="J442" s="6" t="n">
-        <v>100.162097</v>
+        <v>100.162078</v>
       </c>
       <c r="K442" s="6" t="n">
         <v>100.780384</v>
       </c>
       <c r="L442" s="6" t="n">
-        <v>99.96388899999999</v>
+        <v>99.963785</v>
       </c>
       <c r="M442" s="6" t="n">
         <v>99.80558499999999</v>
@@ -36423,13 +36423,13 @@
         <v>99.99887699999999</v>
       </c>
       <c r="J443" s="9" t="n">
-        <v>100.133713</v>
+        <v>100.133649</v>
       </c>
       <c r="K443" s="9" t="n">
         <v>100.882394</v>
       </c>
       <c r="L443" s="9" t="n">
-        <v>100.002683</v>
+        <v>100.002612</v>
       </c>
       <c r="M443" s="9" t="n">
         <v>99.762361</v>
@@ -36507,13 +36507,13 @@
         <v>100.070359</v>
       </c>
       <c r="J444" s="6" t="n">
-        <v>100.14627</v>
+        <v>100.14632</v>
       </c>
       <c r="K444" s="6" t="n">
         <v>100.972498</v>
       </c>
       <c r="L444" s="6" t="n">
-        <v>100.046603</v>
+        <v>100.046572</v>
       </c>
       <c r="M444" s="6" t="n">
         <v>99.724878</v>
@@ -36591,13 +36591,13 @@
         <v>100.163769</v>
       </c>
       <c r="J445" s="9" t="n">
-        <v>100.20185</v>
+        <v>100.202135</v>
       </c>
       <c r="K445" s="9" t="n">
         <v>101.047141</v>
       </c>
       <c r="L445" s="9" t="n">
-        <v>100.093051</v>
+        <v>100.093063</v>
       </c>
       <c r="M445" s="9" t="n">
         <v>99.692948</v>
@@ -36675,13 +36675,13 @@
         <v>100.270539</v>
       </c>
       <c r="J446" s="6" t="n">
-        <v>100.295854</v>
+        <v>100.296429</v>
       </c>
       <c r="K446" s="6" t="n">
         <v>101.093864</v>
       </c>
       <c r="L446" s="6" t="n">
-        <v>100.139804</v>
+        <v>100.13986</v>
       </c>
       <c r="M446" s="6" t="n">
         <v>99.63210599999999</v>
@@ -36759,13 +36759,13 @@
         <v>100.374292</v>
       </c>
       <c r="J447" s="9" t="n">
-        <v>100.415229</v>
+        <v>100.416139</v>
       </c>
       <c r="K447" s="9" t="n">
         <v>101.098646</v>
       </c>
       <c r="L447" s="9" t="n">
-        <v>100.183494</v>
+        <v>100.183591</v>
       </c>
       <c r="M447" s="9" t="n">
         <v>99.49036599999999</v>
@@ -36843,13 +36843,13 @@
         <v>100.462827</v>
       </c>
       <c r="J448" s="6" t="n">
-        <v>100.543974</v>
+        <v>100.545152</v>
       </c>
       <c r="K448" s="6" t="n">
         <v>101.050675</v>
       </c>
       <c r="L448" s="6" t="n">
-        <v>100.222653</v>
+        <v>100.222783</v>
       </c>
       <c r="M448" s="6" t="n">
         <v>99.30413299999999</v>
@@ -36927,13 +36927,13 @@
         <v>100.525583</v>
       </c>
       <c r="J449" s="9" t="n">
-        <v>100.651616</v>
+        <v>100.652855</v>
       </c>
       <c r="K449" s="9" t="n">
         <v>100.957902</v>
       </c>
       <c r="L449" s="9" t="n">
-        <v>100.258519</v>
+        <v>100.258677</v>
       </c>
       <c r="M449" s="9" t="n">
         <v>99.085402</v>
@@ -37011,13 +37011,13 @@
         <v>100.552171</v>
       </c>
       <c r="J450" s="6" t="n">
-        <v>100.725321</v>
+        <v>100.726413</v>
       </c>
       <c r="K450" s="6" t="n">
         <v>100.833323</v>
       </c>
       <c r="L450" s="6" t="n">
-        <v>100.29361</v>
+        <v>100.293792</v>
       </c>
       <c r="M450" s="6" t="n">
         <v>98.852627</v>
@@ -37095,13 +37095,13 @@
         <v>100.542085</v>
       </c>
       <c r="J451" s="9" t="n">
-        <v>100.750022</v>
+        <v>100.750799</v>
       </c>
       <c r="K451" s="9" t="n">
         <v>100.700657</v>
       </c>
       <c r="L451" s="9" t="n">
-        <v>100.332347</v>
+        <v>100.332558</v>
       </c>
       <c r="M451" s="9" t="n">
         <v>98.66904700000001</v>
@@ -37179,13 +37179,13 @@
         <v>100.509733</v>
       </c>
       <c r="J452" s="6" t="n">
-        <v>100.728781</v>
+        <v>100.729223</v>
       </c>
       <c r="K452" s="6" t="n">
         <v>100.573373</v>
       </c>
       <c r="L452" s="6" t="n">
-        <v>100.378426</v>
+        <v>100.378673</v>
       </c>
       <c r="M452" s="6" t="n">
         <v>98.580573</v>
@@ -37263,13 +37263,13 @@
         <v>100.46267</v>
       </c>
       <c r="J453" s="9" t="n">
-        <v>100.663742</v>
+        <v>100.664028</v>
       </c>
       <c r="K453" s="9" t="n">
         <v>100.464745</v>
       </c>
       <c r="L453" s="9" t="n">
-        <v>100.429635</v>
+        <v>100.429921</v>
       </c>
       <c r="M453" s="9" t="n">
         <v>98.55077</v>
@@ -37347,13 +37347,13 @@
         <v>100.412658</v>
       </c>
       <c r="J454" s="6" t="n">
-        <v>100.583218</v>
+        <v>100.583629</v>
       </c>
       <c r="K454" s="6" t="n">
         <v>100.371692</v>
       </c>
       <c r="L454" s="6" t="n">
-        <v>100.483666</v>
+        <v>100.483996</v>
       </c>
       <c r="M454" s="6" t="n">
         <v>98.556009</v>
@@ -37431,13 +37431,13 @@
         <v>100.374008</v>
       </c>
       <c r="J455" s="9" t="n">
-        <v>100.505462</v>
+        <v>100.5061</v>
       </c>
       <c r="K455" s="9" t="n">
         <v>100.293965</v>
       </c>
       <c r="L455" s="9" t="n">
-        <v>100.53976</v>
+        <v>100.540134</v>
       </c>
       <c r="M455" s="9" t="n">
         <v>98.599481</v>
@@ -37515,13 +37515,13 @@
         <v>100.355325</v>
       </c>
       <c r="J456" s="6" t="n">
-        <v>100.445461</v>
+        <v>100.446362</v>
       </c>
       <c r="K456" s="6" t="n">
         <v>100.232243</v>
       </c>
       <c r="L456" s="6" t="n">
-        <v>100.592774</v>
+        <v>100.593187</v>
       </c>
       <c r="M456" s="6" t="n">
         <v>98.679941</v>
@@ -37599,13 +37599,13 @@
         <v>100.378503</v>
       </c>
       <c r="J457" s="9" t="n">
-        <v>100.423399</v>
+        <v>100.424528</v>
       </c>
       <c r="K457" s="9" t="n">
         <v>100.181076</v>
       </c>
       <c r="L457" s="9" t="n">
-        <v>100.639483</v>
+        <v>100.639926</v>
       </c>
       <c r="M457" s="9" t="n">
         <v>98.772239</v>
@@ -37683,13 +37683,13 @@
         <v>100.442411</v>
       </c>
       <c r="J458" s="6" t="n">
-        <v>100.439941</v>
+        <v>100.441202</v>
       </c>
       <c r="K458" s="6" t="n">
         <v>100.141209</v>
       </c>
       <c r="L458" s="6" t="n">
-        <v>100.68005</v>
+        <v>100.680515</v>
       </c>
       <c r="M458" s="6" t="n">
         <v>98.84582399999999</v>
@@ -37767,13 +37767,13 @@
         <v>100.558685</v>
       </c>
       <c r="J459" s="9" t="n">
-        <v>100.500431</v>
+        <v>100.501744</v>
       </c>
       <c r="K459" s="9" t="n">
         <v>100.114222</v>
       </c>
       <c r="L459" s="9" t="n">
-        <v>100.717413</v>
+        <v>100.717894</v>
       </c>
       <c r="M459" s="9" t="n">
         <v>98.872964</v>
@@ -37851,13 +37851,13 @@
         <v>100.697232</v>
       </c>
       <c r="J460" s="6" t="n">
-        <v>100.57771</v>
+        <v>100.579009</v>
       </c>
       <c r="K460" s="6" t="n">
         <v>100.0992</v>
       </c>
       <c r="L460" s="6" t="n">
-        <v>100.75577</v>
+        <v>100.756268</v>
       </c>
       <c r="M460" s="6" t="n">
         <v>98.86121300000001</v>
@@ -37935,13 +37935,13 @@
         <v>100.8265</v>
       </c>
       <c r="J461" s="9" t="n">
-        <v>100.649656</v>
+        <v>100.65092</v>
       </c>
       <c r="K461" s="9" t="n">
         <v>100.096403</v>
       </c>
       <c r="L461" s="9" t="n">
-        <v>100.798772</v>
+        <v>100.799292</v>
       </c>
       <c r="M461" s="9" t="n">
         <v>98.833736</v>
@@ -38019,13 +38019,13 @@
         <v>100.929015</v>
       </c>
       <c r="J462" s="6" t="n">
-        <v>100.700423</v>
+        <v>100.701616</v>
       </c>
       <c r="K462" s="6" t="n">
         <v>100.093756</v>
       </c>
       <c r="L462" s="6" t="n">
-        <v>100.847758</v>
+        <v>100.848305</v>
       </c>
       <c r="M462" s="6" t="n">
         <v>98.811998</v>
@@ -38103,13 +38103,13 @@
         <v>101.013689</v>
       </c>
       <c r="J463" s="9" t="n">
-        <v>100.742101</v>
+        <v>100.743151</v>
       </c>
       <c r="K463" s="9" t="n">
         <v>100.089575</v>
       </c>
       <c r="L463" s="9" t="n">
-        <v>100.902686</v>
+        <v>100.903266</v>
       </c>
       <c r="M463" s="9" t="n">
         <v>98.79289799999999</v>
@@ -38187,13 +38187,13 @@
         <v>101.078443</v>
       </c>
       <c r="J464" s="6" t="n">
-        <v>100.778534</v>
+        <v>100.779422</v>
       </c>
       <c r="K464" s="6" t="n">
         <v>100.08742</v>
       </c>
       <c r="L464" s="6" t="n">
-        <v>100.960235</v>
+        <v>100.960851</v>
       </c>
       <c r="M464" s="6" t="n">
         <v>98.77428500000001</v>
@@ -38271,13 +38271,13 @@
         <v>101.121419</v>
       </c>
       <c r="J465" s="9" t="n">
-        <v>100.819115</v>
+        <v>100.819922</v>
       </c>
       <c r="K465" s="9" t="n">
         <v>100.082768</v>
       </c>
       <c r="L465" s="9" t="n">
-        <v>101.01637</v>
+        <v>101.017018</v>
       </c>
       <c r="M465" s="9" t="n">
         <v>98.74603999999999</v>
@@ -38355,13 +38355,13 @@
         <v>101.160257</v>
       </c>
       <c r="J466" s="6" t="n">
-        <v>100.879017</v>
+        <v>100.880134</v>
       </c>
       <c r="K466" s="6" t="n">
         <v>100.085121</v>
       </c>
       <c r="L466" s="6" t="n">
-        <v>101.067953</v>
+        <v>101.068626</v>
       </c>
       <c r="M466" s="6" t="n">
         <v>98.69668799999999</v>
@@ -38439,13 +38439,13 @@
         <v>101.191843</v>
       </c>
       <c r="J467" s="9" t="n">
-        <v>100.928198</v>
+        <v>100.929644</v>
       </c>
       <c r="K467" s="9" t="n">
         <v>100.095812</v>
       </c>
       <c r="L467" s="9" t="n">
-        <v>101.113079</v>
+        <v>101.113769</v>
       </c>
       <c r="M467" s="9" t="n">
         <v>98.661429</v>
@@ -38523,13 +38523,13 @@
         <v>101.216272</v>
       </c>
       <c r="J468" s="6" t="n">
-        <v>100.950062</v>
+        <v>100.951699</v>
       </c>
       <c r="K468" s="6" t="n">
         <v>100.113316</v>
       </c>
       <c r="L468" s="6" t="n">
-        <v>101.152061</v>
+        <v>101.152758</v>
       </c>
       <c r="M468" s="6" t="n">
         <v>98.62925300000001</v>
@@ -38607,13 +38607,13 @@
         <v>101.222956</v>
       </c>
       <c r="J469" s="9" t="n">
-        <v>100.932467</v>
+        <v>100.934167</v>
       </c>
       <c r="K469" s="9" t="n">
         <v>100.139078</v>
       </c>
       <c r="L469" s="9" t="n">
-        <v>101.183002</v>
+        <v>101.183695</v>
       </c>
       <c r="M469" s="9" t="n">
         <v>98.61937</v>
@@ -38691,13 +38691,13 @@
         <v>101.200703</v>
       </c>
       <c r="J470" s="6" t="n">
-        <v>100.879283</v>
+        <v>100.881029</v>
       </c>
       <c r="K470" s="6" t="n">
         <v>100.175452</v>
       </c>
       <c r="L470" s="6" t="n">
-        <v>101.20282</v>
+        <v>101.203493</v>
       </c>
       <c r="M470" s="6" t="n">
         <v>98.632058</v>
@@ -38775,13 +38775,13 @@
         <v>101.146362</v>
       </c>
       <c r="J471" s="9" t="n">
-        <v>100.782275</v>
+        <v>100.78398</v>
       </c>
       <c r="K471" s="9" t="n">
         <v>100.215513</v>
       </c>
       <c r="L471" s="9" t="n">
-        <v>101.210348</v>
+        <v>101.210982</v>
       </c>
       <c r="M471" s="9" t="n">
         <v>98.70413000000001</v>
@@ -38859,13 +38859,13 @@
         <v>101.068407</v>
       </c>
       <c r="J472" s="6" t="n">
-        <v>100.666798</v>
+        <v>100.668397</v>
       </c>
       <c r="K472" s="6" t="n">
         <v>100.245473</v>
       </c>
       <c r="L472" s="6" t="n">
-        <v>101.207809</v>
+        <v>101.20839</v>
       </c>
       <c r="M472" s="6" t="n">
         <v>98.84439999999999</v>
@@ -38943,13 +38943,13 @@
         <v>100.98473</v>
       </c>
       <c r="J473" s="9" t="n">
-        <v>100.566505</v>
+        <v>100.567977</v>
       </c>
       <c r="K473" s="9" t="n">
         <v>100.262958</v>
       </c>
       <c r="L473" s="9" t="n">
-        <v>101.200139</v>
+        <v>101.200657</v>
       </c>
       <c r="M473" s="9" t="n">
         <v>99.00823099999999</v>
@@ -39027,13 +39027,13 @@
         <v>100.90681</v>
       </c>
       <c r="J474" s="6" t="n">
-        <v>100.496435</v>
+        <v>100.497751</v>
       </c>
       <c r="K474" s="6" t="n">
         <v>100.276437</v>
       </c>
       <c r="L474" s="6" t="n">
-        <v>101.193676</v>
+        <v>101.194131</v>
       </c>
       <c r="M474" s="6" t="n">
         <v>99.119664</v>
@@ -39111,13 +39111,13 @@
         <v>100.828835</v>
       </c>
       <c r="J475" s="9" t="n">
-        <v>100.452046</v>
+        <v>100.45314</v>
       </c>
       <c r="K475" s="9" t="n">
         <v>100.283821</v>
       </c>
       <c r="L475" s="9" t="n">
-        <v>101.192323</v>
+        <v>101.19272</v>
       </c>
       <c r="M475" s="9" t="n">
         <v>99.1977</v>
@@ -39195,13 +39195,13 @@
         <v>100.7513</v>
       </c>
       <c r="J476" s="6" t="n">
-        <v>100.42138</v>
+        <v>100.422245</v>
       </c>
       <c r="K476" s="6" t="n">
         <v>100.282713</v>
       </c>
       <c r="L476" s="6" t="n">
-        <v>101.19768</v>
+        <v>101.198031</v>
       </c>
       <c r="M476" s="6" t="n">
         <v>99.243132</v>
@@ -39279,13 +39279,13 @@
         <v>100.694886</v>
       </c>
       <c r="J477" s="9" t="n">
-        <v>100.40764</v>
+        <v>100.408371</v>
       </c>
       <c r="K477" s="9" t="n">
         <v>100.282435</v>
       </c>
       <c r="L477" s="9" t="n">
-        <v>101.208948</v>
+        <v>101.209262</v>
       </c>
       <c r="M477" s="9" t="n">
         <v>99.259235</v>
@@ -39363,13 +39363,13 @@
         <v>100.659585</v>
       </c>
       <c r="J478" s="6" t="n">
-        <v>100.387503</v>
+        <v>100.388246</v>
       </c>
       <c r="K478" s="6" t="n">
         <v>100.285163</v>
       </c>
       <c r="L478" s="6" t="n">
-        <v>101.222288</v>
+        <v>101.222569</v>
       </c>
       <c r="M478" s="6" t="n">
         <v>99.265045</v>
@@ -39447,13 +39447,13 @@
         <v>100.644538</v>
       </c>
       <c r="J479" s="9" t="n">
-        <v>100.350805</v>
+        <v>100.351666</v>
       </c>
       <c r="K479" s="9" t="n">
         <v>100.287163</v>
       </c>
       <c r="L479" s="9" t="n">
-        <v>101.233488</v>
+        <v>101.233733</v>
       </c>
       <c r="M479" s="9" t="n">
         <v>99.245042</v>
@@ -39531,13 +39531,13 @@
         <v>100.63335</v>
       </c>
       <c r="J480" s="6" t="n">
-        <v>100.269452</v>
+        <v>100.270376</v>
       </c>
       <c r="K480" s="6" t="n">
         <v>100.279579</v>
       </c>
       <c r="L480" s="6" t="n">
-        <v>101.236804</v>
+        <v>101.237004</v>
       </c>
       <c r="M480" s="6" t="n">
         <v>99.214519</v>
@@ -39615,13 +39615,13 @@
         <v>100.61356</v>
       </c>
       <c r="J481" s="9" t="n">
-        <v>100.137422</v>
+        <v>100.138318</v>
       </c>
       <c r="K481" s="9" t="n">
         <v>100.257203</v>
       </c>
       <c r="L481" s="9" t="n">
-        <v>101.226821</v>
+        <v>101.22696</v>
       </c>
       <c r="M481" s="9" t="n">
         <v>99.189567</v>
@@ -39699,13 +39699,13 @@
         <v>100.568385</v>
       </c>
       <c r="J482" s="6" t="n">
-        <v>99.955972</v>
+        <v>99.956729</v>
       </c>
       <c r="K482" s="6" t="n">
         <v>100.212716</v>
       </c>
       <c r="L482" s="6" t="n">
-        <v>101.196074</v>
+        <v>101.196122</v>
       </c>
       <c r="M482" s="6" t="n">
         <v>99.19387500000001</v>
@@ -39783,13 +39783,13 @@
         <v>100.48129</v>
       </c>
       <c r="J483" s="9" t="n">
-        <v>99.737978</v>
+        <v>99.738558</v>
       </c>
       <c r="K483" s="9" t="n">
         <v>100.14533</v>
       </c>
       <c r="L483" s="9" t="n">
-        <v>101.130893</v>
+        <v>101.130806</v>
       </c>
       <c r="M483" s="9" t="n">
         <v>99.23739500000001</v>
@@ -39867,13 +39867,13 @@
         <v>100.355012</v>
       </c>
       <c r="J484" s="6" t="n">
-        <v>99.51930400000001</v>
+        <v>99.519688</v>
       </c>
       <c r="K484" s="6" t="n">
         <v>100.047472</v>
       </c>
       <c r="L484" s="6" t="n">
-        <v>101.01276</v>
+        <v>101.012468</v>
       </c>
       <c r="M484" s="6" t="n">
         <v>99.32328</v>
@@ -39951,13 +39951,13 @@
         <v>100.177571</v>
       </c>
       <c r="J485" s="9" t="n">
-        <v>99.299888</v>
+        <v>99.300033</v>
       </c>
       <c r="K485" s="9" t="n">
         <v>99.898799</v>
       </c>
       <c r="L485" s="9" t="n">
-        <v>100.820015</v>
+        <v>100.819419</v>
       </c>
       <c r="M485" s="9" t="n">
         <v>99.481589</v>
@@ -40035,13 +40035,13 @@
         <v>99.938339</v>
       </c>
       <c r="J486" s="6" t="n">
-        <v>99.07555600000001</v>
+        <v>99.07543200000001</v>
       </c>
       <c r="K486" s="6" t="n">
         <v>99.685355</v>
       </c>
       <c r="L486" s="6" t="n">
-        <v>100.53203</v>
+        <v>100.531006</v>
       </c>
       <c r="M486" s="6" t="n">
         <v>99.77721</v>
@@ -40119,13 +40119,13 @@
         <v>99.633067</v>
       </c>
       <c r="J487" s="9" t="n">
-        <v>98.826425</v>
+        <v>98.826033</v>
       </c>
       <c r="K487" s="9" t="n">
         <v>99.419527</v>
       </c>
       <c r="L487" s="9" t="n">
-        <v>100.139135</v>
+        <v>100.137542</v>
       </c>
       <c r="M487" s="9" t="n">
         <v>100.21106</v>
@@ -40203,13 +40203,13 @@
         <v>99.312411</v>
       </c>
       <c r="J488" s="6" t="n">
-        <v>98.57699599999999</v>
+        <v>98.57625899999999</v>
       </c>
       <c r="K488" s="6" t="n">
         <v>99.134522</v>
       </c>
       <c r="L488" s="6" t="n">
-        <v>99.660546</v>
+        <v>99.658266</v>
       </c>
       <c r="M488" s="6" t="n">
         <v>100.763144</v>
@@ -40287,13 +40287,13 @@
         <v>87.086179</v>
       </c>
       <c r="J489" s="9" t="n">
-        <v>85.535252</v>
+        <v>85.51202499999999</v>
       </c>
       <c r="K489" s="9" t="n">
         <v>92.09486699999999</v>
       </c>
       <c r="L489" s="9" t="n">
-        <v>99.13992</v>
+        <v>99.136893</v>
       </c>
       <c r="M489" s="9" t="n">
         <v>101.437215</v>
@@ -40371,13 +40371,13 @@
         <v>86.05866899999999</v>
       </c>
       <c r="J490" s="6" t="n">
-        <v>85.48944</v>
+        <v>85.468962</v>
       </c>
       <c r="K490" s="6" t="n">
         <v>92.110906</v>
       </c>
       <c r="L490" s="6" t="n">
-        <v>98.63494799999999</v>
+        <v>98.631197</v>
       </c>
       <c r="M490" s="6" t="n">
         <v>102.116821</v>
@@ -40455,13 +40455,13 @@
         <v>92.06177700000001</v>
       </c>
       <c r="J491" s="9" t="n">
-        <v>93.298743</v>
+        <v>93.293133</v>
       </c>
       <c r="K491" s="9" t="n">
         <v>94.53784899999999</v>
       </c>
       <c r="L491" s="9" t="n">
-        <v>98.20657300000001</v>
+        <v>98.202202</v>
       </c>
       <c r="M491" s="9" t="n">
         <v>102.708314</v>
@@ -40539,13 +40539,13 @@
         <v>93.727487</v>
       </c>
       <c r="J492" s="6" t="n">
-        <v>94.07505</v>
+        <v>94.067013</v>
       </c>
       <c r="K492" s="6" t="n">
         <v>95.715806</v>
       </c>
       <c r="L492" s="6" t="n">
-        <v>97.885499</v>
+        <v>97.880655</v>
       </c>
       <c r="M492" s="6" t="n">
         <v>103.114588</v>
@@ -40623,13 +40623,13 @@
         <v>94.88754400000001</v>
       </c>
       <c r="J493" s="9" t="n">
-        <v>95.363587</v>
+        <v>95.35747499999999</v>
       </c>
       <c r="K493" s="9" t="n">
         <v>96.295664</v>
       </c>
       <c r="L493" s="9" t="n">
-        <v>97.669267</v>
+        <v>97.664091</v>
       </c>
       <c r="M493" s="9" t="n">
         <v>103.325394</v>
@@ -40707,13 +40707,13 @@
         <v>96.065246</v>
       </c>
       <c r="J494" s="6" t="n">
-        <v>96.57366</v>
+        <v>96.56940299999999</v>
       </c>
       <c r="K494" s="6" t="n">
         <v>96.90643</v>
       </c>
       <c r="L494" s="6" t="n">
-        <v>97.542666</v>
+        <v>97.53728</v>
       </c>
       <c r="M494" s="6" t="n">
         <v>103.3754</v>
@@ -40791,13 +40791,13 @@
         <v>97.066833</v>
       </c>
       <c r="J495" s="9" t="n">
-        <v>97.52958700000001</v>
+        <v>97.52677799999999</v>
       </c>
       <c r="K495" s="9" t="n">
         <v>97.46845</v>
       </c>
       <c r="L495" s="9" t="n">
-        <v>97.488848</v>
+        <v>97.483351</v>
       </c>
       <c r="M495" s="9" t="n">
         <v>103.316735</v>
@@ -40875,13 +40875,13 @@
         <v>97.81243600000001</v>
       </c>
       <c r="J496" s="6" t="n">
-        <v>98.168198</v>
+        <v>98.166375</v>
       </c>
       <c r="K496" s="6" t="n">
         <v>97.97136</v>
       </c>
       <c r="L496" s="6" t="n">
-        <v>97.48921199999999</v>
+        <v>97.483677</v>
       </c>
       <c r="M496" s="6" t="n">
         <v>103.208421</v>
@@ -40959,13 +40959,13 @@
         <v>98.303466</v>
       </c>
       <c r="J497" s="9" t="n">
-        <v>98.515196</v>
+        <v>98.513998</v>
       </c>
       <c r="K497" s="9" t="n">
         <v>98.416764</v>
       </c>
       <c r="L497" s="9" t="n">
-        <v>97.529414</v>
+        <v>97.52389599999999</v>
       </c>
       <c r="M497" s="9" t="n">
         <v>103.095652</v>
@@ -41043,13 +41043,13 @@
         <v>98.597145</v>
       </c>
       <c r="J498" s="6" t="n">
-        <v>98.65266200000001</v>
+        <v>98.651777</v>
       </c>
       <c r="K498" s="6" t="n">
         <v>98.81958299999999</v>
       </c>
       <c r="L498" s="6" t="n">
-        <v>97.604879</v>
+        <v>97.59943199999999</v>
       </c>
       <c r="M498" s="6" t="n">
         <v>103.012859</v>
@@ -41127,13 +41127,13 @@
         <v>98.758105</v>
       </c>
       <c r="J499" s="9" t="n">
-        <v>98.676157</v>
+        <v>98.675409</v>
       </c>
       <c r="K499" s="9" t="n">
         <v>99.173204</v>
       </c>
       <c r="L499" s="9" t="n">
-        <v>97.725796</v>
+        <v>97.720494</v>
       </c>
       <c r="M499" s="9" t="n">
         <v>102.901341</v>
@@ -41211,13 +41211,13 @@
         <v>98.83748</v>
       </c>
       <c r="J500" s="6" t="n">
-        <v>98.656131</v>
+        <v>98.65540799999999</v>
       </c>
       <c r="K500" s="6" t="n">
         <v>99.453103</v>
       </c>
       <c r="L500" s="6" t="n">
-        <v>97.905142</v>
+        <v>97.90008</v>
       </c>
       <c r="M500" s="6" t="n">
         <v>102.769381</v>
@@ -41295,13 +41295,13 @@
         <v>98.834453</v>
       </c>
       <c r="J501" s="9" t="n">
-        <v>98.597959</v>
+        <v>98.597115</v>
       </c>
       <c r="K501" s="9" t="n">
         <v>99.63269099999999</v>
       </c>
       <c r="L501" s="9" t="n">
-        <v>98.14818699999999</v>
+        <v>98.143474</v>
       </c>
       <c r="M501" s="9" t="n">
         <v>102.607878</v>
@@ -41379,13 +41379,13 @@
         <v>98.764408</v>
       </c>
       <c r="J502" s="6" t="n">
-        <v>98.52091900000001</v>
+        <v>98.519902</v>
       </c>
       <c r="K502" s="6" t="n">
         <v>99.733542</v>
       </c>
       <c r="L502" s="6" t="n">
-        <v>98.445615</v>
+        <v>98.44132999999999</v>
       </c>
       <c r="M502" s="6" t="n">
         <v>102.415597</v>
@@ -41463,13 +41463,13 @@
         <v>98.649531</v>
       </c>
       <c r="J503" s="9" t="n">
-        <v>98.45438</v>
+        <v>98.453154</v>
       </c>
       <c r="K503" s="9" t="n">
         <v>99.78176000000001</v>
       </c>
       <c r="L503" s="9" t="n">
-        <v>98.759812</v>
+        <v>98.755976</v>
       </c>
       <c r="M503" s="9" t="n">
         <v>102.241828</v>
@@ -41547,13 +41547,13 @@
         <v>98.521581</v>
       </c>
       <c r="J504" s="6" t="n">
-        <v>98.42257499999999</v>
+        <v>98.42110700000001</v>
       </c>
       <c r="K504" s="6" t="n">
         <v>99.807912</v>
       </c>
       <c r="L504" s="6" t="n">
-        <v>99.051681</v>
+        <v>99.048254</v>
       </c>
       <c r="M504" s="6" t="n">
         <v>102.101795</v>
@@ -41631,13 +41631,13 @@
         <v>98.42109600000001</v>
       </c>
       <c r="J505" s="9" t="n">
-        <v>98.44125</v>
+        <v>98.43960199999999</v>
       </c>
       <c r="K505" s="9" t="n">
         <v>99.83334499999999</v>
       </c>
       <c r="L505" s="9" t="n">
-        <v>99.294569</v>
+        <v>99.291479</v>
       </c>
       <c r="M505" s="9" t="n">
         <v>101.976133</v>
@@ -41715,13 +41715,13 @@
         <v>98.39023899999999</v>
       </c>
       <c r="J506" s="6" t="n">
-        <v>98.525616</v>
+        <v>98.52393600000001</v>
       </c>
       <c r="K506" s="6" t="n">
         <v>99.866663</v>
       </c>
       <c r="L506" s="6" t="n">
-        <v>99.482004</v>
+        <v>99.479175</v>
       </c>
       <c r="M506" s="6" t="n">
         <v>101.854597</v>
@@ -41799,13 +41799,13 @@
         <v>98.448289</v>
       </c>
       <c r="J507" s="9" t="n">
-        <v>98.699923</v>
+        <v>98.698481</v>
       </c>
       <c r="K507" s="9" t="n">
         <v>99.912217</v>
       </c>
       <c r="L507" s="9" t="n">
-        <v>99.620707</v>
+        <v>99.618077</v>
       </c>
       <c r="M507" s="9" t="n">
         <v>101.731337</v>
@@ -41883,13 +41883,13 @@
         <v>98.581749</v>
       </c>
       <c r="J508" s="6" t="n">
-        <v>98.95139</v>
+        <v>98.950447</v>
       </c>
       <c r="K508" s="6" t="n">
         <v>99.975185</v>
       </c>
       <c r="L508" s="6" t="n">
-        <v>99.723849</v>
+        <v>99.721377</v>
       </c>
       <c r="M508" s="6" t="n">
         <v>101.6102</v>
@@ -41967,13 +41967,13 @@
         <v>98.764109</v>
       </c>
       <c r="J509" s="9" t="n">
-        <v>99.252528</v>
+        <v>99.252224</v>
       </c>
       <c r="K509" s="9" t="n">
         <v>100.060613</v>
       </c>
       <c r="L509" s="9" t="n">
-        <v>99.802565</v>
+        <v>99.800225</v>
       </c>
       <c r="M509" s="9" t="n">
         <v>101.488279</v>
@@ -42051,13 +42051,13 @@
         <v>98.967977</v>
       </c>
       <c r="J510" s="6" t="n">
-        <v>99.55910299999999</v>
+        <v>99.559568</v>
       </c>
       <c r="K510" s="6" t="n">
         <v>100.175994</v>
       </c>
       <c r="L510" s="6" t="n">
-        <v>99.864835</v>
+        <v>99.862622</v>
       </c>
       <c r="M510" s="6" t="n">
         <v>101.339484</v>
@@ -42135,13 +42135,13 @@
         <v>99.169524</v>
       </c>
       <c r="J511" s="9" t="n">
-        <v>99.831065</v>
+        <v>99.832224</v>
       </c>
       <c r="K511" s="9" t="n">
         <v>100.32811</v>
       </c>
       <c r="L511" s="9" t="n">
-        <v>99.914962</v>
+        <v>99.912885</v>
       </c>
       <c r="M511" s="9" t="n">
         <v>101.133415</v>
@@ -42219,13 +42219,13 @@
         <v>99.35535299999999</v>
       </c>
       <c r="J512" s="6" t="n">
-        <v>100.053127</v>
+        <v>100.054727</v>
       </c>
       <c r="K512" s="6" t="n">
         <v>100.486554</v>
       </c>
       <c r="L512" s="6" t="n">
-        <v>99.955634</v>
+        <v>99.95371900000001</v>
       </c>
       <c r="M512" s="6" t="n">
         <v>100.84374</v>
@@ -42303,13 +42303,13 @@
         <v>99.512</v>
       </c>
       <c r="J513" s="9" t="n">
-        <v>100.210753</v>
+        <v>100.212389</v>
       </c>
       <c r="K513" s="9" t="n">
         <v>100.616418</v>
       </c>
       <c r="L513" s="9" t="n">
-        <v>99.990926</v>
+        <v>99.989208</v>
       </c>
       <c r="M513" s="9" t="n">
         <v>100.554136</v>
@@ -42387,13 +42387,13 @@
         <v>99.634957</v>
       </c>
       <c r="J514" s="6" t="n">
-        <v>100.305668</v>
+        <v>100.306984</v>
       </c>
       <c r="K514" s="6" t="n">
         <v>100.721235</v>
       </c>
       <c r="L514" s="6" t="n">
-        <v>100.023726</v>
+        <v>100.02222</v>
       </c>
       <c r="M514" s="6" t="n">
         <v>100.322507</v>
@@ -42471,13 +42471,13 @@
         <v>99.738906</v>
       </c>
       <c r="J515" s="9" t="n">
-        <v>100.363379</v>
+        <v>100.364155</v>
       </c>
       <c r="K515" s="9" t="n">
         <v>100.799684</v>
       </c>
       <c r="L515" s="9" t="n">
-        <v>100.05859</v>
+        <v>100.057293</v>
       </c>
       <c r="M515" s="9" t="n">
         <v>100.146864</v>
@@ -42555,13 +42555,13 @@
         <v>99.845921</v>
       </c>
       <c r="J516" s="6" t="n">
-        <v>100.415985</v>
+        <v>100.416245</v>
       </c>
       <c r="K516" s="6" t="n">
         <v>100.857179</v>
       </c>
       <c r="L516" s="6" t="n">
-        <v>100.096689</v>
+        <v>100.095591</v>
       </c>
       <c r="M516" s="6" t="n">
         <v>100.011662</v>
@@ -42639,13 +42639,13 @@
         <v>99.961147</v>
       </c>
       <c r="J517" s="9" t="n">
-        <v>100.475087</v>
+        <v>100.475021</v>
       </c>
       <c r="K517" s="9" t="n">
         <v>100.899594</v>
       </c>
       <c r="L517" s="9" t="n">
-        <v>100.137711</v>
+        <v>100.136804</v>
       </c>
       <c r="M517" s="9" t="n">
         <v>99.91291099999999</v>
@@ -42723,13 +42723,13 @@
         <v>100.08228</v>
       </c>
       <c r="J518" s="6" t="n">
-        <v>100.549922</v>
+        <v>100.549796</v>
       </c>
       <c r="K518" s="6" t="n">
         <v>100.921963</v>
       </c>
       <c r="L518" s="6" t="n">
-        <v>100.180559</v>
+        <v>100.179837</v>
       </c>
       <c r="M518" s="6" t="n">
         <v>99.83016600000001</v>
@@ -42807,13 +42807,13 @@
         <v>100.20599</v>
       </c>
       <c r="J519" s="9" t="n">
-        <v>100.655924</v>
+        <v>100.656071</v>
       </c>
       <c r="K519" s="9" t="n">
         <v>100.931414</v>
       </c>
       <c r="L519" s="9" t="n">
-        <v>100.223194</v>
+        <v>100.222659</v>
       </c>
       <c r="M519" s="9" t="n">
         <v>99.740756</v>
@@ -42891,13 +42891,13 @@
         <v>100.32151</v>
       </c>
       <c r="J520" s="6" t="n">
-        <v>100.790659</v>
+        <v>100.791385</v>
       </c>
       <c r="K520" s="6" t="n">
         <v>100.930561</v>
       </c>
       <c r="L520" s="6" t="n">
-        <v>100.264114</v>
+        <v>100.263781</v>
       </c>
       <c r="M520" s="6" t="n">
         <v>99.60321500000001</v>
@@ -42975,13 +42975,13 @@
         <v>100.41259</v>
       </c>
       <c r="J521" s="9" t="n">
-        <v>100.924012</v>
+        <v>100.925472</v>
       </c>
       <c r="K521" s="9" t="n">
         <v>100.928281</v>
       </c>
       <c r="L521" s="9" t="n">
-        <v>100.306068</v>
+        <v>100.305966</v>
       </c>
       <c r="M521" s="9" t="n">
         <v>99.436708</v>
@@ -43059,13 +43059,13 @@
         <v>100.466217</v>
       </c>
       <c r="J522" s="6" t="n">
-        <v>101.025879</v>
+        <v>101.028024</v>
       </c>
       <c r="K522" s="6" t="n">
         <v>100.922353</v>
       </c>
       <c r="L522" s="6" t="n">
-        <v>100.351117</v>
+        <v>100.351294</v>
       </c>
       <c r="M522" s="6" t="n">
         <v>99.248795</v>
@@ -43143,13 +43143,13 @@
         <v>100.494626</v>
       </c>
       <c r="J523" s="9" t="n">
-        <v>101.105997</v>
+        <v>101.108626</v>
       </c>
       <c r="K523" s="9" t="n">
         <v>100.916655</v>
       </c>
       <c r="L523" s="9" t="n">
-        <v>100.400402</v>
+        <v>100.400924</v>
       </c>
       <c r="M523" s="9" t="n">
         <v>99.076531</v>
@@ -43227,13 +43227,13 @@
         <v>100.529188</v>
       </c>
       <c r="J524" s="6" t="n">
-        <v>101.18651</v>
+        <v>101.189325</v>
       </c>
       <c r="K524" s="6" t="n">
         <v>100.922367</v>
       </c>
       <c r="L524" s="6" t="n">
-        <v>100.450407</v>
+        <v>100.451343</v>
       </c>
       <c r="M524" s="6" t="n">
         <v>98.94109899999999</v>
@@ -43311,13 +43311,13 @@
         <v>100.588584</v>
       </c>
       <c r="J525" s="9" t="n">
-        <v>101.281118</v>
+        <v>101.283764</v>
       </c>
       <c r="K525" s="9" t="n">
         <v>100.947822</v>
       </c>
       <c r="L525" s="9" t="n">
-        <v>100.494387</v>
+        <v>100.495799</v>
       </c>
       <c r="M525" s="9" t="n">
         <v>98.844397</v>
@@ -43395,13 +43395,13 @@
         <v>100.663596</v>
       </c>
       <c r="J526" s="6" t="n">
-        <v>101.386863</v>
+        <v>101.388892</v>
       </c>
       <c r="K526" s="6" t="n">
         <v>100.981938</v>
       </c>
       <c r="L526" s="6" t="n">
-        <v>100.528801</v>
+        <v>100.530697</v>
       </c>
       <c r="M526" s="6" t="n">
         <v>98.755256</v>
@@ -43479,13 +43479,13 @@
         <v>100.746361</v>
       </c>
       <c r="J527" s="9" t="n">
-        <v>101.492355</v>
+        <v>101.493341</v>
       </c>
       <c r="K527" s="9" t="n">
         <v>101.015742</v>
       </c>
       <c r="L527" s="9" t="n">
-        <v>100.550895</v>
+        <v>100.55323</v>
       </c>
       <c r="M527" s="9" t="n">
         <v>98.704909</v>
@@ -43563,13 +43563,13 @@
         <v>100.826882</v>
       </c>
       <c r="J528" s="6" t="n">
-        <v>101.585166</v>
+        <v>101.584921</v>
       </c>
       <c r="K528" s="6" t="n">
         <v>101.024907</v>
       </c>
       <c r="L528" s="6" t="n">
-        <v>100.561366</v>
+        <v>100.564068</v>
       </c>
       <c r="M528" s="6" t="n">
         <v>98.723112</v>
@@ -43647,13 +43647,13 @@
         <v>100.898812</v>
       </c>
       <c r="J529" s="9" t="n">
-        <v>101.657075</v>
+        <v>101.655708</v>
       </c>
       <c r="K529" s="9" t="n">
         <v>101.002422</v>
       </c>
       <c r="L529" s="9" t="n">
-        <v>100.563612</v>
+        <v>100.566624</v>
       </c>
       <c r="M529" s="9" t="n">
         <v>98.782865</v>
@@ -43731,13 +43731,13 @@
         <v>100.949689</v>
       </c>
       <c r="J530" s="6" t="n">
-        <v>101.693088</v>
+        <v>101.690968</v>
       </c>
       <c r="K530" s="6" t="n">
         <v>100.951281</v>
       </c>
       <c r="L530" s="6" t="n">
-        <v>100.561817</v>
+        <v>100.565101</v>
       </c>
       <c r="M530" s="6" t="n">
         <v>98.873553</v>
@@ -43815,13 +43815,13 @@
         <v>100.96379</v>
       </c>
       <c r="J531" s="9" t="n">
-        <v>101.668958</v>
+        <v>101.666622</v>
       </c>
       <c r="K531" s="9" t="n">
         <v>100.868401</v>
       </c>
       <c r="L531" s="9" t="n">
-        <v>100.55894</v>
+        <v>100.562499</v>
       </c>
       <c r="M531" s="9" t="n">
         <v>98.978506</v>
@@ -43899,13 +43899,13 @@
         <v>100.945883</v>
       </c>
       <c r="J532" s="6" t="n">
-        <v>101.570448</v>
+        <v>101.568531</v>
       </c>
       <c r="K532" s="6" t="n">
         <v>100.748232</v>
       </c>
       <c r="L532" s="6" t="n">
-        <v>100.555608</v>
+        <v>100.55948</v>
       </c>
       <c r="M532" s="6" t="n">
         <v>99.077924</v>
@@ -43983,13 +43983,13 @@
         <v>100.916478</v>
       </c>
       <c r="J533" s="9" t="n">
-        <v>101.42949</v>
+        <v>101.428694</v>
       </c>
       <c r="K533" s="9" t="n">
         <v>100.595588</v>
       </c>
       <c r="L533" s="9" t="n">
-        <v>100.552071</v>
+        <v>100.556327</v>
       </c>
       <c r="M533" s="9" t="n">
         <v>99.16212299999999</v>
@@ -44067,13 +44067,13 @@
         <v>100.879828</v>
       </c>
       <c r="J534" s="6" t="n">
-        <v>101.265159</v>
+        <v>101.265916</v>
       </c>
       <c r="K534" s="6" t="n">
         <v>100.430872</v>
       </c>
       <c r="L534" s="6" t="n">
-        <v>100.549178</v>
+        <v>100.553928</v>
       </c>
       <c r="M534" s="6" t="n">
         <v>99.22792699999999</v>
@@ -44151,13 +44151,13 @@
         <v>100.837469</v>
       </c>
       <c r="J535" s="9" t="n">
-        <v>101.088497</v>
+        <v>101.090678</v>
       </c>
       <c r="K535" s="9" t="n">
         <v>100.277385</v>
       </c>
       <c r="L535" s="9" t="n">
-        <v>100.546822</v>
+        <v>100.552199</v>
       </c>
       <c r="M535" s="9" t="n">
         <v>99.27713199999999</v>
@@ -44235,13 +44235,13 @@
         <v>100.787246</v>
       </c>
       <c r="J536" s="6" t="n">
-        <v>100.933499</v>
+        <v>100.936379</v>
       </c>
       <c r="K536" s="6" t="n">
         <v>100.139141</v>
       </c>
       <c r="L536" s="6" t="n">
-        <v>100.544965</v>
+        <v>100.551102</v>
       </c>
       <c r="M536" s="6" t="n">
         <v>99.31544700000001</v>
@@ -44319,13 +44319,13 @@
         <v>100.734447</v>
       </c>
       <c r="J537" s="9" t="n">
-        <v>100.807445</v>
+        <v>100.809771</v>
       </c>
       <c r="K537" s="9" t="n">
         <v>100.022404</v>
       </c>
       <c r="L537" s="9" t="n">
-        <v>100.544087</v>
+        <v>100.551086</v>
       </c>
       <c r="M537" s="9" t="n">
         <v>99.340414</v>
@@ -44403,13 +44403,13 @@
         <v>100.700539</v>
       </c>
       <c r="J538" s="6" t="n">
-        <v>100.722628</v>
+        <v>100.722871</v>
       </c>
       <c r="K538" s="6" t="n">
         <v>99.926008</v>
       </c>
       <c r="L538" s="6" t="n">
-        <v>100.541399</v>
+        <v>100.549269</v>
       </c>
       <c r="M538" s="6" t="n">
         <v>99.360646</v>
@@ -44487,13 +44487,13 @@
         <v>100.671965</v>
       </c>
       <c r="J539" s="9" t="n">
-        <v>100.666167</v>
+        <v>100.662984</v>
       </c>
       <c r="K539" s="9" t="n">
         <v>99.850478</v>
       </c>
       <c r="L539" s="9" t="n">
-        <v>100.533408</v>
+        <v>100.542064</v>
       </c>
       <c r="M539" s="9" t="n">
         <v>99.358172</v>
@@ -44571,13 +44571,13 @@
         <v>100.629136</v>
       </c>
       <c r="J540" s="6" t="n">
-        <v>100.610955</v>
+        <v>100.603624</v>
       </c>
       <c r="K540" s="6" t="n">
         <v>99.797224</v>
       </c>
       <c r="L540" s="6" t="n">
-        <v>100.518406</v>
+        <v>100.527691</v>
       </c>
       <c r="M540" s="6" t="n">
         <v>99.311294</v>
@@ -44655,13 +44655,13 @@
         <v>100.549515</v>
       </c>
       <c r="J541" s="9" t="n">
-        <v>100.52654</v>
+        <v>100.51623</v>
       </c>
       <c r="K541" s="9" t="n">
         <v>99.754566</v>
       </c>
       <c r="L541" s="9" t="n">
-        <v>100.493023</v>
+        <v>100.502775</v>
       </c>
       <c r="M541" s="9" t="n">
         <v>99.231814</v>
@@ -44739,13 +44739,13 @@
         <v>100.444459</v>
       </c>
       <c r="J542" s="6" t="n">
-        <v>100.406214</v>
+        <v>100.394529</v>
       </c>
       <c r="K542" s="6" t="n">
         <v>99.718979</v>
       </c>
       <c r="L542" s="6" t="n">
-        <v>100.456489</v>
+        <v>100.466622</v>
       </c>
       <c r="M542" s="6" t="n">
         <v>99.14628500000001</v>
@@ -44823,13 +44823,13 @@
         <v>100.327986</v>
       </c>
       <c r="J543" s="9" t="n">
-        <v>100.252248</v>
+        <v>100.240854</v>
       </c>
       <c r="K543" s="9" t="n">
         <v>99.68764299999999</v>
       </c>
       <c r="L543" s="9" t="n">
-        <v>100.410008</v>
+        <v>100.420502</v>
       </c>
       <c r="M543" s="9" t="n">
         <v>99.082582</v>
@@ -44907,13 +44907,13 @@
         <v>100.229065</v>
       </c>
       <c r="J544" s="6" t="n">
-        <v>100.105833</v>
+        <v>100.096105</v>
       </c>
       <c r="K544" s="6" t="n">
         <v>99.669355</v>
       </c>
       <c r="L544" s="6" t="n">
-        <v>100.356984</v>
+        <v>100.367899</v>
       </c>
       <c r="M544" s="6" t="n">
         <v>99.07983299999999</v>
@@ -44991,13 +44991,13 @@
         <v>100.158131</v>
       </c>
       <c r="J545" s="9" t="n">
-        <v>99.991207</v>
+        <v>99.984133</v>
       </c>
       <c r="K545" s="9" t="n">
         <v>99.669743</v>
       </c>
       <c r="L545" s="9" t="n">
-        <v>100.300164</v>
+        <v>100.311633</v>
       </c>
       <c r="M545" s="9" t="n">
         <v>99.122184</v>
@@ -45075,13 +45075,13 @@
         <v>100.12761</v>
       </c>
       <c r="J546" s="6" t="n">
-        <v>99.930924</v>
+        <v>99.92702199999999</v>
       </c>
       <c r="K546" s="6" t="n">
         <v>99.684161</v>
       </c>
       <c r="L546" s="6" t="n">
-        <v>100.240657</v>
+        <v>100.252883</v>
       </c>
       <c r="M546" s="6" t="n">
         <v>99.187566</v>
@@ -45159,13 +45159,13 @@
         <v>100.11628</v>
       </c>
       <c r="J547" s="9" t="n">
-        <v>99.906791</v>
+        <v>99.9059</v>
       </c>
       <c r="K547" s="9" t="n">
         <v>99.705506</v>
       </c>
       <c r="L547" s="9" t="n">
-        <v>100.179237</v>
+        <v>100.192471</v>
       </c>
       <c r="M547" s="9" t="n">
         <v>99.256524</v>
@@ -45243,13 +45243,13 @@
         <v>100.095003</v>
       </c>
       <c r="J548" s="6" t="n">
-        <v>99.870735</v>
+        <v>99.871627</v>
       </c>
       <c r="K548" s="6" t="n">
         <v>99.72686400000001</v>
       </c>
       <c r="L548" s="6" t="n">
-        <v>100.116159</v>
+        <v>100.130644</v>
       </c>
       <c r="M548" s="6" t="n">
         <v>99.331357</v>
@@ -45327,13 +45327,13 @@
         <v>100.05924</v>
       </c>
       <c r="J549" s="9" t="n">
-        <v>99.809892</v>
+        <v>99.81034200000001</v>
       </c>
       <c r="K549" s="9" t="n">
         <v>99.745225</v>
       </c>
       <c r="L549" s="9" t="n">
-        <v>100.050639</v>
+        <v>100.066523</v>
       </c>
       <c r="M549" s="9" t="n">
         <v>99.437933</v>
@@ -45411,13 +45411,13 @@
         <v>100.01461</v>
       </c>
       <c r="J550" s="6" t="n">
-        <v>99.73273500000001</v>
+        <v>99.729754</v>
       </c>
       <c r="K550" s="6" t="n">
         <v>99.771908</v>
       </c>
       <c r="L550" s="6" t="n">
-        <v>99.983192</v>
+        <v>100.000477</v>
       </c>
       <c r="M550" s="6" t="n">
         <v>99.540244</v>
@@ -45495,13 +45495,13 @@
         <v>99.96387</v>
       </c>
       <c r="J551" s="9" t="n">
-        <v>99.632999</v>
+        <v>99.62351099999999</v>
       </c>
       <c r="K551" s="9" t="n">
         <v>99.802165</v>
       </c>
       <c r="L551" s="9" t="n">
-        <v>99.916234</v>
+        <v>99.93474399999999</v>
       </c>
       <c r="M551" s="9" t="n">
         <v>99.64188</v>
@@ -45579,13 +45579,13 @@
         <v>99.912727</v>
       </c>
       <c r="J552" s="6" t="n">
-        <v>99.528745</v>
+        <v>99.511067</v>
       </c>
       <c r="K552" s="6" t="n">
         <v>99.836992</v>
       </c>
       <c r="L552" s="6" t="n">
-        <v>99.852777</v>
+        <v>99.87217200000001</v>
       </c>
       <c r="M552" s="6" t="n">
         <v>99.75939200000001</v>
@@ -45663,13 +45663,13 @@
         <v>99.875226</v>
       </c>
       <c r="J553" s="9" t="n">
-        <v>99.45269999999999</v>
+        <v>99.429486</v>
       </c>
       <c r="K553" s="9" t="n">
         <v>99.878079</v>
       </c>
       <c r="L553" s="9" t="n">
-        <v>99.796791</v>
+        <v>99.816664</v>
       </c>
       <c r="M553" s="9" t="n">
         <v>99.907774</v>
@@ -45747,13 +45747,13 @@
         <v>99.851462</v>
       </c>
       <c r="J554" s="6" t="n">
-        <v>99.422239</v>
+        <v>99.396497</v>
       </c>
       <c r="K554" s="6" t="n">
         <v>99.92247</v>
       </c>
       <c r="L554" s="6" t="n">
-        <v>99.75166</v>
+        <v>99.771727</v>
       </c>
       <c r="M554" s="6" t="n">
         <v>100.039078</v>
@@ -45831,13 +45831,13 @@
         <v>99.843879</v>
       </c>
       <c r="J555" s="9" t="n">
-        <v>99.43620300000001</v>
+        <v>99.410533</v>
       </c>
       <c r="K555" s="9" t="n">
         <v>99.968703</v>
       </c>
       <c r="L555" s="9" t="n">
-        <v>99.715586</v>
+        <v>99.73569000000001</v>
       </c>
       <c r="M555" s="9" t="n">
         <v>100.117105</v>
@@ -45915,13 +45915,13 @@
         <v>99.83741000000001</v>
       </c>
       <c r="J556" s="6" t="n">
-        <v>99.46972700000001</v>
+        <v>99.446281</v>
       </c>
       <c r="K556" s="6" t="n">
         <v>100.008269</v>
       </c>
       <c r="L556" s="6" t="n">
-        <v>99.68542600000001</v>
+        <v>99.705551</v>
       </c>
       <c r="M556" s="6" t="n">
         <v>100.182459</v>
@@ -45999,13 +45999,13 @@
         <v>99.832916</v>
       </c>
       <c r="J557" s="9" t="n">
-        <v>99.501679</v>
+        <v>99.48218799999999</v>
       </c>
       <c r="K557" s="9" t="n">
         <v>100.028605</v>
       </c>
       <c r="L557" s="9" t="n">
-        <v>99.659211</v>
+        <v>99.679518</v>
       </c>
       <c r="M557" s="9" t="n">
         <v>100.25411</v>
@@ -46083,13 +46083,13 @@
         <v>99.83965499999999</v>
       </c>
       <c r="J558" s="6" t="n">
-        <v>99.532752</v>
+        <v>99.518897</v>
       </c>
       <c r="K558" s="6" t="n">
         <v>100.025105</v>
       </c>
       <c r="L558" s="6" t="n">
-        <v>99.634702</v>
+        <v>99.65561</v>
       </c>
       <c r="M558" s="6" t="n">
         <v>100.365524</v>
@@ -46167,13 +46167,13 @@
         <v>99.886094</v>
       </c>
       <c r="J559" s="9" t="n">
-        <v>99.58583</v>
+        <v>99.57956</v>
       </c>
       <c r="K559" s="9" t="n">
         <v>99.992802</v>
       </c>
       <c r="L559" s="9" t="n">
-        <v>99.61002000000001</v>
+        <v>99.632307</v>
       </c>
       <c r="M559" s="9" t="n">
         <v>100.503205</v>
@@ -46251,13 +46251,13 @@
         <v>99.975599</v>
       </c>
       <c r="J560" s="6" t="n">
-        <v>99.666185</v>
+        <v>99.669968</v>
       </c>
       <c r="K560" s="6" t="n">
         <v>99.94243299999999</v>
       </c>
       <c r="L560" s="6" t="n">
-        <v>99.583399</v>
+        <v>99.608284</v>
       </c>
       <c r="M560" s="6" t="n">
         <v>100.64401</v>
@@ -46335,13 +46335,13 @@
         <v>100.089243</v>
       </c>
       <c r="J561" s="9" t="n">
-        <v>99.77442600000001</v>
+        <v>99.791371</v>
       </c>
       <c r="K561" s="9" t="n">
         <v>99.878412</v>
       </c>
       <c r="L561" s="9" t="n">
-        <v>99.55482000000001</v>
+        <v>99.584</v>
       </c>
       <c r="M561" s="9" t="n">
         <v>100.760031</v>
@@ -46419,13 +46419,13 @@
         <v>100.193386</v>
       </c>
       <c r="J562" s="6" t="n">
-        <v>99.87814</v>
+        <v>99.91174100000001</v>
       </c>
       <c r="K562" s="6" t="n">
         <v>99.80022700000001</v>
       </c>
       <c r="L562" s="6" t="n">
-        <v>99.527219</v>
+        <v>99.562954</v>
       </c>
       <c r="M562" s="6" t="n">
         <v>100.851858</v>
@@ -46503,13 +46503,13 @@
         <v>100.289746</v>
       </c>
       <c r="J563" s="9" t="n">
-        <v>99.980098</v>
+        <v>100.033774</v>
       </c>
       <c r="K563" s="9" t="n">
         <v>99.71626000000001</v>
       </c>
       <c r="L563" s="9" t="n">
-        <v>99.503024</v>
+        <v>99.54803</v>
       </c>
       <c r="M563" s="9" t="n">
         <v>100.920144</v>
@@ -46578,10 +46578,12 @@
         <v>1.013072</v>
       </c>
       <c r="I564" s="6" t="n"/>
-      <c r="J564" s="6" t="n"/>
+      <c r="J564" s="6" t="n">
+        <v>100.158475</v>
+      </c>
       <c r="K564" s="6" t="n"/>
       <c r="L564" s="6" t="n">
-        <v>99.479992</v>
+        <v>99.53705600000001</v>
       </c>
       <c r="M564" s="6" t="n">
         <v>100.970948</v>
